--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -5,22 +5,35 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs - copia/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_50C9ABF45252D60E62355476585DCE3A874705D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E3540EB-D1B2-43AD-8492-503FB4837301}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="11_50C9ABF45252D60E62355476585DCE3A874705D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABB52E6D-B160-49BE-9114-B871354A7110}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="72">
   <si>
     <t>Producto</t>
   </si>
@@ -53,6 +66,189 @@
   </si>
   <si>
     <t>no</t>
+  </si>
+  <si>
+    <t>TERMINALES</t>
+  </si>
+  <si>
+    <t>88%</t>
+  </si>
+  <si>
+    <t>Lider Leider  Alexander Calderon</t>
+  </si>
+  <si>
+    <t>LIDER</t>
+  </si>
+  <si>
+    <t>JUNIN</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>Sin pago (0%)</t>
+  </si>
+  <si>
+    <t>OTROS</t>
+  </si>
+  <si>
+    <t>313%</t>
+  </si>
+  <si>
+    <t>POSTPAGO</t>
+  </si>
+  <si>
+    <t>205%</t>
+  </si>
+  <si>
+    <t>FOCO</t>
+  </si>
+  <si>
+    <t>57%</t>
+  </si>
+  <si>
+    <t>HOGAR</t>
+  </si>
+  <si>
+    <t>33%</t>
+  </si>
+  <si>
+    <t>CVS PLUS</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>5%</t>
+  </si>
+  <si>
+    <t>Cristian Camilo Torres Toro</t>
+  </si>
+  <si>
+    <t>ASESOR</t>
+  </si>
+  <si>
+    <t>Vacaciones del 02 al 18</t>
+  </si>
+  <si>
+    <t>12%</t>
+  </si>
+  <si>
+    <t>11%</t>
+  </si>
+  <si>
+    <t>84%</t>
+  </si>
+  <si>
+    <t>Diana Marcela Taborda Ruiz</t>
+  </si>
+  <si>
+    <t>222%</t>
+  </si>
+  <si>
+    <t>137%</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>73%</t>
+  </si>
+  <si>
+    <t>Sandra Milena Carmona Galeano</t>
+  </si>
+  <si>
+    <t>151%</t>
+  </si>
+  <si>
+    <t>152%</t>
+  </si>
+  <si>
+    <t>89%</t>
+  </si>
+  <si>
+    <t>3%</t>
+  </si>
+  <si>
+    <t>Lider  Bagre</t>
+  </si>
+  <si>
+    <t>EL BAGRE</t>
+  </si>
+  <si>
+    <t>Reemplaza vacaciones cajera del 01 al 18</t>
+  </si>
+  <si>
+    <t>113%</t>
+  </si>
+  <si>
+    <t>Darly Esther Sola Tarriba</t>
+  </si>
+  <si>
+    <t>127%</t>
+  </si>
+  <si>
+    <t>47%</t>
+  </si>
+  <si>
+    <t>92%</t>
+  </si>
+  <si>
+    <t>72%</t>
+  </si>
+  <si>
+    <t>Dayanis  Celsa Gamarra</t>
+  </si>
+  <si>
+    <t>63%</t>
+  </si>
+  <si>
+    <t>115%</t>
+  </si>
+  <si>
+    <t>87%</t>
+  </si>
+  <si>
+    <t>Jeider Alberto Moreno Solano</t>
+  </si>
+  <si>
+    <t>155%</t>
+  </si>
+  <si>
+    <t>69%</t>
+  </si>
+  <si>
+    <t>29%</t>
+  </si>
+  <si>
+    <t>Lider Dabeiba Edwin Dario David Velasquez</t>
+  </si>
+  <si>
+    <t>DABEIBA</t>
+  </si>
+  <si>
+    <t>Vac del 16 al 04 de marzo</t>
+  </si>
+  <si>
+    <t>71%</t>
+  </si>
+  <si>
+    <t>39%</t>
+  </si>
+  <si>
+    <t>Estelli Alejandra Ramirez Florez</t>
+  </si>
+  <si>
+    <t>18%</t>
+  </si>
+  <si>
+    <t>43%</t>
+  </si>
+  <si>
+    <t>56%</t>
   </si>
 </sst>
 </file>
@@ -109,11 +305,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -416,10 +613,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="10" max="10" width="37.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -449,6 +649,1992 @@
       </c>
       <c r="J1" s="1" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="2">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2">
+        <v>29</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="2">
+        <v>38</v>
+      </c>
+      <c r="C3" s="2">
+        <v>119</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4" s="2">
+        <v>21</v>
+      </c>
+      <c r="C4" s="2">
+        <v>43</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5" s="2">
+        <v>14</v>
+      </c>
+      <c r="C5" s="2">
+        <v>8</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B7" s="2">
+        <v>0</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" s="2"/>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8" s="2">
+        <v>44</v>
+      </c>
+      <c r="C8" s="2">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="2">
+        <v>51</v>
+      </c>
+      <c r="C9" s="2">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="2">
+        <v>27</v>
+      </c>
+      <c r="C10" s="2">
+        <v>3</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11" s="2">
+        <v>19</v>
+      </c>
+      <c r="C11" s="2">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="2">
+        <v>4</v>
+      </c>
+      <c r="C12" s="2">
+        <v>0</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J12" s="2"/>
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13" s="2">
+        <v>0</v>
+      </c>
+      <c r="C13" s="2">
+        <v>0</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J13" s="2"/>
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2">
+        <v>44</v>
+      </c>
+      <c r="C14" s="2">
+        <v>37</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J14" s="2"/>
+      <c r="K14" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B15" s="2">
+        <v>51</v>
+      </c>
+      <c r="C15" s="2">
+        <v>113</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J15" s="2"/>
+      <c r="K15" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B16" s="2">
+        <v>27</v>
+      </c>
+      <c r="C16" s="2">
+        <v>37</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" s="2"/>
+      <c r="K16" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B17" s="2">
+        <v>19</v>
+      </c>
+      <c r="C17" s="2">
+        <v>19</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" s="2"/>
+      <c r="K17" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B18" s="2">
+        <v>4</v>
+      </c>
+      <c r="C18" s="2">
+        <v>2</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B19" s="2">
+        <v>0</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20" s="2">
+        <v>44</v>
+      </c>
+      <c r="C20" s="2">
+        <v>32</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B21" s="2">
+        <v>51</v>
+      </c>
+      <c r="C21" s="2">
+        <v>77</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B22" s="2">
+        <v>27</v>
+      </c>
+      <c r="C22" s="2">
+        <v>41</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B23" s="2">
+        <v>19</v>
+      </c>
+      <c r="C23" s="2">
+        <v>17</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B24" s="2">
+        <v>4</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="2">
+        <v>0</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B26" s="2">
+        <v>35</v>
+      </c>
+      <c r="C26" s="2">
+        <v>1</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="K26" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B27" s="2">
+        <v>8</v>
+      </c>
+      <c r="C27" s="2">
+        <v>1</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28" s="2">
+        <v>22</v>
+      </c>
+      <c r="C28" s="2">
+        <v>1</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B29" s="2">
+        <v>10</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B30" s="2">
+        <v>0</v>
+      </c>
+      <c r="C30" s="2">
+        <v>0</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B31" s="2">
+        <v>0</v>
+      </c>
+      <c r="C31" s="2">
+        <v>0</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J31" s="2"/>
+      <c r="K31" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B32" s="2">
+        <v>47</v>
+      </c>
+      <c r="C32" s="2">
+        <v>53</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E32" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G32" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H32" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J32" s="2"/>
+      <c r="K32" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B33" s="2">
+        <v>11</v>
+      </c>
+      <c r="C33" s="2">
+        <v>14</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E33" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H33" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J33" s="2"/>
+      <c r="K33" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B34" s="2">
+        <v>30</v>
+      </c>
+      <c r="C34" s="2">
+        <v>14</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G34" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H34" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J34" s="2"/>
+      <c r="K34" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35" s="2">
+        <v>13</v>
+      </c>
+      <c r="C35" s="2">
+        <v>12</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E35" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G35" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J35" s="2"/>
+      <c r="K35" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36" s="2">
+        <v>0</v>
+      </c>
+      <c r="C36" s="2">
+        <v>0</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H36" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J36" s="2"/>
+      <c r="K36" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B37" s="2">
+        <v>0</v>
+      </c>
+      <c r="C37" s="2">
+        <v>0</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G37" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" s="2"/>
+      <c r="K37" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38" s="2">
+        <v>47</v>
+      </c>
+      <c r="C38" s="2">
+        <v>34</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G38" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H38" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" s="2"/>
+      <c r="K38" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39" s="2">
+        <v>11</v>
+      </c>
+      <c r="C39" s="2">
+        <v>14</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E39" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G39" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H39" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" s="2"/>
+      <c r="K39" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B40" s="2">
+        <v>30</v>
+      </c>
+      <c r="C40" s="2">
+        <v>19</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E40" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H40" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" s="2"/>
+      <c r="K40" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B41" s="2">
+        <v>13</v>
+      </c>
+      <c r="C41" s="2">
+        <v>15</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H41" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J41" s="2"/>
+      <c r="K41" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B42" s="2">
+        <v>0</v>
+      </c>
+      <c r="C42" s="2">
+        <v>0</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E42" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G42" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H42" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J42" s="2"/>
+      <c r="K42" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B43" s="2">
+        <v>0</v>
+      </c>
+      <c r="C43" s="2">
+        <v>0</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E43" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G43" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H43" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J43" s="2"/>
+      <c r="K43" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B44" s="2">
+        <v>47</v>
+      </c>
+      <c r="C44" s="2">
+        <v>41</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="E44" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G44" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H44" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J44" s="2"/>
+      <c r="K44" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B45" s="2">
+        <v>11</v>
+      </c>
+      <c r="C45" s="2">
+        <v>17</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E45" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H45" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J45" s="2"/>
+      <c r="K45" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B46" s="2">
+        <v>30</v>
+      </c>
+      <c r="C46" s="2">
+        <v>15</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J46" s="2"/>
+      <c r="K46" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B47" s="2">
+        <v>13</v>
+      </c>
+      <c r="C47" s="2">
+        <v>9</v>
+      </c>
+      <c r="D47" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E47" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G47" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H47" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" s="2"/>
+      <c r="K47" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B48" s="2">
+        <v>0</v>
+      </c>
+      <c r="C48" s="2">
+        <v>1</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E48" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G48" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H48" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" s="2"/>
+      <c r="K48" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B49" s="2">
+        <v>0</v>
+      </c>
+      <c r="C49" s="2">
+        <v>0</v>
+      </c>
+      <c r="D49" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E49" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G49" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="H49" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" s="2"/>
+      <c r="K49" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B50" s="2">
+        <v>28</v>
+      </c>
+      <c r="C50" s="2">
+        <v>8</v>
+      </c>
+      <c r="D50" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E50" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H50" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="K50" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51" s="2">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2">
+        <v>4</v>
+      </c>
+      <c r="D51" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H51" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J51" s="2"/>
+      <c r="K51" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52" s="2">
+        <v>14</v>
+      </c>
+      <c r="C52" s="2">
+        <v>10</v>
+      </c>
+      <c r="D52" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E52" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H52" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J52" s="2"/>
+      <c r="K52" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53" s="2">
+        <v>6</v>
+      </c>
+      <c r="C53" s="2">
+        <v>2</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H53" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J53" s="2"/>
+      <c r="K53" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B54" s="2">
+        <v>0</v>
+      </c>
+      <c r="C54" s="2">
+        <v>0</v>
+      </c>
+      <c r="D54" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E54" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H54" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J54" s="2"/>
+      <c r="K54" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B55" s="2">
+        <v>0</v>
+      </c>
+      <c r="C55" s="2">
+        <v>0</v>
+      </c>
+      <c r="D55" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E55" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H55" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J55" s="2"/>
+      <c r="K55" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56" s="2">
+        <v>41</v>
+      </c>
+      <c r="C56" s="2">
+        <v>16</v>
+      </c>
+      <c r="D56" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E56" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G56" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H56" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J56" s="2"/>
+      <c r="K56" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57" s="2">
+        <v>11</v>
+      </c>
+      <c r="C57" s="2">
+        <v>2</v>
+      </c>
+      <c r="D57" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G57" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H57" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" s="2"/>
+      <c r="K57" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58" s="2">
+        <v>21</v>
+      </c>
+      <c r="C58" s="2">
+        <v>9</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J58" s="2"/>
+      <c r="K58" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59" s="2">
+        <v>9</v>
+      </c>
+      <c r="C59" s="2">
+        <v>5</v>
+      </c>
+      <c r="D59" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E59" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G59" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H59" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J59" s="2"/>
+      <c r="K59" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60" s="2">
+        <v>0</v>
+      </c>
+      <c r="C60" s="2">
+        <v>0</v>
+      </c>
+      <c r="D60" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E60" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G60" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H60" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J60" s="2"/>
+      <c r="K60" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B61" s="2">
+        <v>0</v>
+      </c>
+      <c r="C61" s="2">
+        <v>0</v>
+      </c>
+      <c r="D61" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E61" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="G61" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="H61" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I61" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J61" s="2"/>
+      <c r="K61" s="2">
+        <v>100</v>
       </c>
     </row>
     <row r="70" spans="10:10" x14ac:dyDescent="0.25">

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="11_50C9ABF45252D60E62355476585DCE3A874705D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{ABB52E6D-B160-49BE-9114-B871354A7110}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_50C9ABF45252D60E62355476585DCE3A874705D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4D788231-AE7F-4A7A-A8FC-A8097868E609}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -305,12 +305,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -616,6 +615,7 @@
   <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="5" max="5" width="39.85546875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="37.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -652,1988 +652,1931 @@
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A2" s="2" t="s">
+      <c r="A2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2">
         <v>33</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2">
         <v>29</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2">
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2">
         <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A3" s="2" t="s">
+      <c r="A3" t="s">
         <v>18</v>
       </c>
-      <c r="B3" s="2">
+      <c r="B3">
         <v>38</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3">
         <v>119</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="G3" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2">
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3">
         <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A4" s="2" t="s">
+      <c r="A4" t="s">
         <v>20</v>
       </c>
-      <c r="B4" s="2">
+      <c r="B4">
         <v>21</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4">
         <v>43</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2">
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4">
         <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A5" s="2" t="s">
+      <c r="A5" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="2">
+      <c r="B5">
         <v>14</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5">
         <v>8</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" t="s">
         <v>23</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="2"/>
-      <c r="K5" s="2">
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5">
         <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A6" s="2" t="s">
+      <c r="A6" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="2">
+      <c r="B6">
         <v>3</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6">
         <v>1</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2">
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="K6">
         <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A7" s="2" t="s">
+      <c r="A7" t="s">
         <v>26</v>
       </c>
-      <c r="B7" s="2">
-        <v>0</v>
-      </c>
-      <c r="C7" s="2">
-        <v>0</v>
-      </c>
-      <c r="D7" s="2" t="s">
+      <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" t="s">
         <v>14</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" t="s">
         <v>15</v>
       </c>
-      <c r="H7" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="2"/>
-      <c r="K7" s="2">
+      <c r="H7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="K7">
         <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+      <c r="A8" t="s">
         <v>11</v>
       </c>
-      <c r="B8" s="2">
+      <c r="B8">
         <v>44</v>
       </c>
-      <c r="C8" s="2">
+      <c r="C8">
         <v>2</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" t="s">
         <v>28</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" t="s">
         <v>29</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G8" s="2" t="s">
+      <c r="F8" t="s">
+        <v>30</v>
+      </c>
+      <c r="G8" t="s">
         <v>15</v>
       </c>
-      <c r="H8" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="2" t="s">
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="J8" t="s">
         <v>31</v>
       </c>
-      <c r="K8" s="2">
+      <c r="K8">
         <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="A9" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="2">
+      <c r="B9">
         <v>51</v>
       </c>
-      <c r="C9" s="2">
+      <c r="C9">
         <v>6</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" t="s">
         <v>32</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="F9" t="s">
+        <v>30</v>
+      </c>
+      <c r="G9" t="s">
         <v>15</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J9" s="2"/>
-      <c r="K9" s="2">
+      <c r="H9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+      <c r="K9">
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A10" s="2" t="s">
+      <c r="A10" t="s">
         <v>20</v>
       </c>
-      <c r="B10" s="2">
+      <c r="B10">
         <v>27</v>
       </c>
-      <c r="C10" s="2">
+      <c r="C10">
         <v>3</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" t="s">
         <v>33</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" t="s">
         <v>29</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="F10" t="s">
+        <v>30</v>
+      </c>
+      <c r="G10" t="s">
         <v>15</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2">
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s">
+        <v>17</v>
+      </c>
+      <c r="K10">
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="A11" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="2">
+      <c r="B11">
         <v>19</v>
       </c>
-      <c r="C11" s="2">
+      <c r="C11">
         <v>2</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" t="s">
         <v>33</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" t="s">
         <v>29</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="F11" t="s">
+        <v>30</v>
+      </c>
+      <c r="G11" t="s">
         <v>15</v>
       </c>
-      <c r="H11" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J11" s="2"/>
-      <c r="K11" s="2">
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+      <c r="K11">
         <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="2" t="s">
+      <c r="A12" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="2">
+      <c r="B12">
         <v>4</v>
       </c>
-      <c r="C12" s="2">
-        <v>0</v>
-      </c>
-      <c r="D12" s="2" t="s">
+      <c r="C12">
+        <v>0</v>
+      </c>
+      <c r="D12" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" t="s">
         <v>29</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="F12" t="s">
+        <v>30</v>
+      </c>
+      <c r="G12" t="s">
         <v>15</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2">
+      <c r="H12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12">
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
+      <c r="A13" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="2">
-        <v>0</v>
-      </c>
-      <c r="C13" s="2">
-        <v>0</v>
-      </c>
-      <c r="D13" s="2" t="s">
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
         <v>27</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" t="s">
         <v>29</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="2" t="s">
+      <c r="F13" t="s">
+        <v>30</v>
+      </c>
+      <c r="G13" t="s">
         <v>15</v>
       </c>
-      <c r="H13" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J13" s="2"/>
-      <c r="K13" s="2">
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="2" t="s">
+      <c r="A14" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14">
         <v>44</v>
       </c>
-      <c r="C14" s="2">
+      <c r="C14">
         <v>37</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" t="s">
         <v>34</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" t="s">
         <v>35</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G14" s="2" t="s">
+      <c r="F14" t="s">
+        <v>30</v>
+      </c>
+      <c r="G14" t="s">
         <v>15</v>
       </c>
-      <c r="H14" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2">
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14">
         <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+      <c r="A15" t="s">
         <v>18</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15">
         <v>51</v>
       </c>
-      <c r="C15" s="2">
+      <c r="C15">
         <v>113</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" t="s">
         <v>36</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" t="s">
         <v>35</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G15" s="2" t="s">
+      <c r="F15" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" t="s">
         <v>15</v>
       </c>
-      <c r="H15" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J15" s="2"/>
-      <c r="K15" s="2">
+      <c r="H15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15">
         <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A16" s="2" t="s">
+      <c r="A16" t="s">
         <v>20</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16">
         <v>27</v>
       </c>
-      <c r="C16" s="2">
+      <c r="C16">
         <v>37</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" t="s">
         <v>37</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G16" s="2" t="s">
+      <c r="F16" t="s">
+        <v>30</v>
+      </c>
+      <c r="G16" t="s">
         <v>15</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2">
+      <c r="H16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" t="s">
+        <v>17</v>
+      </c>
+      <c r="K16">
         <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="2" t="s">
+      <c r="A17" t="s">
         <v>22</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17">
         <v>19</v>
       </c>
-      <c r="C17" s="2">
+      <c r="C17">
         <v>19</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" t="s">
         <v>38</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" t="s">
         <v>35</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G17" s="2" t="s">
+      <c r="F17" t="s">
+        <v>30</v>
+      </c>
+      <c r="G17" t="s">
         <v>15</v>
       </c>
-      <c r="H17" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2">
+      <c r="H17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" t="s">
+        <v>17</v>
+      </c>
+      <c r="K17">
         <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A18" s="2" t="s">
+      <c r="A18" t="s">
         <v>24</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18">
         <v>4</v>
       </c>
-      <c r="C18" s="2">
+      <c r="C18">
         <v>2</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="E18" t="s">
         <v>35</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G18" s="2" t="s">
+      <c r="F18" t="s">
+        <v>30</v>
+      </c>
+      <c r="G18" t="s">
         <v>15</v>
       </c>
-      <c r="H18" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2">
+      <c r="H18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18">
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="2" t="s">
+      <c r="A19" t="s">
         <v>26</v>
       </c>
-      <c r="B19" s="2">
-        <v>0</v>
-      </c>
-      <c r="C19" s="2">
-        <v>0</v>
-      </c>
-      <c r="D19" s="2" t="s">
+      <c r="B19">
+        <v>0</v>
+      </c>
+      <c r="C19">
+        <v>0</v>
+      </c>
+      <c r="D19" t="s">
         <v>27</v>
       </c>
-      <c r="E19" s="2" t="s">
+      <c r="E19" t="s">
         <v>35</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G19" s="2" t="s">
+      <c r="F19" t="s">
+        <v>30</v>
+      </c>
+      <c r="G19" t="s">
         <v>15</v>
       </c>
-      <c r="H19" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J19" s="2"/>
-      <c r="K19" s="2">
+      <c r="H19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" t="s">
+        <v>17</v>
+      </c>
+      <c r="K19">
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="2" t="s">
+      <c r="A20" t="s">
         <v>11</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20">
         <v>44</v>
       </c>
-      <c r="C20" s="2">
+      <c r="C20">
         <v>32</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" t="s">
         <v>40</v>
       </c>
-      <c r="E20" s="2" t="s">
+      <c r="E20" t="s">
         <v>41</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G20" s="2" t="s">
+      <c r="F20" t="s">
+        <v>30</v>
+      </c>
+      <c r="G20" t="s">
         <v>15</v>
       </c>
-      <c r="H20" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J20" s="2"/>
-      <c r="K20" s="2">
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s">
+        <v>17</v>
+      </c>
+      <c r="K20">
         <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="2" t="s">
+      <c r="A21" t="s">
         <v>18</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21">
         <v>51</v>
       </c>
-      <c r="C21" s="2">
+      <c r="C21">
         <v>77</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" t="s">
         <v>42</v>
       </c>
-      <c r="E21" s="2" t="s">
+      <c r="E21" t="s">
         <v>41</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" s="2" t="s">
+      <c r="F21" t="s">
+        <v>30</v>
+      </c>
+      <c r="G21" t="s">
         <v>15</v>
       </c>
-      <c r="H21" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J21" s="2"/>
-      <c r="K21" s="2">
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s">
+        <v>17</v>
+      </c>
+      <c r="K21">
         <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="2" t="s">
+      <c r="A22" t="s">
         <v>20</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22">
         <v>27</v>
       </c>
-      <c r="C22" s="2">
+      <c r="C22">
         <v>41</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" t="s">
         <v>43</v>
       </c>
-      <c r="E22" s="2" t="s">
+      <c r="E22" t="s">
         <v>41</v>
       </c>
-      <c r="F22" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G22" s="2" t="s">
+      <c r="F22" t="s">
+        <v>30</v>
+      </c>
+      <c r="G22" t="s">
         <v>15</v>
       </c>
-      <c r="H22" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J22" s="2"/>
-      <c r="K22" s="2">
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+      <c r="K22">
         <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="2" t="s">
+      <c r="A23" t="s">
         <v>22</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23">
         <v>19</v>
       </c>
-      <c r="C23" s="2">
-        <v>17</v>
-      </c>
-      <c r="D23" s="2" t="s">
+      <c r="C23">
+        <v>17</v>
+      </c>
+      <c r="D23" t="s">
         <v>44</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="E23" t="s">
         <v>41</v>
       </c>
-      <c r="F23" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G23" s="2" t="s">
+      <c r="F23" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23" t="s">
         <v>15</v>
       </c>
-      <c r="H23" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="2"/>
-      <c r="K23" s="2">
+      <c r="H23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23">
         <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A24" s="2" t="s">
+      <c r="A24" t="s">
         <v>24</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24">
         <v>4</v>
       </c>
-      <c r="C24" s="2">
-        <v>0</v>
-      </c>
-      <c r="D24" s="2" t="s">
+      <c r="C24">
+        <v>0</v>
+      </c>
+      <c r="D24" t="s">
         <v>27</v>
       </c>
-      <c r="E24" s="2" t="s">
+      <c r="E24" t="s">
         <v>41</v>
       </c>
-      <c r="F24" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G24" s="2" t="s">
+      <c r="F24" t="s">
+        <v>30</v>
+      </c>
+      <c r="G24" t="s">
         <v>15</v>
       </c>
-      <c r="H24" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="2"/>
-      <c r="K24" s="2">
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24">
         <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A25" s="2" t="s">
+      <c r="A25" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="2">
-        <v>0</v>
-      </c>
-      <c r="C25" s="2">
-        <v>0</v>
-      </c>
-      <c r="D25" s="2" t="s">
+      <c r="B25">
+        <v>0</v>
+      </c>
+      <c r="C25">
+        <v>0</v>
+      </c>
+      <c r="D25" t="s">
         <v>27</v>
       </c>
-      <c r="E25" s="2" t="s">
+      <c r="E25" t="s">
         <v>41</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G25" s="2" t="s">
+      <c r="F25" t="s">
+        <v>30</v>
+      </c>
+      <c r="G25" t="s">
         <v>15</v>
       </c>
-      <c r="H25" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="2"/>
-      <c r="K25" s="2">
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s">
+        <v>17</v>
+      </c>
+      <c r="K25">
         <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="2" t="s">
+      <c r="A26" t="s">
         <v>18</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26">
         <v>35</v>
       </c>
-      <c r="C26" s="2">
+      <c r="C26">
         <v>1</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" t="s">
         <v>45</v>
       </c>
-      <c r="E26" s="2" t="s">
+      <c r="E26" t="s">
         <v>46</v>
       </c>
-      <c r="F26" s="2" t="s">
+      <c r="F26" t="s">
         <v>14</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="2" t="s">
+      <c r="G26" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" t="s">
         <v>48</v>
       </c>
-      <c r="K26" s="2">
+      <c r="K26">
         <v>100</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="2" t="s">
+      <c r="A27" t="s">
         <v>20</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27">
         <v>8</v>
       </c>
-      <c r="C27" s="2">
+      <c r="C27">
         <v>1</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" t="s">
         <v>32</v>
       </c>
-      <c r="E27" s="2" t="s">
+      <c r="E27" t="s">
         <v>46</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F27" t="s">
         <v>14</v>
       </c>
-      <c r="G27" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="2"/>
-      <c r="K27" s="2">
+      <c r="G27" t="s">
+        <v>47</v>
+      </c>
+      <c r="H27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27">
         <v>100</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="2" t="s">
+      <c r="A28" t="s">
         <v>11</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28">
         <v>22</v>
       </c>
-      <c r="C28" s="2">
+      <c r="C28">
         <v>1</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" t="s">
         <v>28</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="E28" t="s">
         <v>46</v>
       </c>
-      <c r="F28" s="2" t="s">
+      <c r="F28" t="s">
         <v>14</v>
       </c>
-      <c r="G28" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="2"/>
-      <c r="K28" s="2">
+      <c r="G28" t="s">
+        <v>47</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28">
         <v>100</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="2" t="s">
+      <c r="A29" t="s">
         <v>22</v>
       </c>
-      <c r="B29" s="2">
+      <c r="B29">
         <v>10</v>
       </c>
-      <c r="C29" s="2">
-        <v>0</v>
-      </c>
-      <c r="D29" s="2" t="s">
+      <c r="C29">
+        <v>0</v>
+      </c>
+      <c r="D29" t="s">
         <v>27</v>
       </c>
-      <c r="E29" s="2" t="s">
+      <c r="E29" t="s">
         <v>46</v>
       </c>
-      <c r="F29" s="2" t="s">
+      <c r="F29" t="s">
         <v>14</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="2"/>
-      <c r="K29" s="2">
+      <c r="G29" t="s">
+        <v>47</v>
+      </c>
+      <c r="H29" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29">
         <v>100</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="2" t="s">
+      <c r="A30" t="s">
         <v>24</v>
       </c>
-      <c r="B30" s="2">
-        <v>0</v>
-      </c>
-      <c r="C30" s="2">
-        <v>0</v>
-      </c>
-      <c r="D30" s="2" t="s">
+      <c r="B30">
+        <v>0</v>
+      </c>
+      <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30" t="s">
         <v>27</v>
       </c>
-      <c r="E30" s="2" t="s">
+      <c r="E30" t="s">
         <v>46</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F30" t="s">
         <v>14</v>
       </c>
-      <c r="G30" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="2"/>
-      <c r="K30" s="2">
+      <c r="G30" t="s">
+        <v>47</v>
+      </c>
+      <c r="H30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30">
         <v>100</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="2" t="s">
+      <c r="A31" t="s">
         <v>26</v>
       </c>
-      <c r="B31" s="2">
-        <v>0</v>
-      </c>
-      <c r="C31" s="2">
-        <v>0</v>
-      </c>
-      <c r="D31" s="2" t="s">
+      <c r="B31">
+        <v>0</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31" t="s">
         <v>27</v>
       </c>
-      <c r="E31" s="2" t="s">
+      <c r="E31" t="s">
         <v>46</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" t="s">
         <v>14</v>
       </c>
-      <c r="G31" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="2"/>
-      <c r="K31" s="2">
+      <c r="G31" t="s">
+        <v>47</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31">
         <v>100</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="2" t="s">
+      <c r="A32" t="s">
         <v>18</v>
       </c>
-      <c r="B32" s="2">
-        <v>47</v>
-      </c>
-      <c r="C32" s="2">
+      <c r="B32">
+        <v>47</v>
+      </c>
+      <c r="C32">
         <v>53</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" t="s">
         <v>49</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="E32" t="s">
         <v>50</v>
       </c>
-      <c r="F32" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="2"/>
-      <c r="K32" s="2">
+      <c r="F32" t="s">
+        <v>30</v>
+      </c>
+      <c r="G32" t="s">
+        <v>47</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32">
         <v>100</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="2" t="s">
+      <c r="A33" t="s">
         <v>20</v>
       </c>
-      <c r="B33" s="2">
+      <c r="B33">
         <v>11</v>
       </c>
-      <c r="C33" s="2">
+      <c r="C33">
         <v>14</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" t="s">
         <v>51</v>
       </c>
-      <c r="E33" s="2" t="s">
+      <c r="E33" t="s">
         <v>50</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G33" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H33" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="2"/>
-      <c r="K33" s="2">
+      <c r="F33" t="s">
+        <v>30</v>
+      </c>
+      <c r="G33" t="s">
+        <v>47</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33">
         <v>100</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="2" t="s">
+      <c r="A34" t="s">
         <v>11</v>
       </c>
-      <c r="B34" s="2">
-        <v>30</v>
-      </c>
-      <c r="C34" s="2">
+      <c r="B34">
+        <v>30</v>
+      </c>
+      <c r="C34">
         <v>14</v>
       </c>
-      <c r="D34" s="2" t="s">
+      <c r="D34" t="s">
         <v>52</v>
       </c>
-      <c r="E34" s="2" t="s">
+      <c r="E34" t="s">
         <v>50</v>
       </c>
-      <c r="F34" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G34" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H34" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="2"/>
-      <c r="K34" s="2">
+      <c r="F34" t="s">
+        <v>30</v>
+      </c>
+      <c r="G34" t="s">
+        <v>47</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34">
         <v>100</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="2" t="s">
+      <c r="A35" t="s">
         <v>22</v>
       </c>
-      <c r="B35" s="2">
+      <c r="B35">
         <v>13</v>
       </c>
-      <c r="C35" s="2">
+      <c r="C35">
         <v>12</v>
       </c>
-      <c r="D35" s="2" t="s">
+      <c r="D35" t="s">
         <v>53</v>
       </c>
-      <c r="E35" s="2" t="s">
+      <c r="E35" t="s">
         <v>50</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G35" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H35" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="2"/>
-      <c r="K35" s="2">
+      <c r="F35" t="s">
+        <v>30</v>
+      </c>
+      <c r="G35" t="s">
+        <v>47</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35">
         <v>100</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="2" t="s">
+      <c r="A36" t="s">
         <v>24</v>
       </c>
-      <c r="B36" s="2">
-        <v>0</v>
-      </c>
-      <c r="C36" s="2">
-        <v>0</v>
-      </c>
-      <c r="D36" s="2" t="s">
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36" t="s">
         <v>27</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="E36" t="s">
         <v>50</v>
       </c>
-      <c r="F36" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I36" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="2"/>
-      <c r="K36" s="2">
+      <c r="F36" t="s">
+        <v>30</v>
+      </c>
+      <c r="G36" t="s">
+        <v>47</v>
+      </c>
+      <c r="H36" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36">
         <v>100</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="2" t="s">
+      <c r="A37" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="2">
-        <v>0</v>
-      </c>
-      <c r="C37" s="2">
-        <v>0</v>
-      </c>
-      <c r="D37" s="2" t="s">
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37" t="s">
         <v>27</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="E37" t="s">
         <v>50</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G37" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H37" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="2"/>
-      <c r="K37" s="2">
+      <c r="F37" t="s">
+        <v>30</v>
+      </c>
+      <c r="G37" t="s">
+        <v>47</v>
+      </c>
+      <c r="H37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" t="s">
+        <v>17</v>
+      </c>
+      <c r="K37">
         <v>100</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="2" t="s">
+      <c r="A38" t="s">
         <v>18</v>
       </c>
-      <c r="B38" s="2">
-        <v>47</v>
-      </c>
-      <c r="C38" s="2">
+      <c r="B38">
+        <v>47</v>
+      </c>
+      <c r="C38">
         <v>34</v>
       </c>
-      <c r="D38" s="2" t="s">
+      <c r="D38" t="s">
         <v>54</v>
       </c>
-      <c r="E38" s="2" t="s">
+      <c r="E38" t="s">
         <v>55</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G38" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H38" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="2"/>
-      <c r="K38" s="2">
+      <c r="F38" t="s">
+        <v>30</v>
+      </c>
+      <c r="G38" t="s">
+        <v>47</v>
+      </c>
+      <c r="H38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" t="s">
+        <v>17</v>
+      </c>
+      <c r="K38">
         <v>100</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="2" t="s">
+      <c r="A39" t="s">
         <v>20</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39">
         <v>11</v>
       </c>
-      <c r="C39" s="2">
+      <c r="C39">
         <v>14</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" t="s">
         <v>51</v>
       </c>
-      <c r="E39" s="2" t="s">
+      <c r="E39" t="s">
         <v>55</v>
       </c>
-      <c r="F39" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G39" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H39" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="2"/>
-      <c r="K39" s="2">
+      <c r="F39" t="s">
+        <v>30</v>
+      </c>
+      <c r="G39" t="s">
+        <v>47</v>
+      </c>
+      <c r="H39" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" t="s">
+        <v>17</v>
+      </c>
+      <c r="K39">
         <v>100</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="2" t="s">
+      <c r="A40" t="s">
         <v>11</v>
       </c>
-      <c r="B40" s="2">
-        <v>30</v>
-      </c>
-      <c r="C40" s="2">
+      <c r="B40">
+        <v>30</v>
+      </c>
+      <c r="C40">
         <v>19</v>
       </c>
-      <c r="D40" s="2" t="s">
+      <c r="D40" t="s">
         <v>56</v>
       </c>
-      <c r="E40" s="2" t="s">
+      <c r="E40" t="s">
         <v>55</v>
       </c>
-      <c r="F40" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H40" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I40" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="2"/>
-      <c r="K40" s="2">
+      <c r="F40" t="s">
+        <v>30</v>
+      </c>
+      <c r="G40" t="s">
+        <v>47</v>
+      </c>
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" t="s">
+        <v>17</v>
+      </c>
+      <c r="K40">
         <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
+      <c r="A41" t="s">
         <v>22</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41">
         <v>13</v>
       </c>
-      <c r="C41" s="2">
+      <c r="C41">
         <v>15</v>
       </c>
-      <c r="D41" s="2" t="s">
+      <c r="D41" t="s">
         <v>57</v>
       </c>
-      <c r="E41" s="2" t="s">
+      <c r="E41" t="s">
         <v>55</v>
       </c>
-      <c r="F41" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G41" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H41" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I41" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J41" s="2"/>
-      <c r="K41" s="2">
+      <c r="F41" t="s">
+        <v>30</v>
+      </c>
+      <c r="G41" t="s">
+        <v>47</v>
+      </c>
+      <c r="H41" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41">
         <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A42" s="2" t="s">
+      <c r="A42" t="s">
         <v>24</v>
       </c>
-      <c r="B42" s="2">
-        <v>0</v>
-      </c>
-      <c r="C42" s="2">
-        <v>0</v>
-      </c>
-      <c r="D42" s="2" t="s">
+      <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42" t="s">
         <v>27</v>
       </c>
-      <c r="E42" s="2" t="s">
+      <c r="E42" t="s">
         <v>55</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H42" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I42" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J42" s="2"/>
-      <c r="K42" s="2">
+      <c r="F42" t="s">
+        <v>30</v>
+      </c>
+      <c r="G42" t="s">
+        <v>47</v>
+      </c>
+      <c r="H42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42">
         <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="2" t="s">
+      <c r="A43" t="s">
         <v>26</v>
       </c>
-      <c r="B43" s="2">
-        <v>0</v>
-      </c>
-      <c r="C43" s="2">
-        <v>0</v>
-      </c>
-      <c r="D43" s="2" t="s">
+      <c r="B43">
+        <v>0</v>
+      </c>
+      <c r="C43">
+        <v>0</v>
+      </c>
+      <c r="D43" t="s">
         <v>27</v>
       </c>
-      <c r="E43" s="2" t="s">
+      <c r="E43" t="s">
         <v>55</v>
       </c>
-      <c r="F43" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G43" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H43" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I43" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J43" s="2"/>
-      <c r="K43" s="2">
+      <c r="F43" t="s">
+        <v>30</v>
+      </c>
+      <c r="G43" t="s">
+        <v>47</v>
+      </c>
+      <c r="H43" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43">
         <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="2" t="s">
+      <c r="A44" t="s">
         <v>18</v>
       </c>
-      <c r="B44" s="2">
-        <v>47</v>
-      </c>
-      <c r="C44" s="2">
+      <c r="B44">
+        <v>47</v>
+      </c>
+      <c r="C44">
         <v>41</v>
       </c>
-      <c r="D44" s="2" t="s">
+      <c r="D44" t="s">
         <v>58</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="E44" t="s">
         <v>59</v>
       </c>
-      <c r="F44" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G44" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H44" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I44" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J44" s="2"/>
-      <c r="K44" s="2">
+      <c r="F44" t="s">
+        <v>30</v>
+      </c>
+      <c r="G44" t="s">
+        <v>47</v>
+      </c>
+      <c r="H44" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44">
         <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A45" s="2" t="s">
+      <c r="A45" t="s">
         <v>20</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45">
         <v>11</v>
       </c>
-      <c r="C45" s="2">
-        <v>17</v>
-      </c>
-      <c r="D45" s="2" t="s">
+      <c r="C45">
+        <v>17</v>
+      </c>
+      <c r="D45" t="s">
         <v>60</v>
       </c>
-      <c r="E45" s="2" t="s">
+      <c r="E45" t="s">
         <v>59</v>
       </c>
-      <c r="F45" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G45" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H45" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I45" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J45" s="2"/>
-      <c r="K45" s="2">
+      <c r="F45" t="s">
+        <v>30</v>
+      </c>
+      <c r="G45" t="s">
+        <v>47</v>
+      </c>
+      <c r="H45" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45">
         <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
+      <c r="A46" t="s">
         <v>11</v>
       </c>
-      <c r="B46" s="2">
-        <v>30</v>
-      </c>
-      <c r="C46" s="2">
+      <c r="B46">
+        <v>30</v>
+      </c>
+      <c r="C46">
         <v>15</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" t="s">
         <v>39</v>
       </c>
-      <c r="E46" s="2" t="s">
+      <c r="E46" t="s">
         <v>59</v>
       </c>
-      <c r="F46" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J46" s="2"/>
-      <c r="K46" s="2">
+      <c r="F46" t="s">
+        <v>30</v>
+      </c>
+      <c r="G46" t="s">
+        <v>47</v>
+      </c>
+      <c r="H46" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46">
         <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="2" t="s">
+      <c r="A47" t="s">
         <v>22</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47">
         <v>13</v>
       </c>
-      <c r="C47" s="2">
+      <c r="C47">
         <v>9</v>
       </c>
-      <c r="D47" s="2" t="s">
+      <c r="D47" t="s">
         <v>61</v>
       </c>
-      <c r="E47" s="2" t="s">
+      <c r="E47" t="s">
         <v>59</v>
       </c>
-      <c r="F47" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G47" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H47" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I47" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J47" s="2"/>
-      <c r="K47" s="2">
+      <c r="F47" t="s">
+        <v>30</v>
+      </c>
+      <c r="G47" t="s">
+        <v>47</v>
+      </c>
+      <c r="H47" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47">
         <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="2" t="s">
+      <c r="A48" t="s">
         <v>24</v>
       </c>
-      <c r="B48" s="2">
-        <v>0</v>
-      </c>
-      <c r="C48" s="2">
+      <c r="B48">
+        <v>0</v>
+      </c>
+      <c r="C48">
         <v>1</v>
       </c>
-      <c r="D48" s="2" t="s">
+      <c r="D48" t="s">
         <v>27</v>
       </c>
-      <c r="E48" s="2" t="s">
+      <c r="E48" t="s">
         <v>59</v>
       </c>
-      <c r="F48" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G48" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H48" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I48" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J48" s="2"/>
-      <c r="K48" s="2">
+      <c r="F48" t="s">
+        <v>30</v>
+      </c>
+      <c r="G48" t="s">
+        <v>47</v>
+      </c>
+      <c r="H48" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" t="s">
+        <v>17</v>
+      </c>
+      <c r="K48">
         <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A49" s="2" t="s">
+      <c r="A49" t="s">
         <v>26</v>
       </c>
-      <c r="B49" s="2">
-        <v>0</v>
-      </c>
-      <c r="C49" s="2">
-        <v>0</v>
-      </c>
-      <c r="D49" s="2" t="s">
+      <c r="B49">
+        <v>0</v>
+      </c>
+      <c r="C49">
+        <v>0</v>
+      </c>
+      <c r="D49" t="s">
         <v>27</v>
       </c>
-      <c r="E49" s="2" t="s">
+      <c r="E49" t="s">
         <v>59</v>
       </c>
-      <c r="F49" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G49" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="H49" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I49" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J49" s="2"/>
-      <c r="K49" s="2">
+      <c r="F49" t="s">
+        <v>30</v>
+      </c>
+      <c r="G49" t="s">
+        <v>47</v>
+      </c>
+      <c r="H49" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" t="s">
+        <v>17</v>
+      </c>
+      <c r="K49">
         <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" s="2" t="s">
+      <c r="A50" t="s">
         <v>18</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50">
         <v>28</v>
       </c>
-      <c r="C50" s="2">
+      <c r="C50">
         <v>8</v>
       </c>
-      <c r="D50" s="2" t="s">
+      <c r="D50" t="s">
         <v>62</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="E50" t="s">
         <v>63</v>
       </c>
-      <c r="F50" s="2" t="s">
+      <c r="F50" t="s">
         <v>14</v>
       </c>
-      <c r="G50" s="2" t="s">
+      <c r="G50" t="s">
         <v>64</v>
       </c>
-      <c r="H50" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I50" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J50" s="2" t="s">
+      <c r="H50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" t="s">
+        <v>17</v>
+      </c>
+      <c r="J50" t="s">
         <v>65</v>
       </c>
-      <c r="K50" s="2">
+      <c r="K50">
         <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A51" s="2" t="s">
+      <c r="A51" t="s">
         <v>20</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51">
         <v>7</v>
       </c>
-      <c r="C51" s="2">
+      <c r="C51">
         <v>4</v>
       </c>
-      <c r="D51" s="2" t="s">
+      <c r="D51" t="s">
         <v>23</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="E51" t="s">
         <v>63</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F51" t="s">
         <v>14</v>
       </c>
-      <c r="G51" s="2" t="s">
+      <c r="G51" t="s">
         <v>64</v>
       </c>
-      <c r="H51" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I51" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J51" s="2"/>
-      <c r="K51" s="2">
+      <c r="H51" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51">
         <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
+      <c r="A52" t="s">
         <v>11</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52">
         <v>14</v>
       </c>
-      <c r="C52" s="2">
+      <c r="C52">
         <v>10</v>
       </c>
-      <c r="D52" s="2" t="s">
+      <c r="D52" t="s">
         <v>66</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="E52" t="s">
         <v>63</v>
       </c>
-      <c r="F52" s="2" t="s">
+      <c r="F52" t="s">
         <v>14</v>
       </c>
-      <c r="G52" s="2" t="s">
+      <c r="G52" t="s">
         <v>64</v>
       </c>
-      <c r="H52" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I52" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J52" s="2"/>
-      <c r="K52" s="2">
+      <c r="H52" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52">
         <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A53" s="2" t="s">
+      <c r="A53" t="s">
         <v>22</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53">
         <v>6</v>
       </c>
-      <c r="C53" s="2">
+      <c r="C53">
         <v>2</v>
       </c>
-      <c r="D53" s="2" t="s">
+      <c r="D53" t="s">
         <v>25</v>
       </c>
-      <c r="E53" s="2" t="s">
+      <c r="E53" t="s">
         <v>63</v>
       </c>
-      <c r="F53" s="2" t="s">
+      <c r="F53" t="s">
         <v>14</v>
       </c>
-      <c r="G53" s="2" t="s">
+      <c r="G53" t="s">
         <v>64</v>
       </c>
-      <c r="H53" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I53" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J53" s="2"/>
-      <c r="K53" s="2">
+      <c r="H53" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" t="s">
+        <v>17</v>
+      </c>
+      <c r="K53">
         <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A54" s="2" t="s">
+      <c r="A54" t="s">
         <v>24</v>
       </c>
-      <c r="B54" s="2">
-        <v>0</v>
-      </c>
-      <c r="C54" s="2">
-        <v>0</v>
-      </c>
-      <c r="D54" s="2" t="s">
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54" t="s">
         <v>27</v>
       </c>
-      <c r="E54" s="2" t="s">
+      <c r="E54" t="s">
         <v>63</v>
       </c>
-      <c r="F54" s="2" t="s">
+      <c r="F54" t="s">
         <v>14</v>
       </c>
-      <c r="G54" s="2" t="s">
+      <c r="G54" t="s">
         <v>64</v>
       </c>
-      <c r="H54" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I54" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J54" s="2"/>
-      <c r="K54" s="2">
+      <c r="H54" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K54">
         <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
+      <c r="A55" t="s">
         <v>26</v>
       </c>
-      <c r="B55" s="2">
-        <v>0</v>
-      </c>
-      <c r="C55" s="2">
-        <v>0</v>
-      </c>
-      <c r="D55" s="2" t="s">
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55" t="s">
         <v>27</v>
       </c>
-      <c r="E55" s="2" t="s">
+      <c r="E55" t="s">
         <v>63</v>
       </c>
-      <c r="F55" s="2" t="s">
+      <c r="F55" t="s">
         <v>14</v>
       </c>
-      <c r="G55" s="2" t="s">
+      <c r="G55" t="s">
         <v>64</v>
       </c>
-      <c r="H55" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I55" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J55" s="2"/>
-      <c r="K55" s="2">
+      <c r="H55" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55" t="s">
+        <v>17</v>
+      </c>
+      <c r="K55">
         <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A56" s="2" t="s">
+      <c r="A56" t="s">
         <v>18</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56">
         <v>41</v>
       </c>
-      <c r="C56" s="2">
-        <v>16</v>
-      </c>
-      <c r="D56" s="2" t="s">
+      <c r="C56">
+        <v>16</v>
+      </c>
+      <c r="D56" t="s">
         <v>67</v>
       </c>
-      <c r="E56" s="2" t="s">
+      <c r="E56" t="s">
         <v>68</v>
       </c>
-      <c r="F56" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G56" s="2" t="s">
+      <c r="F56" t="s">
+        <v>30</v>
+      </c>
+      <c r="G56" t="s">
         <v>64</v>
       </c>
-      <c r="H56" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I56" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J56" s="2"/>
-      <c r="K56" s="2">
+      <c r="H56" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" t="s">
+        <v>17</v>
+      </c>
+      <c r="K56">
         <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A57" s="2" t="s">
+      <c r="A57" t="s">
         <v>20</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57">
         <v>11</v>
       </c>
-      <c r="C57" s="2">
+      <c r="C57">
         <v>2</v>
       </c>
-      <c r="D57" s="2" t="s">
+      <c r="D57" t="s">
         <v>69</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="E57" t="s">
         <v>68</v>
       </c>
-      <c r="F57" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G57" s="2" t="s">
+      <c r="F57" t="s">
+        <v>30</v>
+      </c>
+      <c r="G57" t="s">
         <v>64</v>
       </c>
-      <c r="H57" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I57" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" s="2"/>
-      <c r="K57" s="2">
+      <c r="H57" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" t="s">
+        <v>17</v>
+      </c>
+      <c r="K57">
         <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A58" s="2" t="s">
+      <c r="A58" t="s">
         <v>11</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58">
         <v>21</v>
       </c>
-      <c r="C58" s="2">
+      <c r="C58">
         <v>9</v>
       </c>
-      <c r="D58" s="2" t="s">
+      <c r="D58" t="s">
         <v>70</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="E58" t="s">
         <v>68</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G58" s="2" t="s">
+      <c r="F58" t="s">
+        <v>30</v>
+      </c>
+      <c r="G58" t="s">
         <v>64</v>
       </c>
-      <c r="H58" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J58" s="2"/>
-      <c r="K58" s="2">
+      <c r="H58" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" t="s">
+        <v>17</v>
+      </c>
+      <c r="K58">
         <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A59" s="2" t="s">
+      <c r="A59" t="s">
         <v>22</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59">
         <v>9</v>
       </c>
-      <c r="C59" s="2">
+      <c r="C59">
         <v>5</v>
       </c>
-      <c r="D59" s="2" t="s">
+      <c r="D59" t="s">
         <v>71</v>
       </c>
-      <c r="E59" s="2" t="s">
+      <c r="E59" t="s">
         <v>68</v>
       </c>
-      <c r="F59" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G59" s="2" t="s">
+      <c r="F59" t="s">
+        <v>30</v>
+      </c>
+      <c r="G59" t="s">
         <v>64</v>
       </c>
-      <c r="H59" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I59" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="2"/>
-      <c r="K59" s="2">
+      <c r="H59" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" t="s">
+        <v>17</v>
+      </c>
+      <c r="K59">
         <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A60" s="2" t="s">
+      <c r="A60" t="s">
         <v>24</v>
       </c>
-      <c r="B60" s="2">
-        <v>0</v>
-      </c>
-      <c r="C60" s="2">
-        <v>0</v>
-      </c>
-      <c r="D60" s="2" t="s">
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60" t="s">
         <v>27</v>
       </c>
-      <c r="E60" s="2" t="s">
+      <c r="E60" t="s">
         <v>68</v>
       </c>
-      <c r="F60" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G60" s="2" t="s">
+      <c r="F60" t="s">
+        <v>30</v>
+      </c>
+      <c r="G60" t="s">
         <v>64</v>
       </c>
-      <c r="H60" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I60" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="2"/>
-      <c r="K60" s="2">
+      <c r="H60" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" t="s">
+        <v>17</v>
+      </c>
+      <c r="K60">
         <v>100</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A61" s="2" t="s">
+      <c r="A61" t="s">
         <v>26</v>
       </c>
-      <c r="B61" s="2">
-        <v>0</v>
-      </c>
-      <c r="C61" s="2">
-        <v>0</v>
-      </c>
-      <c r="D61" s="2" t="s">
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61" t="s">
         <v>27</v>
       </c>
-      <c r="E61" s="2" t="s">
+      <c r="E61" t="s">
         <v>68</v>
       </c>
-      <c r="F61" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G61" s="2" t="s">
+      <c r="F61" t="s">
+        <v>30</v>
+      </c>
+      <c r="G61" t="s">
         <v>64</v>
       </c>
-      <c r="H61" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I61" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="J61" s="2"/>
-      <c r="K61" s="2">
+      <c r="H61" t="s">
+        <v>16</v>
+      </c>
+      <c r="I61" t="s">
+        <v>17</v>
+      </c>
+      <c r="K61">
         <v>100</v>
       </c>
     </row>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/Liquidacióncvs - copia/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/02 Febrero/Liquidacióncvs - copia/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_50C9ABF45252D60E62355476585DCE3A874705D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4E3540EB-D1B2-43AD-8492-503FB4837301}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="11_37DD5EEF9561BE0E62355476585DCE3A8747A48A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03BDCBB9-D9D6-4274-9836-07094D5FDBC0}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="74">
   <si>
     <t>Producto</t>
   </si>
@@ -52,7 +52,196 @@
     <t>Observación</t>
   </si>
   <si>
-    <t>no</t>
+    <t>ACC</t>
+  </si>
+  <si>
+    <t>POSTPAGO</t>
+  </si>
+  <si>
+    <t>108%</t>
+  </si>
+  <si>
+    <t>Lider Frontino Cely Ruiz</t>
+  </si>
+  <si>
+    <t>LIDER</t>
+  </si>
+  <si>
+    <t>FRONTINO</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>Sin pago (0%)</t>
+  </si>
+  <si>
+    <t>HOGAR</t>
+  </si>
+  <si>
+    <t>0%</t>
+  </si>
+  <si>
+    <t>TERMINALES</t>
+  </si>
+  <si>
+    <t>90%</t>
+  </si>
+  <si>
+    <t>OTROS</t>
+  </si>
+  <si>
+    <t>127%</t>
+  </si>
+  <si>
+    <t>CVS PLUS</t>
+  </si>
+  <si>
+    <t>cumplió el cvs al 40%</t>
+  </si>
+  <si>
+    <t>Diana Marcela Moreno Durango</t>
+  </si>
+  <si>
+    <t>ASESOR</t>
+  </si>
+  <si>
+    <t>Elaboró 18 días</t>
+  </si>
+  <si>
+    <t>35%</t>
+  </si>
+  <si>
+    <t>meta 68 %cump.47%</t>
+  </si>
+  <si>
+    <t>61%</t>
+  </si>
+  <si>
+    <t>meta 36 %cump. 83%</t>
+  </si>
+  <si>
+    <t>56%</t>
+  </si>
+  <si>
+    <t>Lider Dabeiba Edwin Dario David Velasquez</t>
+  </si>
+  <si>
+    <t>DABEIBA</t>
+  </si>
+  <si>
+    <t>Vac del 16 al 04 de mar - total días 16 meta 5 %cum 80%</t>
+  </si>
+  <si>
+    <t>46%</t>
+  </si>
+  <si>
+    <t>meta 13  %cump. 93%</t>
+  </si>
+  <si>
+    <t>29%</t>
+  </si>
+  <si>
+    <t>meta 14 %cump. 62%</t>
+  </si>
+  <si>
+    <t>meta puntos 102%</t>
+  </si>
+  <si>
+    <t>83%</t>
+  </si>
+  <si>
+    <t>Estelli Alejandra Ramirez Florez</t>
+  </si>
+  <si>
+    <t>79%</t>
+  </si>
+  <si>
+    <t>65%</t>
+  </si>
+  <si>
+    <t>316%</t>
+  </si>
+  <si>
+    <t>Lider Leider  Alexander Calderon</t>
+  </si>
+  <si>
+    <t>JUNIN</t>
+  </si>
+  <si>
+    <t>107%</t>
+  </si>
+  <si>
+    <t>125%</t>
+  </si>
+  <si>
+    <t>370%</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>Cristian Camilo Torres Toro</t>
+  </si>
+  <si>
+    <t>meta 10 %cump.250%</t>
+  </si>
+  <si>
+    <t>27%</t>
+  </si>
+  <si>
+    <t>meta 1  %cump.100%</t>
+  </si>
+  <si>
+    <t>47%</t>
+  </si>
+  <si>
+    <t>meta 30  %cump.127%</t>
+  </si>
+  <si>
+    <t>143%</t>
+  </si>
+  <si>
+    <t>Vac del 2 al 18</t>
+  </si>
+  <si>
+    <t>193%</t>
+  </si>
+  <si>
+    <t>Diana Marcela Taborda Ruiz</t>
+  </si>
+  <si>
+    <t>430%</t>
+  </si>
+  <si>
+    <t>104%</t>
+  </si>
+  <si>
+    <t>302%</t>
+  </si>
+  <si>
+    <t>168%</t>
+  </si>
+  <si>
+    <t>Sandra Milena Carmona Galeano</t>
+  </si>
+  <si>
+    <t>vac del 23 al 12 - 18 días</t>
+  </si>
+  <si>
+    <t>54%</t>
+  </si>
+  <si>
+    <t>meta 3 %cump. 67%</t>
+  </si>
+  <si>
+    <t>73%</t>
+  </si>
+  <si>
+    <t>meta 61 %cump. 98%</t>
+  </si>
+  <si>
+    <t>153%</t>
   </si>
 </sst>
 </file>
@@ -416,10 +605,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J70"/>
+  <dimension ref="A1:K51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -450,10 +639,1671 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="70" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J70" t="s">
+      <c r="K1" s="1" t="s">
         <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2">
+        <v>13</v>
+      </c>
+      <c r="C2">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="K2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3">
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <v>0</v>
+      </c>
+      <c r="D3" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G3" t="s">
+        <v>15</v>
+      </c>
+      <c r="H3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I3" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B4">
+        <v>91</v>
+      </c>
+      <c r="C4">
+        <v>82</v>
+      </c>
+      <c r="D4" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+      <c r="H4" t="s">
+        <v>16</v>
+      </c>
+      <c r="I4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B5">
+        <v>49</v>
+      </c>
+      <c r="C5">
+        <v>62</v>
+      </c>
+      <c r="D5" t="s">
+        <v>23</v>
+      </c>
+      <c r="E5" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G5" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" t="s">
+        <v>16</v>
+      </c>
+      <c r="I5" t="s">
+        <v>17</v>
+      </c>
+      <c r="K5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>24</v>
+      </c>
+      <c r="B6">
+        <v>750</v>
+      </c>
+      <c r="C6">
+        <v>0</v>
+      </c>
+      <c r="D6" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" t="s">
+        <v>14</v>
+      </c>
+      <c r="G6" t="s">
+        <v>15</v>
+      </c>
+      <c r="H6" t="s">
+        <v>16</v>
+      </c>
+      <c r="I6" t="s">
+        <v>17</v>
+      </c>
+      <c r="J6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7">
+        <v>13</v>
+      </c>
+      <c r="C7">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+      <c r="H7" t="s">
+        <v>16</v>
+      </c>
+      <c r="I7" t="s">
+        <v>17</v>
+      </c>
+      <c r="J7" t="s">
+        <v>28</v>
+      </c>
+      <c r="K7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8">
+        <v>0</v>
+      </c>
+      <c r="C8">
+        <v>0</v>
+      </c>
+      <c r="D8" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" t="s">
+        <v>26</v>
+      </c>
+      <c r="F8" t="s">
+        <v>27</v>
+      </c>
+      <c r="G8" t="s">
+        <v>15</v>
+      </c>
+      <c r="H8" t="s">
+        <v>16</v>
+      </c>
+      <c r="I8" t="s">
+        <v>17</v>
+      </c>
+      <c r="K8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>91</v>
+      </c>
+      <c r="C9">
+        <v>32</v>
+      </c>
+      <c r="D9" t="s">
+        <v>29</v>
+      </c>
+      <c r="E9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
+      </c>
+      <c r="H9" t="s">
+        <v>16</v>
+      </c>
+      <c r="I9" t="s">
+        <v>17</v>
+      </c>
+      <c r="J9" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10">
+        <v>49</v>
+      </c>
+      <c r="C10">
+        <v>30</v>
+      </c>
+      <c r="D10" t="s">
+        <v>31</v>
+      </c>
+      <c r="E10" t="s">
+        <v>26</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>15</v>
+      </c>
+      <c r="H10" t="s">
+        <v>16</v>
+      </c>
+      <c r="I10" t="s">
+        <v>17</v>
+      </c>
+      <c r="J10" t="s">
+        <v>32</v>
+      </c>
+      <c r="K10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>24</v>
+      </c>
+      <c r="B11">
+        <v>750</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" t="s">
+        <v>26</v>
+      </c>
+      <c r="F11" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" t="s">
+        <v>15</v>
+      </c>
+      <c r="H11" t="s">
+        <v>16</v>
+      </c>
+      <c r="I11" t="s">
+        <v>17</v>
+      </c>
+      <c r="J11" t="s">
+        <v>25</v>
+      </c>
+      <c r="K11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12">
+        <v>13</v>
+      </c>
+      <c r="C12">
+        <v>14</v>
+      </c>
+      <c r="D12" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" t="s">
+        <v>13</v>
+      </c>
+      <c r="F12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G12" t="s">
+        <v>15</v>
+      </c>
+      <c r="H12" t="s">
+        <v>16</v>
+      </c>
+      <c r="I12" t="s">
+        <v>17</v>
+      </c>
+      <c r="K12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>18</v>
+      </c>
+      <c r="B13">
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <v>0</v>
+      </c>
+      <c r="D13" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" t="s">
+        <v>13</v>
+      </c>
+      <c r="F13" t="s">
+        <v>14</v>
+      </c>
+      <c r="G13" t="s">
+        <v>15</v>
+      </c>
+      <c r="H13" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14">
+        <v>91</v>
+      </c>
+      <c r="C14">
+        <v>82</v>
+      </c>
+      <c r="D14" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" t="s">
+        <v>13</v>
+      </c>
+      <c r="F14" t="s">
+        <v>14</v>
+      </c>
+      <c r="G14" t="s">
+        <v>15</v>
+      </c>
+      <c r="H14" t="s">
+        <v>16</v>
+      </c>
+      <c r="I14" t="s">
+        <v>17</v>
+      </c>
+      <c r="K14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15">
+        <v>49</v>
+      </c>
+      <c r="C15">
+        <v>62</v>
+      </c>
+      <c r="D15" t="s">
+        <v>23</v>
+      </c>
+      <c r="E15" t="s">
+        <v>13</v>
+      </c>
+      <c r="F15" t="s">
+        <v>14</v>
+      </c>
+      <c r="G15" t="s">
+        <v>15</v>
+      </c>
+      <c r="H15" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" t="s">
+        <v>17</v>
+      </c>
+      <c r="K15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>24</v>
+      </c>
+      <c r="B16">
+        <v>750</v>
+      </c>
+      <c r="C16">
+        <v>0</v>
+      </c>
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" t="s">
+        <v>13</v>
+      </c>
+      <c r="F16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G16" t="s">
+        <v>15</v>
+      </c>
+      <c r="H16" t="s">
+        <v>16</v>
+      </c>
+      <c r="I16" t="s">
+        <v>17</v>
+      </c>
+      <c r="J16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>13</v>
+      </c>
+      <c r="C17">
+        <v>14</v>
+      </c>
+      <c r="D17" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" t="s">
+        <v>26</v>
+      </c>
+      <c r="F17" t="s">
+        <v>27</v>
+      </c>
+      <c r="G17" t="s">
+        <v>15</v>
+      </c>
+      <c r="H17" t="s">
+        <v>16</v>
+      </c>
+      <c r="I17" t="s">
+        <v>17</v>
+      </c>
+      <c r="J17" t="s">
+        <v>28</v>
+      </c>
+      <c r="K17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>18</v>
+      </c>
+      <c r="B18">
+        <v>0</v>
+      </c>
+      <c r="C18">
+        <v>0</v>
+      </c>
+      <c r="D18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" t="s">
+        <v>26</v>
+      </c>
+      <c r="F18" t="s">
+        <v>27</v>
+      </c>
+      <c r="G18" t="s">
+        <v>15</v>
+      </c>
+      <c r="H18" t="s">
+        <v>16</v>
+      </c>
+      <c r="I18" t="s">
+        <v>17</v>
+      </c>
+      <c r="K18">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>20</v>
+      </c>
+      <c r="B19">
+        <v>91</v>
+      </c>
+      <c r="C19">
+        <v>32</v>
+      </c>
+      <c r="D19" t="s">
+        <v>29</v>
+      </c>
+      <c r="E19" t="s">
+        <v>26</v>
+      </c>
+      <c r="F19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G19" t="s">
+        <v>15</v>
+      </c>
+      <c r="H19" t="s">
+        <v>16</v>
+      </c>
+      <c r="I19" t="s">
+        <v>17</v>
+      </c>
+      <c r="J19" t="s">
+        <v>30</v>
+      </c>
+      <c r="K19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20">
+        <v>49</v>
+      </c>
+      <c r="C20">
+        <v>30</v>
+      </c>
+      <c r="D20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E20" t="s">
+        <v>26</v>
+      </c>
+      <c r="F20" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" t="s">
+        <v>15</v>
+      </c>
+      <c r="H20" t="s">
+        <v>16</v>
+      </c>
+      <c r="I20" t="s">
+        <v>17</v>
+      </c>
+      <c r="J20" t="s">
+        <v>32</v>
+      </c>
+      <c r="K20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>24</v>
+      </c>
+      <c r="B21">
+        <v>750</v>
+      </c>
+      <c r="C21">
+        <v>0</v>
+      </c>
+      <c r="D21" t="s">
+        <v>19</v>
+      </c>
+      <c r="E21" t="s">
+        <v>26</v>
+      </c>
+      <c r="F21" t="s">
+        <v>27</v>
+      </c>
+      <c r="G21" t="s">
+        <v>15</v>
+      </c>
+      <c r="H21" t="s">
+        <v>16</v>
+      </c>
+      <c r="I21" t="s">
+        <v>17</v>
+      </c>
+      <c r="J21" t="s">
+        <v>25</v>
+      </c>
+      <c r="K21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>7</v>
+      </c>
+      <c r="C22">
+        <v>4</v>
+      </c>
+      <c r="D22" t="s">
+        <v>33</v>
+      </c>
+      <c r="E22" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" t="s">
+        <v>14</v>
+      </c>
+      <c r="G22" t="s">
+        <v>35</v>
+      </c>
+      <c r="H22" t="s">
+        <v>16</v>
+      </c>
+      <c r="I22" t="s">
+        <v>17</v>
+      </c>
+      <c r="J22" t="s">
+        <v>36</v>
+      </c>
+      <c r="K22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23">
+        <v>0</v>
+      </c>
+      <c r="C23">
+        <v>0</v>
+      </c>
+      <c r="D23" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" t="s">
+        <v>34</v>
+      </c>
+      <c r="F23" t="s">
+        <v>14</v>
+      </c>
+      <c r="G23" t="s">
+        <v>35</v>
+      </c>
+      <c r="H23" t="s">
+        <v>16</v>
+      </c>
+      <c r="I23" t="s">
+        <v>17</v>
+      </c>
+      <c r="K23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>20</v>
+      </c>
+      <c r="B24">
+        <v>26</v>
+      </c>
+      <c r="C24">
+        <v>12</v>
+      </c>
+      <c r="D24" t="s">
+        <v>37</v>
+      </c>
+      <c r="E24" t="s">
+        <v>34</v>
+      </c>
+      <c r="F24" t="s">
+        <v>14</v>
+      </c>
+      <c r="G24" t="s">
+        <v>35</v>
+      </c>
+      <c r="H24" t="s">
+        <v>16</v>
+      </c>
+      <c r="I24" t="s">
+        <v>17</v>
+      </c>
+      <c r="J24" t="s">
+        <v>38</v>
+      </c>
+      <c r="K24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>22</v>
+      </c>
+      <c r="B25">
+        <v>28</v>
+      </c>
+      <c r="C25">
+        <v>8</v>
+      </c>
+      <c r="D25" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" t="s">
+        <v>34</v>
+      </c>
+      <c r="F25" t="s">
+        <v>14</v>
+      </c>
+      <c r="G25" t="s">
+        <v>35</v>
+      </c>
+      <c r="H25" t="s">
+        <v>16</v>
+      </c>
+      <c r="I25" t="s">
+        <v>17</v>
+      </c>
+      <c r="J25" t="s">
+        <v>40</v>
+      </c>
+      <c r="K25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26">
+        <v>480</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" t="s">
+        <v>34</v>
+      </c>
+      <c r="F26" t="s">
+        <v>14</v>
+      </c>
+      <c r="G26" t="s">
+        <v>35</v>
+      </c>
+      <c r="H26" t="s">
+        <v>16</v>
+      </c>
+      <c r="I26" t="s">
+        <v>17</v>
+      </c>
+      <c r="J26" t="s">
+        <v>41</v>
+      </c>
+      <c r="K26">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>11</v>
+      </c>
+      <c r="C27">
+        <v>9</v>
+      </c>
+      <c r="D27" t="s">
+        <v>42</v>
+      </c>
+      <c r="E27" t="s">
+        <v>43</v>
+      </c>
+      <c r="F27" t="s">
+        <v>27</v>
+      </c>
+      <c r="G27" t="s">
+        <v>35</v>
+      </c>
+      <c r="H27" t="s">
+        <v>16</v>
+      </c>
+      <c r="I27" t="s">
+        <v>17</v>
+      </c>
+      <c r="K27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>18</v>
+      </c>
+      <c r="B28">
+        <v>0</v>
+      </c>
+      <c r="C28">
+        <v>0</v>
+      </c>
+      <c r="D28" t="s">
+        <v>19</v>
+      </c>
+      <c r="E28" t="s">
+        <v>43</v>
+      </c>
+      <c r="F28" t="s">
+        <v>27</v>
+      </c>
+      <c r="G28" t="s">
+        <v>35</v>
+      </c>
+      <c r="H28" t="s">
+        <v>16</v>
+      </c>
+      <c r="I28" t="s">
+        <v>17</v>
+      </c>
+      <c r="K28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>20</v>
+      </c>
+      <c r="B29">
+        <v>39</v>
+      </c>
+      <c r="C29">
+        <v>31</v>
+      </c>
+      <c r="D29" t="s">
+        <v>44</v>
+      </c>
+      <c r="E29" t="s">
+        <v>43</v>
+      </c>
+      <c r="F29" t="s">
+        <v>27</v>
+      </c>
+      <c r="G29" t="s">
+        <v>35</v>
+      </c>
+      <c r="H29" t="s">
+        <v>16</v>
+      </c>
+      <c r="I29" t="s">
+        <v>17</v>
+      </c>
+      <c r="K29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>22</v>
+      </c>
+      <c r="B30">
+        <v>41</v>
+      </c>
+      <c r="C30">
+        <v>27</v>
+      </c>
+      <c r="D30" t="s">
+        <v>45</v>
+      </c>
+      <c r="E30" t="s">
+        <v>43</v>
+      </c>
+      <c r="F30" t="s">
+        <v>27</v>
+      </c>
+      <c r="G30" t="s">
+        <v>35</v>
+      </c>
+      <c r="H30" t="s">
+        <v>16</v>
+      </c>
+      <c r="I30" t="s">
+        <v>17</v>
+      </c>
+      <c r="K30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>24</v>
+      </c>
+      <c r="B31">
+        <v>720</v>
+      </c>
+      <c r="C31">
+        <v>0</v>
+      </c>
+      <c r="D31" t="s">
+        <v>19</v>
+      </c>
+      <c r="E31" t="s">
+        <v>43</v>
+      </c>
+      <c r="F31" t="s">
+        <v>27</v>
+      </c>
+      <c r="G31" t="s">
+        <v>35</v>
+      </c>
+      <c r="H31" t="s">
+        <v>16</v>
+      </c>
+      <c r="I31" t="s">
+        <v>17</v>
+      </c>
+      <c r="K31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>21</v>
+      </c>
+      <c r="C32">
+        <v>65</v>
+      </c>
+      <c r="D32" t="s">
+        <v>46</v>
+      </c>
+      <c r="E32" t="s">
+        <v>47</v>
+      </c>
+      <c r="F32" t="s">
+        <v>14</v>
+      </c>
+      <c r="G32" t="s">
+        <v>48</v>
+      </c>
+      <c r="H32" t="s">
+        <v>16</v>
+      </c>
+      <c r="I32" t="s">
+        <v>17</v>
+      </c>
+      <c r="K32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33">
+        <v>3</v>
+      </c>
+      <c r="C33">
+        <v>3</v>
+      </c>
+      <c r="D33" t="s">
+        <v>49</v>
+      </c>
+      <c r="E33" t="s">
+        <v>47</v>
+      </c>
+      <c r="F33" t="s">
+        <v>14</v>
+      </c>
+      <c r="G33" t="s">
+        <v>48</v>
+      </c>
+      <c r="H33" t="s">
+        <v>16</v>
+      </c>
+      <c r="I33" t="s">
+        <v>17</v>
+      </c>
+      <c r="K33">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>20</v>
+      </c>
+      <c r="B34">
+        <v>61</v>
+      </c>
+      <c r="C34">
+        <v>77</v>
+      </c>
+      <c r="D34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" t="s">
+        <v>47</v>
+      </c>
+      <c r="F34" t="s">
+        <v>14</v>
+      </c>
+      <c r="G34" t="s">
+        <v>48</v>
+      </c>
+      <c r="H34" t="s">
+        <v>16</v>
+      </c>
+      <c r="I34" t="s">
+        <v>17</v>
+      </c>
+      <c r="K34">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>22</v>
+      </c>
+      <c r="B35">
+        <v>38</v>
+      </c>
+      <c r="C35">
+        <v>142</v>
+      </c>
+      <c r="D35" t="s">
+        <v>51</v>
+      </c>
+      <c r="E35" t="s">
+        <v>47</v>
+      </c>
+      <c r="F35" t="s">
+        <v>14</v>
+      </c>
+      <c r="G35" t="s">
+        <v>48</v>
+      </c>
+      <c r="H35" t="s">
+        <v>16</v>
+      </c>
+      <c r="I35" t="s">
+        <v>17</v>
+      </c>
+      <c r="K35">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>24</v>
+      </c>
+      <c r="B36">
+        <v>300</v>
+      </c>
+      <c r="C36">
+        <v>0</v>
+      </c>
+      <c r="D36" t="s">
+        <v>19</v>
+      </c>
+      <c r="E36" t="s">
+        <v>47</v>
+      </c>
+      <c r="F36" t="s">
+        <v>14</v>
+      </c>
+      <c r="G36" t="s">
+        <v>48</v>
+      </c>
+      <c r="H36" t="s">
+        <v>16</v>
+      </c>
+      <c r="I36" t="s">
+        <v>17</v>
+      </c>
+      <c r="K36">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>11</v>
+      </c>
+      <c r="B37">
+        <v>27</v>
+      </c>
+      <c r="C37">
+        <v>25</v>
+      </c>
+      <c r="D37" t="s">
+        <v>52</v>
+      </c>
+      <c r="E37" t="s">
+        <v>53</v>
+      </c>
+      <c r="F37" t="s">
+        <v>27</v>
+      </c>
+      <c r="G37" t="s">
+        <v>48</v>
+      </c>
+      <c r="H37" t="s">
+        <v>16</v>
+      </c>
+      <c r="I37" t="s">
+        <v>17</v>
+      </c>
+      <c r="J37" t="s">
+        <v>54</v>
+      </c>
+      <c r="K37">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>18</v>
+      </c>
+      <c r="B38">
+        <v>4</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="s">
+        <v>55</v>
+      </c>
+      <c r="E38" t="s">
+        <v>53</v>
+      </c>
+      <c r="F38" t="s">
+        <v>27</v>
+      </c>
+      <c r="G38" t="s">
+        <v>48</v>
+      </c>
+      <c r="H38" t="s">
+        <v>16</v>
+      </c>
+      <c r="I38" t="s">
+        <v>17</v>
+      </c>
+      <c r="J38" t="s">
+        <v>56</v>
+      </c>
+      <c r="K38">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>20</v>
+      </c>
+      <c r="B39">
+        <v>82</v>
+      </c>
+      <c r="C39">
+        <v>38</v>
+      </c>
+      <c r="D39" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" t="s">
+        <v>53</v>
+      </c>
+      <c r="F39" t="s">
+        <v>27</v>
+      </c>
+      <c r="G39" t="s">
+        <v>48</v>
+      </c>
+      <c r="H39" t="s">
+        <v>16</v>
+      </c>
+      <c r="I39" t="s">
+        <v>17</v>
+      </c>
+      <c r="J39" t="s">
+        <v>58</v>
+      </c>
+      <c r="K39">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>22</v>
+      </c>
+      <c r="B40">
+        <v>51</v>
+      </c>
+      <c r="C40">
+        <v>73</v>
+      </c>
+      <c r="D40" t="s">
+        <v>59</v>
+      </c>
+      <c r="E40" t="s">
+        <v>53</v>
+      </c>
+      <c r="F40" t="s">
+        <v>27</v>
+      </c>
+      <c r="G40" t="s">
+        <v>48</v>
+      </c>
+      <c r="H40" t="s">
+        <v>16</v>
+      </c>
+      <c r="I40" t="s">
+        <v>17</v>
+      </c>
+      <c r="J40" t="s">
+        <v>60</v>
+      </c>
+      <c r="K40">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B41">
+        <v>399</v>
+      </c>
+      <c r="C41">
+        <v>0</v>
+      </c>
+      <c r="D41" t="s">
+        <v>19</v>
+      </c>
+      <c r="E41" t="s">
+        <v>53</v>
+      </c>
+      <c r="F41" t="s">
+        <v>27</v>
+      </c>
+      <c r="G41" t="s">
+        <v>48</v>
+      </c>
+      <c r="H41" t="s">
+        <v>16</v>
+      </c>
+      <c r="I41" t="s">
+        <v>17</v>
+      </c>
+      <c r="K41">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>11</v>
+      </c>
+      <c r="B42">
+        <v>27</v>
+      </c>
+      <c r="C42">
+        <v>53</v>
+      </c>
+      <c r="D42" t="s">
+        <v>61</v>
+      </c>
+      <c r="E42" t="s">
+        <v>62</v>
+      </c>
+      <c r="F42" t="s">
+        <v>27</v>
+      </c>
+      <c r="G42" t="s">
+        <v>48</v>
+      </c>
+      <c r="H42" t="s">
+        <v>16</v>
+      </c>
+      <c r="I42" t="s">
+        <v>17</v>
+      </c>
+      <c r="K42">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>18</v>
+      </c>
+      <c r="B43">
+        <v>4</v>
+      </c>
+      <c r="C43">
+        <v>16</v>
+      </c>
+      <c r="D43" t="s">
+        <v>63</v>
+      </c>
+      <c r="E43" t="s">
+        <v>62</v>
+      </c>
+      <c r="F43" t="s">
+        <v>27</v>
+      </c>
+      <c r="G43" t="s">
+        <v>48</v>
+      </c>
+      <c r="H43" t="s">
+        <v>16</v>
+      </c>
+      <c r="I43" t="s">
+        <v>17</v>
+      </c>
+      <c r="K43">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>20</v>
+      </c>
+      <c r="B44">
+        <v>82</v>
+      </c>
+      <c r="C44">
+        <v>85</v>
+      </c>
+      <c r="D44" t="s">
+        <v>64</v>
+      </c>
+      <c r="E44" t="s">
+        <v>62</v>
+      </c>
+      <c r="F44" t="s">
+        <v>27</v>
+      </c>
+      <c r="G44" t="s">
+        <v>48</v>
+      </c>
+      <c r="H44" t="s">
+        <v>16</v>
+      </c>
+      <c r="I44" t="s">
+        <v>17</v>
+      </c>
+      <c r="K44">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>22</v>
+      </c>
+      <c r="B45">
+        <v>51</v>
+      </c>
+      <c r="C45">
+        <v>154</v>
+      </c>
+      <c r="D45" t="s">
+        <v>65</v>
+      </c>
+      <c r="E45" t="s">
+        <v>62</v>
+      </c>
+      <c r="F45" t="s">
+        <v>27</v>
+      </c>
+      <c r="G45" t="s">
+        <v>48</v>
+      </c>
+      <c r="H45" t="s">
+        <v>16</v>
+      </c>
+      <c r="I45" t="s">
+        <v>17</v>
+      </c>
+      <c r="K45">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>24</v>
+      </c>
+      <c r="B46">
+        <v>399</v>
+      </c>
+      <c r="C46">
+        <v>0</v>
+      </c>
+      <c r="D46" t="s">
+        <v>19</v>
+      </c>
+      <c r="E46" t="s">
+        <v>62</v>
+      </c>
+      <c r="F46" t="s">
+        <v>27</v>
+      </c>
+      <c r="G46" t="s">
+        <v>48</v>
+      </c>
+      <c r="H46" t="s">
+        <v>16</v>
+      </c>
+      <c r="I46" t="s">
+        <v>17</v>
+      </c>
+      <c r="K46">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>11</v>
+      </c>
+      <c r="B47">
+        <v>27</v>
+      </c>
+      <c r="C47">
+        <v>46</v>
+      </c>
+      <c r="D47" t="s">
+        <v>66</v>
+      </c>
+      <c r="E47" t="s">
+        <v>67</v>
+      </c>
+      <c r="F47" t="s">
+        <v>27</v>
+      </c>
+      <c r="G47" t="s">
+        <v>48</v>
+      </c>
+      <c r="H47" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" t="s">
+        <v>17</v>
+      </c>
+      <c r="J47" t="s">
+        <v>68</v>
+      </c>
+      <c r="K47">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>18</v>
+      </c>
+      <c r="B48">
+        <v>4</v>
+      </c>
+      <c r="C48">
+        <v>2</v>
+      </c>
+      <c r="D48" t="s">
+        <v>69</v>
+      </c>
+      <c r="E48" t="s">
+        <v>67</v>
+      </c>
+      <c r="F48" t="s">
+        <v>27</v>
+      </c>
+      <c r="G48" t="s">
+        <v>48</v>
+      </c>
+      <c r="H48" t="s">
+        <v>16</v>
+      </c>
+      <c r="I48" t="s">
+        <v>17</v>
+      </c>
+      <c r="J48" t="s">
+        <v>70</v>
+      </c>
+      <c r="K48">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49">
+        <v>82</v>
+      </c>
+      <c r="C49">
+        <v>60</v>
+      </c>
+      <c r="D49" t="s">
+        <v>71</v>
+      </c>
+      <c r="E49" t="s">
+        <v>67</v>
+      </c>
+      <c r="F49" t="s">
+        <v>27</v>
+      </c>
+      <c r="G49" t="s">
+        <v>48</v>
+      </c>
+      <c r="H49" t="s">
+        <v>16</v>
+      </c>
+      <c r="I49" t="s">
+        <v>17</v>
+      </c>
+      <c r="J49" t="s">
+        <v>72</v>
+      </c>
+      <c r="K49">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>22</v>
+      </c>
+      <c r="B50">
+        <v>51</v>
+      </c>
+      <c r="C50">
+        <v>78</v>
+      </c>
+      <c r="D50" t="s">
+        <v>73</v>
+      </c>
+      <c r="E50" t="s">
+        <v>67</v>
+      </c>
+      <c r="F50" t="s">
+        <v>27</v>
+      </c>
+      <c r="G50" t="s">
+        <v>48</v>
+      </c>
+      <c r="H50" t="s">
+        <v>16</v>
+      </c>
+      <c r="I50" t="s">
+        <v>17</v>
+      </c>
+      <c r="K50">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>24</v>
+      </c>
+      <c r="B51">
+        <v>399</v>
+      </c>
+      <c r="C51">
+        <v>0</v>
+      </c>
+      <c r="D51" t="s">
+        <v>19</v>
+      </c>
+      <c r="E51" t="s">
+        <v>67</v>
+      </c>
+      <c r="F51" t="s">
+        <v>27</v>
+      </c>
+      <c r="G51" t="s">
+        <v>48</v>
+      </c>
+      <c r="H51" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -5,22 +5,35 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/02 Febrero/Liquidacióncvs - copia/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/03 Marzo/Liquidacióncvs/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="11_37DD5EEF9561BE0E62355476585DCE3A8747A48A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{03BDCBB9-D9D6-4274-9836-07094D5FDBC0}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_50C9ABF45252D60E62355476585DCE3A874705D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D696614-1D97-4EB1-9565-92B28C3A979C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="72">
   <si>
     <t>Producto</t>
   </si>
@@ -52,196 +65,190 @@
     <t>Observación</t>
   </si>
   <si>
-    <t>ACC</t>
+    <t>no</t>
+  </si>
+  <si>
+    <t>TERMINALES</t>
+  </si>
+  <si>
+    <t>88%</t>
+  </si>
+  <si>
+    <t>Lider Leider  Alexander Calderon</t>
+  </si>
+  <si>
+    <t>LIDER</t>
+  </si>
+  <si>
+    <t>JUNIN</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>Sin pago (0%)</t>
+  </si>
+  <si>
+    <t>OTROS</t>
+  </si>
+  <si>
+    <t>313%</t>
   </si>
   <si>
     <t>POSTPAGO</t>
   </si>
   <si>
-    <t>108%</t>
-  </si>
-  <si>
-    <t>Lider Frontino Cely Ruiz</t>
-  </si>
-  <si>
-    <t>LIDER</t>
-  </si>
-  <si>
-    <t>FRONTINO</t>
-  </si>
-  <si>
-    <t>2026-02</t>
-  </si>
-  <si>
-    <t>Sin pago (0%)</t>
+    <t>205%</t>
+  </si>
+  <si>
+    <t>FOCO</t>
+  </si>
+  <si>
+    <t>57%</t>
   </si>
   <si>
     <t>HOGAR</t>
   </si>
   <si>
+    <t>33%</t>
+  </si>
+  <si>
+    <t>CVS PLUS</t>
+  </si>
+  <si>
     <t>0%</t>
   </si>
   <si>
-    <t>TERMINALES</t>
-  </si>
-  <si>
-    <t>90%</t>
-  </si>
-  <si>
-    <t>OTROS</t>
+    <t>5%</t>
+  </si>
+  <si>
+    <t>Cristian Camilo Torres Toro</t>
+  </si>
+  <si>
+    <t>ASESOR</t>
+  </si>
+  <si>
+    <t>Vacaciones del 02 al 18</t>
+  </si>
+  <si>
+    <t>12%</t>
+  </si>
+  <si>
+    <t>11%</t>
+  </si>
+  <si>
+    <t>84%</t>
+  </si>
+  <si>
+    <t>Diana Marcela Taborda Ruiz</t>
+  </si>
+  <si>
+    <t>222%</t>
+  </si>
+  <si>
+    <t>137%</t>
+  </si>
+  <si>
+    <t>100%</t>
+  </si>
+  <si>
+    <t>50%</t>
+  </si>
+  <si>
+    <t>73%</t>
+  </si>
+  <si>
+    <t>Sandra Milena Carmona Galeano</t>
+  </si>
+  <si>
+    <t>151%</t>
+  </si>
+  <si>
+    <t>152%</t>
+  </si>
+  <si>
+    <t>89%</t>
+  </si>
+  <si>
+    <t>3%</t>
+  </si>
+  <si>
+    <t>Lider  Bagre</t>
+  </si>
+  <si>
+    <t>EL BAGRE</t>
+  </si>
+  <si>
+    <t>Reemplaza vacaciones cajera del 01 al 18</t>
+  </si>
+  <si>
+    <t>113%</t>
+  </si>
+  <si>
+    <t>Darly Esther Sola Tarriba</t>
   </si>
   <si>
     <t>127%</t>
   </si>
   <si>
-    <t>CVS PLUS</t>
-  </si>
-  <si>
-    <t>cumplió el cvs al 40%</t>
-  </si>
-  <si>
-    <t>Diana Marcela Moreno Durango</t>
-  </si>
-  <si>
-    <t>ASESOR</t>
-  </si>
-  <si>
-    <t>Elaboró 18 días</t>
-  </si>
-  <si>
-    <t>35%</t>
-  </si>
-  <si>
-    <t>meta 68 %cump.47%</t>
-  </si>
-  <si>
-    <t>61%</t>
-  </si>
-  <si>
-    <t>meta 36 %cump. 83%</t>
+    <t>47%</t>
+  </si>
+  <si>
+    <t>92%</t>
+  </si>
+  <si>
+    <t>72%</t>
+  </si>
+  <si>
+    <t>Dayanis  Celsa Gamarra</t>
+  </si>
+  <si>
+    <t>63%</t>
+  </si>
+  <si>
+    <t>115%</t>
+  </si>
+  <si>
+    <t>87%</t>
+  </si>
+  <si>
+    <t>Jeider Alberto Moreno Solano</t>
+  </si>
+  <si>
+    <t>155%</t>
+  </si>
+  <si>
+    <t>69%</t>
+  </si>
+  <si>
+    <t>29%</t>
+  </si>
+  <si>
+    <t>Lider Dabeiba Edwin Dario David Velasquez</t>
+  </si>
+  <si>
+    <t>DABEIBA</t>
+  </si>
+  <si>
+    <t>Vac del 16 al 04 de marzo</t>
+  </si>
+  <si>
+    <t>71%</t>
+  </si>
+  <si>
+    <t>39%</t>
+  </si>
+  <si>
+    <t>Estelli Alejandra Ramirez Florez</t>
+  </si>
+  <si>
+    <t>18%</t>
+  </si>
+  <si>
+    <t>43%</t>
   </si>
   <si>
     <t>56%</t>
-  </si>
-  <si>
-    <t>Lider Dabeiba Edwin Dario David Velasquez</t>
-  </si>
-  <si>
-    <t>DABEIBA</t>
-  </si>
-  <si>
-    <t>Vac del 16 al 04 de mar - total días 16 meta 5 %cum 80%</t>
-  </si>
-  <si>
-    <t>46%</t>
-  </si>
-  <si>
-    <t>meta 13  %cump. 93%</t>
-  </si>
-  <si>
-    <t>29%</t>
-  </si>
-  <si>
-    <t>meta 14 %cump. 62%</t>
-  </si>
-  <si>
-    <t>meta puntos 102%</t>
-  </si>
-  <si>
-    <t>83%</t>
-  </si>
-  <si>
-    <t>Estelli Alejandra Ramirez Florez</t>
-  </si>
-  <si>
-    <t>79%</t>
-  </si>
-  <si>
-    <t>65%</t>
-  </si>
-  <si>
-    <t>316%</t>
-  </si>
-  <si>
-    <t>Lider Leider  Alexander Calderon</t>
-  </si>
-  <si>
-    <t>JUNIN</t>
-  </si>
-  <si>
-    <t>107%</t>
-  </si>
-  <si>
-    <t>125%</t>
-  </si>
-  <si>
-    <t>370%</t>
-  </si>
-  <si>
-    <t>91%</t>
-  </si>
-  <si>
-    <t>Cristian Camilo Torres Toro</t>
-  </si>
-  <si>
-    <t>meta 10 %cump.250%</t>
-  </si>
-  <si>
-    <t>27%</t>
-  </si>
-  <si>
-    <t>meta 1  %cump.100%</t>
-  </si>
-  <si>
-    <t>47%</t>
-  </si>
-  <si>
-    <t>meta 30  %cump.127%</t>
-  </si>
-  <si>
-    <t>143%</t>
-  </si>
-  <si>
-    <t>Vac del 2 al 18</t>
-  </si>
-  <si>
-    <t>193%</t>
-  </si>
-  <si>
-    <t>Diana Marcela Taborda Ruiz</t>
-  </si>
-  <si>
-    <t>430%</t>
-  </si>
-  <si>
-    <t>104%</t>
-  </si>
-  <si>
-    <t>302%</t>
-  </si>
-  <si>
-    <t>168%</t>
-  </si>
-  <si>
-    <t>Sandra Milena Carmona Galeano</t>
-  </si>
-  <si>
-    <t>vac del 23 al 12 - 18 días</t>
-  </si>
-  <si>
-    <t>54%</t>
-  </si>
-  <si>
-    <t>meta 3 %cump. 67%</t>
-  </si>
-  <si>
-    <t>73%</t>
-  </si>
-  <si>
-    <t>meta 61 %cump. 98%</t>
-  </si>
-  <si>
-    <t>153%</t>
   </si>
 </sst>
 </file>
@@ -605,8 +612,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K51"/>
+  <dimension ref="A1:K70"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="5" max="5" width="39.85546875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="37.28515625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -639,19 +650,16 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="C2">
-        <v>14</v>
+        <v>29</v>
       </c>
       <c r="D2" t="s">
         <v>12</v>
@@ -672,7 +680,7 @@
         <v>17</v>
       </c>
       <c r="K2">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -680,10 +688,10 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="C3">
-        <v>0</v>
+        <v>119</v>
       </c>
       <c r="D3" t="s">
         <v>19</v>
@@ -704,7 +712,7 @@
         <v>17</v>
       </c>
       <c r="K3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -712,10 +720,10 @@
         <v>20</v>
       </c>
       <c r="B4">
-        <v>91</v>
+        <v>21</v>
       </c>
       <c r="C4">
-        <v>82</v>
+        <v>43</v>
       </c>
       <c r="D4" t="s">
         <v>21</v>
@@ -736,7 +744,7 @@
         <v>17</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -744,10 +752,10 @@
         <v>22</v>
       </c>
       <c r="B5">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="C5">
-        <v>62</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
         <v>23</v>
@@ -768,7 +776,7 @@
         <v>17</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -776,13 +784,13 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>750</v>
+        <v>3</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="E6" t="s">
         <v>13</v>
@@ -799,31 +807,28 @@
       <c r="I6" t="s">
         <v>17</v>
       </c>
-      <c r="J6" t="s">
-        <v>25</v>
-      </c>
       <c r="K6">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B7">
+        <v>0</v>
+      </c>
+      <c r="C7">
+        <v>0</v>
+      </c>
+      <c r="D7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E7" t="s">
         <v>13</v>
       </c>
-      <c r="C7">
+      <c r="F7" t="s">
         <v>14</v>
-      </c>
-      <c r="D7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" t="s">
-        <v>26</v>
-      </c>
-      <c r="F7" t="s">
-        <v>27</v>
       </c>
       <c r="G7" t="s">
         <v>15</v>
@@ -834,31 +839,28 @@
       <c r="I7" t="s">
         <v>17</v>
       </c>
-      <c r="J7" t="s">
-        <v>28</v>
-      </c>
       <c r="K7">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B8">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D8" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E8" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F8" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G8" t="s">
         <v>15</v>
@@ -869,28 +871,31 @@
       <c r="I8" t="s">
         <v>17</v>
       </c>
+      <c r="J8" t="s">
+        <v>31</v>
+      </c>
       <c r="K8">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9" t="s">
         <v>32</v>
       </c>
-      <c r="D9" t="s">
+      <c r="E9" t="s">
         <v>29</v>
       </c>
-      <c r="E9" t="s">
-        <v>26</v>
-      </c>
       <c r="F9" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G9" t="s">
         <v>15</v>
@@ -901,31 +906,28 @@
       <c r="I9" t="s">
         <v>17</v>
       </c>
-      <c r="J9" t="s">
-        <v>30</v>
-      </c>
       <c r="K9">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10">
-        <v>49</v>
+        <v>27</v>
       </c>
       <c r="C10">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E10" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G10" t="s">
         <v>15</v>
@@ -936,31 +938,28 @@
       <c r="I10" t="s">
         <v>17</v>
       </c>
-      <c r="J10" t="s">
-        <v>32</v>
-      </c>
       <c r="K10">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11">
-        <v>750</v>
+        <v>19</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>19</v>
+        <v>33</v>
       </c>
       <c r="E11" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F11" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G11" t="s">
         <v>15</v>
@@ -971,31 +970,28 @@
       <c r="I11" t="s">
         <v>17</v>
       </c>
-      <c r="J11" t="s">
-        <v>25</v>
-      </c>
       <c r="K11">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B12">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="C12">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="D12" t="s">
-        <v>12</v>
+        <v>27</v>
       </c>
       <c r="E12" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F12" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G12" t="s">
         <v>15</v>
@@ -1007,12 +1003,12 @@
         <v>17</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B13">
         <v>0</v>
@@ -1021,13 +1017,13 @@
         <v>0</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E13" t="s">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F13" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G13" t="s">
         <v>15</v>
@@ -1039,27 +1035,27 @@
         <v>17</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B14">
-        <v>91</v>
+        <v>44</v>
       </c>
       <c r="C14">
-        <v>82</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>21</v>
+        <v>34</v>
       </c>
       <c r="E14" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F14" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G14" t="s">
         <v>15</v>
@@ -1071,27 +1067,27 @@
         <v>17</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B15">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C15">
-        <v>62</v>
+        <v>113</v>
       </c>
       <c r="D15" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="E15" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F15" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G15" t="s">
         <v>15</v>
@@ -1103,27 +1099,27 @@
         <v>17</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B16">
-        <v>750</v>
+        <v>27</v>
       </c>
       <c r="C16">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="E16" t="s">
-        <v>13</v>
+        <v>35</v>
       </c>
       <c r="F16" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G16" t="s">
         <v>15</v>
@@ -1134,31 +1130,28 @@
       <c r="I16" t="s">
         <v>17</v>
       </c>
-      <c r="J16" t="s">
-        <v>25</v>
-      </c>
       <c r="K16">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="C17">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="D17" t="s">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="E17" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F17" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G17" t="s">
         <v>15</v>
@@ -1169,31 +1162,28 @@
       <c r="I17" t="s">
         <v>17</v>
       </c>
-      <c r="J17" t="s">
-        <v>28</v>
-      </c>
       <c r="K17">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B18">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C18">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D18" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E18" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F18" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G18" t="s">
         <v>15</v>
@@ -1205,27 +1195,27 @@
         <v>17</v>
       </c>
       <c r="K18">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B19">
-        <v>91</v>
+        <v>0</v>
       </c>
       <c r="C19">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="D19" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E19" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="F19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G19" t="s">
         <v>15</v>
@@ -1236,31 +1226,28 @@
       <c r="I19" t="s">
         <v>17</v>
       </c>
-      <c r="J19" t="s">
-        <v>30</v>
-      </c>
       <c r="K19">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B20">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="C20">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="D20" t="s">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="E20" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F20" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G20" t="s">
         <v>15</v>
@@ -1271,31 +1258,28 @@
       <c r="I20" t="s">
         <v>17</v>
       </c>
-      <c r="J20" t="s">
-        <v>32</v>
-      </c>
       <c r="K20">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B21">
-        <v>750</v>
+        <v>51</v>
       </c>
       <c r="C21">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="D21" t="s">
-        <v>19</v>
+        <v>42</v>
       </c>
       <c r="E21" t="s">
-        <v>26</v>
+        <v>41</v>
       </c>
       <c r="F21" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G21" t="s">
         <v>15</v>
@@ -1306,34 +1290,31 @@
       <c r="I21" t="s">
         <v>17</v>
       </c>
-      <c r="J21" t="s">
-        <v>25</v>
-      </c>
       <c r="K21">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B22">
-        <v>7</v>
+        <v>27</v>
       </c>
       <c r="C22">
-        <v>4</v>
+        <v>41</v>
       </c>
       <c r="D22" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
       <c r="E22" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F22" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G22" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
@@ -1341,34 +1322,31 @@
       <c r="I22" t="s">
         <v>17</v>
       </c>
-      <c r="J22" t="s">
-        <v>36</v>
-      </c>
       <c r="K22">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="D23" t="s">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="E23" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F23" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G23" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
@@ -1377,30 +1355,30 @@
         <v>17</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B24">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="C24">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="D24" t="s">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="E24" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F24" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G24" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
@@ -1408,34 +1386,31 @@
       <c r="I24" t="s">
         <v>17</v>
       </c>
-      <c r="J24" t="s">
-        <v>38</v>
-      </c>
       <c r="K24">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B25">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="C25">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="E25" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F25" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G25" t="s">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -1443,34 +1418,31 @@
       <c r="I25" t="s">
         <v>17</v>
       </c>
-      <c r="J25" t="s">
-        <v>40</v>
-      </c>
       <c r="K25">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B26">
-        <v>480</v>
+        <v>35</v>
       </c>
       <c r="C26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D26" t="s">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="E26" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F26" t="s">
         <v>14</v>
       </c>
       <c r="G26" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -1479,7 +1451,7 @@
         <v>17</v>
       </c>
       <c r="J26" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="K26">
         <v>100</v>
@@ -1487,25 +1459,25 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B27">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C27">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D27" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
       <c r="E27" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F27" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -1519,25 +1491,25 @@
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B28">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>19</v>
+        <v>28</v>
       </c>
       <c r="E28" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F28" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -1551,25 +1523,25 @@
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B29">
-        <v>39</v>
+        <v>10</v>
       </c>
       <c r="C29">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="D29" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="E29" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F29" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -1583,25 +1555,25 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B30">
-        <v>41</v>
+        <v>0</v>
       </c>
       <c r="C30">
+        <v>0</v>
+      </c>
+      <c r="D30" t="s">
         <v>27</v>
       </c>
-      <c r="D30" t="s">
-        <v>45</v>
-      </c>
       <c r="E30" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F30" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -1615,25 +1587,25 @@
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B31">
-        <v>720</v>
+        <v>0</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E31" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="F31" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -1647,25 +1619,25 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B32">
-        <v>21</v>
+        <v>47</v>
       </c>
       <c r="C32">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="E32" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F32" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G32" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -1679,25 +1651,25 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B33">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="C33">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="E33" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F33" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G33" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -1711,25 +1683,25 @@
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B34">
-        <v>61</v>
+        <v>30</v>
       </c>
       <c r="C34">
-        <v>77</v>
+        <v>14</v>
       </c>
       <c r="D34" t="s">
+        <v>52</v>
+      </c>
+      <c r="E34" t="s">
         <v>50</v>
       </c>
-      <c r="E34" t="s">
-        <v>47</v>
-      </c>
       <c r="F34" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -1746,22 +1718,22 @@
         <v>22</v>
       </c>
       <c r="B35">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="C35">
-        <v>142</v>
+        <v>12</v>
       </c>
       <c r="D35" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E35" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F35" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G35" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -1778,22 +1750,22 @@
         <v>24</v>
       </c>
       <c r="B36">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="E36" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="F36" t="s">
-        <v>14</v>
+        <v>30</v>
       </c>
       <c r="G36" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -1807,34 +1779,31 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37">
+        <v>0</v>
+      </c>
+      <c r="D37" t="s">
         <v>27</v>
       </c>
-      <c r="C37">
-        <v>25</v>
-      </c>
-      <c r="D37" t="s">
-        <v>52</v>
-      </c>
       <c r="E37" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F37" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G37" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
       </c>
       <c r="I37" t="s">
         <v>17</v>
-      </c>
-      <c r="J37" t="s">
-        <v>54</v>
       </c>
       <c r="K37">
         <v>100</v>
@@ -1845,31 +1814,28 @@
         <v>18</v>
       </c>
       <c r="B38">
-        <v>4</v>
+        <v>47</v>
       </c>
       <c r="C38">
-        <v>1</v>
+        <v>34</v>
       </c>
       <c r="D38" t="s">
+        <v>54</v>
+      </c>
+      <c r="E38" t="s">
         <v>55</v>
       </c>
-      <c r="E38" t="s">
-        <v>53</v>
-      </c>
       <c r="F38" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G38" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
       </c>
       <c r="I38" t="s">
         <v>17</v>
-      </c>
-      <c r="J38" t="s">
-        <v>56</v>
       </c>
       <c r="K38">
         <v>100</v>
@@ -1880,31 +1846,28 @@
         <v>20</v>
       </c>
       <c r="B39">
-        <v>82</v>
+        <v>11</v>
       </c>
       <c r="C39">
-        <v>38</v>
+        <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="E39" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F39" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G39" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
       </c>
       <c r="I39" t="s">
         <v>17</v>
-      </c>
-      <c r="J39" t="s">
-        <v>58</v>
       </c>
       <c r="K39">
         <v>100</v>
@@ -1912,34 +1875,31 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B40">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="C40">
-        <v>73</v>
+        <v>19</v>
       </c>
       <c r="D40" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E40" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F40" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G40" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
       </c>
       <c r="I40" t="s">
         <v>17</v>
-      </c>
-      <c r="J40" t="s">
-        <v>60</v>
       </c>
       <c r="K40">
         <v>100</v>
@@ -1947,25 +1907,25 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B41">
-        <v>399</v>
+        <v>13</v>
       </c>
       <c r="C41">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D41" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="E41" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F41" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G41" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
@@ -1979,25 +1939,25 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B42">
+        <v>0</v>
+      </c>
+      <c r="C42">
+        <v>0</v>
+      </c>
+      <c r="D42" t="s">
         <v>27</v>
       </c>
-      <c r="C42">
-        <v>53</v>
-      </c>
-      <c r="D42" t="s">
-        <v>61</v>
-      </c>
       <c r="E42" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F42" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G42" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
@@ -2011,25 +1971,25 @@
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B43">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C43">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="E43" t="s">
-        <v>62</v>
+        <v>55</v>
       </c>
       <c r="F43" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G43" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
@@ -2043,25 +2003,25 @@
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B44">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="C44">
-        <v>85</v>
+        <v>41</v>
       </c>
       <c r="D44" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="E44" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F44" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G44" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
@@ -2075,25 +2035,25 @@
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B45">
-        <v>51</v>
+        <v>11</v>
       </c>
       <c r="C45">
-        <v>154</v>
+        <v>17</v>
       </c>
       <c r="D45" t="s">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="E45" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F45" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G45" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
@@ -2107,25 +2067,25 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B46">
-        <v>399</v>
+        <v>30</v>
       </c>
       <c r="C46">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="D46" t="s">
-        <v>19</v>
+        <v>39</v>
       </c>
       <c r="E46" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F46" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G46" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
@@ -2139,34 +2099,31 @@
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B47">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C47">
-        <v>46</v>
+        <v>9</v>
       </c>
       <c r="D47" t="s">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="E47" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F47" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G47" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
       </c>
       <c r="I47" t="s">
         <v>17</v>
-      </c>
-      <c r="J47" t="s">
-        <v>68</v>
       </c>
       <c r="K47">
         <v>100</v>
@@ -2174,34 +2131,31 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B48">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D48" t="s">
-        <v>69</v>
+        <v>27</v>
       </c>
       <c r="E48" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F48" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
       </c>
       <c r="I48" t="s">
         <v>17</v>
-      </c>
-      <c r="J48" t="s">
-        <v>70</v>
       </c>
       <c r="K48">
         <v>100</v>
@@ -2209,34 +2163,31 @@
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="B49">
-        <v>82</v>
+        <v>0</v>
       </c>
       <c r="C49">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="D49" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="E49" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="F49" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G49" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
       </c>
       <c r="I49" t="s">
         <v>17</v>
-      </c>
-      <c r="J49" t="s">
-        <v>72</v>
       </c>
       <c r="K49">
         <v>100</v>
@@ -2244,31 +2195,34 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B50">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="C50">
-        <v>78</v>
+        <v>8</v>
       </c>
       <c r="D50" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="E50" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="F50" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>48</v>
+        <v>64</v>
       </c>
       <c r="H50" t="s">
         <v>16</v>
       </c>
       <c r="I50" t="s">
         <v>17</v>
+      </c>
+      <c r="J50" t="s">
+        <v>65</v>
       </c>
       <c r="K50">
         <v>100</v>
@@ -2276,34 +2230,359 @@
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>20</v>
+      </c>
+      <c r="B51">
+        <v>7</v>
+      </c>
+      <c r="C51">
+        <v>4</v>
+      </c>
+      <c r="D51" t="s">
+        <v>23</v>
+      </c>
+      <c r="E51" t="s">
+        <v>63</v>
+      </c>
+      <c r="F51" t="s">
+        <v>14</v>
+      </c>
+      <c r="G51" t="s">
+        <v>64</v>
+      </c>
+      <c r="H51" t="s">
+        <v>16</v>
+      </c>
+      <c r="I51" t="s">
+        <v>17</v>
+      </c>
+      <c r="K51">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>11</v>
+      </c>
+      <c r="B52">
+        <v>14</v>
+      </c>
+      <c r="C52">
+        <v>10</v>
+      </c>
+      <c r="D52" t="s">
+        <v>66</v>
+      </c>
+      <c r="E52" t="s">
+        <v>63</v>
+      </c>
+      <c r="F52" t="s">
+        <v>14</v>
+      </c>
+      <c r="G52" t="s">
+        <v>64</v>
+      </c>
+      <c r="H52" t="s">
+        <v>16</v>
+      </c>
+      <c r="I52" t="s">
+        <v>17</v>
+      </c>
+      <c r="K52">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>22</v>
+      </c>
+      <c r="B53">
+        <v>6</v>
+      </c>
+      <c r="C53">
+        <v>2</v>
+      </c>
+      <c r="D53" t="s">
+        <v>25</v>
+      </c>
+      <c r="E53" t="s">
+        <v>63</v>
+      </c>
+      <c r="F53" t="s">
+        <v>14</v>
+      </c>
+      <c r="G53" t="s">
+        <v>64</v>
+      </c>
+      <c r="H53" t="s">
+        <v>16</v>
+      </c>
+      <c r="I53" t="s">
+        <v>17</v>
+      </c>
+      <c r="K53">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
         <v>24</v>
       </c>
-      <c r="B51">
-        <v>399</v>
-      </c>
-      <c r="C51">
-        <v>0</v>
-      </c>
-      <c r="D51" t="s">
-        <v>19</v>
-      </c>
-      <c r="E51" t="s">
+      <c r="B54">
+        <v>0</v>
+      </c>
+      <c r="C54">
+        <v>0</v>
+      </c>
+      <c r="D54" t="s">
+        <v>27</v>
+      </c>
+      <c r="E54" t="s">
+        <v>63</v>
+      </c>
+      <c r="F54" t="s">
+        <v>14</v>
+      </c>
+      <c r="G54" t="s">
+        <v>64</v>
+      </c>
+      <c r="H54" t="s">
+        <v>16</v>
+      </c>
+      <c r="I54" t="s">
+        <v>17</v>
+      </c>
+      <c r="K54">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>26</v>
+      </c>
+      <c r="B55">
+        <v>0</v>
+      </c>
+      <c r="C55">
+        <v>0</v>
+      </c>
+      <c r="D55" t="s">
+        <v>27</v>
+      </c>
+      <c r="E55" t="s">
+        <v>63</v>
+      </c>
+      <c r="F55" t="s">
+        <v>14</v>
+      </c>
+      <c r="G55" t="s">
+        <v>64</v>
+      </c>
+      <c r="H55" t="s">
+        <v>16</v>
+      </c>
+      <c r="I55" t="s">
+        <v>17</v>
+      </c>
+      <c r="K55">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>18</v>
+      </c>
+      <c r="B56">
+        <v>41</v>
+      </c>
+      <c r="C56">
+        <v>16</v>
+      </c>
+      <c r="D56" t="s">
         <v>67</v>
       </c>
-      <c r="F51" t="s">
+      <c r="E56" t="s">
+        <v>68</v>
+      </c>
+      <c r="F56" t="s">
+        <v>30</v>
+      </c>
+      <c r="G56" t="s">
+        <v>64</v>
+      </c>
+      <c r="H56" t="s">
+        <v>16</v>
+      </c>
+      <c r="I56" t="s">
+        <v>17</v>
+      </c>
+      <c r="K56">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>20</v>
+      </c>
+      <c r="B57">
+        <v>11</v>
+      </c>
+      <c r="C57">
+        <v>2</v>
+      </c>
+      <c r="D57" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" t="s">
+        <v>68</v>
+      </c>
+      <c r="F57" t="s">
+        <v>30</v>
+      </c>
+      <c r="G57" t="s">
+        <v>64</v>
+      </c>
+      <c r="H57" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" t="s">
+        <v>17</v>
+      </c>
+      <c r="K57">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>11</v>
+      </c>
+      <c r="B58">
+        <v>21</v>
+      </c>
+      <c r="C58">
+        <v>9</v>
+      </c>
+      <c r="D58" t="s">
+        <v>70</v>
+      </c>
+      <c r="E58" t="s">
+        <v>68</v>
+      </c>
+      <c r="F58" t="s">
+        <v>30</v>
+      </c>
+      <c r="G58" t="s">
+        <v>64</v>
+      </c>
+      <c r="H58" t="s">
+        <v>16</v>
+      </c>
+      <c r="I58" t="s">
+        <v>17</v>
+      </c>
+      <c r="K58">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>22</v>
+      </c>
+      <c r="B59">
+        <v>9</v>
+      </c>
+      <c r="C59">
+        <v>5</v>
+      </c>
+      <c r="D59" t="s">
+        <v>71</v>
+      </c>
+      <c r="E59" t="s">
+        <v>68</v>
+      </c>
+      <c r="F59" t="s">
+        <v>30</v>
+      </c>
+      <c r="G59" t="s">
+        <v>64</v>
+      </c>
+      <c r="H59" t="s">
+        <v>16</v>
+      </c>
+      <c r="I59" t="s">
+        <v>17</v>
+      </c>
+      <c r="K59">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>24</v>
+      </c>
+      <c r="B60">
+        <v>0</v>
+      </c>
+      <c r="C60">
+        <v>0</v>
+      </c>
+      <c r="D60" t="s">
         <v>27</v>
       </c>
-      <c r="G51" t="s">
-        <v>48</v>
-      </c>
-      <c r="H51" t="s">
-        <v>16</v>
-      </c>
-      <c r="I51" t="s">
-        <v>17</v>
-      </c>
-      <c r="K51">
-        <v>100</v>
+      <c r="E60" t="s">
+        <v>68</v>
+      </c>
+      <c r="F60" t="s">
+        <v>30</v>
+      </c>
+      <c r="G60" t="s">
+        <v>64</v>
+      </c>
+      <c r="H60" t="s">
+        <v>16</v>
+      </c>
+      <c r="I60" t="s">
+        <v>17</v>
+      </c>
+      <c r="K60">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>26</v>
+      </c>
+      <c r="B61">
+        <v>0</v>
+      </c>
+      <c r="C61">
+        <v>0</v>
+      </c>
+      <c r="D61" t="s">
+        <v>27</v>
+      </c>
+      <c r="E61" t="s">
+        <v>68</v>
+      </c>
+      <c r="F61" t="s">
+        <v>30</v>
+      </c>
+      <c r="G61" t="s">
+        <v>64</v>
+      </c>
+      <c r="H61" t="s">
+        <v>16</v>
+      </c>
+      <c r="I61" t="s">
+        <v>17</v>
+      </c>
+      <c r="K61">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="70" spans="10:10" x14ac:dyDescent="0.25">
+      <c r="J70" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -5,35 +5,22 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/03 Marzo/Liquidacióncvs/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/02 Febrero/Liquidacióncvs - copia/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="11_50C9ABF45252D60E62355476585DCE3A874705D4" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0D696614-1D97-4EB1-9565-92B28C3A979C}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="11_37DD5EEF9561BE0E62355476585DCE3A8747A48A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D011DC07-FF31-42EF-95ED-EAE288DFB386}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="193">
   <si>
     <t>Producto</t>
   </si>
@@ -65,190 +52,553 @@
     <t>Observación</t>
   </si>
   <si>
-    <t>no</t>
+    <t>ACC</t>
+  </si>
+  <si>
+    <t>POSTPAGO</t>
+  </si>
+  <si>
+    <t>108%</t>
+  </si>
+  <si>
+    <t>Lider Frontino Cely Ruiz</t>
+  </si>
+  <si>
+    <t>LIDER</t>
+  </si>
+  <si>
+    <t>FRONTINO</t>
+  </si>
+  <si>
+    <t>2026-02</t>
+  </si>
+  <si>
+    <t>Sin pago (0%)</t>
+  </si>
+  <si>
+    <t>HOGAR</t>
+  </si>
+  <si>
+    <t>0%</t>
   </si>
   <si>
     <t>TERMINALES</t>
   </si>
   <si>
-    <t>88%</t>
+    <t>90%</t>
+  </si>
+  <si>
+    <t>OTROS</t>
+  </si>
+  <si>
+    <t>127%</t>
+  </si>
+  <si>
+    <t>CVS PLUS</t>
+  </si>
+  <si>
+    <t>cumplió el cvs al 40%</t>
+  </si>
+  <si>
+    <t>Diana Marcela Moreno Durango</t>
+  </si>
+  <si>
+    <t>ASESOR</t>
+  </si>
+  <si>
+    <t>Elaboró 18 días</t>
+  </si>
+  <si>
+    <t>35%</t>
+  </si>
+  <si>
+    <t>meta 68 %cump.47%</t>
+  </si>
+  <si>
+    <t>61%</t>
+  </si>
+  <si>
+    <t>meta 36 %cump. 83%</t>
+  </si>
+  <si>
+    <t>56%</t>
+  </si>
+  <si>
+    <t>Lider Dabeiba Edwin Dario David Velasquez</t>
+  </si>
+  <si>
+    <t>DABEIBA</t>
+  </si>
+  <si>
+    <t>Vac del 16 al 04 de mar - total días 16 meta 5 %cum 80%</t>
+  </si>
+  <si>
+    <t>46%</t>
+  </si>
+  <si>
+    <t>meta 13  %cump. 93%</t>
+  </si>
+  <si>
+    <t>29%</t>
+  </si>
+  <si>
+    <t>meta 14 %cump. 62%</t>
+  </si>
+  <si>
+    <t>meta puntos 102%</t>
+  </si>
+  <si>
+    <t>83%</t>
+  </si>
+  <si>
+    <t>Estelli Alejandra Ramirez Florez</t>
+  </si>
+  <si>
+    <t>79%</t>
+  </si>
+  <si>
+    <t>65%</t>
+  </si>
+  <si>
+    <t>316%</t>
   </si>
   <si>
     <t>Lider Leider  Alexander Calderon</t>
   </si>
   <si>
-    <t>LIDER</t>
-  </si>
-  <si>
     <t>JUNIN</t>
   </si>
   <si>
-    <t>2026-02</t>
-  </si>
-  <si>
-    <t>Sin pago (0%)</t>
-  </si>
-  <si>
-    <t>OTROS</t>
-  </si>
-  <si>
-    <t>313%</t>
-  </si>
-  <si>
-    <t>POSTPAGO</t>
-  </si>
-  <si>
-    <t>205%</t>
-  </si>
-  <si>
-    <t>FOCO</t>
-  </si>
-  <si>
-    <t>57%</t>
-  </si>
-  <si>
-    <t>HOGAR</t>
-  </si>
-  <si>
-    <t>33%</t>
-  </si>
-  <si>
-    <t>CVS PLUS</t>
-  </si>
-  <si>
-    <t>0%</t>
+    <t>107%</t>
+  </si>
+  <si>
+    <t>125%</t>
+  </si>
+  <si>
+    <t>370%</t>
+  </si>
+  <si>
+    <t>91%</t>
+  </si>
+  <si>
+    <t>Cristian Camilo Torres Toro</t>
+  </si>
+  <si>
+    <t>meta 10 %cump.250%</t>
+  </si>
+  <si>
+    <t>27%</t>
+  </si>
+  <si>
+    <t>meta 1  %cump.100%</t>
+  </si>
+  <si>
+    <t>47%</t>
+  </si>
+  <si>
+    <t>meta 30  %cump.127%</t>
+  </si>
+  <si>
+    <t>143%</t>
+  </si>
+  <si>
+    <t>Vac del 2 al 18</t>
+  </si>
+  <si>
+    <t>193%</t>
+  </si>
+  <si>
+    <t>Diana Marcela Taborda Ruiz</t>
+  </si>
+  <si>
+    <t>430%</t>
+  </si>
+  <si>
+    <t>104%</t>
+  </si>
+  <si>
+    <t>302%</t>
+  </si>
+  <si>
+    <t>168%</t>
+  </si>
+  <si>
+    <t>Sandra Milena Carmona Galeano</t>
+  </si>
+  <si>
+    <t>vac del 23 al 12 - 18 días</t>
+  </si>
+  <si>
+    <t>54%</t>
+  </si>
+  <si>
+    <t>meta 3 %cump. 67%</t>
+  </si>
+  <si>
+    <t>73%</t>
+  </si>
+  <si>
+    <t>meta 61 %cump. 98%</t>
+  </si>
+  <si>
+    <t>153%</t>
+  </si>
+  <si>
+    <t>Puntos % cumpli 195%</t>
+  </si>
+  <si>
+    <t>ITAGUI</t>
+  </si>
+  <si>
+    <t>Yanina Rocio Lozano Martinez</t>
+  </si>
+  <si>
+    <t>34%</t>
+  </si>
+  <si>
+    <t>30%</t>
+  </si>
+  <si>
+    <t>Manuela  Vinasco Trejos</t>
+  </si>
+  <si>
+    <t>157%</t>
+  </si>
+  <si>
+    <t>240%</t>
+  </si>
+  <si>
+    <t>145%</t>
+  </si>
+  <si>
+    <t>Lider Luz Stella Serna</t>
+  </si>
+  <si>
+    <t>204%</t>
+  </si>
+  <si>
+    <t>123%</t>
+  </si>
+  <si>
+    <t>200%</t>
+  </si>
+  <si>
+    <t>164%</t>
+  </si>
+  <si>
+    <t>GIRARDOTA</t>
+  </si>
+  <si>
+    <t>Narelig Alejandra GarcÃ­a Ramirez</t>
+  </si>
+  <si>
+    <t>118%</t>
+  </si>
+  <si>
+    <t>87%</t>
+  </si>
+  <si>
+    <t>139%</t>
+  </si>
+  <si>
+    <t>130%</t>
+  </si>
+  <si>
+    <t>Lider Girardota Paulina Andrea Zapata Jimenez</t>
+  </si>
+  <si>
+    <t>51%</t>
+  </si>
+  <si>
+    <t>cumplimiento 81%</t>
+  </si>
+  <si>
+    <t>GENERAL</t>
+  </si>
+  <si>
+    <t>Coordinador y Supervisora</t>
+  </si>
+  <si>
+    <t>115%</t>
+  </si>
+  <si>
+    <t>176%</t>
+  </si>
+  <si>
+    <t>elab. 18 días  % puntos 86%</t>
+  </si>
+  <si>
+    <t>ENVIGADO</t>
+  </si>
+  <si>
+    <t>Luz Enith Sanchez Galeano</t>
+  </si>
+  <si>
+    <t>102%</t>
+  </si>
+  <si>
+    <t>meta 20 %cum. 135%</t>
+  </si>
+  <si>
+    <t>58%</t>
+  </si>
+  <si>
+    <t>meta 5  % cump. 20%</t>
+  </si>
+  <si>
+    <t>17%</t>
+  </si>
+  <si>
+    <t>meta 22 % cum 164%</t>
+  </si>
+  <si>
+    <t>Andrea  Arenas Hurtado</t>
+  </si>
+  <si>
+    <t>85%</t>
+  </si>
+  <si>
+    <t>150%</t>
+  </si>
+  <si>
+    <t>103%</t>
+  </si>
+  <si>
+    <t>Lider Marcela Valencia Tabares</t>
+  </si>
+  <si>
+    <t>575%</t>
+  </si>
+  <si>
+    <t>EL BAGRE</t>
+  </si>
+  <si>
+    <t>Jeider Alberto Moreno Solano</t>
+  </si>
+  <si>
+    <t>162%</t>
+  </si>
+  <si>
+    <t>74%</t>
+  </si>
+  <si>
+    <t>1504%</t>
+  </si>
+  <si>
+    <t>242%</t>
+  </si>
+  <si>
+    <t>Dayanis  Celsa Gamarra</t>
+  </si>
+  <si>
+    <t>126%</t>
+  </si>
+  <si>
+    <t>94%</t>
+  </si>
+  <si>
+    <t>152%</t>
+  </si>
+  <si>
+    <t>Darly Esther Sola Tarriba</t>
+  </si>
+  <si>
+    <t>80%</t>
+  </si>
+  <si>
+    <t>Lider  Bagre</t>
+  </si>
+  <si>
+    <t>11%</t>
   </si>
   <si>
     <t>5%</t>
   </si>
   <si>
-    <t>Cristian Camilo Torres Toro</t>
-  </si>
-  <si>
-    <t>ASESOR</t>
-  </si>
-  <si>
-    <t>Vacaciones del 02 al 18</t>
-  </si>
-  <si>
-    <t>12%</t>
-  </si>
-  <si>
-    <t>11%</t>
-  </si>
-  <si>
-    <t>84%</t>
-  </si>
-  <si>
-    <t>Diana Marcela Taborda Ruiz</t>
-  </si>
-  <si>
-    <t>222%</t>
-  </si>
-  <si>
-    <t>137%</t>
-  </si>
-  <si>
-    <t>100%</t>
+    <t>24%</t>
+  </si>
+  <si>
+    <t>DON MATIAS</t>
+  </si>
+  <si>
+    <t>Evelyn Daniela Lopera Lopera</t>
+  </si>
+  <si>
+    <t>42%</t>
+  </si>
+  <si>
+    <t>167%</t>
+  </si>
+  <si>
+    <t>81%</t>
+  </si>
+  <si>
+    <t>Lider Don Matias Diana Ruiz</t>
+  </si>
+  <si>
+    <t>187%</t>
+  </si>
+  <si>
+    <t>89%</t>
+  </si>
+  <si>
+    <t>1000%</t>
+  </si>
+  <si>
+    <t>142%</t>
+  </si>
+  <si>
+    <t>COPACABANA</t>
+  </si>
+  <si>
+    <t>Bibiana Farley Rios Agudelo</t>
+  </si>
+  <si>
+    <t>82%</t>
+  </si>
+  <si>
+    <t>60%</t>
+  </si>
+  <si>
+    <t>133%</t>
+  </si>
+  <si>
+    <t>96%</t>
+  </si>
+  <si>
+    <t>Alexandra Patricia Duque</t>
+  </si>
+  <si>
+    <t>113%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Milena Jaramillo HolguÃ­n</t>
+  </si>
+  <si>
+    <t>55%</t>
+  </si>
+  <si>
+    <t>360%</t>
+  </si>
+  <si>
+    <t>111%</t>
+  </si>
+  <si>
+    <t>CIUDAD BOLIVAR</t>
+  </si>
+  <si>
+    <t>Leidy Yaneth Galeano Ortiz</t>
+  </si>
+  <si>
+    <t>98%</t>
+  </si>
+  <si>
+    <t>500%</t>
+  </si>
+  <si>
+    <t>Lider Natalie Bolivar Restrepo</t>
+  </si>
+  <si>
+    <t>CAUCASIA</t>
+  </si>
+  <si>
+    <t>Tatiana  Guerra Gonzalez</t>
+  </si>
+  <si>
+    <t>69%</t>
   </si>
   <si>
     <t>50%</t>
   </si>
   <si>
-    <t>73%</t>
-  </si>
-  <si>
-    <t>Sandra Milena Carmona Galeano</t>
-  </si>
-  <si>
-    <t>151%</t>
-  </si>
-  <si>
-    <t>152%</t>
-  </si>
-  <si>
-    <t>89%</t>
-  </si>
-  <si>
-    <t>3%</t>
-  </si>
-  <si>
-    <t>Lider  Bagre</t>
-  </si>
-  <si>
-    <t>EL BAGRE</t>
-  </si>
-  <si>
-    <t>Reemplaza vacaciones cajera del 01 al 18</t>
-  </si>
-  <si>
-    <t>113%</t>
-  </si>
-  <si>
-    <t>Darly Esther Sola Tarriba</t>
-  </si>
-  <si>
-    <t>127%</t>
-  </si>
-  <si>
-    <t>47%</t>
+    <t>CALDAS</t>
+  </si>
+  <si>
+    <t>Maria Camila Arango VÃ©lez</t>
   </si>
   <si>
     <t>92%</t>
   </si>
   <si>
-    <t>72%</t>
-  </si>
-  <si>
-    <t>Dayanis  Celsa Gamarra</t>
-  </si>
-  <si>
-    <t>63%</t>
-  </si>
-  <si>
-    <t>115%</t>
-  </si>
-  <si>
-    <t>87%</t>
-  </si>
-  <si>
-    <t>Jeider Alberto Moreno Solano</t>
-  </si>
-  <si>
-    <t>155%</t>
-  </si>
-  <si>
-    <t>69%</t>
-  </si>
-  <si>
-    <t>29%</t>
-  </si>
-  <si>
-    <t>Lider Dabeiba Edwin Dario David Velasquez</t>
-  </si>
-  <si>
-    <t>DABEIBA</t>
-  </si>
-  <si>
-    <t>Vac del 16 al 04 de marzo</t>
-  </si>
-  <si>
-    <t>71%</t>
-  </si>
-  <si>
-    <t>39%</t>
-  </si>
-  <si>
-    <t>Estelli Alejandra Ramirez Florez</t>
-  </si>
-  <si>
-    <t>18%</t>
-  </si>
-  <si>
-    <t>43%</t>
-  </si>
-  <si>
-    <t>56%</t>
+    <t>70%</t>
+  </si>
+  <si>
+    <t>453%</t>
+  </si>
+  <si>
+    <t>138%</t>
+  </si>
+  <si>
+    <t>Johnson AndrÃ©s Gutierrez Escobar</t>
+  </si>
+  <si>
+    <t>109%</t>
+  </si>
+  <si>
+    <t>120%</t>
+  </si>
+  <si>
+    <t>Lider Yolima Mesa Zapata</t>
+  </si>
+  <si>
+    <t>122%</t>
+  </si>
+  <si>
+    <t>BELLO</t>
+  </si>
+  <si>
+    <t>Nasly Johanna Martinez Ocampo</t>
+  </si>
+  <si>
+    <t>76%</t>
+  </si>
+  <si>
+    <t>347%</t>
+  </si>
+  <si>
+    <t>Jessica Catherine Gutierrez Garcia</t>
+  </si>
+  <si>
+    <t>62%</t>
+  </si>
+  <si>
+    <t>213%</t>
+  </si>
+  <si>
+    <t>LÃ­der Sandra Arbelaez</t>
+  </si>
+  <si>
+    <t>99%</t>
+  </si>
+  <si>
+    <t>480%</t>
+  </si>
+  <si>
+    <t>31%</t>
+  </si>
+  <si>
+    <t>BARBOSA</t>
+  </si>
+  <si>
+    <t>Sene Del Socorro Suarez Torres</t>
+  </si>
+  <si>
+    <t>44%</t>
+  </si>
+  <si>
+    <t>36%</t>
+  </si>
+  <si>
+    <t>Lider Copacabana Vanessa Carolina Castillo Duran</t>
+  </si>
+  <si>
+    <t>66%</t>
+  </si>
+  <si>
+    <t>75%</t>
+  </si>
+  <si>
+    <t>208%</t>
   </si>
 </sst>
 </file>
@@ -612,11 +962,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K70"/>
+  <dimension ref="A1:K186"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="5" max="5" width="39.85546875" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="37.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="50" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -650,28 +1002,31 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2">
-        <v>33</v>
+        <v>15</v>
       </c>
       <c r="C2">
-        <v>29</v>
+        <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
       <c r="F2" t="s">
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
@@ -680,7 +1035,7 @@
         <v>17</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.25">
@@ -688,22 +1043,22 @@
         <v>18</v>
       </c>
       <c r="B3">
-        <v>38</v>
+        <v>2</v>
       </c>
       <c r="C3">
-        <v>119</v>
+        <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>192</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
@@ -712,7 +1067,7 @@
         <v>17</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.25">
@@ -720,22 +1075,22 @@
         <v>20</v>
       </c>
       <c r="B4">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="C4">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -744,7 +1099,7 @@
         <v>17</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.25">
@@ -752,22 +1107,22 @@
         <v>22</v>
       </c>
       <c r="B5">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="C5">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>190</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
@@ -776,7 +1131,7 @@
         <v>17</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.25">
@@ -784,22 +1139,22 @@
         <v>24</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>600</v>
       </c>
       <c r="C6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>13</v>
+        <v>189</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -808,30 +1163,30 @@
         <v>17</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>188</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>186</v>
       </c>
       <c r="F7" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
@@ -840,30 +1195,30 @@
         <v>17</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B8">
-        <v>44</v>
+        <v>4</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>28</v>
+        <v>153</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
+        <v>186</v>
       </c>
       <c r="F8" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -871,34 +1226,31 @@
       <c r="I8" t="s">
         <v>17</v>
       </c>
-      <c r="J8" t="s">
-        <v>31</v>
-      </c>
       <c r="K8">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B9">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>32</v>
+        <v>187</v>
       </c>
       <c r="E9" t="s">
-        <v>29</v>
+        <v>186</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G9" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
@@ -907,30 +1259,30 @@
         <v>17</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="C10">
-        <v>3</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>29</v>
+        <v>186</v>
       </c>
       <c r="F10" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -939,30 +1291,30 @@
         <v>17</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B11">
+        <v>900</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" t="s">
         <v>19</v>
       </c>
-      <c r="C11">
-        <v>2</v>
-      </c>
-      <c r="D11" t="s">
-        <v>33</v>
-      </c>
       <c r="E11" t="s">
-        <v>29</v>
+        <v>186</v>
       </c>
       <c r="F11" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G11" t="s">
-        <v>15</v>
+        <v>185</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -971,30 +1323,30 @@
         <v>17</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>81</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B12">
+        <v>13</v>
+      </c>
+      <c r="C12">
         <v>4</v>
       </c>
-      <c r="C12">
-        <v>0</v>
-      </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>184</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>181</v>
       </c>
       <c r="F12" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -1003,30 +1355,30 @@
         <v>17</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B13">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>183</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>181</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -1035,30 +1387,30 @@
         <v>17</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B14">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C14">
-        <v>37</v>
+        <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>34</v>
+        <v>95</v>
       </c>
       <c r="E14" t="s">
-        <v>35</v>
+        <v>181</v>
       </c>
       <c r="F14" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -1067,30 +1419,30 @@
         <v>17</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B15">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C15">
-        <v>113</v>
+        <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>36</v>
+        <v>182</v>
       </c>
       <c r="E15" t="s">
-        <v>35</v>
+        <v>181</v>
       </c>
       <c r="F15" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -1099,30 +1451,30 @@
         <v>17</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B16">
-        <v>27</v>
+        <v>375</v>
       </c>
       <c r="C16">
-        <v>37</v>
+        <v>0</v>
       </c>
       <c r="D16" t="s">
-        <v>37</v>
+        <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>35</v>
+        <v>181</v>
       </c>
       <c r="F16" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
@@ -1131,30 +1483,30 @@
         <v>17</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B17">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>165</v>
       </c>
       <c r="E17" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G17" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
@@ -1163,30 +1515,30 @@
         <v>17</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B18">
         <v>4</v>
       </c>
       <c r="C18">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>39</v>
+        <v>180</v>
       </c>
       <c r="E18" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="F18" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G18" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
@@ -1195,30 +1547,30 @@
         <v>17</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B19">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="C19">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>27</v>
+        <v>179</v>
       </c>
       <c r="E19" t="s">
-        <v>35</v>
+        <v>178</v>
       </c>
       <c r="F19" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
@@ -1227,30 +1579,30 @@
         <v>17</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B20">
+        <v>48</v>
+      </c>
+      <c r="C20">
         <v>44</v>
       </c>
-      <c r="C20">
-        <v>32</v>
-      </c>
       <c r="D20" t="s">
-        <v>40</v>
+        <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>41</v>
+        <v>178</v>
       </c>
       <c r="F20" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G20" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -1259,30 +1611,30 @@
         <v>17</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B21">
-        <v>51</v>
+        <v>562</v>
       </c>
       <c r="C21">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="D21" t="s">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>41</v>
+        <v>178</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G21" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
@@ -1291,30 +1643,30 @@
         <v>17</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
         <v>20</v>
       </c>
-      <c r="B22">
-        <v>27</v>
-      </c>
       <c r="C22">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>43</v>
+        <v>91</v>
       </c>
       <c r="E22" t="s">
-        <v>41</v>
+        <v>175</v>
       </c>
       <c r="F22" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G22" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
@@ -1323,30 +1675,30 @@
         <v>17</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B23">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="C23">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>44</v>
+        <v>177</v>
       </c>
       <c r="E23" t="s">
-        <v>41</v>
+        <v>175</v>
       </c>
       <c r="F23" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G23" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
@@ -1355,30 +1707,30 @@
         <v>17</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B24">
-        <v>4</v>
+        <v>50</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>27</v>
+        <v>176</v>
       </c>
       <c r="E24" t="s">
-        <v>41</v>
+        <v>175</v>
       </c>
       <c r="F24" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G24" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
@@ -1387,30 +1739,30 @@
         <v>17</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B25">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>27</v>
+        <v>113</v>
       </c>
       <c r="E25" t="s">
-        <v>41</v>
+        <v>175</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G25" t="s">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -1419,30 +1771,30 @@
         <v>17</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B26">
-        <v>35</v>
+        <v>562</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="s">
-        <v>45</v>
+        <v>19</v>
       </c>
       <c r="E26" t="s">
-        <v>46</v>
+        <v>175</v>
       </c>
       <c r="F26" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G26" t="s">
-        <v>47</v>
+        <v>174</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -1450,34 +1802,31 @@
       <c r="I26" t="s">
         <v>17</v>
       </c>
-      <c r="J26" t="s">
-        <v>48</v>
-      </c>
       <c r="K26">
-        <v>100</v>
+        <v>76</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B27">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="C27">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="D27" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="E27" t="s">
-        <v>46</v>
+        <v>172</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -1486,30 +1835,30 @@
         <v>17</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B28">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="C28">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" t="s">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>46</v>
+        <v>172</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -1518,30 +1867,30 @@
         <v>17</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B29">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>27</v>
+        <v>139</v>
       </c>
       <c r="E29" t="s">
-        <v>46</v>
+        <v>172</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -1550,30 +1899,30 @@
         <v>17</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B30">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C30">
-        <v>0</v>
+        <v>56</v>
       </c>
       <c r="D30" t="s">
-        <v>27</v>
+        <v>173</v>
       </c>
       <c r="E30" t="s">
-        <v>46</v>
+        <v>172</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -1582,30 +1931,30 @@
         <v>17</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B31">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="C31">
         <v>0</v>
       </c>
       <c r="D31" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>46</v>
+        <v>172</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -1614,30 +1963,30 @@
         <v>17</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B32">
-        <v>47</v>
+        <v>23</v>
       </c>
       <c r="C32">
-        <v>53</v>
+        <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>49</v>
+        <v>171</v>
       </c>
       <c r="E32" t="s">
-        <v>50</v>
+        <v>169</v>
       </c>
       <c r="F32" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -1646,30 +1995,30 @@
         <v>17</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B33">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="C33">
-        <v>14</v>
+        <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>127</v>
       </c>
       <c r="E33" t="s">
-        <v>50</v>
+        <v>169</v>
       </c>
       <c r="F33" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G33" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -1678,30 +2027,30 @@
         <v>17</v>
       </c>
       <c r="K33">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="B34">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="C34">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="D34" t="s">
         <v>52</v>
       </c>
       <c r="E34" t="s">
-        <v>50</v>
+        <v>169</v>
       </c>
       <c r="F34" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G34" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -1710,7 +2059,7 @@
         <v>17</v>
       </c>
       <c r="K34">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.25">
@@ -1718,22 +2067,22 @@
         <v>22</v>
       </c>
       <c r="B35">
-        <v>13</v>
+        <v>69</v>
       </c>
       <c r="C35">
-        <v>12</v>
+        <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>53</v>
+        <v>170</v>
       </c>
       <c r="E35" t="s">
-        <v>50</v>
+        <v>169</v>
       </c>
       <c r="F35" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G35" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -1742,7 +2091,7 @@
         <v>17</v>
       </c>
       <c r="K35">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.25">
@@ -1750,22 +2099,22 @@
         <v>24</v>
       </c>
       <c r="B36">
-        <v>0</v>
+        <v>562</v>
       </c>
       <c r="C36">
         <v>0</v>
       </c>
       <c r="D36" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E36" t="s">
-        <v>50</v>
+        <v>169</v>
       </c>
       <c r="F36" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G36" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -1774,30 +2123,30 @@
         <v>17</v>
       </c>
       <c r="K36">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="B37">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="C37">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>27</v>
+        <v>168</v>
       </c>
       <c r="E37" t="s">
-        <v>50</v>
+        <v>164</v>
       </c>
       <c r="F37" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G37" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -1806,7 +2155,7 @@
         <v>17</v>
       </c>
       <c r="K37">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.25">
@@ -1814,22 +2163,22 @@
         <v>18</v>
       </c>
       <c r="B38">
-        <v>47</v>
+        <v>4</v>
       </c>
       <c r="C38">
-        <v>34</v>
+        <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="E38" t="s">
-        <v>55</v>
+        <v>164</v>
       </c>
       <c r="F38" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G38" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -1838,7 +2187,7 @@
         <v>17</v>
       </c>
       <c r="K38">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.25">
@@ -1846,22 +2195,22 @@
         <v>20</v>
       </c>
       <c r="B39">
-        <v>11</v>
+        <v>60</v>
       </c>
       <c r="C39">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="D39" t="s">
-        <v>51</v>
+        <v>166</v>
       </c>
       <c r="E39" t="s">
-        <v>55</v>
+        <v>164</v>
       </c>
       <c r="F39" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G39" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
@@ -1870,30 +2219,30 @@
         <v>17</v>
       </c>
       <c r="K39">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="B40">
-        <v>30</v>
+        <v>69</v>
       </c>
       <c r="C40">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="D40" t="s">
-        <v>56</v>
+        <v>165</v>
       </c>
       <c r="E40" t="s">
-        <v>55</v>
+        <v>164</v>
       </c>
       <c r="F40" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G40" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -1902,30 +2251,30 @@
         <v>17</v>
       </c>
       <c r="K40">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B41">
-        <v>13</v>
+        <v>562</v>
       </c>
       <c r="C41">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D41" t="s">
-        <v>57</v>
+        <v>19</v>
       </c>
       <c r="E41" t="s">
-        <v>55</v>
+        <v>164</v>
       </c>
       <c r="F41" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G41" t="s">
-        <v>47</v>
+        <v>163</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
@@ -1934,30 +2283,30 @@
         <v>17</v>
       </c>
       <c r="K41">
-        <v>100</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B42">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="C42">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>27</v>
+        <v>162</v>
       </c>
       <c r="E42" t="s">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="F42" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
@@ -1966,12 +2315,12 @@
         <v>17</v>
       </c>
       <c r="K42">
-        <v>100</v>
+        <v>52</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="B43">
         <v>0</v>
@@ -1980,16 +2329,16 @@
         <v>0</v>
       </c>
       <c r="D43" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>55</v>
+        <v>160</v>
       </c>
       <c r="F43" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
@@ -1998,30 +2347,30 @@
         <v>17</v>
       </c>
       <c r="K43">
-        <v>100</v>
+        <v>52</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B44">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="C44">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>58</v>
+        <v>37</v>
       </c>
       <c r="E44" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="F44" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
@@ -2030,30 +2379,30 @@
         <v>17</v>
       </c>
       <c r="K44">
-        <v>100</v>
+        <v>52</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B45">
-        <v>11</v>
+        <v>32</v>
       </c>
       <c r="C45">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>60</v>
+        <v>161</v>
       </c>
       <c r="E45" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="F45" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
@@ -2062,30 +2411,30 @@
         <v>17</v>
       </c>
       <c r="K45">
-        <v>100</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="B46">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="C46">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="D46" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="E46" t="s">
-        <v>59</v>
+        <v>160</v>
       </c>
       <c r="F46" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>47</v>
+        <v>159</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
@@ -2094,62 +2443,62 @@
         <v>17</v>
       </c>
       <c r="K46">
-        <v>100</v>
+        <v>52</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B47">
         <v>13</v>
       </c>
       <c r="C47">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="D47" t="s">
+        <v>52</v>
+      </c>
+      <c r="E47" t="s">
+        <v>158</v>
+      </c>
+      <c r="F47" t="s">
+        <v>14</v>
+      </c>
+      <c r="G47" t="s">
+        <v>154</v>
+      </c>
+      <c r="H47" t="s">
+        <v>16</v>
+      </c>
+      <c r="I47" t="s">
+        <v>17</v>
+      </c>
+      <c r="K47">
         <v>61</v>
-      </c>
-      <c r="E47" t="s">
-        <v>59</v>
-      </c>
-      <c r="F47" t="s">
-        <v>30</v>
-      </c>
-      <c r="G47" t="s">
-        <v>47</v>
-      </c>
-      <c r="H47" t="s">
-        <v>16</v>
-      </c>
-      <c r="I47" t="s">
-        <v>17</v>
-      </c>
-      <c r="K47">
-        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="B48">
         <v>0</v>
       </c>
       <c r="C48">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>27</v>
+        <v>140</v>
       </c>
       <c r="E48" t="s">
-        <v>59</v>
+        <v>158</v>
       </c>
       <c r="F48" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>47</v>
+        <v>154</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
@@ -2158,30 +2507,30 @@
         <v>17</v>
       </c>
       <c r="K48">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="B49">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="C49">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>27</v>
+        <v>44</v>
       </c>
       <c r="E49" t="s">
-        <v>59</v>
+        <v>158</v>
       </c>
       <c r="F49" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>47</v>
+        <v>154</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
@@ -2190,30 +2539,30 @@
         <v>17</v>
       </c>
       <c r="K49">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="B50">
-        <v>28</v>
+        <v>54</v>
       </c>
       <c r="C50">
-        <v>8</v>
+        <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>62</v>
+        <v>136</v>
       </c>
       <c r="E50" t="s">
-        <v>63</v>
+        <v>158</v>
       </c>
       <c r="F50" t="s">
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="H50" t="s">
         <v>16</v>
@@ -2221,34 +2570,31 @@
       <c r="I50" t="s">
         <v>17</v>
       </c>
-      <c r="J50" t="s">
-        <v>65</v>
-      </c>
       <c r="K50">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="B51">
-        <v>7</v>
+        <v>320</v>
       </c>
       <c r="C51">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D51" t="s">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E51" t="s">
-        <v>63</v>
+        <v>158</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="H51" t="s">
         <v>16</v>
@@ -2257,7 +2603,7 @@
         <v>17</v>
       </c>
       <c r="K51">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.25">
@@ -2265,22 +2611,22 @@
         <v>11</v>
       </c>
       <c r="B52">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="C52">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>66</v>
+        <v>31</v>
       </c>
       <c r="E52" t="s">
-        <v>63</v>
+        <v>155</v>
       </c>
       <c r="F52" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G52" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="H52" t="s">
         <v>16</v>
@@ -2289,30 +2635,30 @@
         <v>17</v>
       </c>
       <c r="K52">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B53">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="C53">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>25</v>
+        <v>157</v>
       </c>
       <c r="E53" t="s">
-        <v>63</v>
+        <v>155</v>
       </c>
       <c r="F53" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G53" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="H53" t="s">
         <v>16</v>
@@ -2321,30 +2667,30 @@
         <v>17</v>
       </c>
       <c r="K53">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B54">
-        <v>0</v>
+        <v>51</v>
       </c>
       <c r="C54">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="D54" t="s">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="E54" t="s">
-        <v>63</v>
+        <v>155</v>
       </c>
       <c r="F54" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G54" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
@@ -2353,30 +2699,30 @@
         <v>17</v>
       </c>
       <c r="K54">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B55">
-        <v>0</v>
+        <v>81</v>
       </c>
       <c r="C55">
-        <v>0</v>
+        <v>79</v>
       </c>
       <c r="D55" t="s">
-        <v>27</v>
+        <v>156</v>
       </c>
       <c r="E55" t="s">
-        <v>63</v>
+        <v>155</v>
       </c>
       <c r="F55" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G55" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="H55" t="s">
         <v>16</v>
@@ -2385,30 +2731,30 @@
         <v>17</v>
       </c>
       <c r="K55">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="B56">
-        <v>41</v>
+        <v>480</v>
       </c>
       <c r="C56">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D56" t="s">
-        <v>67</v>
+        <v>19</v>
       </c>
       <c r="E56" t="s">
-        <v>68</v>
+        <v>155</v>
       </c>
       <c r="F56" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>64</v>
+        <v>154</v>
       </c>
       <c r="H56" t="s">
         <v>16</v>
@@ -2417,30 +2763,30 @@
         <v>17</v>
       </c>
       <c r="K56">
-        <v>100</v>
+        <v>61</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="B57">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C57">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>69</v>
+        <v>153</v>
       </c>
       <c r="E57" t="s">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="F57" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>64</v>
+        <v>142</v>
       </c>
       <c r="H57" t="s">
         <v>16</v>
@@ -2449,30 +2795,30 @@
         <v>17</v>
       </c>
       <c r="K57">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="B58">
-        <v>21</v>
+        <v>2</v>
       </c>
       <c r="C58">
         <v>9</v>
       </c>
       <c r="D58" t="s">
-        <v>70</v>
+        <v>152</v>
       </c>
       <c r="E58" t="s">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="F58" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>64</v>
+        <v>142</v>
       </c>
       <c r="H58" t="s">
         <v>16</v>
@@ -2481,30 +2827,30 @@
         <v>17</v>
       </c>
       <c r="K58">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B59">
-        <v>9</v>
+        <v>31</v>
       </c>
       <c r="C59">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>71</v>
+        <v>151</v>
       </c>
       <c r="E59" t="s">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="F59" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>64</v>
+        <v>142</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -2513,30 +2859,30 @@
         <v>17</v>
       </c>
       <c r="K59">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B60">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="C60">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="D60" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
       <c r="E60" t="s">
-        <v>68</v>
+        <v>150</v>
       </c>
       <c r="F60" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="G60" t="s">
-        <v>64</v>
+        <v>142</v>
       </c>
       <c r="H60" t="s">
         <v>16</v>
@@ -2545,44 +2891,4105 @@
         <v>17</v>
       </c>
       <c r="K60">
-        <v>100</v>
+        <v>65</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B61">
-        <v>0</v>
+        <v>375</v>
       </c>
       <c r="C61">
         <v>0</v>
       </c>
       <c r="D61" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="E61" t="s">
+        <v>150</v>
+      </c>
+      <c r="F61" t="s">
+        <v>14</v>
+      </c>
+      <c r="G61" t="s">
+        <v>142</v>
+      </c>
+      <c r="H61" t="s">
+        <v>16</v>
+      </c>
+      <c r="I61" t="s">
+        <v>17</v>
+      </c>
+      <c r="K61">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>11</v>
+      </c>
+      <c r="B62">
+        <v>18</v>
+      </c>
+      <c r="C62">
+        <v>18</v>
+      </c>
+      <c r="D62" t="s">
+        <v>104</v>
+      </c>
+      <c r="E62" t="s">
+        <v>148</v>
+      </c>
+      <c r="F62" t="s">
+        <v>27</v>
+      </c>
+      <c r="G62" t="s">
+        <v>142</v>
+      </c>
+      <c r="H62" t="s">
+        <v>16</v>
+      </c>
+      <c r="I62" t="s">
+        <v>17</v>
+      </c>
+      <c r="K62">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>18</v>
+      </c>
+      <c r="B63">
+        <v>4</v>
+      </c>
+      <c r="C63">
+        <v>5</v>
+      </c>
+      <c r="D63" t="s">
+        <v>146</v>
+      </c>
+      <c r="E63" t="s">
+        <v>148</v>
+      </c>
+      <c r="F63" t="s">
+        <v>27</v>
+      </c>
+      <c r="G63" t="s">
+        <v>142</v>
+      </c>
+      <c r="H63" t="s">
+        <v>16</v>
+      </c>
+      <c r="I63" t="s">
+        <v>17</v>
+      </c>
+      <c r="K63">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>20</v>
+      </c>
+      <c r="B64">
+        <v>46</v>
+      </c>
+      <c r="C64">
+        <v>37</v>
+      </c>
+      <c r="D64" t="s">
+        <v>127</v>
+      </c>
+      <c r="E64" t="s">
+        <v>148</v>
+      </c>
+      <c r="F64" t="s">
+        <v>27</v>
+      </c>
+      <c r="G64" t="s">
+        <v>142</v>
+      </c>
+      <c r="H64" t="s">
+        <v>16</v>
+      </c>
+      <c r="I64" t="s">
+        <v>17</v>
+      </c>
+      <c r="K64">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>22</v>
+      </c>
+      <c r="B65">
+        <v>55</v>
+      </c>
+      <c r="C65">
+        <v>62</v>
+      </c>
+      <c r="D65" t="s">
+        <v>149</v>
+      </c>
+      <c r="E65" t="s">
+        <v>148</v>
+      </c>
+      <c r="F65" t="s">
+        <v>27</v>
+      </c>
+      <c r="G65" t="s">
+        <v>142</v>
+      </c>
+      <c r="H65" t="s">
+        <v>16</v>
+      </c>
+      <c r="I65" t="s">
+        <v>17</v>
+      </c>
+      <c r="K65">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>24</v>
+      </c>
+      <c r="B66">
+        <v>562</v>
+      </c>
+      <c r="C66">
+        <v>0</v>
+      </c>
+      <c r="D66" t="s">
+        <v>19</v>
+      </c>
+      <c r="E66" t="s">
+        <v>148</v>
+      </c>
+      <c r="F66" t="s">
+        <v>27</v>
+      </c>
+      <c r="G66" t="s">
+        <v>142</v>
+      </c>
+      <c r="H66" t="s">
+        <v>16</v>
+      </c>
+      <c r="I66" t="s">
+        <v>17</v>
+      </c>
+      <c r="K66">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>11</v>
+      </c>
+      <c r="B67">
+        <v>18</v>
+      </c>
+      <c r="C67">
+        <v>17</v>
+      </c>
+      <c r="D67" t="s">
+        <v>147</v>
+      </c>
+      <c r="E67" t="s">
+        <v>143</v>
+      </c>
+      <c r="F67" t="s">
+        <v>27</v>
+      </c>
+      <c r="G67" t="s">
+        <v>142</v>
+      </c>
+      <c r="H67" t="s">
+        <v>16</v>
+      </c>
+      <c r="I67" t="s">
+        <v>17</v>
+      </c>
+      <c r="K67">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>18</v>
+      </c>
+      <c r="B68">
+        <v>4</v>
+      </c>
+      <c r="C68">
+        <v>5</v>
+      </c>
+      <c r="D68" t="s">
+        <v>146</v>
+      </c>
+      <c r="E68" t="s">
+        <v>143</v>
+      </c>
+      <c r="F68" t="s">
+        <v>27</v>
+      </c>
+      <c r="G68" t="s">
+        <v>142</v>
+      </c>
+      <c r="H68" t="s">
+        <v>16</v>
+      </c>
+      <c r="I68" t="s">
+        <v>17</v>
+      </c>
+      <c r="K68">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>20</v>
+      </c>
+      <c r="B69">
+        <v>46</v>
+      </c>
+      <c r="C69">
+        <v>28</v>
+      </c>
+      <c r="D69" t="s">
+        <v>145</v>
+      </c>
+      <c r="E69" t="s">
+        <v>143</v>
+      </c>
+      <c r="F69" t="s">
+        <v>27</v>
+      </c>
+      <c r="G69" t="s">
+        <v>142</v>
+      </c>
+      <c r="H69" t="s">
+        <v>16</v>
+      </c>
+      <c r="I69" t="s">
+        <v>17</v>
+      </c>
+      <c r="K69">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>22</v>
+      </c>
+      <c r="B70">
+        <v>55</v>
+      </c>
+      <c r="C70">
+        <v>45</v>
+      </c>
+      <c r="D70" t="s">
+        <v>144</v>
+      </c>
+      <c r="E70" t="s">
+        <v>143</v>
+      </c>
+      <c r="F70" t="s">
+        <v>27</v>
+      </c>
+      <c r="G70" t="s">
+        <v>142</v>
+      </c>
+      <c r="H70" t="s">
+        <v>16</v>
+      </c>
+      <c r="I70" t="s">
+        <v>17</v>
+      </c>
+      <c r="K70">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>24</v>
+      </c>
+      <c r="B71">
+        <v>562</v>
+      </c>
+      <c r="C71">
+        <v>0</v>
+      </c>
+      <c r="D71" t="s">
+        <v>19</v>
+      </c>
+      <c r="E71" t="s">
+        <v>143</v>
+      </c>
+      <c r="F71" t="s">
+        <v>27</v>
+      </c>
+      <c r="G71" t="s">
+        <v>142</v>
+      </c>
+      <c r="H71" t="s">
+        <v>16</v>
+      </c>
+      <c r="I71" t="s">
+        <v>17</v>
+      </c>
+      <c r="K71">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>11</v>
+      </c>
+      <c r="B72">
+        <v>7</v>
+      </c>
+      <c r="C72">
+        <v>4</v>
+      </c>
+      <c r="D72" t="s">
+        <v>33</v>
+      </c>
+      <c r="E72" t="s">
+        <v>34</v>
+      </c>
+      <c r="F72" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" t="s">
+        <v>35</v>
+      </c>
+      <c r="H72" t="s">
+        <v>16</v>
+      </c>
+      <c r="I72" t="s">
+        <v>17</v>
+      </c>
+      <c r="J72" t="s">
+        <v>36</v>
+      </c>
+      <c r="K72">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>18</v>
+      </c>
+      <c r="B73">
+        <v>0</v>
+      </c>
+      <c r="C73">
+        <v>0</v>
+      </c>
+      <c r="D73" t="s">
+        <v>19</v>
+      </c>
+      <c r="E73" t="s">
+        <v>34</v>
+      </c>
+      <c r="F73" t="s">
+        <v>14</v>
+      </c>
+      <c r="G73" t="s">
+        <v>35</v>
+      </c>
+      <c r="H73" t="s">
+        <v>16</v>
+      </c>
+      <c r="I73" t="s">
+        <v>17</v>
+      </c>
+      <c r="K73">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>20</v>
+      </c>
+      <c r="B74">
+        <v>26</v>
+      </c>
+      <c r="C74">
+        <v>12</v>
+      </c>
+      <c r="D74" t="s">
+        <v>37</v>
+      </c>
+      <c r="E74" t="s">
+        <v>34</v>
+      </c>
+      <c r="F74" t="s">
+        <v>14</v>
+      </c>
+      <c r="G74" t="s">
+        <v>35</v>
+      </c>
+      <c r="H74" t="s">
+        <v>16</v>
+      </c>
+      <c r="I74" t="s">
+        <v>17</v>
+      </c>
+      <c r="J74" t="s">
+        <v>38</v>
+      </c>
+      <c r="K74">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>22</v>
+      </c>
+      <c r="B75">
+        <v>28</v>
+      </c>
+      <c r="C75">
+        <v>8</v>
+      </c>
+      <c r="D75" t="s">
+        <v>39</v>
+      </c>
+      <c r="E75" t="s">
+        <v>34</v>
+      </c>
+      <c r="F75" t="s">
+        <v>14</v>
+      </c>
+      <c r="G75" t="s">
+        <v>35</v>
+      </c>
+      <c r="H75" t="s">
+        <v>16</v>
+      </c>
+      <c r="I75" t="s">
+        <v>17</v>
+      </c>
+      <c r="J75" t="s">
+        <v>40</v>
+      </c>
+      <c r="K75">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>24</v>
+      </c>
+      <c r="B76">
+        <v>480</v>
+      </c>
+      <c r="C76">
+        <v>0</v>
+      </c>
+      <c r="D76" t="s">
+        <v>19</v>
+      </c>
+      <c r="E76" t="s">
+        <v>34</v>
+      </c>
+      <c r="F76" t="s">
+        <v>14</v>
+      </c>
+      <c r="G76" t="s">
+        <v>35</v>
+      </c>
+      <c r="H76" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" t="s">
+        <v>17</v>
+      </c>
+      <c r="J76" t="s">
+        <v>41</v>
+      </c>
+      <c r="K76">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>11</v>
+      </c>
+      <c r="B77">
+        <v>11</v>
+      </c>
+      <c r="C77">
+        <v>9</v>
+      </c>
+      <c r="D77" t="s">
+        <v>42</v>
+      </c>
+      <c r="E77" t="s">
+        <v>43</v>
+      </c>
+      <c r="F77" t="s">
+        <v>27</v>
+      </c>
+      <c r="G77" t="s">
+        <v>35</v>
+      </c>
+      <c r="H77" t="s">
+        <v>16</v>
+      </c>
+      <c r="I77" t="s">
+        <v>17</v>
+      </c>
+      <c r="K77">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>18</v>
+      </c>
+      <c r="B78">
+        <v>0</v>
+      </c>
+      <c r="C78">
+        <v>0</v>
+      </c>
+      <c r="D78" t="s">
+        <v>19</v>
+      </c>
+      <c r="E78" t="s">
+        <v>43</v>
+      </c>
+      <c r="F78" t="s">
+        <v>27</v>
+      </c>
+      <c r="G78" t="s">
+        <v>35</v>
+      </c>
+      <c r="H78" t="s">
+        <v>16</v>
+      </c>
+      <c r="I78" t="s">
+        <v>17</v>
+      </c>
+      <c r="K78">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>20</v>
+      </c>
+      <c r="B79">
+        <v>39</v>
+      </c>
+      <c r="C79">
+        <v>31</v>
+      </c>
+      <c r="D79" t="s">
+        <v>44</v>
+      </c>
+      <c r="E79" t="s">
+        <v>43</v>
+      </c>
+      <c r="F79" t="s">
+        <v>27</v>
+      </c>
+      <c r="G79" t="s">
+        <v>35</v>
+      </c>
+      <c r="H79" t="s">
+        <v>16</v>
+      </c>
+      <c r="I79" t="s">
+        <v>17</v>
+      </c>
+      <c r="K79">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>22</v>
+      </c>
+      <c r="B80">
+        <v>41</v>
+      </c>
+      <c r="C80">
+        <v>27</v>
+      </c>
+      <c r="D80" t="s">
+        <v>45</v>
+      </c>
+      <c r="E80" t="s">
+        <v>43</v>
+      </c>
+      <c r="F80" t="s">
+        <v>27</v>
+      </c>
+      <c r="G80" t="s">
+        <v>35</v>
+      </c>
+      <c r="H80" t="s">
+        <v>16</v>
+      </c>
+      <c r="I80" t="s">
+        <v>17</v>
+      </c>
+      <c r="K80">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>24</v>
+      </c>
+      <c r="B81">
+        <v>720</v>
+      </c>
+      <c r="C81">
+        <v>0</v>
+      </c>
+      <c r="D81" t="s">
+        <v>19</v>
+      </c>
+      <c r="E81" t="s">
+        <v>43</v>
+      </c>
+      <c r="F81" t="s">
+        <v>27</v>
+      </c>
+      <c r="G81" t="s">
+        <v>35</v>
+      </c>
+      <c r="H81" t="s">
+        <v>16</v>
+      </c>
+      <c r="I81" t="s">
+        <v>17</v>
+      </c>
+      <c r="K81">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>11</v>
+      </c>
+      <c r="B82">
+        <v>15</v>
+      </c>
+      <c r="C82">
+        <v>21</v>
+      </c>
+      <c r="D82" t="s">
+        <v>141</v>
+      </c>
+      <c r="E82" t="s">
+        <v>137</v>
+      </c>
+      <c r="F82" t="s">
+        <v>14</v>
+      </c>
+      <c r="G82" t="s">
+        <v>132</v>
+      </c>
+      <c r="H82" t="s">
+        <v>16</v>
+      </c>
+      <c r="I82" t="s">
+        <v>17</v>
+      </c>
+      <c r="K82">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>18</v>
+      </c>
+      <c r="B83">
+        <v>0</v>
+      </c>
+      <c r="C83">
+        <v>4</v>
+      </c>
+      <c r="D83" t="s">
+        <v>140</v>
+      </c>
+      <c r="E83" t="s">
+        <v>137</v>
+      </c>
+      <c r="F83" t="s">
+        <v>14</v>
+      </c>
+      <c r="G83" t="s">
+        <v>132</v>
+      </c>
+      <c r="H83" t="s">
+        <v>16</v>
+      </c>
+      <c r="I83" t="s">
+        <v>17</v>
+      </c>
+      <c r="K83">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>20</v>
+      </c>
+      <c r="B84">
+        <v>24</v>
+      </c>
+      <c r="C84">
+        <v>21</v>
+      </c>
+      <c r="D84" t="s">
+        <v>139</v>
+      </c>
+      <c r="E84" t="s">
+        <v>137</v>
+      </c>
+      <c r="F84" t="s">
+        <v>14</v>
+      </c>
+      <c r="G84" t="s">
+        <v>132</v>
+      </c>
+      <c r="H84" t="s">
+        <v>16</v>
+      </c>
+      <c r="I84" t="s">
+        <v>17</v>
+      </c>
+      <c r="K84">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>22</v>
+      </c>
+      <c r="B85">
+        <v>27</v>
+      </c>
+      <c r="C85">
+        <v>51</v>
+      </c>
+      <c r="D85" t="s">
+        <v>138</v>
+      </c>
+      <c r="E85" t="s">
+        <v>137</v>
+      </c>
+      <c r="F85" t="s">
+        <v>14</v>
+      </c>
+      <c r="G85" t="s">
+        <v>132</v>
+      </c>
+      <c r="H85" t="s">
+        <v>16</v>
+      </c>
+      <c r="I85" t="s">
+        <v>17</v>
+      </c>
+      <c r="K85">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>24</v>
+      </c>
+      <c r="B86">
+        <v>480</v>
+      </c>
+      <c r="C86">
+        <v>0</v>
+      </c>
+      <c r="D86" t="s">
+        <v>19</v>
+      </c>
+      <c r="E86" t="s">
+        <v>137</v>
+      </c>
+      <c r="F86" t="s">
+        <v>14</v>
+      </c>
+      <c r="G86" t="s">
+        <v>132</v>
+      </c>
+      <c r="H86" t="s">
+        <v>16</v>
+      </c>
+      <c r="I86" t="s">
+        <v>17</v>
+      </c>
+      <c r="K86">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>11</v>
+      </c>
+      <c r="B87">
+        <v>22</v>
+      </c>
+      <c r="C87">
+        <v>18</v>
+      </c>
+      <c r="D87" t="s">
+        <v>136</v>
+      </c>
+      <c r="E87" t="s">
+        <v>133</v>
+      </c>
+      <c r="F87" t="s">
+        <v>27</v>
+      </c>
+      <c r="G87" t="s">
+        <v>132</v>
+      </c>
+      <c r="H87" t="s">
+        <v>16</v>
+      </c>
+      <c r="I87" t="s">
+        <v>17</v>
+      </c>
+      <c r="K87">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>18</v>
+      </c>
+      <c r="B88">
+        <v>1</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="D88" t="s">
+        <v>135</v>
+      </c>
+      <c r="E88" t="s">
+        <v>133</v>
+      </c>
+      <c r="F88" t="s">
+        <v>27</v>
+      </c>
+      <c r="G88" t="s">
+        <v>132</v>
+      </c>
+      <c r="H88" t="s">
+        <v>16</v>
+      </c>
+      <c r="I88" t="s">
+        <v>17</v>
+      </c>
+      <c r="K88">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>20</v>
+      </c>
+      <c r="B89">
+        <v>35</v>
+      </c>
+      <c r="C89">
+        <v>15</v>
+      </c>
+      <c r="D89" t="s">
+        <v>134</v>
+      </c>
+      <c r="E89" t="s">
+        <v>133</v>
+      </c>
+      <c r="F89" t="s">
+        <v>27</v>
+      </c>
+      <c r="G89" t="s">
+        <v>132</v>
+      </c>
+      <c r="H89" t="s">
+        <v>16</v>
+      </c>
+      <c r="I89" t="s">
+        <v>17</v>
+      </c>
+      <c r="K89">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>22</v>
+      </c>
+      <c r="B90">
+        <v>41</v>
+      </c>
+      <c r="C90">
+        <v>48</v>
+      </c>
+      <c r="D90" t="s">
+        <v>90</v>
+      </c>
+      <c r="E90" t="s">
+        <v>133</v>
+      </c>
+      <c r="F90" t="s">
+        <v>27</v>
+      </c>
+      <c r="G90" t="s">
+        <v>132</v>
+      </c>
+      <c r="H90" t="s">
+        <v>16</v>
+      </c>
+      <c r="I90" t="s">
+        <v>17</v>
+      </c>
+      <c r="K90">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>24</v>
+      </c>
+      <c r="B91">
+        <v>720</v>
+      </c>
+      <c r="C91">
+        <v>0</v>
+      </c>
+      <c r="D91" t="s">
+        <v>19</v>
+      </c>
+      <c r="E91" t="s">
+        <v>133</v>
+      </c>
+      <c r="F91" t="s">
+        <v>27</v>
+      </c>
+      <c r="G91" t="s">
+        <v>132</v>
+      </c>
+      <c r="H91" t="s">
+        <v>16</v>
+      </c>
+      <c r="I91" t="s">
+        <v>17</v>
+      </c>
+      <c r="K91">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>11</v>
+      </c>
+      <c r="B92">
+        <v>8</v>
+      </c>
+      <c r="C92">
+        <v>2</v>
+      </c>
+      <c r="D92" t="s">
+        <v>131</v>
+      </c>
+      <c r="E92" t="s">
+        <v>128</v>
+      </c>
+      <c r="F92" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92" t="s">
+        <v>116</v>
+      </c>
+      <c r="H92" t="s">
+        <v>16</v>
+      </c>
+      <c r="I92" t="s">
+        <v>17</v>
+      </c>
+      <c r="K92">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>18</v>
+      </c>
+      <c r="B93">
+        <v>0</v>
+      </c>
+      <c r="C93">
+        <v>0</v>
+      </c>
+      <c r="D93" t="s">
+        <v>19</v>
+      </c>
+      <c r="E93" t="s">
+        <v>128</v>
+      </c>
+      <c r="F93" t="s">
+        <v>14</v>
+      </c>
+      <c r="G93" t="s">
+        <v>116</v>
+      </c>
+      <c r="H93" t="s">
+        <v>16</v>
+      </c>
+      <c r="I93" t="s">
+        <v>17</v>
+      </c>
+      <c r="K93">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>20</v>
+      </c>
+      <c r="B94">
+        <v>42</v>
+      </c>
+      <c r="C94">
+        <v>2</v>
+      </c>
+      <c r="D94" t="s">
+        <v>130</v>
+      </c>
+      <c r="E94" t="s">
+        <v>128</v>
+      </c>
+      <c r="F94" t="s">
+        <v>14</v>
+      </c>
+      <c r="G94" t="s">
+        <v>116</v>
+      </c>
+      <c r="H94" t="s">
+        <v>16</v>
+      </c>
+      <c r="I94" t="s">
+        <v>17</v>
+      </c>
+      <c r="K94">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>22</v>
+      </c>
+      <c r="B95">
+        <v>35</v>
+      </c>
+      <c r="C95">
+        <v>4</v>
+      </c>
+      <c r="D95" t="s">
+        <v>129</v>
+      </c>
+      <c r="E95" t="s">
+        <v>128</v>
+      </c>
+      <c r="F95" t="s">
+        <v>14</v>
+      </c>
+      <c r="G95" t="s">
+        <v>116</v>
+      </c>
+      <c r="H95" t="s">
+        <v>16</v>
+      </c>
+      <c r="I95" t="s">
+        <v>17</v>
+      </c>
+      <c r="K95">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>24</v>
+      </c>
+      <c r="B96">
+        <v>300</v>
+      </c>
+      <c r="C96">
+        <v>0</v>
+      </c>
+      <c r="D96" t="s">
+        <v>19</v>
+      </c>
+      <c r="E96" t="s">
+        <v>128</v>
+      </c>
+      <c r="F96" t="s">
+        <v>14</v>
+      </c>
+      <c r="G96" t="s">
+        <v>116</v>
+      </c>
+      <c r="H96" t="s">
+        <v>16</v>
+      </c>
+      <c r="I96" t="s">
+        <v>17</v>
+      </c>
+      <c r="K96">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>11</v>
+      </c>
+      <c r="B97">
+        <v>11</v>
+      </c>
+      <c r="C97">
+        <v>16</v>
+      </c>
+      <c r="D97" t="s">
+        <v>59</v>
+      </c>
+      <c r="E97" t="s">
+        <v>126</v>
+      </c>
+      <c r="F97" t="s">
+        <v>27</v>
+      </c>
+      <c r="G97" t="s">
+        <v>116</v>
+      </c>
+      <c r="H97" t="s">
+        <v>16</v>
+      </c>
+      <c r="I97" t="s">
+        <v>17</v>
+      </c>
+      <c r="K97">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>18</v>
+      </c>
+      <c r="B98">
+        <v>0</v>
+      </c>
+      <c r="C98">
+        <v>0</v>
+      </c>
+      <c r="D98" t="s">
+        <v>19</v>
+      </c>
+      <c r="E98" t="s">
+        <v>126</v>
+      </c>
+      <c r="F98" t="s">
+        <v>27</v>
+      </c>
+      <c r="G98" t="s">
+        <v>116</v>
+      </c>
+      <c r="H98" t="s">
+        <v>16</v>
+      </c>
+      <c r="I98" t="s">
+        <v>17</v>
+      </c>
+      <c r="K98">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>20</v>
+      </c>
+      <c r="B99">
+        <v>55</v>
+      </c>
+      <c r="C99">
+        <v>44</v>
+      </c>
+      <c r="D99" t="s">
+        <v>127</v>
+      </c>
+      <c r="E99" t="s">
+        <v>126</v>
+      </c>
+      <c r="F99" t="s">
+        <v>27</v>
+      </c>
+      <c r="G99" t="s">
+        <v>116</v>
+      </c>
+      <c r="H99" t="s">
+        <v>16</v>
+      </c>
+      <c r="I99" t="s">
+        <v>17</v>
+      </c>
+      <c r="K99">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>22</v>
+      </c>
+      <c r="B100">
+        <v>47</v>
+      </c>
+      <c r="C100">
+        <v>71</v>
+      </c>
+      <c r="D100" t="s">
+        <v>125</v>
+      </c>
+      <c r="E100" t="s">
+        <v>126</v>
+      </c>
+      <c r="F100" t="s">
+        <v>27</v>
+      </c>
+      <c r="G100" t="s">
+        <v>116</v>
+      </c>
+      <c r="H100" t="s">
+        <v>16</v>
+      </c>
+      <c r="I100" t="s">
+        <v>17</v>
+      </c>
+      <c r="K100">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>24</v>
+      </c>
+      <c r="B101">
+        <v>399</v>
+      </c>
+      <c r="C101">
+        <v>0</v>
+      </c>
+      <c r="D101" t="s">
+        <v>19</v>
+      </c>
+      <c r="E101" t="s">
+        <v>126</v>
+      </c>
+      <c r="F101" t="s">
+        <v>27</v>
+      </c>
+      <c r="G101" t="s">
+        <v>116</v>
+      </c>
+      <c r="H101" t="s">
+        <v>16</v>
+      </c>
+      <c r="I101" t="s">
+        <v>17</v>
+      </c>
+      <c r="K101">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>11</v>
+      </c>
+      <c r="B102">
+        <v>11</v>
+      </c>
+      <c r="C102">
+        <v>17</v>
+      </c>
+      <c r="D102" t="s">
+        <v>125</v>
+      </c>
+      <c r="E102" t="s">
+        <v>122</v>
+      </c>
+      <c r="F102" t="s">
+        <v>27</v>
+      </c>
+      <c r="G102" t="s">
+        <v>116</v>
+      </c>
+      <c r="H102" t="s">
+        <v>16</v>
+      </c>
+      <c r="I102" t="s">
+        <v>17</v>
+      </c>
+      <c r="K102">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>18</v>
+      </c>
+      <c r="B103">
+        <v>0</v>
+      </c>
+      <c r="C103">
+        <v>0</v>
+      </c>
+      <c r="D103" t="s">
+        <v>19</v>
+      </c>
+      <c r="E103" t="s">
+        <v>122</v>
+      </c>
+      <c r="F103" t="s">
+        <v>27</v>
+      </c>
+      <c r="G103" t="s">
+        <v>116</v>
+      </c>
+      <c r="H103" t="s">
+        <v>16</v>
+      </c>
+      <c r="I103" t="s">
+        <v>17</v>
+      </c>
+      <c r="K103">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>20</v>
+      </c>
+      <c r="B104">
+        <v>55</v>
+      </c>
+      <c r="C104">
+        <v>52</v>
+      </c>
+      <c r="D104" t="s">
+        <v>124</v>
+      </c>
+      <c r="E104" t="s">
+        <v>122</v>
+      </c>
+      <c r="F104" t="s">
+        <v>27</v>
+      </c>
+      <c r="G104" t="s">
+        <v>116</v>
+      </c>
+      <c r="H104" t="s">
+        <v>16</v>
+      </c>
+      <c r="I104" t="s">
+        <v>17</v>
+      </c>
+      <c r="K104">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>22</v>
+      </c>
+      <c r="B105">
+        <v>47</v>
+      </c>
+      <c r="C105">
+        <v>59</v>
+      </c>
+      <c r="D105" t="s">
+        <v>123</v>
+      </c>
+      <c r="E105" t="s">
+        <v>122</v>
+      </c>
+      <c r="F105" t="s">
+        <v>27</v>
+      </c>
+      <c r="G105" t="s">
+        <v>116</v>
+      </c>
+      <c r="H105" t="s">
+        <v>16</v>
+      </c>
+      <c r="I105" t="s">
+        <v>17</v>
+      </c>
+      <c r="K105">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>24</v>
+      </c>
+      <c r="B106">
+        <v>399</v>
+      </c>
+      <c r="C106">
+        <v>0</v>
+      </c>
+      <c r="D106" t="s">
+        <v>19</v>
+      </c>
+      <c r="E106" t="s">
+        <v>122</v>
+      </c>
+      <c r="F106" t="s">
+        <v>27</v>
+      </c>
+      <c r="G106" t="s">
+        <v>116</v>
+      </c>
+      <c r="H106" t="s">
+        <v>16</v>
+      </c>
+      <c r="I106" t="s">
+        <v>17</v>
+      </c>
+      <c r="K106">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>11</v>
+      </c>
+      <c r="B107">
+        <v>11</v>
+      </c>
+      <c r="C107">
+        <v>27</v>
+      </c>
+      <c r="D107" t="s">
+        <v>121</v>
+      </c>
+      <c r="E107" t="s">
+        <v>117</v>
+      </c>
+      <c r="F107" t="s">
+        <v>27</v>
+      </c>
+      <c r="G107" t="s">
+        <v>116</v>
+      </c>
+      <c r="H107" t="s">
+        <v>16</v>
+      </c>
+      <c r="I107" t="s">
+        <v>17</v>
+      </c>
+      <c r="K107">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>18</v>
+      </c>
+      <c r="B108">
+        <v>0</v>
+      </c>
+      <c r="C108">
+        <v>4</v>
+      </c>
+      <c r="D108" t="s">
+        <v>120</v>
+      </c>
+      <c r="E108" t="s">
+        <v>117</v>
+      </c>
+      <c r="F108" t="s">
+        <v>27</v>
+      </c>
+      <c r="G108" t="s">
+        <v>116</v>
+      </c>
+      <c r="H108" t="s">
+        <v>16</v>
+      </c>
+      <c r="I108" t="s">
+        <v>17</v>
+      </c>
+      <c r="K108">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>20</v>
+      </c>
+      <c r="B109">
+        <v>55</v>
+      </c>
+      <c r="C109">
+        <v>41</v>
+      </c>
+      <c r="D109" t="s">
+        <v>119</v>
+      </c>
+      <c r="E109" t="s">
+        <v>117</v>
+      </c>
+      <c r="F109" t="s">
+        <v>27</v>
+      </c>
+      <c r="G109" t="s">
+        <v>116</v>
+      </c>
+      <c r="H109" t="s">
+        <v>16</v>
+      </c>
+      <c r="I109" t="s">
+        <v>17</v>
+      </c>
+      <c r="K109">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>22</v>
+      </c>
+      <c r="B110">
+        <v>47</v>
+      </c>
+      <c r="C110">
+        <v>76</v>
+      </c>
+      <c r="D110" t="s">
+        <v>118</v>
+      </c>
+      <c r="E110" t="s">
+        <v>117</v>
+      </c>
+      <c r="F110" t="s">
+        <v>27</v>
+      </c>
+      <c r="G110" t="s">
+        <v>116</v>
+      </c>
+      <c r="H110" t="s">
+        <v>16</v>
+      </c>
+      <c r="I110" t="s">
+        <v>17</v>
+      </c>
+      <c r="K110">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>24</v>
+      </c>
+      <c r="B111">
+        <v>399</v>
+      </c>
+      <c r="C111">
+        <v>0</v>
+      </c>
+      <c r="D111" t="s">
+        <v>19</v>
+      </c>
+      <c r="E111" t="s">
+        <v>117</v>
+      </c>
+      <c r="F111" t="s">
+        <v>27</v>
+      </c>
+      <c r="G111" t="s">
+        <v>116</v>
+      </c>
+      <c r="H111" t="s">
+        <v>16</v>
+      </c>
+      <c r="I111" t="s">
+        <v>17</v>
+      </c>
+      <c r="K111">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>11</v>
+      </c>
+      <c r="B112">
+        <v>20</v>
+      </c>
+      <c r="C112">
+        <v>24</v>
+      </c>
+      <c r="D112" t="s">
+        <v>85</v>
+      </c>
+      <c r="E112" t="s">
+        <v>114</v>
+      </c>
+      <c r="F112" t="s">
+        <v>14</v>
+      </c>
+      <c r="G112" t="s">
+        <v>102</v>
+      </c>
+      <c r="H112" t="s">
+        <v>16</v>
+      </c>
+      <c r="I112" t="s">
+        <v>17</v>
+      </c>
+      <c r="K112">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>18</v>
+      </c>
+      <c r="B113">
+        <v>4</v>
+      </c>
+      <c r="C113">
+        <v>23</v>
+      </c>
+      <c r="D113" t="s">
+        <v>115</v>
+      </c>
+      <c r="E113" t="s">
+        <v>114</v>
+      </c>
+      <c r="F113" t="s">
+        <v>14</v>
+      </c>
+      <c r="G113" t="s">
+        <v>102</v>
+      </c>
+      <c r="H113" t="s">
+        <v>16</v>
+      </c>
+      <c r="I113" t="s">
+        <v>17</v>
+      </c>
+      <c r="K113">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>20</v>
+      </c>
+      <c r="B114">
+        <v>31</v>
+      </c>
+      <c r="C114">
+        <v>28</v>
+      </c>
+      <c r="D114" t="s">
+        <v>21</v>
+      </c>
+      <c r="E114" t="s">
+        <v>114</v>
+      </c>
+      <c r="F114" t="s">
+        <v>14</v>
+      </c>
+      <c r="G114" t="s">
+        <v>102</v>
+      </c>
+      <c r="H114" t="s">
+        <v>16</v>
+      </c>
+      <c r="I114" t="s">
+        <v>17</v>
+      </c>
+      <c r="K114">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>22</v>
+      </c>
+      <c r="B115">
+        <v>50</v>
+      </c>
+      <c r="C115">
+        <v>63</v>
+      </c>
+      <c r="D115" t="s">
+        <v>23</v>
+      </c>
+      <c r="E115" t="s">
+        <v>114</v>
+      </c>
+      <c r="F115" t="s">
+        <v>14</v>
+      </c>
+      <c r="G115" t="s">
+        <v>102</v>
+      </c>
+      <c r="H115" t="s">
+        <v>16</v>
+      </c>
+      <c r="I115" t="s">
+        <v>17</v>
+      </c>
+      <c r="K115">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>24</v>
+      </c>
+      <c r="B116">
+        <v>375</v>
+      </c>
+      <c r="C116">
+        <v>0</v>
+      </c>
+      <c r="D116" t="s">
+        <v>19</v>
+      </c>
+      <c r="E116" t="s">
+        <v>114</v>
+      </c>
+      <c r="F116" t="s">
+        <v>14</v>
+      </c>
+      <c r="G116" t="s">
+        <v>102</v>
+      </c>
+      <c r="H116" t="s">
+        <v>16</v>
+      </c>
+      <c r="I116" t="s">
+        <v>17</v>
+      </c>
+      <c r="K116">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>11</v>
+      </c>
+      <c r="B117">
+        <v>29</v>
+      </c>
+      <c r="C117">
+        <v>30</v>
+      </c>
+      <c r="D117" t="s">
+        <v>113</v>
+      </c>
+      <c r="E117" t="s">
+        <v>110</v>
+      </c>
+      <c r="F117" t="s">
+        <v>27</v>
+      </c>
+      <c r="G117" t="s">
+        <v>102</v>
+      </c>
+      <c r="H117" t="s">
+        <v>16</v>
+      </c>
+      <c r="I117" t="s">
+        <v>17</v>
+      </c>
+      <c r="K117">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>18</v>
+      </c>
+      <c r="B118">
+        <v>6</v>
+      </c>
+      <c r="C118">
+        <v>9</v>
+      </c>
+      <c r="D118" t="s">
+        <v>112</v>
+      </c>
+      <c r="E118" t="s">
+        <v>110</v>
+      </c>
+      <c r="F118" t="s">
+        <v>27</v>
+      </c>
+      <c r="G118" t="s">
+        <v>102</v>
+      </c>
+      <c r="H118" t="s">
+        <v>16</v>
+      </c>
+      <c r="I118" t="s">
+        <v>17</v>
+      </c>
+      <c r="K118">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>20</v>
+      </c>
+      <c r="B119">
+        <v>47</v>
+      </c>
+      <c r="C119">
+        <v>40</v>
+      </c>
+      <c r="D119" t="s">
+        <v>111</v>
+      </c>
+      <c r="E119" t="s">
+        <v>110</v>
+      </c>
+      <c r="F119" t="s">
+        <v>27</v>
+      </c>
+      <c r="G119" t="s">
+        <v>102</v>
+      </c>
+      <c r="H119" t="s">
+        <v>16</v>
+      </c>
+      <c r="I119" t="s">
+        <v>17</v>
+      </c>
+      <c r="K119">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>22</v>
+      </c>
+      <c r="B120">
+        <v>74</v>
+      </c>
+      <c r="C120">
+        <v>94</v>
+      </c>
+      <c r="D120" t="s">
+        <v>23</v>
+      </c>
+      <c r="E120" t="s">
+        <v>110</v>
+      </c>
+      <c r="F120" t="s">
+        <v>27</v>
+      </c>
+      <c r="G120" t="s">
+        <v>102</v>
+      </c>
+      <c r="H120" t="s">
+        <v>16</v>
+      </c>
+      <c r="I120" t="s">
+        <v>17</v>
+      </c>
+      <c r="K120">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>24</v>
+      </c>
+      <c r="B121">
+        <v>562</v>
+      </c>
+      <c r="C121">
+        <v>0</v>
+      </c>
+      <c r="D121" t="s">
+        <v>19</v>
+      </c>
+      <c r="E121" t="s">
+        <v>110</v>
+      </c>
+      <c r="F121" t="s">
+        <v>27</v>
+      </c>
+      <c r="G121" t="s">
+        <v>102</v>
+      </c>
+      <c r="H121" t="s">
+        <v>16</v>
+      </c>
+      <c r="I121" t="s">
+        <v>17</v>
+      </c>
+      <c r="K121">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>11</v>
+      </c>
+      <c r="B122">
+        <v>29</v>
+      </c>
+      <c r="C122">
+        <v>36</v>
+      </c>
+      <c r="D122" t="s">
+        <v>85</v>
+      </c>
+      <c r="E122" t="s">
+        <v>103</v>
+      </c>
+      <c r="F122" t="s">
+        <v>27</v>
+      </c>
+      <c r="G122" t="s">
+        <v>102</v>
+      </c>
+      <c r="H122" t="s">
+        <v>16</v>
+      </c>
+      <c r="I122" t="s">
+        <v>17</v>
+      </c>
+      <c r="J122" t="s">
+        <v>109</v>
+      </c>
+      <c r="K122">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>18</v>
+      </c>
+      <c r="B123">
+        <v>6</v>
+      </c>
+      <c r="C123">
+        <v>1</v>
+      </c>
+      <c r="D123" t="s">
+        <v>108</v>
+      </c>
+      <c r="E123" t="s">
+        <v>103</v>
+      </c>
+      <c r="F123" t="s">
+        <v>27</v>
+      </c>
+      <c r="G123" t="s">
+        <v>102</v>
+      </c>
+      <c r="H123" t="s">
+        <v>16</v>
+      </c>
+      <c r="I123" t="s">
+        <v>17</v>
+      </c>
+      <c r="J123" t="s">
+        <v>107</v>
+      </c>
+      <c r="K123">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>20</v>
+      </c>
+      <c r="B124">
+        <v>47</v>
+      </c>
+      <c r="C124">
+        <v>27</v>
+      </c>
+      <c r="D124" t="s">
+        <v>106</v>
+      </c>
+      <c r="E124" t="s">
+        <v>103</v>
+      </c>
+      <c r="F124" t="s">
+        <v>27</v>
+      </c>
+      <c r="G124" t="s">
+        <v>102</v>
+      </c>
+      <c r="H124" t="s">
+        <v>16</v>
+      </c>
+      <c r="I124" t="s">
+        <v>17</v>
+      </c>
+      <c r="J124" t="s">
+        <v>105</v>
+      </c>
+      <c r="K124">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>22</v>
+      </c>
+      <c r="B125">
+        <v>74</v>
+      </c>
+      <c r="C125">
+        <v>76</v>
+      </c>
+      <c r="D125" t="s">
+        <v>104</v>
+      </c>
+      <c r="E125" t="s">
+        <v>103</v>
+      </c>
+      <c r="F125" t="s">
+        <v>27</v>
+      </c>
+      <c r="G125" t="s">
+        <v>102</v>
+      </c>
+      <c r="H125" t="s">
+        <v>16</v>
+      </c>
+      <c r="I125" t="s">
+        <v>17</v>
+      </c>
+      <c r="K125">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>24</v>
+      </c>
+      <c r="B126">
+        <v>562</v>
+      </c>
+      <c r="C126">
+        <v>0</v>
+      </c>
+      <c r="D126" t="s">
+        <v>19</v>
+      </c>
+      <c r="E126" t="s">
+        <v>103</v>
+      </c>
+      <c r="F126" t="s">
+        <v>27</v>
+      </c>
+      <c r="G126" t="s">
+        <v>102</v>
+      </c>
+      <c r="H126" t="s">
+        <v>16</v>
+      </c>
+      <c r="I126" t="s">
+        <v>17</v>
+      </c>
+      <c r="J126" t="s">
+        <v>101</v>
+      </c>
+      <c r="K126">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>11</v>
+      </c>
+      <c r="B127">
+        <v>13</v>
+      </c>
+      <c r="C127">
+        <v>14</v>
+      </c>
+      <c r="D127" t="s">
+        <v>12</v>
+      </c>
+      <c r="E127" t="s">
+        <v>13</v>
+      </c>
+      <c r="F127" t="s">
+        <v>14</v>
+      </c>
+      <c r="G127" t="s">
+        <v>15</v>
+      </c>
+      <c r="H127" t="s">
+        <v>16</v>
+      </c>
+      <c r="I127" t="s">
+        <v>17</v>
+      </c>
+      <c r="K127">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>18</v>
+      </c>
+      <c r="B128">
+        <v>0</v>
+      </c>
+      <c r="C128">
+        <v>0</v>
+      </c>
+      <c r="D128" t="s">
+        <v>19</v>
+      </c>
+      <c r="E128" t="s">
+        <v>13</v>
+      </c>
+      <c r="F128" t="s">
+        <v>14</v>
+      </c>
+      <c r="G128" t="s">
+        <v>15</v>
+      </c>
+      <c r="H128" t="s">
+        <v>16</v>
+      </c>
+      <c r="I128" t="s">
+        <v>17</v>
+      </c>
+      <c r="K128">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>20</v>
+      </c>
+      <c r="B129">
+        <v>91</v>
+      </c>
+      <c r="C129">
+        <v>82</v>
+      </c>
+      <c r="D129" t="s">
+        <v>21</v>
+      </c>
+      <c r="E129" t="s">
+        <v>13</v>
+      </c>
+      <c r="F129" t="s">
+        <v>14</v>
+      </c>
+      <c r="G129" t="s">
+        <v>15</v>
+      </c>
+      <c r="H129" t="s">
+        <v>16</v>
+      </c>
+      <c r="I129" t="s">
+        <v>17</v>
+      </c>
+      <c r="K129">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>22</v>
+      </c>
+      <c r="B130">
+        <v>49</v>
+      </c>
+      <c r="C130">
+        <v>62</v>
+      </c>
+      <c r="D130" t="s">
+        <v>23</v>
+      </c>
+      <c r="E130" t="s">
+        <v>13</v>
+      </c>
+      <c r="F130" t="s">
+        <v>14</v>
+      </c>
+      <c r="G130" t="s">
+        <v>15</v>
+      </c>
+      <c r="H130" t="s">
+        <v>16</v>
+      </c>
+      <c r="I130" t="s">
+        <v>17</v>
+      </c>
+      <c r="K130">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>24</v>
+      </c>
+      <c r="B131">
+        <v>750</v>
+      </c>
+      <c r="C131">
+        <v>0</v>
+      </c>
+      <c r="D131" t="s">
+        <v>19</v>
+      </c>
+      <c r="E131" t="s">
+        <v>13</v>
+      </c>
+      <c r="F131" t="s">
+        <v>14</v>
+      </c>
+      <c r="G131" t="s">
+        <v>15</v>
+      </c>
+      <c r="H131" t="s">
+        <v>16</v>
+      </c>
+      <c r="I131" t="s">
+        <v>17</v>
+      </c>
+      <c r="J131" t="s">
+        <v>25</v>
+      </c>
+      <c r="K131">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>11</v>
+      </c>
+      <c r="B132">
+        <v>13</v>
+      </c>
+      <c r="C132">
+        <v>14</v>
+      </c>
+      <c r="D132" t="s">
+        <v>12</v>
+      </c>
+      <c r="E132" t="s">
+        <v>26</v>
+      </c>
+      <c r="F132" t="s">
+        <v>27</v>
+      </c>
+      <c r="G132" t="s">
+        <v>15</v>
+      </c>
+      <c r="H132" t="s">
+        <v>16</v>
+      </c>
+      <c r="I132" t="s">
+        <v>17</v>
+      </c>
+      <c r="J132" t="s">
+        <v>28</v>
+      </c>
+      <c r="K132">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>18</v>
+      </c>
+      <c r="B133">
+        <v>0</v>
+      </c>
+      <c r="C133">
+        <v>0</v>
+      </c>
+      <c r="D133" t="s">
+        <v>19</v>
+      </c>
+      <c r="E133" t="s">
+        <v>26</v>
+      </c>
+      <c r="F133" t="s">
+        <v>27</v>
+      </c>
+      <c r="G133" t="s">
+        <v>15</v>
+      </c>
+      <c r="H133" t="s">
+        <v>16</v>
+      </c>
+      <c r="I133" t="s">
+        <v>17</v>
+      </c>
+      <c r="K133">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>20</v>
+      </c>
+      <c r="B134">
+        <v>91</v>
+      </c>
+      <c r="C134">
+        <v>32</v>
+      </c>
+      <c r="D134" t="s">
+        <v>29</v>
+      </c>
+      <c r="E134" t="s">
+        <v>26</v>
+      </c>
+      <c r="F134" t="s">
+        <v>27</v>
+      </c>
+      <c r="G134" t="s">
+        <v>15</v>
+      </c>
+      <c r="H134" t="s">
+        <v>16</v>
+      </c>
+      <c r="I134" t="s">
+        <v>17</v>
+      </c>
+      <c r="J134" t="s">
+        <v>30</v>
+      </c>
+      <c r="K134">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>22</v>
+      </c>
+      <c r="B135">
+        <v>49</v>
+      </c>
+      <c r="C135">
+        <v>30</v>
+      </c>
+      <c r="D135" t="s">
+        <v>31</v>
+      </c>
+      <c r="E135" t="s">
+        <v>26</v>
+      </c>
+      <c r="F135" t="s">
+        <v>27</v>
+      </c>
+      <c r="G135" t="s">
+        <v>15</v>
+      </c>
+      <c r="H135" t="s">
+        <v>16</v>
+      </c>
+      <c r="I135" t="s">
+        <v>17</v>
+      </c>
+      <c r="J135" t="s">
+        <v>32</v>
+      </c>
+      <c r="K135">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>24</v>
+      </c>
+      <c r="B136">
+        <v>750</v>
+      </c>
+      <c r="C136">
+        <v>0</v>
+      </c>
+      <c r="D136" t="s">
+        <v>19</v>
+      </c>
+      <c r="E136" t="s">
+        <v>26</v>
+      </c>
+      <c r="F136" t="s">
+        <v>27</v>
+      </c>
+      <c r="G136" t="s">
+        <v>15</v>
+      </c>
+      <c r="H136" t="s">
+        <v>16</v>
+      </c>
+      <c r="I136" t="s">
+        <v>17</v>
+      </c>
+      <c r="J136" t="s">
+        <v>25</v>
+      </c>
+      <c r="K136">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>11</v>
+      </c>
+      <c r="B137">
+        <v>840</v>
+      </c>
+      <c r="C137">
+        <v>988</v>
+      </c>
+      <c r="D137" t="s">
+        <v>90</v>
+      </c>
+      <c r="E137" t="s">
+        <v>98</v>
+      </c>
+      <c r="F137" t="s">
+        <v>14</v>
+      </c>
+      <c r="G137" t="s">
+        <v>97</v>
+      </c>
+      <c r="H137" t="s">
+        <v>16</v>
+      </c>
+      <c r="I137" t="s">
+        <v>17</v>
+      </c>
+      <c r="K137">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>18</v>
+      </c>
+      <c r="B138">
+        <v>131</v>
+      </c>
+      <c r="C138">
+        <v>231</v>
+      </c>
+      <c r="D138" t="s">
+        <v>100</v>
+      </c>
+      <c r="E138" t="s">
+        <v>98</v>
+      </c>
+      <c r="F138" t="s">
+        <v>14</v>
+      </c>
+      <c r="G138" t="s">
+        <v>97</v>
+      </c>
+      <c r="H138" t="s">
+        <v>16</v>
+      </c>
+      <c r="I138" t="s">
+        <v>17</v>
+      </c>
+      <c r="K138">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>20</v>
+      </c>
+      <c r="B139">
+        <v>2433</v>
+      </c>
+      <c r="C139">
+        <v>1767</v>
+      </c>
+      <c r="D139" t="s">
+        <v>71</v>
+      </c>
+      <c r="E139" t="s">
+        <v>98</v>
+      </c>
+      <c r="F139" t="s">
+        <v>14</v>
+      </c>
+      <c r="G139" t="s">
+        <v>97</v>
+      </c>
+      <c r="H139" t="s">
+        <v>16</v>
+      </c>
+      <c r="I139" t="s">
+        <v>17</v>
+      </c>
+      <c r="K139">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>22</v>
+      </c>
+      <c r="B140">
+        <v>2738</v>
+      </c>
+      <c r="C140">
+        <v>3162</v>
+      </c>
+      <c r="D140" t="s">
+        <v>99</v>
+      </c>
+      <c r="E140" t="s">
+        <v>98</v>
+      </c>
+      <c r="F140" t="s">
+        <v>14</v>
+      </c>
+      <c r="G140" t="s">
+        <v>97</v>
+      </c>
+      <c r="H140" t="s">
+        <v>16</v>
+      </c>
+      <c r="I140" t="s">
+        <v>17</v>
+      </c>
+      <c r="K140">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>24</v>
+      </c>
+      <c r="B141">
+        <v>27700</v>
+      </c>
+      <c r="C141">
+        <v>0</v>
+      </c>
+      <c r="D141" t="s">
+        <v>19</v>
+      </c>
+      <c r="E141" t="s">
+        <v>98</v>
+      </c>
+      <c r="F141" t="s">
+        <v>14</v>
+      </c>
+      <c r="G141" t="s">
+        <v>97</v>
+      </c>
+      <c r="H141" t="s">
+        <v>16</v>
+      </c>
+      <c r="I141" t="s">
+        <v>17</v>
+      </c>
+      <c r="J141" t="s">
+        <v>96</v>
+      </c>
+      <c r="K141">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>11</v>
+      </c>
+      <c r="B142">
+        <v>13</v>
+      </c>
+      <c r="C142">
+        <v>16</v>
+      </c>
+      <c r="D142" t="s">
+        <v>50</v>
+      </c>
+      <c r="E142" t="s">
+        <v>94</v>
+      </c>
+      <c r="F142" t="s">
+        <v>14</v>
+      </c>
+      <c r="G142" t="s">
+        <v>88</v>
+      </c>
+      <c r="H142" t="s">
+        <v>16</v>
+      </c>
+      <c r="I142" t="s">
+        <v>17</v>
+      </c>
+      <c r="K142">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>18</v>
+      </c>
+      <c r="B143">
+        <v>2</v>
+      </c>
+      <c r="C143">
+        <v>3</v>
+      </c>
+      <c r="D143" t="s">
+        <v>50</v>
+      </c>
+      <c r="E143" t="s">
+        <v>94</v>
+      </c>
+      <c r="F143" t="s">
+        <v>14</v>
+      </c>
+      <c r="G143" t="s">
+        <v>88</v>
+      </c>
+      <c r="H143" t="s">
+        <v>16</v>
+      </c>
+      <c r="I143" t="s">
+        <v>17</v>
+      </c>
+      <c r="K143">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>20</v>
+      </c>
+      <c r="B144">
+        <v>29</v>
+      </c>
+      <c r="C144">
+        <v>15</v>
+      </c>
+      <c r="D144" t="s">
+        <v>95</v>
+      </c>
+      <c r="E144" t="s">
+        <v>94</v>
+      </c>
+      <c r="F144" t="s">
+        <v>14</v>
+      </c>
+      <c r="G144" t="s">
+        <v>88</v>
+      </c>
+      <c r="H144" t="s">
+        <v>16</v>
+      </c>
+      <c r="I144" t="s">
+        <v>17</v>
+      </c>
+      <c r="K144">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>22</v>
+      </c>
+      <c r="B145">
+        <v>51</v>
+      </c>
+      <c r="C145">
+        <v>63</v>
+      </c>
+      <c r="D145" t="s">
+        <v>85</v>
+      </c>
+      <c r="E145" t="s">
+        <v>94</v>
+      </c>
+      <c r="F145" t="s">
+        <v>14</v>
+      </c>
+      <c r="G145" t="s">
+        <v>88</v>
+      </c>
+      <c r="H145" t="s">
+        <v>16</v>
+      </c>
+      <c r="I145" t="s">
+        <v>17</v>
+      </c>
+      <c r="K145">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>24</v>
+      </c>
+      <c r="B146">
+        <v>480</v>
+      </c>
+      <c r="C146">
+        <v>0</v>
+      </c>
+      <c r="D146" t="s">
+        <v>19</v>
+      </c>
+      <c r="E146" t="s">
+        <v>94</v>
+      </c>
+      <c r="F146" t="s">
+        <v>14</v>
+      </c>
+      <c r="G146" t="s">
+        <v>88</v>
+      </c>
+      <c r="H146" t="s">
+        <v>16</v>
+      </c>
+      <c r="I146" t="s">
+        <v>17</v>
+      </c>
+      <c r="K146">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>11</v>
+      </c>
+      <c r="B147">
+        <v>19</v>
+      </c>
+      <c r="C147">
+        <v>25</v>
+      </c>
+      <c r="D147" t="s">
+        <v>93</v>
+      </c>
+      <c r="E147" t="s">
+        <v>89</v>
+      </c>
+      <c r="F147" t="s">
+        <v>27</v>
+      </c>
+      <c r="G147" t="s">
+        <v>88</v>
+      </c>
+      <c r="H147" t="s">
+        <v>16</v>
+      </c>
+      <c r="I147" t="s">
+        <v>17</v>
+      </c>
+      <c r="K147">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>18</v>
+      </c>
+      <c r="B148">
+        <v>4</v>
+      </c>
+      <c r="C148">
+        <v>5</v>
+      </c>
+      <c r="D148" t="s">
+        <v>92</v>
+      </c>
+      <c r="E148" t="s">
+        <v>89</v>
+      </c>
+      <c r="F148" t="s">
+        <v>27</v>
+      </c>
+      <c r="G148" t="s">
+        <v>88</v>
+      </c>
+      <c r="H148" t="s">
+        <v>16</v>
+      </c>
+      <c r="I148" t="s">
+        <v>17</v>
+      </c>
+      <c r="K148">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>20</v>
+      </c>
+      <c r="B149">
+        <v>44</v>
+      </c>
+      <c r="C149">
+        <v>38</v>
+      </c>
+      <c r="D149" t="s">
+        <v>91</v>
+      </c>
+      <c r="E149" t="s">
+        <v>89</v>
+      </c>
+      <c r="F149" t="s">
+        <v>27</v>
+      </c>
+      <c r="G149" t="s">
+        <v>88</v>
+      </c>
+      <c r="H149" t="s">
+        <v>16</v>
+      </c>
+      <c r="I149" t="s">
+        <v>17</v>
+      </c>
+      <c r="K149">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>22</v>
+      </c>
+      <c r="B150">
+        <v>77</v>
+      </c>
+      <c r="C150">
+        <v>91</v>
+      </c>
+      <c r="D150" t="s">
+        <v>90</v>
+      </c>
+      <c r="E150" t="s">
+        <v>89</v>
+      </c>
+      <c r="F150" t="s">
+        <v>27</v>
+      </c>
+      <c r="G150" t="s">
+        <v>88</v>
+      </c>
+      <c r="H150" t="s">
+        <v>16</v>
+      </c>
+      <c r="I150" t="s">
+        <v>17</v>
+      </c>
+      <c r="K150">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>24</v>
+      </c>
+      <c r="B151">
+        <v>720</v>
+      </c>
+      <c r="C151">
+        <v>0</v>
+      </c>
+      <c r="D151" t="s">
+        <v>19</v>
+      </c>
+      <c r="E151" t="s">
+        <v>89</v>
+      </c>
+      <c r="F151" t="s">
+        <v>27</v>
+      </c>
+      <c r="G151" t="s">
+        <v>88</v>
+      </c>
+      <c r="H151" t="s">
+        <v>16</v>
+      </c>
+      <c r="I151" t="s">
+        <v>17</v>
+      </c>
+      <c r="K151">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>11</v>
+      </c>
+      <c r="B152">
+        <v>11</v>
+      </c>
+      <c r="C152">
+        <v>18</v>
+      </c>
+      <c r="D152" t="s">
+        <v>87</v>
+      </c>
+      <c r="E152" t="s">
+        <v>83</v>
+      </c>
+      <c r="F152" t="s">
+        <v>14</v>
+      </c>
+      <c r="G152" t="s">
+        <v>75</v>
+      </c>
+      <c r="H152" t="s">
+        <v>16</v>
+      </c>
+      <c r="I152" t="s">
+        <v>17</v>
+      </c>
+      <c r="K152">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>18</v>
+      </c>
+      <c r="B153">
+        <v>2</v>
+      </c>
+      <c r="C153">
+        <v>5</v>
+      </c>
+      <c r="D153" t="s">
+        <v>86</v>
+      </c>
+      <c r="E153" t="s">
+        <v>83</v>
+      </c>
+      <c r="F153" t="s">
+        <v>14</v>
+      </c>
+      <c r="G153" t="s">
+        <v>75</v>
+      </c>
+      <c r="H153" t="s">
+        <v>16</v>
+      </c>
+      <c r="I153" t="s">
+        <v>17</v>
+      </c>
+      <c r="K153">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>20</v>
+      </c>
+      <c r="B154">
+        <v>24</v>
+      </c>
+      <c r="C154">
+        <v>29</v>
+      </c>
+      <c r="D154" t="s">
+        <v>85</v>
+      </c>
+      <c r="E154" t="s">
+        <v>83</v>
+      </c>
+      <c r="F154" t="s">
+        <v>14</v>
+      </c>
+      <c r="G154" t="s">
+        <v>75</v>
+      </c>
+      <c r="H154" t="s">
+        <v>16</v>
+      </c>
+      <c r="I154" t="s">
+        <v>17</v>
+      </c>
+      <c r="K154">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>22</v>
+      </c>
+      <c r="B155">
+        <v>38</v>
+      </c>
+      <c r="C155">
+        <v>77</v>
+      </c>
+      <c r="D155" t="s">
+        <v>84</v>
+      </c>
+      <c r="E155" t="s">
+        <v>83</v>
+      </c>
+      <c r="F155" t="s">
+        <v>14</v>
+      </c>
+      <c r="G155" t="s">
+        <v>75</v>
+      </c>
+      <c r="H155" t="s">
+        <v>16</v>
+      </c>
+      <c r="I155" t="s">
+        <v>17</v>
+      </c>
+      <c r="K155">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>24</v>
+      </c>
+      <c r="B156">
+        <v>375</v>
+      </c>
+      <c r="C156">
+        <v>0</v>
+      </c>
+      <c r="D156" t="s">
+        <v>19</v>
+      </c>
+      <c r="E156" t="s">
+        <v>83</v>
+      </c>
+      <c r="F156" t="s">
+        <v>14</v>
+      </c>
+      <c r="G156" t="s">
+        <v>75</v>
+      </c>
+      <c r="H156" t="s">
+        <v>16</v>
+      </c>
+      <c r="I156" t="s">
+        <v>17</v>
+      </c>
+      <c r="K156">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>11</v>
+      </c>
+      <c r="B157">
+        <v>16</v>
+      </c>
+      <c r="C157">
+        <v>24</v>
+      </c>
+      <c r="D157" t="s">
+        <v>82</v>
+      </c>
+      <c r="E157" t="s">
+        <v>79</v>
+      </c>
+      <c r="F157" t="s">
+        <v>27</v>
+      </c>
+      <c r="G157" t="s">
+        <v>75</v>
+      </c>
+      <c r="H157" t="s">
+        <v>16</v>
+      </c>
+      <c r="I157" t="s">
+        <v>17</v>
+      </c>
+      <c r="K157">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>18</v>
+      </c>
+      <c r="B158">
+        <v>4</v>
+      </c>
+      <c r="C158">
+        <v>9</v>
+      </c>
+      <c r="D158" t="s">
+        <v>81</v>
+      </c>
+      <c r="E158" t="s">
+        <v>79</v>
+      </c>
+      <c r="F158" t="s">
+        <v>27</v>
+      </c>
+      <c r="G158" t="s">
+        <v>75</v>
+      </c>
+      <c r="H158" t="s">
+        <v>16</v>
+      </c>
+      <c r="I158" t="s">
+        <v>17</v>
+      </c>
+      <c r="K158">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>20</v>
+      </c>
+      <c r="B159">
+        <v>35</v>
+      </c>
+      <c r="C159">
+        <v>44</v>
+      </c>
+      <c r="D159" t="s">
+        <v>50</v>
+      </c>
+      <c r="E159" t="s">
+        <v>79</v>
+      </c>
+      <c r="F159" t="s">
+        <v>27</v>
+      </c>
+      <c r="G159" t="s">
+        <v>75</v>
+      </c>
+      <c r="H159" t="s">
+        <v>16</v>
+      </c>
+      <c r="I159" t="s">
+        <v>17</v>
+      </c>
+      <c r="K159">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>22</v>
+      </c>
+      <c r="B160">
+        <v>57</v>
+      </c>
+      <c r="C160">
+        <v>89</v>
+      </c>
+      <c r="D160" t="s">
+        <v>80</v>
+      </c>
+      <c r="E160" t="s">
+        <v>79</v>
+      </c>
+      <c r="F160" t="s">
+        <v>27</v>
+      </c>
+      <c r="G160" t="s">
+        <v>75</v>
+      </c>
+      <c r="H160" t="s">
+        <v>16</v>
+      </c>
+      <c r="I160" t="s">
+        <v>17</v>
+      </c>
+      <c r="K160">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>24</v>
+      </c>
+      <c r="B161">
+        <v>562</v>
+      </c>
+      <c r="C161">
+        <v>0</v>
+      </c>
+      <c r="D161" t="s">
+        <v>19</v>
+      </c>
+      <c r="E161" t="s">
+        <v>79</v>
+      </c>
+      <c r="F161" t="s">
+        <v>27</v>
+      </c>
+      <c r="G161" t="s">
+        <v>75</v>
+      </c>
+      <c r="H161" t="s">
+        <v>16</v>
+      </c>
+      <c r="I161" t="s">
+        <v>17</v>
+      </c>
+      <c r="K161">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>11</v>
+      </c>
+      <c r="B162">
+        <v>16</v>
+      </c>
+      <c r="C162">
+        <v>5</v>
+      </c>
+      <c r="D162" t="s">
+        <v>78</v>
+      </c>
+      <c r="E162" t="s">
+        <v>76</v>
+      </c>
+      <c r="F162" t="s">
+        <v>27</v>
+      </c>
+      <c r="G162" t="s">
+        <v>75</v>
+      </c>
+      <c r="H162" t="s">
+        <v>16</v>
+      </c>
+      <c r="I162" t="s">
+        <v>17</v>
+      </c>
+      <c r="K162">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>18</v>
+      </c>
+      <c r="B163">
+        <v>4</v>
+      </c>
+      <c r="C163">
+        <v>0</v>
+      </c>
+      <c r="D163" t="s">
+        <v>19</v>
+      </c>
+      <c r="E163" t="s">
+        <v>76</v>
+      </c>
+      <c r="F163" t="s">
+        <v>27</v>
+      </c>
+      <c r="G163" t="s">
+        <v>75</v>
+      </c>
+      <c r="H163" t="s">
+        <v>16</v>
+      </c>
+      <c r="I163" t="s">
+        <v>17</v>
+      </c>
+      <c r="K163">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>20</v>
+      </c>
+      <c r="B164">
+        <v>35</v>
+      </c>
+      <c r="C164">
+        <v>12</v>
+      </c>
+      <c r="D164" t="s">
+        <v>77</v>
+      </c>
+      <c r="E164" t="s">
+        <v>76</v>
+      </c>
+      <c r="F164" t="s">
+        <v>27</v>
+      </c>
+      <c r="G164" t="s">
+        <v>75</v>
+      </c>
+      <c r="H164" t="s">
+        <v>16</v>
+      </c>
+      <c r="I164" t="s">
+        <v>17</v>
+      </c>
+      <c r="K164">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>22</v>
+      </c>
+      <c r="B165">
+        <v>57</v>
+      </c>
+      <c r="C165">
+        <v>19</v>
+      </c>
+      <c r="D165" t="s">
+        <v>77</v>
+      </c>
+      <c r="E165" t="s">
+        <v>76</v>
+      </c>
+      <c r="F165" t="s">
+        <v>27</v>
+      </c>
+      <c r="G165" t="s">
+        <v>75</v>
+      </c>
+      <c r="H165" t="s">
+        <v>16</v>
+      </c>
+      <c r="I165" t="s">
+        <v>17</v>
+      </c>
+      <c r="K165">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>24</v>
+      </c>
+      <c r="B166">
+        <v>562</v>
+      </c>
+      <c r="C166">
+        <v>0</v>
+      </c>
+      <c r="D166" t="s">
+        <v>19</v>
+      </c>
+      <c r="E166" t="s">
+        <v>76</v>
+      </c>
+      <c r="F166" t="s">
+        <v>27</v>
+      </c>
+      <c r="G166" t="s">
+        <v>75</v>
+      </c>
+      <c r="H166" t="s">
+        <v>16</v>
+      </c>
+      <c r="I166" t="s">
+        <v>17</v>
+      </c>
+      <c r="K166">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>11</v>
+      </c>
+      <c r="B167">
+        <v>21</v>
+      </c>
+      <c r="C167">
+        <v>65</v>
+      </c>
+      <c r="D167" t="s">
+        <v>46</v>
+      </c>
+      <c r="E167" t="s">
+        <v>47</v>
+      </c>
+      <c r="F167" t="s">
+        <v>14</v>
+      </c>
+      <c r="G167" t="s">
+        <v>48</v>
+      </c>
+      <c r="H167" t="s">
+        <v>16</v>
+      </c>
+      <c r="I167" t="s">
+        <v>17</v>
+      </c>
+      <c r="K167">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>18</v>
+      </c>
+      <c r="B168">
+        <v>3</v>
+      </c>
+      <c r="C168">
+        <v>3</v>
+      </c>
+      <c r="D168" t="s">
+        <v>49</v>
+      </c>
+      <c r="E168" t="s">
+        <v>47</v>
+      </c>
+      <c r="F168" t="s">
+        <v>14</v>
+      </c>
+      <c r="G168" t="s">
+        <v>48</v>
+      </c>
+      <c r="H168" t="s">
+        <v>16</v>
+      </c>
+      <c r="I168" t="s">
+        <v>17</v>
+      </c>
+      <c r="K168">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>20</v>
+      </c>
+      <c r="B169">
+        <v>61</v>
+      </c>
+      <c r="C169">
+        <v>77</v>
+      </c>
+      <c r="D169" t="s">
+        <v>50</v>
+      </c>
+      <c r="E169" t="s">
+        <v>47</v>
+      </c>
+      <c r="F169" t="s">
+        <v>14</v>
+      </c>
+      <c r="G169" t="s">
+        <v>48</v>
+      </c>
+      <c r="H169" t="s">
+        <v>16</v>
+      </c>
+      <c r="I169" t="s">
+        <v>17</v>
+      </c>
+      <c r="K169">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>22</v>
+      </c>
+      <c r="B170">
+        <v>38</v>
+      </c>
+      <c r="C170">
+        <v>142</v>
+      </c>
+      <c r="D170" t="s">
+        <v>51</v>
+      </c>
+      <c r="E170" t="s">
+        <v>47</v>
+      </c>
+      <c r="F170" t="s">
+        <v>14</v>
+      </c>
+      <c r="G170" t="s">
+        <v>48</v>
+      </c>
+      <c r="H170" t="s">
+        <v>16</v>
+      </c>
+      <c r="I170" t="s">
+        <v>17</v>
+      </c>
+      <c r="K170">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>24</v>
+      </c>
+      <c r="B171">
+        <v>300</v>
+      </c>
+      <c r="C171">
+        <v>0</v>
+      </c>
+      <c r="D171" t="s">
+        <v>19</v>
+      </c>
+      <c r="E171" t="s">
+        <v>47</v>
+      </c>
+      <c r="F171" t="s">
+        <v>14</v>
+      </c>
+      <c r="G171" t="s">
+        <v>48</v>
+      </c>
+      <c r="H171" t="s">
+        <v>16</v>
+      </c>
+      <c r="I171" t="s">
+        <v>17</v>
+      </c>
+      <c r="K171">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>11</v>
+      </c>
+      <c r="B172">
+        <v>27</v>
+      </c>
+      <c r="C172">
+        <v>25</v>
+      </c>
+      <c r="D172" t="s">
+        <v>52</v>
+      </c>
+      <c r="E172" t="s">
+        <v>53</v>
+      </c>
+      <c r="F172" t="s">
+        <v>27</v>
+      </c>
+      <c r="G172" t="s">
+        <v>48</v>
+      </c>
+      <c r="H172" t="s">
+        <v>16</v>
+      </c>
+      <c r="I172" t="s">
+        <v>17</v>
+      </c>
+      <c r="J172" t="s">
+        <v>54</v>
+      </c>
+      <c r="K172">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>18</v>
+      </c>
+      <c r="B173">
+        <v>4</v>
+      </c>
+      <c r="C173">
+        <v>1</v>
+      </c>
+      <c r="D173" t="s">
+        <v>55</v>
+      </c>
+      <c r="E173" t="s">
+        <v>53</v>
+      </c>
+      <c r="F173" t="s">
+        <v>27</v>
+      </c>
+      <c r="G173" t="s">
+        <v>48</v>
+      </c>
+      <c r="H173" t="s">
+        <v>16</v>
+      </c>
+      <c r="I173" t="s">
+        <v>17</v>
+      </c>
+      <c r="J173" t="s">
+        <v>56</v>
+      </c>
+      <c r="K173">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>20</v>
+      </c>
+      <c r="B174">
+        <v>82</v>
+      </c>
+      <c r="C174">
+        <v>38</v>
+      </c>
+      <c r="D174" t="s">
+        <v>57</v>
+      </c>
+      <c r="E174" t="s">
+        <v>53</v>
+      </c>
+      <c r="F174" t="s">
+        <v>27</v>
+      </c>
+      <c r="G174" t="s">
+        <v>48</v>
+      </c>
+      <c r="H174" t="s">
+        <v>16</v>
+      </c>
+      <c r="I174" t="s">
+        <v>17</v>
+      </c>
+      <c r="J174" t="s">
+        <v>58</v>
+      </c>
+      <c r="K174">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>22</v>
+      </c>
+      <c r="B175">
+        <v>51</v>
+      </c>
+      <c r="C175">
+        <v>73</v>
+      </c>
+      <c r="D175" t="s">
+        <v>59</v>
+      </c>
+      <c r="E175" t="s">
+        <v>53</v>
+      </c>
+      <c r="F175" t="s">
+        <v>27</v>
+      </c>
+      <c r="G175" t="s">
+        <v>48</v>
+      </c>
+      <c r="H175" t="s">
+        <v>16</v>
+      </c>
+      <c r="I175" t="s">
+        <v>17</v>
+      </c>
+      <c r="J175" t="s">
+        <v>60</v>
+      </c>
+      <c r="K175">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>24</v>
+      </c>
+      <c r="B176">
+        <v>399</v>
+      </c>
+      <c r="C176">
+        <v>0</v>
+      </c>
+      <c r="D176" t="s">
+        <v>19</v>
+      </c>
+      <c r="E176" t="s">
+        <v>53</v>
+      </c>
+      <c r="F176" t="s">
+        <v>27</v>
+      </c>
+      <c r="G176" t="s">
+        <v>48</v>
+      </c>
+      <c r="H176" t="s">
+        <v>16</v>
+      </c>
+      <c r="I176" t="s">
+        <v>17</v>
+      </c>
+      <c r="J176" t="s">
+        <v>74</v>
+      </c>
+      <c r="K176">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A177" t="s">
+        <v>11</v>
+      </c>
+      <c r="B177">
+        <v>27</v>
+      </c>
+      <c r="C177">
+        <v>53</v>
+      </c>
+      <c r="D177" t="s">
+        <v>61</v>
+      </c>
+      <c r="E177" t="s">
+        <v>62</v>
+      </c>
+      <c r="F177" t="s">
+        <v>27</v>
+      </c>
+      <c r="G177" t="s">
+        <v>48</v>
+      </c>
+      <c r="H177" t="s">
+        <v>16</v>
+      </c>
+      <c r="I177" t="s">
+        <v>17</v>
+      </c>
+      <c r="K177">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>18</v>
+      </c>
+      <c r="B178">
+        <v>4</v>
+      </c>
+      <c r="C178">
+        <v>16</v>
+      </c>
+      <c r="D178" t="s">
+        <v>63</v>
+      </c>
+      <c r="E178" t="s">
+        <v>62</v>
+      </c>
+      <c r="F178" t="s">
+        <v>27</v>
+      </c>
+      <c r="G178" t="s">
+        <v>48</v>
+      </c>
+      <c r="H178" t="s">
+        <v>16</v>
+      </c>
+      <c r="I178" t="s">
+        <v>17</v>
+      </c>
+      <c r="K178">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>20</v>
+      </c>
+      <c r="B179">
+        <v>82</v>
+      </c>
+      <c r="C179">
+        <v>85</v>
+      </c>
+      <c r="D179" t="s">
+        <v>64</v>
+      </c>
+      <c r="E179" t="s">
+        <v>62</v>
+      </c>
+      <c r="F179" t="s">
+        <v>27</v>
+      </c>
+      <c r="G179" t="s">
+        <v>48</v>
+      </c>
+      <c r="H179" t="s">
+        <v>16</v>
+      </c>
+      <c r="I179" t="s">
+        <v>17</v>
+      </c>
+      <c r="K179">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A180" t="s">
+        <v>22</v>
+      </c>
+      <c r="B180">
+        <v>51</v>
+      </c>
+      <c r="C180">
+        <v>154</v>
+      </c>
+      <c r="D180" t="s">
+        <v>65</v>
+      </c>
+      <c r="E180" t="s">
+        <v>62</v>
+      </c>
+      <c r="F180" t="s">
+        <v>27</v>
+      </c>
+      <c r="G180" t="s">
+        <v>48</v>
+      </c>
+      <c r="H180" t="s">
+        <v>16</v>
+      </c>
+      <c r="I180" t="s">
+        <v>17</v>
+      </c>
+      <c r="K180">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A181" t="s">
+        <v>24</v>
+      </c>
+      <c r="B181">
+        <v>399</v>
+      </c>
+      <c r="C181">
+        <v>0</v>
+      </c>
+      <c r="D181" t="s">
+        <v>19</v>
+      </c>
+      <c r="E181" t="s">
+        <v>62</v>
+      </c>
+      <c r="F181" t="s">
+        <v>27</v>
+      </c>
+      <c r="G181" t="s">
+        <v>48</v>
+      </c>
+      <c r="H181" t="s">
+        <v>16</v>
+      </c>
+      <c r="I181" t="s">
+        <v>17</v>
+      </c>
+      <c r="K181">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A182" t="s">
+        <v>11</v>
+      </c>
+      <c r="B182">
+        <v>27</v>
+      </c>
+      <c r="C182">
+        <v>46</v>
+      </c>
+      <c r="D182" t="s">
+        <v>66</v>
+      </c>
+      <c r="E182" t="s">
+        <v>67</v>
+      </c>
+      <c r="F182" t="s">
+        <v>27</v>
+      </c>
+      <c r="G182" t="s">
+        <v>48</v>
+      </c>
+      <c r="H182" t="s">
+        <v>16</v>
+      </c>
+      <c r="I182" t="s">
+        <v>17</v>
+      </c>
+      <c r="J182" t="s">
         <v>68</v>
       </c>
-      <c r="F61" t="s">
-        <v>30</v>
-      </c>
-      <c r="G61" t="s">
-        <v>64</v>
-      </c>
-      <c r="H61" t="s">
-        <v>16</v>
-      </c>
-      <c r="I61" t="s">
-        <v>17</v>
-      </c>
-      <c r="K61">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="70" spans="10:10" x14ac:dyDescent="0.25">
-      <c r="J70" t="s">
-        <v>10</v>
+      <c r="K182">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A183" t="s">
+        <v>18</v>
+      </c>
+      <c r="B183">
+        <v>4</v>
+      </c>
+      <c r="C183">
+        <v>2</v>
+      </c>
+      <c r="D183" t="s">
+        <v>69</v>
+      </c>
+      <c r="E183" t="s">
+        <v>67</v>
+      </c>
+      <c r="F183" t="s">
+        <v>27</v>
+      </c>
+      <c r="G183" t="s">
+        <v>48</v>
+      </c>
+      <c r="H183" t="s">
+        <v>16</v>
+      </c>
+      <c r="I183" t="s">
+        <v>17</v>
+      </c>
+      <c r="J183" t="s">
+        <v>70</v>
+      </c>
+      <c r="K183">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A184" t="s">
+        <v>20</v>
+      </c>
+      <c r="B184">
+        <v>82</v>
+      </c>
+      <c r="C184">
+        <v>60</v>
+      </c>
+      <c r="D184" t="s">
+        <v>71</v>
+      </c>
+      <c r="E184" t="s">
+        <v>67</v>
+      </c>
+      <c r="F184" t="s">
+        <v>27</v>
+      </c>
+      <c r="G184" t="s">
+        <v>48</v>
+      </c>
+      <c r="H184" t="s">
+        <v>16</v>
+      </c>
+      <c r="I184" t="s">
+        <v>17</v>
+      </c>
+      <c r="J184" t="s">
+        <v>72</v>
+      </c>
+      <c r="K184">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
+        <v>22</v>
+      </c>
+      <c r="B185">
+        <v>51</v>
+      </c>
+      <c r="C185">
+        <v>78</v>
+      </c>
+      <c r="D185" t="s">
+        <v>73</v>
+      </c>
+      <c r="E185" t="s">
+        <v>67</v>
+      </c>
+      <c r="F185" t="s">
+        <v>27</v>
+      </c>
+      <c r="G185" t="s">
+        <v>48</v>
+      </c>
+      <c r="H185" t="s">
+        <v>16</v>
+      </c>
+      <c r="I185" t="s">
+        <v>17</v>
+      </c>
+      <c r="K185">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A186" t="s">
+        <v>24</v>
+      </c>
+      <c r="B186">
+        <v>399</v>
+      </c>
+      <c r="C186">
+        <v>0</v>
+      </c>
+      <c r="D186" t="s">
+        <v>19</v>
+      </c>
+      <c r="E186" t="s">
+        <v>67</v>
+      </c>
+      <c r="F186" t="s">
+        <v>27</v>
+      </c>
+      <c r="G186" t="s">
+        <v>48</v>
+      </c>
+      <c r="H186" t="s">
+        <v>16</v>
+      </c>
+      <c r="I186" t="s">
+        <v>17</v>
+      </c>
+      <c r="K186">
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/02 Febrero/Liquidacióncvs - copia/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="11_37DD5EEF9561BE0E62355476585DCE3A8747A48A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D011DC07-FF31-42EF-95ED-EAE288DFB386}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="11_37DD5EEF9561BE0E62355476585DCE3A8747A48A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F963326F-A99C-455A-BFA9-41F37E7BA84D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1328" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="247">
   <si>
     <t>Producto</t>
   </si>
@@ -599,6 +599,168 @@
   </si>
   <si>
     <t>208%</t>
+  </si>
+  <si>
+    <t>ZARAGOZA</t>
+  </si>
+  <si>
+    <t>Paola Andrea Castillo Perez</t>
+  </si>
+  <si>
+    <t>116%</t>
+  </si>
+  <si>
+    <t>Lider Zargoza Kelly Celsa</t>
+  </si>
+  <si>
+    <t>141%</t>
+  </si>
+  <si>
+    <t>YARUMAL</t>
+  </si>
+  <si>
+    <t>Laura Carolina Chavarria Amariles</t>
+  </si>
+  <si>
+    <t>84%</t>
+  </si>
+  <si>
+    <t>Lider Geraldin Angulo Jaramillo</t>
+  </si>
+  <si>
+    <t>110%</t>
+  </si>
+  <si>
+    <t>170%</t>
+  </si>
+  <si>
+    <t>TERMINAL NORTE</t>
+  </si>
+  <si>
+    <t>Elizabeth  Quintero Mejia</t>
+  </si>
+  <si>
+    <t>59%</t>
+  </si>
+  <si>
+    <t>Dailyn Del Valle Alvarez Rueda</t>
+  </si>
+  <si>
+    <t>119%</t>
+  </si>
+  <si>
+    <t>53%</t>
+  </si>
+  <si>
+    <t>124%</t>
+  </si>
+  <si>
+    <t>Lider Terminal Paula Andrea Cano Monsalve</t>
+  </si>
+  <si>
+    <t>194%</t>
+  </si>
+  <si>
+    <t>147%</t>
+  </si>
+  <si>
+    <t>SEGOVIA</t>
+  </si>
+  <si>
+    <t>Luisa Fernanda Miranda Rodriguez</t>
+  </si>
+  <si>
+    <t>149%</t>
+  </si>
+  <si>
+    <t>49%</t>
+  </si>
+  <si>
+    <t>191%</t>
+  </si>
+  <si>
+    <t>Lider Dayana Lopez Llorente</t>
+  </si>
+  <si>
+    <t>140%</t>
+  </si>
+  <si>
+    <t>SABANETA</t>
+  </si>
+  <si>
+    <t>Yessica  Restrepo Caicedo</t>
+  </si>
+  <si>
+    <t>63%</t>
+  </si>
+  <si>
+    <t>19%</t>
+  </si>
+  <si>
+    <t>Jhon Alejandro Cardona Quintero</t>
+  </si>
+  <si>
+    <t>97%</t>
+  </si>
+  <si>
+    <t>Lider Paola Andrea Clavijo</t>
+  </si>
+  <si>
+    <t>327%</t>
+  </si>
+  <si>
+    <t>PRADO</t>
+  </si>
+  <si>
+    <t>LÃ­der Prado Sandra Milena Mejia Builes</t>
+  </si>
+  <si>
+    <t>86%</t>
+  </si>
+  <si>
+    <t>169%</t>
+  </si>
+  <si>
+    <t>NECHI</t>
+  </si>
+  <si>
+    <t>LeidisÂ  Rosa Luna Serpa</t>
+  </si>
+  <si>
+    <t>64%</t>
+  </si>
+  <si>
+    <t>Lider Nechi Maricela Ravelo Hernandez</t>
+  </si>
+  <si>
+    <t>188%</t>
+  </si>
+  <si>
+    <t>93%</t>
+  </si>
+  <si>
+    <t>3000%</t>
+  </si>
+  <si>
+    <t>135%</t>
+  </si>
+  <si>
+    <t>LA ESTRELLA</t>
+  </si>
+  <si>
+    <t>Darinela  Chavarria Carvajal</t>
+  </si>
+  <si>
+    <t>LÃ­der Estrella Milton Hernando Barrera Castro</t>
+  </si>
+  <si>
+    <t>106%</t>
+  </si>
+  <si>
+    <t>38%</t>
+  </si>
+  <si>
+    <t>88%</t>
   </si>
 </sst>
 </file>
@@ -962,7 +1124,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K186"/>
+  <dimension ref="A1:K271"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -6992,6 +7154,2726 @@
         <v>92</v>
       </c>
     </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A187" t="s">
+        <v>11</v>
+      </c>
+      <c r="B187">
+        <v>7</v>
+      </c>
+      <c r="C187">
+        <v>6</v>
+      </c>
+      <c r="D187" t="s">
+        <v>246</v>
+      </c>
+      <c r="E187" t="s">
+        <v>243</v>
+      </c>
+      <c r="F187" t="s">
+        <v>14</v>
+      </c>
+      <c r="G187" t="s">
+        <v>241</v>
+      </c>
+      <c r="H187" t="s">
+        <v>16</v>
+      </c>
+      <c r="I187" t="s">
+        <v>17</v>
+      </c>
+      <c r="K187">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A188" t="s">
+        <v>18</v>
+      </c>
+      <c r="B188">
+        <v>2</v>
+      </c>
+      <c r="C188">
+        <v>0</v>
+      </c>
+      <c r="D188" t="s">
+        <v>19</v>
+      </c>
+      <c r="E188" t="s">
+        <v>243</v>
+      </c>
+      <c r="F188" t="s">
+        <v>14</v>
+      </c>
+      <c r="G188" t="s">
+        <v>241</v>
+      </c>
+      <c r="H188" t="s">
+        <v>16</v>
+      </c>
+      <c r="I188" t="s">
+        <v>17</v>
+      </c>
+      <c r="K188">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>20</v>
+      </c>
+      <c r="B189">
+        <v>13</v>
+      </c>
+      <c r="C189">
+        <v>5</v>
+      </c>
+      <c r="D189" t="s">
+        <v>245</v>
+      </c>
+      <c r="E189" t="s">
+        <v>243</v>
+      </c>
+      <c r="F189" t="s">
+        <v>14</v>
+      </c>
+      <c r="G189" t="s">
+        <v>241</v>
+      </c>
+      <c r="H189" t="s">
+        <v>16</v>
+      </c>
+      <c r="I189" t="s">
+        <v>17</v>
+      </c>
+      <c r="K189">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>22</v>
+      </c>
+      <c r="B190">
+        <v>22</v>
+      </c>
+      <c r="C190">
+        <v>23</v>
+      </c>
+      <c r="D190" t="s">
+        <v>244</v>
+      </c>
+      <c r="E190" t="s">
+        <v>243</v>
+      </c>
+      <c r="F190" t="s">
+        <v>14</v>
+      </c>
+      <c r="G190" t="s">
+        <v>241</v>
+      </c>
+      <c r="H190" t="s">
+        <v>16</v>
+      </c>
+      <c r="I190" t="s">
+        <v>17</v>
+      </c>
+      <c r="K190">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>24</v>
+      </c>
+      <c r="B191">
+        <v>480</v>
+      </c>
+      <c r="C191">
+        <v>0</v>
+      </c>
+      <c r="D191" t="s">
+        <v>19</v>
+      </c>
+      <c r="E191" t="s">
+        <v>243</v>
+      </c>
+      <c r="F191" t="s">
+        <v>14</v>
+      </c>
+      <c r="G191" t="s">
+        <v>241</v>
+      </c>
+      <c r="H191" t="s">
+        <v>16</v>
+      </c>
+      <c r="I191" t="s">
+        <v>17</v>
+      </c>
+      <c r="K191">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>11</v>
+      </c>
+      <c r="B192">
+        <v>10</v>
+      </c>
+      <c r="C192">
+        <v>6</v>
+      </c>
+      <c r="D192" t="s">
+        <v>206</v>
+      </c>
+      <c r="E192" t="s">
+        <v>242</v>
+      </c>
+      <c r="F192" t="s">
+        <v>27</v>
+      </c>
+      <c r="G192" t="s">
+        <v>241</v>
+      </c>
+      <c r="H192" t="s">
+        <v>16</v>
+      </c>
+      <c r="I192" t="s">
+        <v>17</v>
+      </c>
+      <c r="K192">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A193" t="s">
+        <v>18</v>
+      </c>
+      <c r="B193">
+        <v>4</v>
+      </c>
+      <c r="C193">
+        <v>7</v>
+      </c>
+      <c r="D193" t="s">
+        <v>212</v>
+      </c>
+      <c r="E193" t="s">
+        <v>242</v>
+      </c>
+      <c r="F193" t="s">
+        <v>27</v>
+      </c>
+      <c r="G193" t="s">
+        <v>241</v>
+      </c>
+      <c r="H193" t="s">
+        <v>16</v>
+      </c>
+      <c r="I193" t="s">
+        <v>17</v>
+      </c>
+      <c r="K193">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A194" t="s">
+        <v>20</v>
+      </c>
+      <c r="B194">
+        <v>20</v>
+      </c>
+      <c r="C194">
+        <v>17</v>
+      </c>
+      <c r="D194" t="s">
+        <v>231</v>
+      </c>
+      <c r="E194" t="s">
+        <v>242</v>
+      </c>
+      <c r="F194" t="s">
+        <v>27</v>
+      </c>
+      <c r="G194" t="s">
+        <v>241</v>
+      </c>
+      <c r="H194" t="s">
+        <v>16</v>
+      </c>
+      <c r="I194" t="s">
+        <v>17</v>
+      </c>
+      <c r="K194">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>22</v>
+      </c>
+      <c r="B195">
+        <v>32</v>
+      </c>
+      <c r="C195">
+        <v>42</v>
+      </c>
+      <c r="D195" t="s">
+        <v>93</v>
+      </c>
+      <c r="E195" t="s">
+        <v>242</v>
+      </c>
+      <c r="F195" t="s">
+        <v>27</v>
+      </c>
+      <c r="G195" t="s">
+        <v>241</v>
+      </c>
+      <c r="H195" t="s">
+        <v>16</v>
+      </c>
+      <c r="I195" t="s">
+        <v>17</v>
+      </c>
+      <c r="K195">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>24</v>
+      </c>
+      <c r="B196">
+        <v>720</v>
+      </c>
+      <c r="C196">
+        <v>0</v>
+      </c>
+      <c r="D196" t="s">
+        <v>19</v>
+      </c>
+      <c r="E196" t="s">
+        <v>242</v>
+      </c>
+      <c r="F196" t="s">
+        <v>27</v>
+      </c>
+      <c r="G196" t="s">
+        <v>241</v>
+      </c>
+      <c r="H196" t="s">
+        <v>16</v>
+      </c>
+      <c r="I196" t="s">
+        <v>17</v>
+      </c>
+      <c r="K196">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A197" t="s">
+        <v>11</v>
+      </c>
+      <c r="B197">
+        <v>5</v>
+      </c>
+      <c r="C197">
+        <v>7</v>
+      </c>
+      <c r="D197" t="s">
+        <v>240</v>
+      </c>
+      <c r="E197" t="s">
+        <v>236</v>
+      </c>
+      <c r="F197" t="s">
+        <v>14</v>
+      </c>
+      <c r="G197" t="s">
+        <v>233</v>
+      </c>
+      <c r="H197" t="s">
+        <v>16</v>
+      </c>
+      <c r="I197" t="s">
+        <v>17</v>
+      </c>
+      <c r="K197">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A198" t="s">
+        <v>18</v>
+      </c>
+      <c r="B198">
+        <v>0</v>
+      </c>
+      <c r="C198">
+        <v>12</v>
+      </c>
+      <c r="D198" t="s">
+        <v>239</v>
+      </c>
+      <c r="E198" t="s">
+        <v>236</v>
+      </c>
+      <c r="F198" t="s">
+        <v>14</v>
+      </c>
+      <c r="G198" t="s">
+        <v>233</v>
+      </c>
+      <c r="H198" t="s">
+        <v>16</v>
+      </c>
+      <c r="I198" t="s">
+        <v>17</v>
+      </c>
+      <c r="K198">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A199" t="s">
+        <v>20</v>
+      </c>
+      <c r="B199">
+        <v>43</v>
+      </c>
+      <c r="C199">
+        <v>40</v>
+      </c>
+      <c r="D199" t="s">
+        <v>238</v>
+      </c>
+      <c r="E199" t="s">
+        <v>236</v>
+      </c>
+      <c r="F199" t="s">
+        <v>14</v>
+      </c>
+      <c r="G199" t="s">
+        <v>233</v>
+      </c>
+      <c r="H199" t="s">
+        <v>16</v>
+      </c>
+      <c r="I199" t="s">
+        <v>17</v>
+      </c>
+      <c r="K199">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A200" t="s">
+        <v>22</v>
+      </c>
+      <c r="B200">
+        <v>24</v>
+      </c>
+      <c r="C200">
+        <v>45</v>
+      </c>
+      <c r="D200" t="s">
+        <v>237</v>
+      </c>
+      <c r="E200" t="s">
+        <v>236</v>
+      </c>
+      <c r="F200" t="s">
+        <v>14</v>
+      </c>
+      <c r="G200" t="s">
+        <v>233</v>
+      </c>
+      <c r="H200" t="s">
+        <v>16</v>
+      </c>
+      <c r="I200" t="s">
+        <v>17</v>
+      </c>
+      <c r="K200">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A201" t="s">
+        <v>24</v>
+      </c>
+      <c r="B201">
+        <v>320</v>
+      </c>
+      <c r="C201">
+        <v>0</v>
+      </c>
+      <c r="D201" t="s">
+        <v>19</v>
+      </c>
+      <c r="E201" t="s">
+        <v>236</v>
+      </c>
+      <c r="F201" t="s">
+        <v>14</v>
+      </c>
+      <c r="G201" t="s">
+        <v>233</v>
+      </c>
+      <c r="H201" t="s">
+        <v>16</v>
+      </c>
+      <c r="I201" t="s">
+        <v>17</v>
+      </c>
+      <c r="K201">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>11</v>
+      </c>
+      <c r="B202">
+        <v>8</v>
+      </c>
+      <c r="C202">
+        <v>5</v>
+      </c>
+      <c r="D202" t="s">
+        <v>235</v>
+      </c>
+      <c r="E202" t="s">
+        <v>234</v>
+      </c>
+      <c r="F202" t="s">
+        <v>27</v>
+      </c>
+      <c r="G202" t="s">
+        <v>233</v>
+      </c>
+      <c r="H202" t="s">
+        <v>16</v>
+      </c>
+      <c r="I202" t="s">
+        <v>17</v>
+      </c>
+      <c r="K202">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>18</v>
+      </c>
+      <c r="B203">
+        <v>1</v>
+      </c>
+      <c r="C203">
+        <v>3</v>
+      </c>
+      <c r="D203" t="s">
+        <v>157</v>
+      </c>
+      <c r="E203" t="s">
+        <v>234</v>
+      </c>
+      <c r="F203" t="s">
+        <v>27</v>
+      </c>
+      <c r="G203" t="s">
+        <v>233</v>
+      </c>
+      <c r="H203" t="s">
+        <v>16</v>
+      </c>
+      <c r="I203" t="s">
+        <v>17</v>
+      </c>
+      <c r="K203">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>20</v>
+      </c>
+      <c r="B204">
+        <v>64</v>
+      </c>
+      <c r="C204">
+        <v>36</v>
+      </c>
+      <c r="D204" t="s">
+        <v>33</v>
+      </c>
+      <c r="E204" t="s">
+        <v>234</v>
+      </c>
+      <c r="F204" t="s">
+        <v>27</v>
+      </c>
+      <c r="G204" t="s">
+        <v>233</v>
+      </c>
+      <c r="H204" t="s">
+        <v>16</v>
+      </c>
+      <c r="I204" t="s">
+        <v>17</v>
+      </c>
+      <c r="K204">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>22</v>
+      </c>
+      <c r="B205">
+        <v>36</v>
+      </c>
+      <c r="C205">
+        <v>32</v>
+      </c>
+      <c r="D205" t="s">
+        <v>139</v>
+      </c>
+      <c r="E205" t="s">
+        <v>234</v>
+      </c>
+      <c r="F205" t="s">
+        <v>27</v>
+      </c>
+      <c r="G205" t="s">
+        <v>233</v>
+      </c>
+      <c r="H205" t="s">
+        <v>16</v>
+      </c>
+      <c r="I205" t="s">
+        <v>17</v>
+      </c>
+      <c r="K205">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>24</v>
+      </c>
+      <c r="B206">
+        <v>480</v>
+      </c>
+      <c r="C206">
+        <v>0</v>
+      </c>
+      <c r="D206" t="s">
+        <v>19</v>
+      </c>
+      <c r="E206" t="s">
+        <v>234</v>
+      </c>
+      <c r="F206" t="s">
+        <v>27</v>
+      </c>
+      <c r="G206" t="s">
+        <v>233</v>
+      </c>
+      <c r="H206" t="s">
+        <v>16</v>
+      </c>
+      <c r="I206" t="s">
+        <v>17</v>
+      </c>
+      <c r="K206">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>11</v>
+      </c>
+      <c r="B207">
+        <v>16</v>
+      </c>
+      <c r="C207">
+        <v>27</v>
+      </c>
+      <c r="D207" t="s">
+        <v>232</v>
+      </c>
+      <c r="E207" t="s">
+        <v>230</v>
+      </c>
+      <c r="F207" t="s">
+        <v>14</v>
+      </c>
+      <c r="G207" t="s">
+        <v>229</v>
+      </c>
+      <c r="H207" t="s">
+        <v>16</v>
+      </c>
+      <c r="I207" t="s">
+        <v>17</v>
+      </c>
+      <c r="K207">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>18</v>
+      </c>
+      <c r="B208">
+        <v>4</v>
+      </c>
+      <c r="C208">
+        <v>8</v>
+      </c>
+      <c r="D208" t="s">
+        <v>86</v>
+      </c>
+      <c r="E208" t="s">
+        <v>230</v>
+      </c>
+      <c r="F208" t="s">
+        <v>14</v>
+      </c>
+      <c r="G208" t="s">
+        <v>229</v>
+      </c>
+      <c r="H208" t="s">
+        <v>16</v>
+      </c>
+      <c r="I208" t="s">
+        <v>17</v>
+      </c>
+      <c r="K208">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A209" t="s">
+        <v>20</v>
+      </c>
+      <c r="B209">
+        <v>39</v>
+      </c>
+      <c r="C209">
+        <v>44</v>
+      </c>
+      <c r="D209" t="s">
+        <v>149</v>
+      </c>
+      <c r="E209" t="s">
+        <v>230</v>
+      </c>
+      <c r="F209" t="s">
+        <v>14</v>
+      </c>
+      <c r="G209" t="s">
+        <v>229</v>
+      </c>
+      <c r="H209" t="s">
+        <v>16</v>
+      </c>
+      <c r="I209" t="s">
+        <v>17</v>
+      </c>
+      <c r="K209">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>22</v>
+      </c>
+      <c r="B210">
+        <v>74</v>
+      </c>
+      <c r="C210">
+        <v>64</v>
+      </c>
+      <c r="D210" t="s">
+        <v>231</v>
+      </c>
+      <c r="E210" t="s">
+        <v>230</v>
+      </c>
+      <c r="F210" t="s">
+        <v>14</v>
+      </c>
+      <c r="G210" t="s">
+        <v>229</v>
+      </c>
+      <c r="H210" t="s">
+        <v>16</v>
+      </c>
+      <c r="I210" t="s">
+        <v>17</v>
+      </c>
+      <c r="K210">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A211" t="s">
+        <v>24</v>
+      </c>
+      <c r="B211">
+        <v>1200</v>
+      </c>
+      <c r="C211">
+        <v>0</v>
+      </c>
+      <c r="D211" t="s">
+        <v>19</v>
+      </c>
+      <c r="E211" t="s">
+        <v>230</v>
+      </c>
+      <c r="F211" t="s">
+        <v>14</v>
+      </c>
+      <c r="G211" t="s">
+        <v>229</v>
+      </c>
+      <c r="H211" t="s">
+        <v>16</v>
+      </c>
+      <c r="I211" t="s">
+        <v>17</v>
+      </c>
+      <c r="K211">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A212" t="s">
+        <v>11</v>
+      </c>
+      <c r="B212">
+        <v>16</v>
+      </c>
+      <c r="C212">
+        <v>18</v>
+      </c>
+      <c r="D212" t="s">
+        <v>195</v>
+      </c>
+      <c r="E212" t="s">
+        <v>227</v>
+      </c>
+      <c r="F212" t="s">
+        <v>14</v>
+      </c>
+      <c r="G212" t="s">
+        <v>221</v>
+      </c>
+      <c r="H212" t="s">
+        <v>16</v>
+      </c>
+      <c r="I212" t="s">
+        <v>17</v>
+      </c>
+      <c r="K212">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A213" t="s">
+        <v>18</v>
+      </c>
+      <c r="B213">
+        <v>3</v>
+      </c>
+      <c r="C213">
+        <v>9</v>
+      </c>
+      <c r="D213" t="s">
+        <v>228</v>
+      </c>
+      <c r="E213" t="s">
+        <v>227</v>
+      </c>
+      <c r="F213" t="s">
+        <v>14</v>
+      </c>
+      <c r="G213" t="s">
+        <v>221</v>
+      </c>
+      <c r="H213" t="s">
+        <v>16</v>
+      </c>
+      <c r="I213" t="s">
+        <v>17</v>
+      </c>
+      <c r="K213">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A214" t="s">
+        <v>20</v>
+      </c>
+      <c r="B214">
+        <v>24</v>
+      </c>
+      <c r="C214">
+        <v>23</v>
+      </c>
+      <c r="D214" t="s">
+        <v>147</v>
+      </c>
+      <c r="E214" t="s">
+        <v>227</v>
+      </c>
+      <c r="F214" t="s">
+        <v>14</v>
+      </c>
+      <c r="G214" t="s">
+        <v>221</v>
+      </c>
+      <c r="H214" t="s">
+        <v>16</v>
+      </c>
+      <c r="I214" t="s">
+        <v>17</v>
+      </c>
+      <c r="K214">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A215" t="s">
+        <v>22</v>
+      </c>
+      <c r="B215">
+        <v>45</v>
+      </c>
+      <c r="C215">
+        <v>51</v>
+      </c>
+      <c r="D215" t="s">
+        <v>149</v>
+      </c>
+      <c r="E215" t="s">
+        <v>227</v>
+      </c>
+      <c r="F215" t="s">
+        <v>14</v>
+      </c>
+      <c r="G215" t="s">
+        <v>221</v>
+      </c>
+      <c r="H215" t="s">
+        <v>16</v>
+      </c>
+      <c r="I215" t="s">
+        <v>17</v>
+      </c>
+      <c r="K215">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A216" t="s">
+        <v>24</v>
+      </c>
+      <c r="B216">
+        <v>375</v>
+      </c>
+      <c r="C216">
+        <v>0</v>
+      </c>
+      <c r="D216" t="s">
+        <v>19</v>
+      </c>
+      <c r="E216" t="s">
+        <v>227</v>
+      </c>
+      <c r="F216" t="s">
+        <v>14</v>
+      </c>
+      <c r="G216" t="s">
+        <v>221</v>
+      </c>
+      <c r="H216" t="s">
+        <v>16</v>
+      </c>
+      <c r="I216" t="s">
+        <v>17</v>
+      </c>
+      <c r="K216">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A217" t="s">
+        <v>11</v>
+      </c>
+      <c r="B217">
+        <v>23</v>
+      </c>
+      <c r="C217">
+        <v>27</v>
+      </c>
+      <c r="D217" t="s">
+        <v>195</v>
+      </c>
+      <c r="E217" t="s">
+        <v>225</v>
+      </c>
+      <c r="F217" t="s">
+        <v>27</v>
+      </c>
+      <c r="G217" t="s">
+        <v>221</v>
+      </c>
+      <c r="H217" t="s">
+        <v>16</v>
+      </c>
+      <c r="I217" t="s">
+        <v>17</v>
+      </c>
+      <c r="K217">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A218" t="s">
+        <v>18</v>
+      </c>
+      <c r="B218">
+        <v>4</v>
+      </c>
+      <c r="C218">
+        <v>4</v>
+      </c>
+      <c r="D218" t="s">
+        <v>226</v>
+      </c>
+      <c r="E218" t="s">
+        <v>225</v>
+      </c>
+      <c r="F218" t="s">
+        <v>27</v>
+      </c>
+      <c r="G218" t="s">
+        <v>221</v>
+      </c>
+      <c r="H218" t="s">
+        <v>16</v>
+      </c>
+      <c r="I218" t="s">
+        <v>17</v>
+      </c>
+      <c r="K218">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A219" t="s">
+        <v>20</v>
+      </c>
+      <c r="B219">
+        <v>36</v>
+      </c>
+      <c r="C219">
+        <v>37</v>
+      </c>
+      <c r="D219" t="s">
+        <v>113</v>
+      </c>
+      <c r="E219" t="s">
+        <v>225</v>
+      </c>
+      <c r="F219" t="s">
+        <v>27</v>
+      </c>
+      <c r="G219" t="s">
+        <v>221</v>
+      </c>
+      <c r="H219" t="s">
+        <v>16</v>
+      </c>
+      <c r="I219" t="s">
+        <v>17</v>
+      </c>
+      <c r="K219">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A220" t="s">
+        <v>22</v>
+      </c>
+      <c r="B220">
+        <v>68</v>
+      </c>
+      <c r="C220">
+        <v>77</v>
+      </c>
+      <c r="D220" t="s">
+        <v>149</v>
+      </c>
+      <c r="E220" t="s">
+        <v>225</v>
+      </c>
+      <c r="F220" t="s">
+        <v>27</v>
+      </c>
+      <c r="G220" t="s">
+        <v>221</v>
+      </c>
+      <c r="H220" t="s">
+        <v>16</v>
+      </c>
+      <c r="I220" t="s">
+        <v>17</v>
+      </c>
+      <c r="K220">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A221" t="s">
+        <v>24</v>
+      </c>
+      <c r="B221">
+        <v>562</v>
+      </c>
+      <c r="C221">
+        <v>0</v>
+      </c>
+      <c r="D221" t="s">
+        <v>19</v>
+      </c>
+      <c r="E221" t="s">
+        <v>225</v>
+      </c>
+      <c r="F221" t="s">
+        <v>27</v>
+      </c>
+      <c r="G221" t="s">
+        <v>221</v>
+      </c>
+      <c r="H221" t="s">
+        <v>16</v>
+      </c>
+      <c r="I221" t="s">
+        <v>17</v>
+      </c>
+      <c r="K221">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A222" t="s">
+        <v>11</v>
+      </c>
+      <c r="B222">
+        <v>23</v>
+      </c>
+      <c r="C222">
+        <v>13</v>
+      </c>
+      <c r="D222" t="s">
+        <v>33</v>
+      </c>
+      <c r="E222" t="s">
+        <v>222</v>
+      </c>
+      <c r="F222" t="s">
+        <v>27</v>
+      </c>
+      <c r="G222" t="s">
+        <v>221</v>
+      </c>
+      <c r="H222" t="s">
+        <v>16</v>
+      </c>
+      <c r="I222" t="s">
+        <v>17</v>
+      </c>
+      <c r="K222">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A223" t="s">
+        <v>18</v>
+      </c>
+      <c r="B223">
+        <v>4</v>
+      </c>
+      <c r="C223">
+        <v>1</v>
+      </c>
+      <c r="D223" t="s">
+        <v>131</v>
+      </c>
+      <c r="E223" t="s">
+        <v>222</v>
+      </c>
+      <c r="F223" t="s">
+        <v>27</v>
+      </c>
+      <c r="G223" t="s">
+        <v>221</v>
+      </c>
+      <c r="H223" t="s">
+        <v>16</v>
+      </c>
+      <c r="I223" t="s">
+        <v>17</v>
+      </c>
+      <c r="K223">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
+        <v>20</v>
+      </c>
+      <c r="B224">
+        <v>36</v>
+      </c>
+      <c r="C224">
+        <v>7</v>
+      </c>
+      <c r="D224" t="s">
+        <v>224</v>
+      </c>
+      <c r="E224" t="s">
+        <v>222</v>
+      </c>
+      <c r="F224" t="s">
+        <v>27</v>
+      </c>
+      <c r="G224" t="s">
+        <v>221</v>
+      </c>
+      <c r="H224" t="s">
+        <v>16</v>
+      </c>
+      <c r="I224" t="s">
+        <v>17</v>
+      </c>
+      <c r="K224">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>22</v>
+      </c>
+      <c r="B225">
+        <v>68</v>
+      </c>
+      <c r="C225">
+        <v>43</v>
+      </c>
+      <c r="D225" t="s">
+        <v>223</v>
+      </c>
+      <c r="E225" t="s">
+        <v>222</v>
+      </c>
+      <c r="F225" t="s">
+        <v>27</v>
+      </c>
+      <c r="G225" t="s">
+        <v>221</v>
+      </c>
+      <c r="H225" t="s">
+        <v>16</v>
+      </c>
+      <c r="I225" t="s">
+        <v>17</v>
+      </c>
+      <c r="K225">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>24</v>
+      </c>
+      <c r="B226">
+        <v>562</v>
+      </c>
+      <c r="C226">
+        <v>0</v>
+      </c>
+      <c r="D226" t="s">
+        <v>19</v>
+      </c>
+      <c r="E226" t="s">
+        <v>222</v>
+      </c>
+      <c r="F226" t="s">
+        <v>27</v>
+      </c>
+      <c r="G226" t="s">
+        <v>221</v>
+      </c>
+      <c r="H226" t="s">
+        <v>16</v>
+      </c>
+      <c r="I226" t="s">
+        <v>17</v>
+      </c>
+      <c r="K226">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
+        <v>11</v>
+      </c>
+      <c r="B227">
+        <v>14</v>
+      </c>
+      <c r="C227">
+        <v>19</v>
+      </c>
+      <c r="D227" t="s">
+        <v>220</v>
+      </c>
+      <c r="E227" t="s">
+        <v>219</v>
+      </c>
+      <c r="F227" t="s">
+        <v>14</v>
+      </c>
+      <c r="G227" t="s">
+        <v>214</v>
+      </c>
+      <c r="H227" t="s">
+        <v>16</v>
+      </c>
+      <c r="I227" t="s">
+        <v>17</v>
+      </c>
+      <c r="K227">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
+        <v>18</v>
+      </c>
+      <c r="B228">
+        <v>0</v>
+      </c>
+      <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228" t="s">
+        <v>19</v>
+      </c>
+      <c r="E228" t="s">
+        <v>219</v>
+      </c>
+      <c r="F228" t="s">
+        <v>14</v>
+      </c>
+      <c r="G228" t="s">
+        <v>214</v>
+      </c>
+      <c r="H228" t="s">
+        <v>16</v>
+      </c>
+      <c r="I228" t="s">
+        <v>17</v>
+      </c>
+      <c r="K228">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
+        <v>20</v>
+      </c>
+      <c r="B229">
+        <v>31</v>
+      </c>
+      <c r="C229">
+        <v>23</v>
+      </c>
+      <c r="D229" t="s">
+        <v>119</v>
+      </c>
+      <c r="E229" t="s">
+        <v>219</v>
+      </c>
+      <c r="F229" t="s">
+        <v>14</v>
+      </c>
+      <c r="G229" t="s">
+        <v>214</v>
+      </c>
+      <c r="H229" t="s">
+        <v>16</v>
+      </c>
+      <c r="I229" t="s">
+        <v>17</v>
+      </c>
+      <c r="K229">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
+        <v>22</v>
+      </c>
+      <c r="B230">
+        <v>73</v>
+      </c>
+      <c r="C230">
+        <v>67</v>
+      </c>
+      <c r="D230" t="s">
+        <v>165</v>
+      </c>
+      <c r="E230" t="s">
+        <v>219</v>
+      </c>
+      <c r="F230" t="s">
+        <v>14</v>
+      </c>
+      <c r="G230" t="s">
+        <v>214</v>
+      </c>
+      <c r="H230" t="s">
+        <v>16</v>
+      </c>
+      <c r="I230" t="s">
+        <v>17</v>
+      </c>
+      <c r="K230">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>24</v>
+      </c>
+      <c r="B231">
+        <v>480</v>
+      </c>
+      <c r="C231">
+        <v>0</v>
+      </c>
+      <c r="D231" t="s">
+        <v>19</v>
+      </c>
+      <c r="E231" t="s">
+        <v>219</v>
+      </c>
+      <c r="F231" t="s">
+        <v>14</v>
+      </c>
+      <c r="G231" t="s">
+        <v>214</v>
+      </c>
+      <c r="H231" t="s">
+        <v>16</v>
+      </c>
+      <c r="I231" t="s">
+        <v>17</v>
+      </c>
+      <c r="K231">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A232" t="s">
+        <v>11</v>
+      </c>
+      <c r="B232">
+        <v>20</v>
+      </c>
+      <c r="C232">
+        <v>39</v>
+      </c>
+      <c r="D232" t="s">
+        <v>218</v>
+      </c>
+      <c r="E232" t="s">
+        <v>215</v>
+      </c>
+      <c r="F232" t="s">
+        <v>27</v>
+      </c>
+      <c r="G232" t="s">
+        <v>214</v>
+      </c>
+      <c r="H232" t="s">
+        <v>16</v>
+      </c>
+      <c r="I232" t="s">
+        <v>17</v>
+      </c>
+      <c r="K232">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A233" t="s">
+        <v>18</v>
+      </c>
+      <c r="B233">
+        <v>0</v>
+      </c>
+      <c r="C233">
+        <v>0</v>
+      </c>
+      <c r="D233" t="s">
+        <v>19</v>
+      </c>
+      <c r="E233" t="s">
+        <v>215</v>
+      </c>
+      <c r="F233" t="s">
+        <v>27</v>
+      </c>
+      <c r="G233" t="s">
+        <v>214</v>
+      </c>
+      <c r="H233" t="s">
+        <v>16</v>
+      </c>
+      <c r="I233" t="s">
+        <v>17</v>
+      </c>
+      <c r="K233">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A234" t="s">
+        <v>20</v>
+      </c>
+      <c r="B234">
+        <v>47</v>
+      </c>
+      <c r="C234">
+        <v>23</v>
+      </c>
+      <c r="D234" t="s">
+        <v>217</v>
+      </c>
+      <c r="E234" t="s">
+        <v>215</v>
+      </c>
+      <c r="F234" t="s">
+        <v>27</v>
+      </c>
+      <c r="G234" t="s">
+        <v>214</v>
+      </c>
+      <c r="H234" t="s">
+        <v>16</v>
+      </c>
+      <c r="I234" t="s">
+        <v>17</v>
+      </c>
+      <c r="K234">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A235" t="s">
+        <v>22</v>
+      </c>
+      <c r="B235">
+        <v>110</v>
+      </c>
+      <c r="C235">
+        <v>164</v>
+      </c>
+      <c r="D235" t="s">
+        <v>216</v>
+      </c>
+      <c r="E235" t="s">
+        <v>215</v>
+      </c>
+      <c r="F235" t="s">
+        <v>27</v>
+      </c>
+      <c r="G235" t="s">
+        <v>214</v>
+      </c>
+      <c r="H235" t="s">
+        <v>16</v>
+      </c>
+      <c r="I235" t="s">
+        <v>17</v>
+      </c>
+      <c r="K235">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A236" t="s">
+        <v>24</v>
+      </c>
+      <c r="B236">
+        <v>720</v>
+      </c>
+      <c r="C236">
+        <v>0</v>
+      </c>
+      <c r="D236" t="s">
+        <v>19</v>
+      </c>
+      <c r="E236" t="s">
+        <v>215</v>
+      </c>
+      <c r="F236" t="s">
+        <v>27</v>
+      </c>
+      <c r="G236" t="s">
+        <v>214</v>
+      </c>
+      <c r="H236" t="s">
+        <v>16</v>
+      </c>
+      <c r="I236" t="s">
+        <v>17</v>
+      </c>
+      <c r="K236">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A237" t="s">
+        <v>11</v>
+      </c>
+      <c r="B237">
+        <v>8</v>
+      </c>
+      <c r="C237">
+        <v>11</v>
+      </c>
+      <c r="D237" t="s">
+        <v>213</v>
+      </c>
+      <c r="E237" t="s">
+        <v>211</v>
+      </c>
+      <c r="F237" t="s">
+        <v>14</v>
+      </c>
+      <c r="G237" t="s">
+        <v>204</v>
+      </c>
+      <c r="H237" t="s">
+        <v>16</v>
+      </c>
+      <c r="I237" t="s">
+        <v>17</v>
+      </c>
+      <c r="K237">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A238" t="s">
+        <v>18</v>
+      </c>
+      <c r="B238">
+        <v>2</v>
+      </c>
+      <c r="C238">
+        <v>0</v>
+      </c>
+      <c r="D238" t="s">
+        <v>19</v>
+      </c>
+      <c r="E238" t="s">
+        <v>211</v>
+      </c>
+      <c r="F238" t="s">
+        <v>14</v>
+      </c>
+      <c r="G238" t="s">
+        <v>204</v>
+      </c>
+      <c r="H238" t="s">
+        <v>16</v>
+      </c>
+      <c r="I238" t="s">
+        <v>17</v>
+      </c>
+      <c r="K238">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A239" t="s">
+        <v>20</v>
+      </c>
+      <c r="B239">
+        <v>30</v>
+      </c>
+      <c r="C239">
+        <v>31</v>
+      </c>
+      <c r="D239" t="s">
+        <v>113</v>
+      </c>
+      <c r="E239" t="s">
+        <v>211</v>
+      </c>
+      <c r="F239" t="s">
+        <v>14</v>
+      </c>
+      <c r="G239" t="s">
+        <v>204</v>
+      </c>
+      <c r="H239" t="s">
+        <v>16</v>
+      </c>
+      <c r="I239" t="s">
+        <v>17</v>
+      </c>
+      <c r="K239">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A240" t="s">
+        <v>22</v>
+      </c>
+      <c r="B240">
+        <v>32</v>
+      </c>
+      <c r="C240">
+        <v>61</v>
+      </c>
+      <c r="D240" t="s">
+        <v>212</v>
+      </c>
+      <c r="E240" t="s">
+        <v>211</v>
+      </c>
+      <c r="F240" t="s">
+        <v>14</v>
+      </c>
+      <c r="G240" t="s">
+        <v>204</v>
+      </c>
+      <c r="H240" t="s">
+        <v>16</v>
+      </c>
+      <c r="I240" t="s">
+        <v>17</v>
+      </c>
+      <c r="K240">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
+        <v>24</v>
+      </c>
+      <c r="B241">
+        <v>375</v>
+      </c>
+      <c r="C241">
+        <v>0</v>
+      </c>
+      <c r="D241" t="s">
+        <v>19</v>
+      </c>
+      <c r="E241" t="s">
+        <v>211</v>
+      </c>
+      <c r="F241" t="s">
+        <v>14</v>
+      </c>
+      <c r="G241" t="s">
+        <v>204</v>
+      </c>
+      <c r="H241" t="s">
+        <v>16</v>
+      </c>
+      <c r="I241" t="s">
+        <v>17</v>
+      </c>
+      <c r="K241">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A242" t="s">
+        <v>11</v>
+      </c>
+      <c r="B242">
+        <v>11</v>
+      </c>
+      <c r="C242">
+        <v>14</v>
+      </c>
+      <c r="D242" t="s">
+        <v>210</v>
+      </c>
+      <c r="E242" t="s">
+        <v>207</v>
+      </c>
+      <c r="F242" t="s">
+        <v>27</v>
+      </c>
+      <c r="G242" t="s">
+        <v>204</v>
+      </c>
+      <c r="H242" t="s">
+        <v>16</v>
+      </c>
+      <c r="I242" t="s">
+        <v>17</v>
+      </c>
+      <c r="K242">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A243" t="s">
+        <v>18</v>
+      </c>
+      <c r="B243">
+        <v>4</v>
+      </c>
+      <c r="C243">
+        <v>2</v>
+      </c>
+      <c r="D243" t="s">
+        <v>209</v>
+      </c>
+      <c r="E243" t="s">
+        <v>207</v>
+      </c>
+      <c r="F243" t="s">
+        <v>27</v>
+      </c>
+      <c r="G243" t="s">
+        <v>204</v>
+      </c>
+      <c r="H243" t="s">
+        <v>16</v>
+      </c>
+      <c r="I243" t="s">
+        <v>17</v>
+      </c>
+      <c r="K243">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>20</v>
+      </c>
+      <c r="B244">
+        <v>45</v>
+      </c>
+      <c r="C244">
+        <v>24</v>
+      </c>
+      <c r="D244" t="s">
+        <v>209</v>
+      </c>
+      <c r="E244" t="s">
+        <v>207</v>
+      </c>
+      <c r="F244" t="s">
+        <v>27</v>
+      </c>
+      <c r="G244" t="s">
+        <v>204</v>
+      </c>
+      <c r="H244" t="s">
+        <v>16</v>
+      </c>
+      <c r="I244" t="s">
+        <v>17</v>
+      </c>
+      <c r="K244">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A245" t="s">
+        <v>22</v>
+      </c>
+      <c r="B245">
+        <v>47</v>
+      </c>
+      <c r="C245">
+        <v>56</v>
+      </c>
+      <c r="D245" t="s">
+        <v>208</v>
+      </c>
+      <c r="E245" t="s">
+        <v>207</v>
+      </c>
+      <c r="F245" t="s">
+        <v>27</v>
+      </c>
+      <c r="G245" t="s">
+        <v>204</v>
+      </c>
+      <c r="H245" t="s">
+        <v>16</v>
+      </c>
+      <c r="I245" t="s">
+        <v>17</v>
+      </c>
+      <c r="K245">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>24</v>
+      </c>
+      <c r="B246">
+        <v>562</v>
+      </c>
+      <c r="C246">
+        <v>0</v>
+      </c>
+      <c r="D246" t="s">
+        <v>19</v>
+      </c>
+      <c r="E246" t="s">
+        <v>207</v>
+      </c>
+      <c r="F246" t="s">
+        <v>27</v>
+      </c>
+      <c r="G246" t="s">
+        <v>204</v>
+      </c>
+      <c r="H246" t="s">
+        <v>16</v>
+      </c>
+      <c r="I246" t="s">
+        <v>17</v>
+      </c>
+      <c r="K246">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>11</v>
+      </c>
+      <c r="B247">
+        <v>11</v>
+      </c>
+      <c r="C247">
+        <v>7</v>
+      </c>
+      <c r="D247" t="s">
+        <v>179</v>
+      </c>
+      <c r="E247" t="s">
+        <v>205</v>
+      </c>
+      <c r="F247" t="s">
+        <v>27</v>
+      </c>
+      <c r="G247" t="s">
+        <v>204</v>
+      </c>
+      <c r="H247" t="s">
+        <v>16</v>
+      </c>
+      <c r="I247" t="s">
+        <v>17</v>
+      </c>
+      <c r="K247">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
+        <v>18</v>
+      </c>
+      <c r="B248">
+        <v>4</v>
+      </c>
+      <c r="C248">
+        <v>0</v>
+      </c>
+      <c r="D248" t="s">
+        <v>19</v>
+      </c>
+      <c r="E248" t="s">
+        <v>205</v>
+      </c>
+      <c r="F248" t="s">
+        <v>27</v>
+      </c>
+      <c r="G248" t="s">
+        <v>204</v>
+      </c>
+      <c r="H248" t="s">
+        <v>16</v>
+      </c>
+      <c r="I248" t="s">
+        <v>17</v>
+      </c>
+      <c r="K248">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
+        <v>20</v>
+      </c>
+      <c r="B249">
+        <v>45</v>
+      </c>
+      <c r="C249">
+        <v>19</v>
+      </c>
+      <c r="D249" t="s">
+        <v>134</v>
+      </c>
+      <c r="E249" t="s">
+        <v>205</v>
+      </c>
+      <c r="F249" t="s">
+        <v>27</v>
+      </c>
+      <c r="G249" t="s">
+        <v>204</v>
+      </c>
+      <c r="H249" t="s">
+        <v>16</v>
+      </c>
+      <c r="I249" t="s">
+        <v>17</v>
+      </c>
+      <c r="K249">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A250" t="s">
+        <v>22</v>
+      </c>
+      <c r="B250">
+        <v>47</v>
+      </c>
+      <c r="C250">
+        <v>28</v>
+      </c>
+      <c r="D250" t="s">
+        <v>206</v>
+      </c>
+      <c r="E250" t="s">
+        <v>205</v>
+      </c>
+      <c r="F250" t="s">
+        <v>27</v>
+      </c>
+      <c r="G250" t="s">
+        <v>204</v>
+      </c>
+      <c r="H250" t="s">
+        <v>16</v>
+      </c>
+      <c r="I250" t="s">
+        <v>17</v>
+      </c>
+      <c r="K250">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
+        <v>24</v>
+      </c>
+      <c r="B251">
+        <v>562</v>
+      </c>
+      <c r="C251">
+        <v>0</v>
+      </c>
+      <c r="D251" t="s">
+        <v>19</v>
+      </c>
+      <c r="E251" t="s">
+        <v>205</v>
+      </c>
+      <c r="F251" t="s">
+        <v>27</v>
+      </c>
+      <c r="G251" t="s">
+        <v>204</v>
+      </c>
+      <c r="H251" t="s">
+        <v>16</v>
+      </c>
+      <c r="I251" t="s">
+        <v>17</v>
+      </c>
+      <c r="K251">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>11</v>
+      </c>
+      <c r="B252">
+        <v>9</v>
+      </c>
+      <c r="C252">
+        <v>15</v>
+      </c>
+      <c r="D252" t="s">
+        <v>203</v>
+      </c>
+      <c r="E252" t="s">
+        <v>201</v>
+      </c>
+      <c r="F252" t="s">
+        <v>14</v>
+      </c>
+      <c r="G252" t="s">
+        <v>198</v>
+      </c>
+      <c r="H252" t="s">
+        <v>16</v>
+      </c>
+      <c r="I252" t="s">
+        <v>17</v>
+      </c>
+      <c r="K252">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A253" t="s">
+        <v>18</v>
+      </c>
+      <c r="B253">
+        <v>2</v>
+      </c>
+      <c r="C253">
+        <v>5</v>
+      </c>
+      <c r="D253" t="s">
+        <v>192</v>
+      </c>
+      <c r="E253" t="s">
+        <v>201</v>
+      </c>
+      <c r="F253" t="s">
+        <v>14</v>
+      </c>
+      <c r="G253" t="s">
+        <v>198</v>
+      </c>
+      <c r="H253" t="s">
+        <v>16</v>
+      </c>
+      <c r="I253" t="s">
+        <v>17</v>
+      </c>
+      <c r="K253">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A254" t="s">
+        <v>20</v>
+      </c>
+      <c r="B254">
+        <v>31</v>
+      </c>
+      <c r="C254">
+        <v>31</v>
+      </c>
+      <c r="D254" t="s">
+        <v>182</v>
+      </c>
+      <c r="E254" t="s">
+        <v>201</v>
+      </c>
+      <c r="F254" t="s">
+        <v>14</v>
+      </c>
+      <c r="G254" t="s">
+        <v>198</v>
+      </c>
+      <c r="H254" t="s">
+        <v>16</v>
+      </c>
+      <c r="I254" t="s">
+        <v>17</v>
+      </c>
+      <c r="K254">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A255" t="s">
+        <v>22</v>
+      </c>
+      <c r="B255">
+        <v>67</v>
+      </c>
+      <c r="C255">
+        <v>74</v>
+      </c>
+      <c r="D255" t="s">
+        <v>202</v>
+      </c>
+      <c r="E255" t="s">
+        <v>201</v>
+      </c>
+      <c r="F255" t="s">
+        <v>14</v>
+      </c>
+      <c r="G255" t="s">
+        <v>198</v>
+      </c>
+      <c r="H255" t="s">
+        <v>16</v>
+      </c>
+      <c r="I255" t="s">
+        <v>17</v>
+      </c>
+      <c r="K255">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A256" t="s">
+        <v>24</v>
+      </c>
+      <c r="B256">
+        <v>480</v>
+      </c>
+      <c r="C256">
+        <v>0</v>
+      </c>
+      <c r="D256" t="s">
+        <v>19</v>
+      </c>
+      <c r="E256" t="s">
+        <v>201</v>
+      </c>
+      <c r="F256" t="s">
+        <v>14</v>
+      </c>
+      <c r="G256" t="s">
+        <v>198</v>
+      </c>
+      <c r="H256" t="s">
+        <v>16</v>
+      </c>
+      <c r="I256" t="s">
+        <v>17</v>
+      </c>
+      <c r="K256">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>11</v>
+      </c>
+      <c r="B257">
+        <v>13</v>
+      </c>
+      <c r="C257">
+        <v>22</v>
+      </c>
+      <c r="D257" t="s">
+        <v>135</v>
+      </c>
+      <c r="E257" t="s">
+        <v>199</v>
+      </c>
+      <c r="F257" t="s">
+        <v>27</v>
+      </c>
+      <c r="G257" t="s">
+        <v>198</v>
+      </c>
+      <c r="H257" t="s">
+        <v>16</v>
+      </c>
+      <c r="I257" t="s">
+        <v>17</v>
+      </c>
+      <c r="K257">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A258" t="s">
+        <v>18</v>
+      </c>
+      <c r="B258">
+        <v>4</v>
+      </c>
+      <c r="C258">
+        <v>6</v>
+      </c>
+      <c r="D258" t="s">
+        <v>135</v>
+      </c>
+      <c r="E258" t="s">
+        <v>199</v>
+      </c>
+      <c r="F258" t="s">
+        <v>27</v>
+      </c>
+      <c r="G258" t="s">
+        <v>198</v>
+      </c>
+      <c r="H258" t="s">
+        <v>16</v>
+      </c>
+      <c r="I258" t="s">
+        <v>17</v>
+      </c>
+      <c r="K258">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A259" t="s">
+        <v>20</v>
+      </c>
+      <c r="B259">
+        <v>47</v>
+      </c>
+      <c r="C259">
+        <v>24</v>
+      </c>
+      <c r="D259" t="s">
+        <v>95</v>
+      </c>
+      <c r="E259" t="s">
+        <v>199</v>
+      </c>
+      <c r="F259" t="s">
+        <v>27</v>
+      </c>
+      <c r="G259" t="s">
+        <v>198</v>
+      </c>
+      <c r="H259" t="s">
+        <v>16</v>
+      </c>
+      <c r="I259" t="s">
+        <v>17</v>
+      </c>
+      <c r="K259">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>22</v>
+      </c>
+      <c r="B260">
+        <v>101</v>
+      </c>
+      <c r="C260">
+        <v>85</v>
+      </c>
+      <c r="D260" t="s">
+        <v>200</v>
+      </c>
+      <c r="E260" t="s">
+        <v>199</v>
+      </c>
+      <c r="F260" t="s">
+        <v>27</v>
+      </c>
+      <c r="G260" t="s">
+        <v>198</v>
+      </c>
+      <c r="H260" t="s">
+        <v>16</v>
+      </c>
+      <c r="I260" t="s">
+        <v>17</v>
+      </c>
+      <c r="K260">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>24</v>
+      </c>
+      <c r="B261">
+        <v>720</v>
+      </c>
+      <c r="C261">
+        <v>0</v>
+      </c>
+      <c r="D261" t="s">
+        <v>19</v>
+      </c>
+      <c r="E261" t="s">
+        <v>199</v>
+      </c>
+      <c r="F261" t="s">
+        <v>27</v>
+      </c>
+      <c r="G261" t="s">
+        <v>198</v>
+      </c>
+      <c r="H261" t="s">
+        <v>16</v>
+      </c>
+      <c r="I261" t="s">
+        <v>17</v>
+      </c>
+      <c r="K261">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>11</v>
+      </c>
+      <c r="B262">
+        <v>9</v>
+      </c>
+      <c r="C262">
+        <v>13</v>
+      </c>
+      <c r="D262" t="s">
+        <v>197</v>
+      </c>
+      <c r="E262" t="s">
+        <v>196</v>
+      </c>
+      <c r="F262" t="s">
+        <v>14</v>
+      </c>
+      <c r="G262" t="s">
+        <v>193</v>
+      </c>
+      <c r="H262" t="s">
+        <v>16</v>
+      </c>
+      <c r="I262" t="s">
+        <v>17</v>
+      </c>
+      <c r="K262">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>18</v>
+      </c>
+      <c r="B263">
+        <v>0</v>
+      </c>
+      <c r="C263">
+        <v>0</v>
+      </c>
+      <c r="D263" t="s">
+        <v>19</v>
+      </c>
+      <c r="E263" t="s">
+        <v>196</v>
+      </c>
+      <c r="F263" t="s">
+        <v>14</v>
+      </c>
+      <c r="G263" t="s">
+        <v>193</v>
+      </c>
+      <c r="H263" t="s">
+        <v>16</v>
+      </c>
+      <c r="I263" t="s">
+        <v>17</v>
+      </c>
+      <c r="K263">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>20</v>
+      </c>
+      <c r="B264">
+        <v>38</v>
+      </c>
+      <c r="C264">
+        <v>47</v>
+      </c>
+      <c r="D264" t="s">
+        <v>50</v>
+      </c>
+      <c r="E264" t="s">
+        <v>196</v>
+      </c>
+      <c r="F264" t="s">
+        <v>14</v>
+      </c>
+      <c r="G264" t="s">
+        <v>193</v>
+      </c>
+      <c r="H264" t="s">
+        <v>16</v>
+      </c>
+      <c r="I264" t="s">
+        <v>17</v>
+      </c>
+      <c r="K264">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>22</v>
+      </c>
+      <c r="B265">
+        <v>37</v>
+      </c>
+      <c r="C265">
+        <v>38</v>
+      </c>
+      <c r="D265" t="s">
+        <v>113</v>
+      </c>
+      <c r="E265" t="s">
+        <v>196</v>
+      </c>
+      <c r="F265" t="s">
+        <v>14</v>
+      </c>
+      <c r="G265" t="s">
+        <v>193</v>
+      </c>
+      <c r="H265" t="s">
+        <v>16</v>
+      </c>
+      <c r="I265" t="s">
+        <v>17</v>
+      </c>
+      <c r="K265">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
+        <v>24</v>
+      </c>
+      <c r="B266">
+        <v>480</v>
+      </c>
+      <c r="C266">
+        <v>0</v>
+      </c>
+      <c r="D266" t="s">
+        <v>19</v>
+      </c>
+      <c r="E266" t="s">
+        <v>196</v>
+      </c>
+      <c r="F266" t="s">
+        <v>14</v>
+      </c>
+      <c r="G266" t="s">
+        <v>193</v>
+      </c>
+      <c r="H266" t="s">
+        <v>16</v>
+      </c>
+      <c r="I266" t="s">
+        <v>17</v>
+      </c>
+      <c r="K266">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
+        <v>11</v>
+      </c>
+      <c r="B267">
+        <v>14</v>
+      </c>
+      <c r="C267">
+        <v>16</v>
+      </c>
+      <c r="D267" t="s">
+        <v>195</v>
+      </c>
+      <c r="E267" t="s">
+        <v>194</v>
+      </c>
+      <c r="F267" t="s">
+        <v>27</v>
+      </c>
+      <c r="G267" t="s">
+        <v>193</v>
+      </c>
+      <c r="H267" t="s">
+        <v>16</v>
+      </c>
+      <c r="I267" t="s">
+        <v>17</v>
+      </c>
+      <c r="K267">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
+        <v>18</v>
+      </c>
+      <c r="B268">
+        <v>0</v>
+      </c>
+      <c r="C268">
+        <v>0</v>
+      </c>
+      <c r="D268" t="s">
+        <v>19</v>
+      </c>
+      <c r="E268" t="s">
+        <v>194</v>
+      </c>
+      <c r="F268" t="s">
+        <v>27</v>
+      </c>
+      <c r="G268" t="s">
+        <v>193</v>
+      </c>
+      <c r="H268" t="s">
+        <v>16</v>
+      </c>
+      <c r="I268" t="s">
+        <v>17</v>
+      </c>
+      <c r="K268">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
+        <v>20</v>
+      </c>
+      <c r="B269">
+        <v>56</v>
+      </c>
+      <c r="C269">
+        <v>34</v>
+      </c>
+      <c r="D269" t="s">
+        <v>145</v>
+      </c>
+      <c r="E269" t="s">
+        <v>194</v>
+      </c>
+      <c r="F269" t="s">
+        <v>27</v>
+      </c>
+      <c r="G269" t="s">
+        <v>193</v>
+      </c>
+      <c r="H269" t="s">
+        <v>16</v>
+      </c>
+      <c r="I269" t="s">
+        <v>17</v>
+      </c>
+      <c r="K269">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
+        <v>22</v>
+      </c>
+      <c r="B270">
+        <v>55</v>
+      </c>
+      <c r="C270">
+        <v>69</v>
+      </c>
+      <c r="D270" t="s">
+        <v>50</v>
+      </c>
+      <c r="E270" t="s">
+        <v>194</v>
+      </c>
+      <c r="F270" t="s">
+        <v>27</v>
+      </c>
+      <c r="G270" t="s">
+        <v>193</v>
+      </c>
+      <c r="H270" t="s">
+        <v>16</v>
+      </c>
+      <c r="I270" t="s">
+        <v>17</v>
+      </c>
+      <c r="K270">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
+        <v>24</v>
+      </c>
+      <c r="B271">
+        <v>720</v>
+      </c>
+      <c r="C271">
+        <v>0</v>
+      </c>
+      <c r="D271" t="s">
+        <v>19</v>
+      </c>
+      <c r="E271" t="s">
+        <v>194</v>
+      </c>
+      <c r="F271" t="s">
+        <v>27</v>
+      </c>
+      <c r="G271" t="s">
+        <v>193</v>
+      </c>
+      <c r="H271" t="s">
+        <v>16</v>
+      </c>
+      <c r="I271" t="s">
+        <v>17</v>
+      </c>
+      <c r="K271">
+        <v>119</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/02 Febrero/Liquidacióncvs - copia/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/02 Febrero/Liquidacióncvs - liquidación/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_37DD5EEF9561BE0E62355476585DCE3A8747A48A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F963326F-A99C-455A-BFA9-41F37E7BA84D}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="11_37DD5EEF9561BE0E62355476585DCE3A8747A48A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4779DC04-4745-473F-975B-84614F994CC6}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1923" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="257">
   <si>
     <t>Producto</t>
   </si>
@@ -253,21 +253,9 @@
     <t>Yanina Rocio Lozano Martinez</t>
   </si>
   <si>
-    <t>34%</t>
-  </si>
-  <si>
-    <t>30%</t>
-  </si>
-  <si>
     <t>Manuela  Vinasco Trejos</t>
   </si>
   <si>
-    <t>157%</t>
-  </si>
-  <si>
-    <t>240%</t>
-  </si>
-  <si>
     <t>145%</t>
   </si>
   <si>
@@ -649,9 +637,6 @@
     <t>119%</t>
   </si>
   <si>
-    <t>53%</t>
-  </si>
-  <si>
     <t>124%</t>
   </si>
   <si>
@@ -700,15 +685,9 @@
     <t>Jhon Alejandro Cardona Quintero</t>
   </si>
   <si>
-    <t>97%</t>
-  </si>
-  <si>
     <t>Lider Paola Andrea Clavijo</t>
   </si>
   <si>
-    <t>327%</t>
-  </si>
-  <si>
     <t>PRADO</t>
   </si>
   <si>
@@ -733,15 +712,9 @@
     <t>Lider Nechi Maricela Ravelo Hernandez</t>
   </si>
   <si>
-    <t>188%</t>
-  </si>
-  <si>
     <t>93%</t>
   </si>
   <si>
-    <t>3000%</t>
-  </si>
-  <si>
     <t>135%</t>
   </si>
   <si>
@@ -761,6 +734,63 @@
   </si>
   <si>
     <t>88%</t>
+  </si>
+  <si>
+    <t>39%</t>
+  </si>
+  <si>
+    <t>23%</t>
+  </si>
+  <si>
+    <t>Renunció el 14</t>
+  </si>
+  <si>
+    <t>166%</t>
+  </si>
+  <si>
+    <t>507%</t>
+  </si>
+  <si>
+    <t>440%</t>
+  </si>
+  <si>
+    <t>incapacidad 4 días</t>
+  </si>
+  <si>
+    <t>112%</t>
+  </si>
+  <si>
+    <t>182%</t>
+  </si>
+  <si>
+    <t>incapacidad 2 días</t>
+  </si>
+  <si>
+    <t>meta 15  cum.213%</t>
+  </si>
+  <si>
+    <t>meta 26 cum.138%</t>
+  </si>
+  <si>
+    <t>inc. cvs plus meta 4 cum.125%</t>
+  </si>
+  <si>
+    <t>183%</t>
+  </si>
+  <si>
+    <t>meta 20 %cum. 155%</t>
+  </si>
+  <si>
+    <t>meta 19 % cum. 84%</t>
+  </si>
+  <si>
+    <t>meta 2</t>
+  </si>
+  <si>
+    <t>Cap  c-plus 10 hab meta 5 %145%</t>
+  </si>
+  <si>
+    <t>206%</t>
   </si>
 </sst>
 </file>
@@ -779,7 +809,6 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1182,13 +1211,13 @@
         <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F2" t="s">
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
@@ -1211,16 +1240,16 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="E3" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
@@ -1243,16 +1272,16 @@
         <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="E4" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -1275,16 +1304,16 @@
         <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="E5" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
@@ -1310,13 +1339,13 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -1339,16 +1368,16 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="E7" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F7" t="s">
         <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
@@ -1371,16 +1400,16 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E8" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F8" t="s">
         <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -1403,16 +1432,16 @@
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="E9" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F9" t="s">
         <v>27</v>
       </c>
       <c r="G9" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
@@ -1438,13 +1467,13 @@
         <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F10" t="s">
         <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -1470,13 +1499,13 @@
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="F11" t="s">
         <v>27</v>
       </c>
       <c r="G11" t="s">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -1499,16 +1528,16 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E12" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -1531,16 +1560,16 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="E13" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -1563,16 +1592,16 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -1595,16 +1624,16 @@
         <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E15" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -1630,13 +1659,13 @@
         <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
@@ -1659,16 +1688,16 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E17" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F17" t="s">
         <v>27</v>
       </c>
       <c r="G17" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
@@ -1691,16 +1720,16 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="E18" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F18" t="s">
         <v>27</v>
       </c>
       <c r="G18" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
@@ -1723,16 +1752,16 @@
         <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E19" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F19" t="s">
         <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
@@ -1758,13 +1787,13 @@
         <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F20" t="s">
         <v>27</v>
       </c>
       <c r="G20" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -1790,13 +1819,13 @@
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="F21" t="s">
         <v>27</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
@@ -1819,16 +1848,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F22" t="s">
         <v>27</v>
       </c>
       <c r="G22" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
@@ -1851,16 +1880,16 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="E23" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F23" t="s">
         <v>27</v>
       </c>
       <c r="G23" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
@@ -1883,16 +1912,16 @@
         <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="E24" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F24" t="s">
         <v>27</v>
       </c>
       <c r="G24" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
@@ -1915,16 +1944,16 @@
         <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E25" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F25" t="s">
         <v>27</v>
       </c>
       <c r="G25" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -1950,13 +1979,13 @@
         <v>19</v>
       </c>
       <c r="E26" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="F26" t="s">
         <v>27</v>
       </c>
       <c r="G26" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -1979,16 +2008,16 @@
         <v>19</v>
       </c>
       <c r="D27" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E27" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -2014,13 +2043,13 @@
         <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -2043,16 +2072,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E29" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -2075,16 +2104,16 @@
         <v>56</v>
       </c>
       <c r="D30" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="E30" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -2110,13 +2139,13 @@
         <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -2139,16 +2168,16 @@
         <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E32" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F32" t="s">
         <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -2171,16 +2200,16 @@
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E33" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F33" t="s">
         <v>27</v>
       </c>
       <c r="G33" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -2206,13 +2235,13 @@
         <v>52</v>
       </c>
       <c r="E34" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F34" t="s">
         <v>27</v>
       </c>
       <c r="G34" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -2235,16 +2264,16 @@
         <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="E35" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F35" t="s">
         <v>27</v>
       </c>
       <c r="G35" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -2270,13 +2299,13 @@
         <v>19</v>
       </c>
       <c r="E36" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F36" t="s">
         <v>27</v>
       </c>
       <c r="G36" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -2299,16 +2328,16 @@
         <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E37" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F37" t="s">
         <v>27</v>
       </c>
       <c r="G37" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -2331,16 +2360,16 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="E38" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F38" t="s">
         <v>27</v>
       </c>
       <c r="G38" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -2363,16 +2392,16 @@
         <v>42</v>
       </c>
       <c r="D39" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="E39" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F39" t="s">
         <v>27</v>
       </c>
       <c r="G39" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
@@ -2395,16 +2424,16 @@
         <v>63</v>
       </c>
       <c r="D40" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="E40" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F40" t="s">
         <v>27</v>
       </c>
       <c r="G40" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -2430,13 +2459,13 @@
         <v>19</v>
       </c>
       <c r="E41" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F41" t="s">
         <v>27</v>
       </c>
       <c r="G41" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
@@ -2459,16 +2488,16 @@
         <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="E42" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
@@ -2494,13 +2523,13 @@
         <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
@@ -2526,13 +2555,13 @@
         <v>37</v>
       </c>
       <c r="E44" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
@@ -2555,16 +2584,16 @@
         <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="E45" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
@@ -2590,13 +2619,13 @@
         <v>19</v>
       </c>
       <c r="E46" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
@@ -2622,13 +2651,13 @@
         <v>52</v>
       </c>
       <c r="E47" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
@@ -2651,16 +2680,16 @@
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E48" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
@@ -2686,13 +2715,13 @@
         <v>44</v>
       </c>
       <c r="E49" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F49" t="s">
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
@@ -2715,16 +2744,16 @@
         <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E50" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F50" t="s">
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H50" t="s">
         <v>16</v>
@@ -2750,13 +2779,13 @@
         <v>19</v>
       </c>
       <c r="E51" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H51" t="s">
         <v>16</v>
@@ -2782,13 +2811,13 @@
         <v>31</v>
       </c>
       <c r="E52" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F52" t="s">
         <v>27</v>
       </c>
       <c r="G52" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H52" t="s">
         <v>16</v>
@@ -2811,16 +2840,16 @@
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="E53" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F53" t="s">
         <v>27</v>
       </c>
       <c r="G53" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H53" t="s">
         <v>16</v>
@@ -2846,13 +2875,13 @@
         <v>45</v>
       </c>
       <c r="E54" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F54" t="s">
         <v>27</v>
       </c>
       <c r="G54" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
@@ -2875,16 +2904,16 @@
         <v>79</v>
       </c>
       <c r="D55" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E55" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F55" t="s">
         <v>27</v>
       </c>
       <c r="G55" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H55" t="s">
         <v>16</v>
@@ -2910,13 +2939,13 @@
         <v>19</v>
       </c>
       <c r="E56" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="F56" t="s">
         <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="H56" t="s">
         <v>16</v>
@@ -2939,16 +2968,16 @@
         <v>13</v>
       </c>
       <c r="D57" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E57" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F57" t="s">
         <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H57" t="s">
         <v>16</v>
@@ -2971,16 +3000,16 @@
         <v>9</v>
       </c>
       <c r="D58" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E58" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F58" t="s">
         <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H58" t="s">
         <v>16</v>
@@ -3003,16 +3032,16 @@
         <v>17</v>
       </c>
       <c r="D59" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="E59" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F59" t="s">
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -3035,16 +3064,16 @@
         <v>31</v>
       </c>
       <c r="D60" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E60" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F60" t="s">
         <v>14</v>
       </c>
       <c r="G60" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H60" t="s">
         <v>16</v>
@@ -3070,13 +3099,13 @@
         <v>19</v>
       </c>
       <c r="E61" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F61" t="s">
         <v>14</v>
       </c>
       <c r="G61" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H61" t="s">
         <v>16</v>
@@ -3099,16 +3128,16 @@
         <v>18</v>
       </c>
       <c r="D62" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E62" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F62" t="s">
         <v>27</v>
       </c>
       <c r="G62" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H62" t="s">
         <v>16</v>
@@ -3131,16 +3160,16 @@
         <v>5</v>
       </c>
       <c r="D63" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E63" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F63" t="s">
         <v>27</v>
       </c>
       <c r="G63" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H63" t="s">
         <v>16</v>
@@ -3163,16 +3192,16 @@
         <v>37</v>
       </c>
       <c r="D64" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E64" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F64" t="s">
         <v>27</v>
       </c>
       <c r="G64" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H64" t="s">
         <v>16</v>
@@ -3195,16 +3224,16 @@
         <v>62</v>
       </c>
       <c r="D65" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E65" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F65" t="s">
         <v>27</v>
       </c>
       <c r="G65" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H65" t="s">
         <v>16</v>
@@ -3230,13 +3259,13 @@
         <v>19</v>
       </c>
       <c r="E66" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="F66" t="s">
         <v>27</v>
       </c>
       <c r="G66" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H66" t="s">
         <v>16</v>
@@ -3259,16 +3288,16 @@
         <v>17</v>
       </c>
       <c r="D67" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="E67" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F67" t="s">
         <v>27</v>
       </c>
       <c r="G67" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H67" t="s">
         <v>16</v>
@@ -3291,16 +3320,16 @@
         <v>5</v>
       </c>
       <c r="D68" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="E68" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F68" t="s">
         <v>27</v>
       </c>
       <c r="G68" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H68" t="s">
         <v>16</v>
@@ -3323,16 +3352,16 @@
         <v>28</v>
       </c>
       <c r="D69" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="E69" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F69" t="s">
         <v>27</v>
       </c>
       <c r="G69" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H69" t="s">
         <v>16</v>
@@ -3355,16 +3384,16 @@
         <v>45</v>
       </c>
       <c r="D70" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="E70" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F70" t="s">
         <v>27</v>
       </c>
       <c r="G70" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H70" t="s">
         <v>16</v>
@@ -3390,13 +3419,13 @@
         <v>19</v>
       </c>
       <c r="E71" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="F71" t="s">
         <v>27</v>
       </c>
       <c r="G71" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H71" t="s">
         <v>16</v>
@@ -3751,16 +3780,16 @@
         <v>21</v>
       </c>
       <c r="D82" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E82" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F82" t="s">
         <v>14</v>
       </c>
       <c r="G82" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H82" t="s">
         <v>16</v>
@@ -3783,16 +3812,16 @@
         <v>4</v>
       </c>
       <c r="D83" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="E83" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F83" t="s">
         <v>14</v>
       </c>
       <c r="G83" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H83" t="s">
         <v>16</v>
@@ -3815,16 +3844,16 @@
         <v>21</v>
       </c>
       <c r="D84" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="E84" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F84" t="s">
         <v>14</v>
       </c>
       <c r="G84" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H84" t="s">
         <v>16</v>
@@ -3847,16 +3876,16 @@
         <v>51</v>
       </c>
       <c r="D85" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="E85" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F85" t="s">
         <v>14</v>
       </c>
       <c r="G85" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H85" t="s">
         <v>16</v>
@@ -3882,13 +3911,13 @@
         <v>19</v>
       </c>
       <c r="E86" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F86" t="s">
         <v>14</v>
       </c>
       <c r="G86" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H86" t="s">
         <v>16</v>
@@ -3911,16 +3940,16 @@
         <v>18</v>
       </c>
       <c r="D87" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E87" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F87" t="s">
         <v>27</v>
       </c>
       <c r="G87" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H87" t="s">
         <v>16</v>
@@ -3943,16 +3972,16 @@
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E88" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F88" t="s">
         <v>27</v>
       </c>
       <c r="G88" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H88" t="s">
         <v>16</v>
@@ -3975,16 +4004,16 @@
         <v>15</v>
       </c>
       <c r="D89" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="E89" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F89" t="s">
         <v>27</v>
       </c>
       <c r="G89" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H89" t="s">
         <v>16</v>
@@ -4007,16 +4036,16 @@
         <v>48</v>
       </c>
       <c r="D90" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E90" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F90" t="s">
         <v>27</v>
       </c>
       <c r="G90" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H90" t="s">
         <v>16</v>
@@ -4042,13 +4071,13 @@
         <v>19</v>
       </c>
       <c r="E91" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F91" t="s">
         <v>27</v>
       </c>
       <c r="G91" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="H91" t="s">
         <v>16</v>
@@ -4071,16 +4100,16 @@
         <v>2</v>
       </c>
       <c r="D92" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="E92" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F92" t="s">
         <v>14</v>
       </c>
       <c r="G92" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H92" t="s">
         <v>16</v>
@@ -4106,13 +4135,13 @@
         <v>19</v>
       </c>
       <c r="E93" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F93" t="s">
         <v>14</v>
       </c>
       <c r="G93" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H93" t="s">
         <v>16</v>
@@ -4135,16 +4164,16 @@
         <v>2</v>
       </c>
       <c r="D94" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="E94" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F94" t="s">
         <v>14</v>
       </c>
       <c r="G94" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H94" t="s">
         <v>16</v>
@@ -4167,16 +4196,16 @@
         <v>4</v>
       </c>
       <c r="D95" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="E95" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F95" t="s">
         <v>14</v>
       </c>
       <c r="G95" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H95" t="s">
         <v>16</v>
@@ -4202,13 +4231,13 @@
         <v>19</v>
       </c>
       <c r="E96" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F96" t="s">
         <v>14</v>
       </c>
       <c r="G96" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H96" t="s">
         <v>16</v>
@@ -4234,13 +4263,13 @@
         <v>59</v>
       </c>
       <c r="E97" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F97" t="s">
         <v>27</v>
       </c>
       <c r="G97" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H97" t="s">
         <v>16</v>
@@ -4266,13 +4295,13 @@
         <v>19</v>
       </c>
       <c r="E98" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F98" t="s">
         <v>27</v>
       </c>
       <c r="G98" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H98" t="s">
         <v>16</v>
@@ -4295,16 +4324,16 @@
         <v>44</v>
       </c>
       <c r="D99" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E99" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F99" t="s">
         <v>27</v>
       </c>
       <c r="G99" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H99" t="s">
         <v>16</v>
@@ -4327,16 +4356,16 @@
         <v>71</v>
       </c>
       <c r="D100" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E100" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F100" t="s">
         <v>27</v>
       </c>
       <c r="G100" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H100" t="s">
         <v>16</v>
@@ -4362,13 +4391,13 @@
         <v>19</v>
       </c>
       <c r="E101" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="F101" t="s">
         <v>27</v>
       </c>
       <c r="G101" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H101" t="s">
         <v>16</v>
@@ -4391,16 +4420,16 @@
         <v>17</v>
       </c>
       <c r="D102" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E102" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F102" t="s">
         <v>27</v>
       </c>
       <c r="G102" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H102" t="s">
         <v>16</v>
@@ -4426,13 +4455,13 @@
         <v>19</v>
       </c>
       <c r="E103" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F103" t="s">
         <v>27</v>
       </c>
       <c r="G103" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H103" t="s">
         <v>16</v>
@@ -4455,16 +4484,16 @@
         <v>52</v>
       </c>
       <c r="D104" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E104" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F104" t="s">
         <v>27</v>
       </c>
       <c r="G104" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H104" t="s">
         <v>16</v>
@@ -4487,16 +4516,16 @@
         <v>59</v>
       </c>
       <c r="D105" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="E105" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F105" t="s">
         <v>27</v>
       </c>
       <c r="G105" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H105" t="s">
         <v>16</v>
@@ -4522,13 +4551,13 @@
         <v>19</v>
       </c>
       <c r="E106" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="F106" t="s">
         <v>27</v>
       </c>
       <c r="G106" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H106" t="s">
         <v>16</v>
@@ -4551,16 +4580,16 @@
         <v>27</v>
       </c>
       <c r="D107" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E107" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F107" t="s">
         <v>27</v>
       </c>
       <c r="G107" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H107" t="s">
         <v>16</v>
@@ -4583,16 +4612,16 @@
         <v>4</v>
       </c>
       <c r="D108" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="E108" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F108" t="s">
         <v>27</v>
       </c>
       <c r="G108" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H108" t="s">
         <v>16</v>
@@ -4615,16 +4644,16 @@
         <v>41</v>
       </c>
       <c r="D109" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E109" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F109" t="s">
         <v>27</v>
       </c>
       <c r="G109" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H109" t="s">
         <v>16</v>
@@ -4647,16 +4676,16 @@
         <v>76</v>
       </c>
       <c r="D110" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="E110" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F110" t="s">
         <v>27</v>
       </c>
       <c r="G110" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H110" t="s">
         <v>16</v>
@@ -4682,13 +4711,13 @@
         <v>19</v>
       </c>
       <c r="E111" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="F111" t="s">
         <v>27</v>
       </c>
       <c r="G111" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="H111" t="s">
         <v>16</v>
@@ -4711,16 +4740,16 @@
         <v>24</v>
       </c>
       <c r="D112" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E112" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F112" t="s">
         <v>14</v>
       </c>
       <c r="G112" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H112" t="s">
         <v>16</v>
@@ -4743,16 +4772,16 @@
         <v>23</v>
       </c>
       <c r="D113" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="E113" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F113" t="s">
         <v>14</v>
       </c>
       <c r="G113" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H113" t="s">
         <v>16</v>
@@ -4778,13 +4807,13 @@
         <v>21</v>
       </c>
       <c r="E114" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F114" t="s">
         <v>14</v>
       </c>
       <c r="G114" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H114" t="s">
         <v>16</v>
@@ -4810,13 +4839,13 @@
         <v>23</v>
       </c>
       <c r="E115" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F115" t="s">
         <v>14</v>
       </c>
       <c r="G115" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H115" t="s">
         <v>16</v>
@@ -4842,13 +4871,13 @@
         <v>19</v>
       </c>
       <c r="E116" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="F116" t="s">
         <v>14</v>
       </c>
       <c r="G116" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H116" t="s">
         <v>16</v>
@@ -4871,16 +4900,16 @@
         <v>30</v>
       </c>
       <c r="D117" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="E117" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F117" t="s">
         <v>27</v>
       </c>
       <c r="G117" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H117" t="s">
         <v>16</v>
@@ -4903,16 +4932,16 @@
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="E118" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F118" t="s">
         <v>27</v>
       </c>
       <c r="G118" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H118" t="s">
         <v>16</v>
@@ -4935,16 +4964,16 @@
         <v>40</v>
       </c>
       <c r="D119" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="E119" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F119" t="s">
         <v>27</v>
       </c>
       <c r="G119" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H119" t="s">
         <v>16</v>
@@ -4970,13 +4999,13 @@
         <v>23</v>
       </c>
       <c r="E120" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F120" t="s">
         <v>27</v>
       </c>
       <c r="G120" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H120" t="s">
         <v>16</v>
@@ -5002,13 +5031,13 @@
         <v>19</v>
       </c>
       <c r="E121" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="F121" t="s">
         <v>27</v>
       </c>
       <c r="G121" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H121" t="s">
         <v>16</v>
@@ -5031,16 +5060,16 @@
         <v>36</v>
       </c>
       <c r="D122" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E122" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F122" t="s">
         <v>27</v>
       </c>
       <c r="G122" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H122" t="s">
         <v>16</v>
@@ -5049,7 +5078,7 @@
         <v>17</v>
       </c>
       <c r="J122" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="K122">
         <v>80</v>
@@ -5066,25 +5095,25 @@
         <v>1</v>
       </c>
       <c r="D123" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="E123" t="s">
+        <v>99</v>
+      </c>
+      <c r="F123" t="s">
+        <v>27</v>
+      </c>
+      <c r="G123" t="s">
+        <v>98</v>
+      </c>
+      <c r="H123" t="s">
+        <v>16</v>
+      </c>
+      <c r="I123" t="s">
+        <v>17</v>
+      </c>
+      <c r="J123" t="s">
         <v>103</v>
-      </c>
-      <c r="F123" t="s">
-        <v>27</v>
-      </c>
-      <c r="G123" t="s">
-        <v>102</v>
-      </c>
-      <c r="H123" t="s">
-        <v>16</v>
-      </c>
-      <c r="I123" t="s">
-        <v>17</v>
-      </c>
-      <c r="J123" t="s">
-        <v>107</v>
       </c>
       <c r="K123">
         <v>80</v>
@@ -5101,16 +5130,16 @@
         <v>27</v>
       </c>
       <c r="D124" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E124" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F124" t="s">
         <v>27</v>
       </c>
       <c r="G124" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H124" t="s">
         <v>16</v>
@@ -5119,7 +5148,7 @@
         <v>17</v>
       </c>
       <c r="J124" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="K124">
         <v>80</v>
@@ -5136,16 +5165,16 @@
         <v>76</v>
       </c>
       <c r="D125" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E125" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F125" t="s">
         <v>27</v>
       </c>
       <c r="G125" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H125" t="s">
         <v>16</v>
@@ -5171,13 +5200,13 @@
         <v>19</v>
       </c>
       <c r="E126" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F126" t="s">
         <v>27</v>
       </c>
       <c r="G126" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="H126" t="s">
         <v>16</v>
@@ -5186,7 +5215,7 @@
         <v>17</v>
       </c>
       <c r="J126" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="K126">
         <v>80</v>
@@ -5538,16 +5567,16 @@
         <v>988</v>
       </c>
       <c r="D137" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E137" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F137" t="s">
         <v>14</v>
       </c>
       <c r="G137" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H137" t="s">
         <v>16</v>
@@ -5570,16 +5599,16 @@
         <v>231</v>
       </c>
       <c r="D138" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E138" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F138" t="s">
         <v>14</v>
       </c>
       <c r="G138" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H138" t="s">
         <v>16</v>
@@ -5605,13 +5634,13 @@
         <v>71</v>
       </c>
       <c r="E139" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F139" t="s">
         <v>14</v>
       </c>
       <c r="G139" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H139" t="s">
         <v>16</v>
@@ -5634,16 +5663,16 @@
         <v>3162</v>
       </c>
       <c r="D140" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="E140" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F140" t="s">
         <v>14</v>
       </c>
       <c r="G140" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H140" t="s">
         <v>16</v>
@@ -5669,13 +5698,13 @@
         <v>19</v>
       </c>
       <c r="E141" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F141" t="s">
         <v>14</v>
       </c>
       <c r="G141" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="H141" t="s">
         <v>16</v>
@@ -5684,7 +5713,7 @@
         <v>17</v>
       </c>
       <c r="J141" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="K141">
         <v>79</v>
@@ -5704,13 +5733,13 @@
         <v>50</v>
       </c>
       <c r="E142" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F142" t="s">
         <v>14</v>
       </c>
       <c r="G142" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H142" t="s">
         <v>16</v>
@@ -5736,13 +5765,13 @@
         <v>50</v>
       </c>
       <c r="E143" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F143" t="s">
         <v>14</v>
       </c>
       <c r="G143" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H143" t="s">
         <v>16</v>
@@ -5765,16 +5794,16 @@
         <v>15</v>
       </c>
       <c r="D144" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E144" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F144" t="s">
         <v>14</v>
       </c>
       <c r="G144" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H144" t="s">
         <v>16</v>
@@ -5797,16 +5826,16 @@
         <v>63</v>
       </c>
       <c r="D145" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="E145" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F145" t="s">
         <v>14</v>
       </c>
       <c r="G145" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H145" t="s">
         <v>16</v>
@@ -5832,13 +5861,13 @@
         <v>19</v>
       </c>
       <c r="E146" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="F146" t="s">
         <v>14</v>
       </c>
       <c r="G146" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H146" t="s">
         <v>16</v>
@@ -5861,16 +5890,16 @@
         <v>25</v>
       </c>
       <c r="D147" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E147" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F147" t="s">
         <v>27</v>
       </c>
       <c r="G147" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H147" t="s">
         <v>16</v>
@@ -5893,16 +5922,16 @@
         <v>5</v>
       </c>
       <c r="D148" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E148" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F148" t="s">
         <v>27</v>
       </c>
       <c r="G148" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H148" t="s">
         <v>16</v>
@@ -5925,16 +5954,16 @@
         <v>38</v>
       </c>
       <c r="D149" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E149" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F149" t="s">
         <v>27</v>
       </c>
       <c r="G149" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H149" t="s">
         <v>16</v>
@@ -5957,16 +5986,16 @@
         <v>91</v>
       </c>
       <c r="D150" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E150" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F150" t="s">
         <v>27</v>
       </c>
       <c r="G150" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H150" t="s">
         <v>16</v>
@@ -5992,13 +6021,13 @@
         <v>19</v>
       </c>
       <c r="E151" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="F151" t="s">
         <v>27</v>
       </c>
       <c r="G151" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="H151" t="s">
         <v>16</v>
@@ -6015,22 +6044,22 @@
         <v>11</v>
       </c>
       <c r="B152">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="C152">
-        <v>18</v>
+        <v>65</v>
       </c>
       <c r="D152" t="s">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="E152" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="F152" t="s">
         <v>14</v>
       </c>
       <c r="G152" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="H152" t="s">
         <v>16</v>
@@ -6039,7 +6068,7 @@
         <v>17</v>
       </c>
       <c r="K152">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -6047,22 +6076,22 @@
         <v>18</v>
       </c>
       <c r="B153">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C153">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D153" t="s">
-        <v>86</v>
+        <v>49</v>
       </c>
       <c r="E153" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="F153" t="s">
         <v>14</v>
       </c>
       <c r="G153" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="H153" t="s">
         <v>16</v>
@@ -6071,7 +6100,7 @@
         <v>17</v>
       </c>
       <c r="K153">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -6079,22 +6108,22 @@
         <v>20</v>
       </c>
       <c r="B154">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="C154">
-        <v>29</v>
+        <v>77</v>
       </c>
       <c r="D154" t="s">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E154" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="F154" t="s">
         <v>14</v>
       </c>
       <c r="G154" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="H154" t="s">
         <v>16</v>
@@ -6103,7 +6132,7 @@
         <v>17</v>
       </c>
       <c r="K154">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -6114,19 +6143,19 @@
         <v>38</v>
       </c>
       <c r="C155">
-        <v>77</v>
+        <v>142</v>
       </c>
       <c r="D155" t="s">
-        <v>84</v>
+        <v>51</v>
       </c>
       <c r="E155" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="F155" t="s">
         <v>14</v>
       </c>
       <c r="G155" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="H155" t="s">
         <v>16</v>
@@ -6135,7 +6164,7 @@
         <v>17</v>
       </c>
       <c r="K155">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -6143,7 +6172,7 @@
         <v>24</v>
       </c>
       <c r="B156">
-        <v>375</v>
+        <v>300</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -6152,13 +6181,13 @@
         <v>19</v>
       </c>
       <c r="E156" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="F156" t="s">
         <v>14</v>
       </c>
       <c r="G156" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="H156" t="s">
         <v>16</v>
@@ -6167,7 +6196,7 @@
         <v>17</v>
       </c>
       <c r="K156">
-        <v>63</v>
+        <v>92</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -6175,22 +6204,22 @@
         <v>11</v>
       </c>
       <c r="B157">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C157">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D157" t="s">
-        <v>82</v>
+        <v>52</v>
       </c>
       <c r="E157" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="F157" t="s">
         <v>27</v>
       </c>
       <c r="G157" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="H157" t="s">
         <v>16</v>
@@ -6198,8 +6227,11 @@
       <c r="I157" t="s">
         <v>17</v>
       </c>
+      <c r="J157" t="s">
+        <v>54</v>
+      </c>
       <c r="K157">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -6210,19 +6242,19 @@
         <v>4</v>
       </c>
       <c r="C158">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="D158" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="E158" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="F158" t="s">
         <v>27</v>
       </c>
       <c r="G158" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="H158" t="s">
         <v>16</v>
@@ -6230,8 +6262,11 @@
       <c r="I158" t="s">
         <v>17</v>
       </c>
+      <c r="J158" t="s">
+        <v>56</v>
+      </c>
       <c r="K158">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -6239,22 +6274,22 @@
         <v>20</v>
       </c>
       <c r="B159">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C159">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="D159" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="E159" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="F159" t="s">
         <v>27</v>
       </c>
       <c r="G159" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="H159" t="s">
         <v>16</v>
@@ -6262,8 +6297,11 @@
       <c r="I159" t="s">
         <v>17</v>
       </c>
+      <c r="J159" t="s">
+        <v>58</v>
+      </c>
       <c r="K159">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -6271,22 +6309,22 @@
         <v>22</v>
       </c>
       <c r="B160">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C160">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="D160" t="s">
-        <v>80</v>
+        <v>59</v>
       </c>
       <c r="E160" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="F160" t="s">
         <v>27</v>
       </c>
       <c r="G160" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="H160" t="s">
         <v>16</v>
@@ -6294,8 +6332,11 @@
       <c r="I160" t="s">
         <v>17</v>
       </c>
+      <c r="J160" t="s">
+        <v>60</v>
+      </c>
       <c r="K160">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -6303,7 +6344,7 @@
         <v>24</v>
       </c>
       <c r="B161">
-        <v>562</v>
+        <v>399</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -6312,13 +6353,13 @@
         <v>19</v>
       </c>
       <c r="E161" t="s">
-        <v>79</v>
+        <v>53</v>
       </c>
       <c r="F161" t="s">
         <v>27</v>
       </c>
       <c r="G161" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="H161" t="s">
         <v>16</v>
@@ -6326,8 +6367,11 @@
       <c r="I161" t="s">
         <v>17</v>
       </c>
+      <c r="J161" t="s">
+        <v>74</v>
+      </c>
       <c r="K161">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
@@ -6335,22 +6379,22 @@
         <v>11</v>
       </c>
       <c r="B162">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="C162">
-        <v>5</v>
+        <v>53</v>
       </c>
       <c r="D162" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="E162" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F162" t="s">
         <v>27</v>
       </c>
       <c r="G162" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="H162" t="s">
         <v>16</v>
@@ -6359,7 +6403,7 @@
         <v>17</v>
       </c>
       <c r="K162">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
@@ -6370,19 +6414,19 @@
         <v>4</v>
       </c>
       <c r="C163">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D163" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="E163" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F163" t="s">
         <v>27</v>
       </c>
       <c r="G163" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="H163" t="s">
         <v>16</v>
@@ -6391,7 +6435,7 @@
         <v>17</v>
       </c>
       <c r="K163">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -6399,22 +6443,22 @@
         <v>20</v>
       </c>
       <c r="B164">
-        <v>35</v>
+        <v>82</v>
       </c>
       <c r="C164">
-        <v>12</v>
+        <v>85</v>
       </c>
       <c r="D164" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="E164" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F164" t="s">
         <v>27</v>
       </c>
       <c r="G164" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="H164" t="s">
         <v>16</v>
@@ -6423,7 +6467,7 @@
         <v>17</v>
       </c>
       <c r="K164">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -6431,22 +6475,22 @@
         <v>22</v>
       </c>
       <c r="B165">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="C165">
-        <v>19</v>
+        <v>154</v>
       </c>
       <c r="D165" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="E165" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F165" t="s">
         <v>27</v>
       </c>
       <c r="G165" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="H165" t="s">
         <v>16</v>
@@ -6455,7 +6499,7 @@
         <v>17</v>
       </c>
       <c r="K165">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -6463,7 +6507,7 @@
         <v>24</v>
       </c>
       <c r="B166">
-        <v>562</v>
+        <v>399</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -6472,13 +6516,13 @@
         <v>19</v>
       </c>
       <c r="E166" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="F166" t="s">
         <v>27</v>
       </c>
       <c r="G166" t="s">
-        <v>75</v>
+        <v>48</v>
       </c>
       <c r="H166" t="s">
         <v>16</v>
@@ -6487,7 +6531,7 @@
         <v>17</v>
       </c>
       <c r="K166">
-        <v>64</v>
+        <v>92</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -6495,19 +6539,19 @@
         <v>11</v>
       </c>
       <c r="B167">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C167">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="D167" t="s">
-        <v>46</v>
+        <v>66</v>
       </c>
       <c r="E167" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="F167" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G167" t="s">
         <v>48</v>
@@ -6517,6 +6561,9 @@
       </c>
       <c r="I167" t="s">
         <v>17</v>
+      </c>
+      <c r="J167" t="s">
+        <v>68</v>
       </c>
       <c r="K167">
         <v>92</v>
@@ -6527,19 +6574,19 @@
         <v>18</v>
       </c>
       <c r="B168">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C168">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D168" t="s">
-        <v>49</v>
+        <v>69</v>
       </c>
       <c r="E168" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="F168" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G168" t="s">
         <v>48</v>
@@ -6549,6 +6596,9 @@
       </c>
       <c r="I168" t="s">
         <v>17</v>
+      </c>
+      <c r="J168" t="s">
+        <v>70</v>
       </c>
       <c r="K168">
         <v>92</v>
@@ -6559,19 +6609,19 @@
         <v>20</v>
       </c>
       <c r="B169">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C169">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="D169" t="s">
-        <v>50</v>
+        <v>71</v>
       </c>
       <c r="E169" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="F169" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G169" t="s">
         <v>48</v>
@@ -6581,6 +6631,9 @@
       </c>
       <c r="I169" t="s">
         <v>17</v>
+      </c>
+      <c r="J169" t="s">
+        <v>72</v>
       </c>
       <c r="K169">
         <v>92</v>
@@ -6591,19 +6644,19 @@
         <v>22</v>
       </c>
       <c r="B170">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C170">
-        <v>142</v>
+        <v>78</v>
       </c>
       <c r="D170" t="s">
-        <v>51</v>
+        <v>73</v>
       </c>
       <c r="E170" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="F170" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G170" t="s">
         <v>48</v>
@@ -6623,7 +6676,7 @@
         <v>24</v>
       </c>
       <c r="B171">
-        <v>300</v>
+        <v>399</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -6632,10 +6685,10 @@
         <v>19</v>
       </c>
       <c r="E171" t="s">
-        <v>47</v>
+        <v>67</v>
       </c>
       <c r="F171" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G171" t="s">
         <v>48</v>
@@ -6655,22 +6708,22 @@
         <v>11</v>
       </c>
       <c r="B172">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C172">
-        <v>25</v>
+        <v>6</v>
       </c>
       <c r="D172" t="s">
-        <v>52</v>
+        <v>237</v>
       </c>
       <c r="E172" t="s">
-        <v>53</v>
+        <v>234</v>
       </c>
       <c r="F172" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G172" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="H172" t="s">
         <v>16</v>
@@ -6678,11 +6731,8 @@
       <c r="I172" t="s">
         <v>17</v>
       </c>
-      <c r="J172" t="s">
-        <v>54</v>
-      </c>
       <c r="K172">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -6690,22 +6740,22 @@
         <v>18</v>
       </c>
       <c r="B173">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C173">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D173" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E173" t="s">
-        <v>53</v>
+        <v>234</v>
       </c>
       <c r="F173" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G173" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="H173" t="s">
         <v>16</v>
@@ -6713,11 +6763,8 @@
       <c r="I173" t="s">
         <v>17</v>
       </c>
-      <c r="J173" t="s">
-        <v>56</v>
-      </c>
       <c r="K173">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -6725,22 +6772,22 @@
         <v>20</v>
       </c>
       <c r="B174">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="C174">
-        <v>38</v>
+        <v>5</v>
       </c>
       <c r="D174" t="s">
-        <v>57</v>
+        <v>236</v>
       </c>
       <c r="E174" t="s">
-        <v>53</v>
+        <v>234</v>
       </c>
       <c r="F174" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G174" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="H174" t="s">
         <v>16</v>
@@ -6748,11 +6795,8 @@
       <c r="I174" t="s">
         <v>17</v>
       </c>
-      <c r="J174" t="s">
-        <v>58</v>
-      </c>
       <c r="K174">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -6760,22 +6804,22 @@
         <v>22</v>
       </c>
       <c r="B175">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C175">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="D175" t="s">
-        <v>59</v>
+        <v>235</v>
       </c>
       <c r="E175" t="s">
-        <v>53</v>
+        <v>234</v>
       </c>
       <c r="F175" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G175" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="H175" t="s">
         <v>16</v>
@@ -6783,11 +6827,8 @@
       <c r="I175" t="s">
         <v>17</v>
       </c>
-      <c r="J175" t="s">
-        <v>60</v>
-      </c>
       <c r="K175">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -6795,7 +6836,7 @@
         <v>24</v>
       </c>
       <c r="B176">
-        <v>399</v>
+        <v>480</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -6804,13 +6845,13 @@
         <v>19</v>
       </c>
       <c r="E176" t="s">
-        <v>53</v>
+        <v>234</v>
       </c>
       <c r="F176" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G176" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="H176" t="s">
         <v>16</v>
@@ -6818,11 +6859,8 @@
       <c r="I176" t="s">
         <v>17</v>
       </c>
-      <c r="J176" t="s">
-        <v>74</v>
-      </c>
       <c r="K176">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -6830,22 +6868,22 @@
         <v>11</v>
       </c>
       <c r="B177">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C177">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="D177" t="s">
-        <v>61</v>
+        <v>202</v>
       </c>
       <c r="E177" t="s">
-        <v>62</v>
+        <v>233</v>
       </c>
       <c r="F177" t="s">
         <v>27</v>
       </c>
       <c r="G177" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="H177" t="s">
         <v>16</v>
@@ -6854,7 +6892,7 @@
         <v>17</v>
       </c>
       <c r="K177">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -6865,19 +6903,19 @@
         <v>4</v>
       </c>
       <c r="C178">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="D178" t="s">
-        <v>63</v>
+        <v>207</v>
       </c>
       <c r="E178" t="s">
-        <v>62</v>
+        <v>233</v>
       </c>
       <c r="F178" t="s">
         <v>27</v>
       </c>
       <c r="G178" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="H178" t="s">
         <v>16</v>
@@ -6886,7 +6924,7 @@
         <v>17</v>
       </c>
       <c r="K178">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -6894,22 +6932,22 @@
         <v>20</v>
       </c>
       <c r="B179">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C179">
-        <v>85</v>
+        <v>17</v>
       </c>
       <c r="D179" t="s">
-        <v>64</v>
+        <v>224</v>
       </c>
       <c r="E179" t="s">
-        <v>62</v>
+        <v>233</v>
       </c>
       <c r="F179" t="s">
         <v>27</v>
       </c>
       <c r="G179" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="H179" t="s">
         <v>16</v>
@@ -6918,7 +6956,7 @@
         <v>17</v>
       </c>
       <c r="K179">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -6926,22 +6964,22 @@
         <v>22</v>
       </c>
       <c r="B180">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C180">
-        <v>154</v>
+        <v>42</v>
       </c>
       <c r="D180" t="s">
-        <v>65</v>
+        <v>89</v>
       </c>
       <c r="E180" t="s">
-        <v>62</v>
+        <v>233</v>
       </c>
       <c r="F180" t="s">
         <v>27</v>
       </c>
       <c r="G180" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="H180" t="s">
         <v>16</v>
@@ -6950,7 +6988,7 @@
         <v>17</v>
       </c>
       <c r="K180">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -6958,7 +6996,7 @@
         <v>24</v>
       </c>
       <c r="B181">
-        <v>399</v>
+        <v>720</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -6967,13 +7005,13 @@
         <v>19</v>
       </c>
       <c r="E181" t="s">
-        <v>62</v>
+        <v>233</v>
       </c>
       <c r="F181" t="s">
         <v>27</v>
       </c>
       <c r="G181" t="s">
-        <v>48</v>
+        <v>232</v>
       </c>
       <c r="H181" t="s">
         <v>16</v>
@@ -6982,7 +7020,7 @@
         <v>17</v>
       </c>
       <c r="K181">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -6990,22 +7028,22 @@
         <v>11</v>
       </c>
       <c r="B182">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="C182">
-        <v>46</v>
+        <v>27</v>
       </c>
       <c r="D182" t="s">
-        <v>66</v>
+        <v>225</v>
       </c>
       <c r="E182" t="s">
-        <v>67</v>
+        <v>223</v>
       </c>
       <c r="F182" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G182" t="s">
-        <v>48</v>
+        <v>222</v>
       </c>
       <c r="H182" t="s">
         <v>16</v>
@@ -7013,11 +7051,8 @@
       <c r="I182" t="s">
         <v>17</v>
       </c>
-      <c r="J182" t="s">
-        <v>68</v>
-      </c>
       <c r="K182">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -7028,19 +7063,19 @@
         <v>4</v>
       </c>
       <c r="C183">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D183" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="E183" t="s">
-        <v>67</v>
+        <v>223</v>
       </c>
       <c r="F183" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G183" t="s">
-        <v>48</v>
+        <v>222</v>
       </c>
       <c r="H183" t="s">
         <v>16</v>
@@ -7048,11 +7083,8 @@
       <c r="I183" t="s">
         <v>17</v>
       </c>
-      <c r="J183" t="s">
-        <v>70</v>
-      </c>
       <c r="K183">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -7060,22 +7092,22 @@
         <v>20</v>
       </c>
       <c r="B184">
-        <v>82</v>
+        <v>39</v>
       </c>
       <c r="C184">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="D184" t="s">
-        <v>71</v>
+        <v>145</v>
       </c>
       <c r="E184" t="s">
-        <v>67</v>
+        <v>223</v>
       </c>
       <c r="F184" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G184" t="s">
-        <v>48</v>
+        <v>222</v>
       </c>
       <c r="H184" t="s">
         <v>16</v>
@@ -7083,11 +7115,8 @@
       <c r="I184" t="s">
         <v>17</v>
       </c>
-      <c r="J184" t="s">
-        <v>72</v>
-      </c>
       <c r="K184">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -7095,22 +7124,22 @@
         <v>22</v>
       </c>
       <c r="B185">
-        <v>51</v>
+        <v>74</v>
       </c>
       <c r="C185">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="D185" t="s">
-        <v>73</v>
+        <v>224</v>
       </c>
       <c r="E185" t="s">
-        <v>67</v>
+        <v>223</v>
       </c>
       <c r="F185" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G185" t="s">
-        <v>48</v>
+        <v>222</v>
       </c>
       <c r="H185" t="s">
         <v>16</v>
@@ -7119,7 +7148,7 @@
         <v>17</v>
       </c>
       <c r="K185">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -7127,7 +7156,7 @@
         <v>24</v>
       </c>
       <c r="B186">
-        <v>399</v>
+        <v>1200</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -7136,13 +7165,13 @@
         <v>19</v>
       </c>
       <c r="E186" t="s">
-        <v>67</v>
+        <v>223</v>
       </c>
       <c r="F186" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G186" t="s">
-        <v>48</v>
+        <v>222</v>
       </c>
       <c r="H186" t="s">
         <v>16</v>
@@ -7151,7 +7180,7 @@
         <v>17</v>
       </c>
       <c r="K186">
-        <v>92</v>
+        <v>79</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -7159,22 +7188,22 @@
         <v>11</v>
       </c>
       <c r="B187">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C187">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D187" t="s">
-        <v>246</v>
+        <v>215</v>
       </c>
       <c r="E187" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="F187" t="s">
         <v>14</v>
       </c>
       <c r="G187" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="H187" t="s">
         <v>16</v>
@@ -7183,7 +7212,7 @@
         <v>17</v>
       </c>
       <c r="K187">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -7191,7 +7220,7 @@
         <v>18</v>
       </c>
       <c r="B188">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C188">
         <v>0</v>
@@ -7200,13 +7229,13 @@
         <v>19</v>
       </c>
       <c r="E188" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="F188" t="s">
         <v>14</v>
       </c>
       <c r="G188" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="H188" t="s">
         <v>16</v>
@@ -7215,7 +7244,7 @@
         <v>17</v>
       </c>
       <c r="K188">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
@@ -7223,22 +7252,22 @@
         <v>20</v>
       </c>
       <c r="B189">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="C189">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="D189" t="s">
-        <v>245</v>
+        <v>115</v>
       </c>
       <c r="E189" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="F189" t="s">
         <v>14</v>
       </c>
       <c r="G189" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="H189" t="s">
         <v>16</v>
@@ -7247,7 +7276,7 @@
         <v>17</v>
       </c>
       <c r="K189">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -7255,22 +7284,22 @@
         <v>22</v>
       </c>
       <c r="B190">
-        <v>22</v>
+        <v>73</v>
       </c>
       <c r="C190">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="D190" t="s">
-        <v>244</v>
+        <v>161</v>
       </c>
       <c r="E190" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="F190" t="s">
         <v>14</v>
       </c>
       <c r="G190" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="H190" t="s">
         <v>16</v>
@@ -7279,7 +7308,7 @@
         <v>17</v>
       </c>
       <c r="K190">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -7296,13 +7325,13 @@
         <v>19</v>
       </c>
       <c r="E191" t="s">
-        <v>243</v>
+        <v>214</v>
       </c>
       <c r="F191" t="s">
         <v>14</v>
       </c>
       <c r="G191" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="H191" t="s">
         <v>16</v>
@@ -7311,7 +7340,7 @@
         <v>17</v>
       </c>
       <c r="K191">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -7319,22 +7348,22 @@
         <v>11</v>
       </c>
       <c r="B192">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="C192">
-        <v>6</v>
+        <v>39</v>
       </c>
       <c r="D192" t="s">
-        <v>206</v>
+        <v>213</v>
       </c>
       <c r="E192" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="F192" t="s">
         <v>27</v>
       </c>
       <c r="G192" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="H192" t="s">
         <v>16</v>
@@ -7343,7 +7372,7 @@
         <v>17</v>
       </c>
       <c r="K192">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -7351,22 +7380,22 @@
         <v>18</v>
       </c>
       <c r="B193">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C193">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D193" t="s">
-        <v>212</v>
+        <v>19</v>
       </c>
       <c r="E193" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="F193" t="s">
         <v>27</v>
       </c>
       <c r="G193" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="H193" t="s">
         <v>16</v>
@@ -7375,7 +7404,7 @@
         <v>17</v>
       </c>
       <c r="K193">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -7383,22 +7412,22 @@
         <v>20</v>
       </c>
       <c r="B194">
-        <v>20</v>
+        <v>47</v>
       </c>
       <c r="C194">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D194" t="s">
-        <v>231</v>
+        <v>212</v>
       </c>
       <c r="E194" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="F194" t="s">
         <v>27</v>
       </c>
       <c r="G194" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="H194" t="s">
         <v>16</v>
@@ -7407,7 +7436,7 @@
         <v>17</v>
       </c>
       <c r="K194">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -7415,22 +7444,22 @@
         <v>22</v>
       </c>
       <c r="B195">
-        <v>32</v>
+        <v>110</v>
       </c>
       <c r="C195">
-        <v>42</v>
+        <v>164</v>
       </c>
       <c r="D195" t="s">
-        <v>93</v>
+        <v>211</v>
       </c>
       <c r="E195" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="F195" t="s">
         <v>27</v>
       </c>
       <c r="G195" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="H195" t="s">
         <v>16</v>
@@ -7439,7 +7468,7 @@
         <v>17</v>
       </c>
       <c r="K195">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -7456,13 +7485,13 @@
         <v>19</v>
       </c>
       <c r="E196" t="s">
-        <v>242</v>
+        <v>210</v>
       </c>
       <c r="F196" t="s">
         <v>27</v>
       </c>
       <c r="G196" t="s">
-        <v>241</v>
+        <v>209</v>
       </c>
       <c r="H196" t="s">
         <v>16</v>
@@ -7471,7 +7500,7 @@
         <v>17</v>
       </c>
       <c r="K196">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -7479,22 +7508,22 @@
         <v>11</v>
       </c>
       <c r="B197">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C197">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="D197" t="s">
-        <v>240</v>
+        <v>199</v>
       </c>
       <c r="E197" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="F197" t="s">
         <v>14</v>
       </c>
       <c r="G197" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="H197" t="s">
         <v>16</v>
@@ -7503,7 +7532,7 @@
         <v>17</v>
       </c>
       <c r="K197">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -7511,22 +7540,22 @@
         <v>18</v>
       </c>
       <c r="B198">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C198">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="D198" t="s">
-        <v>239</v>
+        <v>188</v>
       </c>
       <c r="E198" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="F198" t="s">
         <v>14</v>
       </c>
       <c r="G198" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="H198" t="s">
         <v>16</v>
@@ -7535,7 +7564,7 @@
         <v>17</v>
       </c>
       <c r="K198">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
@@ -7543,22 +7572,22 @@
         <v>20</v>
       </c>
       <c r="B199">
-        <v>43</v>
+        <v>31</v>
       </c>
       <c r="C199">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="D199" t="s">
-        <v>238</v>
+        <v>178</v>
       </c>
       <c r="E199" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="F199" t="s">
         <v>14</v>
       </c>
       <c r="G199" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="H199" t="s">
         <v>16</v>
@@ -7567,7 +7596,7 @@
         <v>17</v>
       </c>
       <c r="K199">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -7575,22 +7604,22 @@
         <v>22</v>
       </c>
       <c r="B200">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="C200">
-        <v>45</v>
+        <v>74</v>
       </c>
       <c r="D200" t="s">
-        <v>237</v>
+        <v>198</v>
       </c>
       <c r="E200" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="F200" t="s">
         <v>14</v>
       </c>
       <c r="G200" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="H200" t="s">
         <v>16</v>
@@ -7599,7 +7628,7 @@
         <v>17</v>
       </c>
       <c r="K200">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -7607,7 +7636,7 @@
         <v>24</v>
       </c>
       <c r="B201">
-        <v>320</v>
+        <v>480</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -7616,13 +7645,13 @@
         <v>19</v>
       </c>
       <c r="E201" t="s">
-        <v>236</v>
+        <v>197</v>
       </c>
       <c r="F201" t="s">
         <v>14</v>
       </c>
       <c r="G201" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="H201" t="s">
         <v>16</v>
@@ -7631,7 +7660,7 @@
         <v>17</v>
       </c>
       <c r="K201">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
@@ -7639,22 +7668,22 @@
         <v>11</v>
       </c>
       <c r="B202">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C202">
-        <v>5</v>
+        <v>22</v>
       </c>
       <c r="D202" t="s">
-        <v>235</v>
+        <v>131</v>
       </c>
       <c r="E202" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="F202" t="s">
         <v>27</v>
       </c>
       <c r="G202" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="H202" t="s">
         <v>16</v>
@@ -7663,7 +7692,7 @@
         <v>17</v>
       </c>
       <c r="K202">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -7671,22 +7700,22 @@
         <v>18</v>
       </c>
       <c r="B203">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C203">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>157</v>
+        <v>131</v>
       </c>
       <c r="E203" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="F203" t="s">
         <v>27</v>
       </c>
       <c r="G203" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="H203" t="s">
         <v>16</v>
@@ -7695,7 +7724,7 @@
         <v>17</v>
       </c>
       <c r="K203">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
@@ -7703,22 +7732,22 @@
         <v>20</v>
       </c>
       <c r="B204">
-        <v>64</v>
+        <v>47</v>
       </c>
       <c r="C204">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="D204" t="s">
-        <v>33</v>
+        <v>91</v>
       </c>
       <c r="E204" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="F204" t="s">
         <v>27</v>
       </c>
       <c r="G204" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="H204" t="s">
         <v>16</v>
@@ -7727,7 +7756,7 @@
         <v>17</v>
       </c>
       <c r="K204">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
@@ -7735,22 +7764,22 @@
         <v>22</v>
       </c>
       <c r="B205">
-        <v>36</v>
+        <v>101</v>
       </c>
       <c r="C205">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="D205" t="s">
-        <v>139</v>
+        <v>196</v>
       </c>
       <c r="E205" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="F205" t="s">
         <v>27</v>
       </c>
       <c r="G205" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="H205" t="s">
         <v>16</v>
@@ -7759,7 +7788,7 @@
         <v>17</v>
       </c>
       <c r="K205">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -7767,7 +7796,7 @@
         <v>24</v>
       </c>
       <c r="B206">
-        <v>480</v>
+        <v>720</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -7776,13 +7805,13 @@
         <v>19</v>
       </c>
       <c r="E206" t="s">
-        <v>234</v>
+        <v>195</v>
       </c>
       <c r="F206" t="s">
         <v>27</v>
       </c>
       <c r="G206" t="s">
-        <v>233</v>
+        <v>194</v>
       </c>
       <c r="H206" t="s">
         <v>16</v>
@@ -7791,7 +7820,7 @@
         <v>17</v>
       </c>
       <c r="K206">
-        <v>62</v>
+        <v>81</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
@@ -7799,22 +7828,22 @@
         <v>11</v>
       </c>
       <c r="B207">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C207">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="D207" t="s">
-        <v>232</v>
+        <v>193</v>
       </c>
       <c r="E207" t="s">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="F207" t="s">
         <v>14</v>
       </c>
       <c r="G207" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="H207" t="s">
         <v>16</v>
@@ -7823,7 +7852,7 @@
         <v>17</v>
       </c>
       <c r="K207">
-        <v>79</v>
+        <v>119</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
@@ -7831,22 +7860,22 @@
         <v>18</v>
       </c>
       <c r="B208">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C208">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D208" t="s">
-        <v>86</v>
+        <v>19</v>
       </c>
       <c r="E208" t="s">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="F208" t="s">
         <v>14</v>
       </c>
       <c r="G208" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="H208" t="s">
         <v>16</v>
@@ -7855,7 +7884,7 @@
         <v>17</v>
       </c>
       <c r="K208">
-        <v>79</v>
+        <v>119</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -7863,22 +7892,22 @@
         <v>20</v>
       </c>
       <c r="B209">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C209">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="D209" t="s">
-        <v>149</v>
+        <v>50</v>
       </c>
       <c r="E209" t="s">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="F209" t="s">
         <v>14</v>
       </c>
       <c r="G209" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="H209" t="s">
         <v>16</v>
@@ -7887,7 +7916,7 @@
         <v>17</v>
       </c>
       <c r="K209">
-        <v>79</v>
+        <v>119</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -7895,22 +7924,22 @@
         <v>22</v>
       </c>
       <c r="B210">
-        <v>74</v>
+        <v>37</v>
       </c>
       <c r="C210">
-        <v>64</v>
+        <v>38</v>
       </c>
       <c r="D210" t="s">
-        <v>231</v>
+        <v>109</v>
       </c>
       <c r="E210" t="s">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="F210" t="s">
         <v>14</v>
       </c>
       <c r="G210" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="H210" t="s">
         <v>16</v>
@@ -7919,7 +7948,7 @@
         <v>17</v>
       </c>
       <c r="K210">
-        <v>79</v>
+        <v>119</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -7927,7 +7956,7 @@
         <v>24</v>
       </c>
       <c r="B211">
-        <v>1200</v>
+        <v>480</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -7936,13 +7965,13 @@
         <v>19</v>
       </c>
       <c r="E211" t="s">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="F211" t="s">
         <v>14</v>
       </c>
       <c r="G211" t="s">
-        <v>229</v>
+        <v>189</v>
       </c>
       <c r="H211" t="s">
         <v>16</v>
@@ -7951,7 +7980,7 @@
         <v>17</v>
       </c>
       <c r="K211">
-        <v>79</v>
+        <v>119</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -7959,22 +7988,22 @@
         <v>11</v>
       </c>
       <c r="B212">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C212">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D212" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="E212" t="s">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="F212" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G212" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="H212" t="s">
         <v>16</v>
@@ -7983,7 +8012,7 @@
         <v>17</v>
       </c>
       <c r="K212">
-        <v>76</v>
+        <v>119</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -7991,22 +8020,22 @@
         <v>18</v>
       </c>
       <c r="B213">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C213">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D213" t="s">
-        <v>228</v>
+        <v>19</v>
       </c>
       <c r="E213" t="s">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="F213" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G213" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="H213" t="s">
         <v>16</v>
@@ -8015,7 +8044,7 @@
         <v>17</v>
       </c>
       <c r="K213">
-        <v>76</v>
+        <v>119</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -8023,22 +8052,22 @@
         <v>20</v>
       </c>
       <c r="B214">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="C214">
-        <v>23</v>
+        <v>34</v>
       </c>
       <c r="D214" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="E214" t="s">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="F214" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G214" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="H214" t="s">
         <v>16</v>
@@ -8047,7 +8076,7 @@
         <v>17</v>
       </c>
       <c r="K214">
-        <v>76</v>
+        <v>119</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -8055,22 +8084,22 @@
         <v>22</v>
       </c>
       <c r="B215">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="C215">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="D215" t="s">
-        <v>149</v>
+        <v>50</v>
       </c>
       <c r="E215" t="s">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="F215" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G215" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="H215" t="s">
         <v>16</v>
@@ -8079,7 +8108,7 @@
         <v>17</v>
       </c>
       <c r="K215">
-        <v>76</v>
+        <v>119</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -8087,7 +8116,7 @@
         <v>24</v>
       </c>
       <c r="B216">
-        <v>375</v>
+        <v>720</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -8096,13 +8125,13 @@
         <v>19</v>
       </c>
       <c r="E216" t="s">
-        <v>227</v>
+        <v>190</v>
       </c>
       <c r="F216" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G216" t="s">
-        <v>221</v>
+        <v>189</v>
       </c>
       <c r="H216" t="s">
         <v>16</v>
@@ -8111,7 +8140,7 @@
         <v>17</v>
       </c>
       <c r="K216">
-        <v>76</v>
+        <v>119</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -8119,22 +8148,22 @@
         <v>11</v>
       </c>
       <c r="B217">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C217">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D217" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="E217" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="F217" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G217" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="H217" t="s">
         <v>16</v>
@@ -8143,7 +8172,7 @@
         <v>17</v>
       </c>
       <c r="K217">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -8151,22 +8180,22 @@
         <v>18</v>
       </c>
       <c r="B218">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C218">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="D218" t="s">
-        <v>226</v>
+        <v>19</v>
       </c>
       <c r="E218" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="F218" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G218" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="H218" t="s">
         <v>16</v>
@@ -8175,7 +8204,7 @@
         <v>17</v>
       </c>
       <c r="K218">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -8183,22 +8212,22 @@
         <v>20</v>
       </c>
       <c r="B219">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="C219">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D219" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="E219" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="F219" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G219" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="H219" t="s">
         <v>16</v>
@@ -8207,7 +8236,7 @@
         <v>17</v>
       </c>
       <c r="K219">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -8215,22 +8244,22 @@
         <v>22</v>
       </c>
       <c r="B220">
-        <v>68</v>
+        <v>32</v>
       </c>
       <c r="C220">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="D220" t="s">
-        <v>149</v>
+        <v>256</v>
       </c>
       <c r="E220" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="F220" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G220" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="H220" t="s">
         <v>16</v>
@@ -8239,7 +8268,7 @@
         <v>17</v>
       </c>
       <c r="K220">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -8247,7 +8276,7 @@
         <v>24</v>
       </c>
       <c r="B221">
-        <v>562</v>
+        <v>375</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -8256,13 +8285,13 @@
         <v>19</v>
       </c>
       <c r="E221" t="s">
-        <v>225</v>
+        <v>206</v>
       </c>
       <c r="F221" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G221" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="H221" t="s">
         <v>16</v>
@@ -8271,7 +8300,7 @@
         <v>17</v>
       </c>
       <c r="K221">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
@@ -8279,22 +8308,22 @@
         <v>11</v>
       </c>
       <c r="B222">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C222">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D222" t="s">
-        <v>33</v>
+        <v>205</v>
       </c>
       <c r="E222" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="F222" t="s">
         <v>27</v>
       </c>
       <c r="G222" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="H222" t="s">
         <v>16</v>
@@ -8303,7 +8332,7 @@
         <v>17</v>
       </c>
       <c r="K222">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
@@ -8314,19 +8343,19 @@
         <v>4</v>
       </c>
       <c r="C223">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D223" t="s">
-        <v>131</v>
+        <v>49</v>
       </c>
       <c r="E223" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="F223" t="s">
         <v>27</v>
       </c>
       <c r="G223" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="H223" t="s">
         <v>16</v>
@@ -8335,7 +8364,7 @@
         <v>17</v>
       </c>
       <c r="K223">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -8343,22 +8372,22 @@
         <v>20</v>
       </c>
       <c r="B224">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="C224">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="D224" t="s">
-        <v>224</v>
+        <v>183</v>
       </c>
       <c r="E224" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="F224" t="s">
         <v>27</v>
       </c>
       <c r="G224" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="H224" t="s">
         <v>16</v>
@@ -8367,7 +8396,7 @@
         <v>17</v>
       </c>
       <c r="K224">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
@@ -8375,22 +8404,22 @@
         <v>22</v>
       </c>
       <c r="B225">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C225">
-        <v>43</v>
+        <v>58</v>
       </c>
       <c r="D225" t="s">
-        <v>223</v>
+        <v>81</v>
       </c>
       <c r="E225" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="F225" t="s">
         <v>27</v>
       </c>
       <c r="G225" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="H225" t="s">
         <v>16</v>
@@ -8399,7 +8428,7 @@
         <v>17</v>
       </c>
       <c r="K225">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
@@ -8416,13 +8445,13 @@
         <v>19</v>
       </c>
       <c r="E226" t="s">
-        <v>222</v>
+        <v>203</v>
       </c>
       <c r="F226" t="s">
         <v>27</v>
       </c>
       <c r="G226" t="s">
-        <v>221</v>
+        <v>200</v>
       </c>
       <c r="H226" t="s">
         <v>16</v>
@@ -8431,7 +8460,7 @@
         <v>17</v>
       </c>
       <c r="K226">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
@@ -8439,22 +8468,22 @@
         <v>11</v>
       </c>
       <c r="B227">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C227">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="D227" t="s">
-        <v>220</v>
+        <v>175</v>
       </c>
       <c r="E227" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="F227" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G227" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="H227" t="s">
         <v>16</v>
@@ -8462,8 +8491,11 @@
       <c r="I227" t="s">
         <v>17</v>
       </c>
+      <c r="J227" t="s">
+        <v>255</v>
+      </c>
       <c r="K227">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
@@ -8471,7 +8503,7 @@
         <v>18</v>
       </c>
       <c r="B228">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C228">
         <v>0</v>
@@ -8480,13 +8512,13 @@
         <v>19</v>
       </c>
       <c r="E228" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="F228" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G228" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="H228" t="s">
         <v>16</v>
@@ -8494,8 +8526,11 @@
       <c r="I228" t="s">
         <v>17</v>
       </c>
+      <c r="J228" t="s">
+        <v>254</v>
+      </c>
       <c r="K228">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
@@ -8503,22 +8538,22 @@
         <v>20</v>
       </c>
       <c r="B229">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C229">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D229" t="s">
-        <v>119</v>
+        <v>184</v>
       </c>
       <c r="E229" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="F229" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G229" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="H229" t="s">
         <v>16</v>
@@ -8526,8 +8561,11 @@
       <c r="I229" t="s">
         <v>17</v>
       </c>
+      <c r="J229" t="s">
+        <v>253</v>
+      </c>
       <c r="K229">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
@@ -8535,22 +8573,22 @@
         <v>22</v>
       </c>
       <c r="B230">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="C230">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="D230" t="s">
-        <v>165</v>
+        <v>186</v>
       </c>
       <c r="E230" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="F230" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G230" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="H230" t="s">
         <v>16</v>
@@ -8558,8 +8596,11 @@
       <c r="I230" t="s">
         <v>17</v>
       </c>
+      <c r="J230" t="s">
+        <v>252</v>
+      </c>
       <c r="K230">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
@@ -8567,7 +8608,7 @@
         <v>24</v>
       </c>
       <c r="B231">
-        <v>480</v>
+        <v>562</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -8576,13 +8617,13 @@
         <v>19</v>
       </c>
       <c r="E231" t="s">
-        <v>219</v>
+        <v>201</v>
       </c>
       <c r="F231" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G231" t="s">
-        <v>214</v>
+        <v>200</v>
       </c>
       <c r="H231" t="s">
         <v>16</v>
@@ -8591,7 +8632,7 @@
         <v>17</v>
       </c>
       <c r="K231">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
@@ -8599,22 +8640,22 @@
         <v>11</v>
       </c>
       <c r="B232">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="C232">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="D232" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="E232" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="F232" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G232" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="H232" t="s">
         <v>16</v>
@@ -8623,7 +8664,7 @@
         <v>17</v>
       </c>
       <c r="K232">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
@@ -8634,19 +8675,19 @@
         <v>0</v>
       </c>
       <c r="C233">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D233" t="s">
-        <v>19</v>
+        <v>153</v>
       </c>
       <c r="E233" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="F233" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G233" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="H233" t="s">
         <v>16</v>
@@ -8655,7 +8696,7 @@
         <v>17</v>
       </c>
       <c r="K233">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
@@ -8663,22 +8704,22 @@
         <v>20</v>
       </c>
       <c r="B234">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="C234">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="D234" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="E234" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="F234" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G234" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="H234" t="s">
         <v>16</v>
@@ -8687,7 +8728,7 @@
         <v>17</v>
       </c>
       <c r="K234">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -8695,22 +8736,22 @@
         <v>22</v>
       </c>
       <c r="B235">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="C235">
-        <v>164</v>
+        <v>44</v>
       </c>
       <c r="D235" t="s">
-        <v>216</v>
+        <v>251</v>
       </c>
       <c r="E235" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="F235" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G235" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="H235" t="s">
         <v>16</v>
@@ -8719,7 +8760,7 @@
         <v>17</v>
       </c>
       <c r="K235">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
@@ -8727,7 +8768,7 @@
         <v>24</v>
       </c>
       <c r="B236">
-        <v>720</v>
+        <v>320</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -8736,13 +8777,13 @@
         <v>19</v>
       </c>
       <c r="E236" t="s">
-        <v>215</v>
+        <v>229</v>
       </c>
       <c r="F236" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G236" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="H236" t="s">
         <v>16</v>
@@ -8751,7 +8792,7 @@
         <v>17</v>
       </c>
       <c r="K236">
-        <v>71</v>
+        <v>62</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
@@ -8762,19 +8803,19 @@
         <v>8</v>
       </c>
       <c r="C237">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="D237" t="s">
-        <v>213</v>
+        <v>228</v>
       </c>
       <c r="E237" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="F237" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G237" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="H237" t="s">
         <v>16</v>
@@ -8782,8 +8823,11 @@
       <c r="I237" t="s">
         <v>17</v>
       </c>
+      <c r="J237" t="s">
+        <v>250</v>
+      </c>
       <c r="K237">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
@@ -8791,7 +8835,7 @@
         <v>18</v>
       </c>
       <c r="B238">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -8800,13 +8844,13 @@
         <v>19</v>
       </c>
       <c r="E238" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="F238" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G238" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="H238" t="s">
         <v>16</v>
@@ -8815,7 +8859,7 @@
         <v>17</v>
       </c>
       <c r="K238">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
@@ -8823,22 +8867,22 @@
         <v>20</v>
       </c>
       <c r="B239">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="C239">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D239" t="s">
-        <v>113</v>
+        <v>33</v>
       </c>
       <c r="E239" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="F239" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G239" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="H239" t="s">
         <v>16</v>
@@ -8846,8 +8890,11 @@
       <c r="I239" t="s">
         <v>17</v>
       </c>
+      <c r="J239" t="s">
+        <v>249</v>
+      </c>
       <c r="K239">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
@@ -8855,22 +8902,22 @@
         <v>22</v>
       </c>
       <c r="B240">
+        <v>36</v>
+      </c>
+      <c r="C240">
         <v>32</v>
       </c>
-      <c r="C240">
-        <v>61</v>
-      </c>
       <c r="D240" t="s">
-        <v>212</v>
+        <v>135</v>
       </c>
       <c r="E240" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="F240" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G240" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="H240" t="s">
         <v>16</v>
@@ -8878,8 +8925,11 @@
       <c r="I240" t="s">
         <v>17</v>
       </c>
+      <c r="J240" t="s">
+        <v>248</v>
+      </c>
       <c r="K240">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
@@ -8887,7 +8937,7 @@
         <v>24</v>
       </c>
       <c r="B241">
-        <v>375</v>
+        <v>480</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -8896,13 +8946,13 @@
         <v>19</v>
       </c>
       <c r="E241" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="F241" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G241" t="s">
-        <v>204</v>
+        <v>226</v>
       </c>
       <c r="H241" t="s">
         <v>16</v>
@@ -8911,7 +8961,7 @@
         <v>17</v>
       </c>
       <c r="K241">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -8919,22 +8969,22 @@
         <v>11</v>
       </c>
       <c r="B242">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C242">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D242" t="s">
-        <v>210</v>
+        <v>191</v>
       </c>
       <c r="E242" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="F242" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G242" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="H242" t="s">
         <v>16</v>
@@ -8942,8 +8992,11 @@
       <c r="I242" t="s">
         <v>17</v>
       </c>
+      <c r="J242" t="s">
+        <v>247</v>
+      </c>
       <c r="K242">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -8951,22 +9004,22 @@
         <v>18</v>
       </c>
       <c r="B243">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C243">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D243" t="s">
-        <v>209</v>
+        <v>246</v>
       </c>
       <c r="E243" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="F243" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G243" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="H243" t="s">
         <v>16</v>
@@ -8975,7 +9028,7 @@
         <v>17</v>
       </c>
       <c r="K243">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -8983,22 +9036,22 @@
         <v>20</v>
       </c>
       <c r="B244">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C244">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="D244" t="s">
-        <v>209</v>
+        <v>237</v>
       </c>
       <c r="E244" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="F244" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G244" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="H244" t="s">
         <v>16</v>
@@ -9007,7 +9060,7 @@
         <v>17</v>
       </c>
       <c r="K244">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -9015,22 +9068,22 @@
         <v>22</v>
       </c>
       <c r="B245">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C245">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D245" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="E245" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="F245" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G245" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="H245" t="s">
         <v>16</v>
@@ -9039,7 +9092,7 @@
         <v>17</v>
       </c>
       <c r="K245">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -9047,7 +9100,7 @@
         <v>24</v>
       </c>
       <c r="B246">
-        <v>562</v>
+        <v>375</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -9056,13 +9109,13 @@
         <v>19</v>
       </c>
       <c r="E246" t="s">
-        <v>207</v>
+        <v>221</v>
       </c>
       <c r="F246" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G246" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="H246" t="s">
         <v>16</v>
@@ -9071,7 +9124,7 @@
         <v>17</v>
       </c>
       <c r="K246">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -9079,22 +9132,22 @@
         <v>11</v>
       </c>
       <c r="B247">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="C247">
-        <v>7</v>
+        <v>26</v>
       </c>
       <c r="D247" t="s">
-        <v>179</v>
+        <v>245</v>
       </c>
       <c r="E247" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="F247" t="s">
         <v>27</v>
       </c>
       <c r="G247" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="H247" t="s">
         <v>16</v>
@@ -9103,7 +9156,7 @@
         <v>17</v>
       </c>
       <c r="K247">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -9114,19 +9167,19 @@
         <v>4</v>
       </c>
       <c r="C248">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D248" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="E248" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="F248" t="s">
         <v>27</v>
       </c>
       <c r="G248" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="H248" t="s">
         <v>16</v>
@@ -9135,7 +9188,7 @@
         <v>17</v>
       </c>
       <c r="K248">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -9143,22 +9196,22 @@
         <v>20</v>
       </c>
       <c r="B249">
-        <v>45</v>
+        <v>36</v>
       </c>
       <c r="C249">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="D249" t="s">
-        <v>134</v>
+        <v>42</v>
       </c>
       <c r="E249" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="F249" t="s">
         <v>27</v>
       </c>
       <c r="G249" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="H249" t="s">
         <v>16</v>
@@ -9167,7 +9220,7 @@
         <v>17</v>
       </c>
       <c r="K249">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -9175,22 +9228,22 @@
         <v>22</v>
       </c>
       <c r="B250">
-        <v>47</v>
+        <v>68</v>
       </c>
       <c r="C250">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="D250" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E250" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="F250" t="s">
         <v>27</v>
       </c>
       <c r="G250" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="H250" t="s">
         <v>16</v>
@@ -9199,7 +9252,7 @@
         <v>17</v>
       </c>
       <c r="K250">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -9216,13 +9269,13 @@
         <v>19</v>
       </c>
       <c r="E251" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="F251" t="s">
         <v>27</v>
       </c>
       <c r="G251" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="H251" t="s">
         <v>16</v>
@@ -9231,7 +9284,7 @@
         <v>17</v>
       </c>
       <c r="K251">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -9239,22 +9292,22 @@
         <v>11</v>
       </c>
       <c r="B252">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="C252">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D252" t="s">
-        <v>203</v>
+        <v>33</v>
       </c>
       <c r="E252" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F252" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G252" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="H252" t="s">
         <v>16</v>
@@ -9262,8 +9315,11 @@
       <c r="I252" t="s">
         <v>17</v>
       </c>
+      <c r="J252" t="s">
+        <v>244</v>
+      </c>
       <c r="K252">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -9271,22 +9327,22 @@
         <v>18</v>
       </c>
       <c r="B253">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C253">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D253" t="s">
-        <v>192</v>
+        <v>71</v>
       </c>
       <c r="E253" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F253" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G253" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="H253" t="s">
         <v>16</v>
@@ -9295,7 +9351,7 @@
         <v>17</v>
       </c>
       <c r="K253">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -9303,22 +9359,22 @@
         <v>20</v>
       </c>
       <c r="B254">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C254">
-        <v>31</v>
+        <v>7</v>
       </c>
       <c r="D254" t="s">
-        <v>182</v>
+        <v>219</v>
       </c>
       <c r="E254" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F254" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G254" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="H254" t="s">
         <v>16</v>
@@ -9327,7 +9383,7 @@
         <v>17</v>
       </c>
       <c r="K254">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -9335,22 +9391,22 @@
         <v>22</v>
       </c>
       <c r="B255">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C255">
-        <v>74</v>
+        <v>43</v>
       </c>
       <c r="D255" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="E255" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F255" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G255" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="H255" t="s">
         <v>16</v>
@@ -9359,7 +9415,7 @@
         <v>17</v>
       </c>
       <c r="K255">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -9367,7 +9423,7 @@
         <v>24</v>
       </c>
       <c r="B256">
-        <v>480</v>
+        <v>562</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -9376,13 +9432,13 @@
         <v>19</v>
       </c>
       <c r="E256" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="F256" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G256" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="H256" t="s">
         <v>16</v>
@@ -9391,7 +9447,7 @@
         <v>17</v>
       </c>
       <c r="K256">
-        <v>81</v>
+        <v>76</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -9399,22 +9455,22 @@
         <v>11</v>
       </c>
       <c r="B257">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C257">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="D257" t="s">
-        <v>135</v>
+        <v>83</v>
       </c>
       <c r="E257" t="s">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="F257" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G257" t="s">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="H257" t="s">
         <v>16</v>
@@ -9423,7 +9479,7 @@
         <v>17</v>
       </c>
       <c r="K257">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -9431,22 +9487,22 @@
         <v>18</v>
       </c>
       <c r="B258">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C258">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D258" t="s">
-        <v>135</v>
+        <v>243</v>
       </c>
       <c r="E258" t="s">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="F258" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G258" t="s">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="H258" t="s">
         <v>16</v>
@@ -9455,7 +9511,7 @@
         <v>17</v>
       </c>
       <c r="K258">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -9463,22 +9519,22 @@
         <v>20</v>
       </c>
       <c r="B259">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C259">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D259" t="s">
-        <v>95</v>
+        <v>235</v>
       </c>
       <c r="E259" t="s">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="F259" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G259" t="s">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="H259" t="s">
         <v>16</v>
@@ -9487,7 +9543,7 @@
         <v>17</v>
       </c>
       <c r="K259">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -9495,22 +9551,22 @@
         <v>22</v>
       </c>
       <c r="B260">
-        <v>101</v>
+        <v>38</v>
       </c>
       <c r="C260">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D260" t="s">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="E260" t="s">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="F260" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G260" t="s">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="H260" t="s">
         <v>16</v>
@@ -9519,7 +9575,7 @@
         <v>17</v>
       </c>
       <c r="K260">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
@@ -9527,7 +9583,7 @@
         <v>24</v>
       </c>
       <c r="B261">
-        <v>720</v>
+        <v>375</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -9536,13 +9592,13 @@
         <v>19</v>
       </c>
       <c r="E261" t="s">
-        <v>199</v>
+        <v>79</v>
       </c>
       <c r="F261" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G261" t="s">
-        <v>198</v>
+        <v>75</v>
       </c>
       <c r="H261" t="s">
         <v>16</v>
@@ -9551,7 +9607,7 @@
         <v>17</v>
       </c>
       <c r="K261">
-        <v>81</v>
+        <v>63</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
@@ -9559,22 +9615,22 @@
         <v>11</v>
       </c>
       <c r="B262">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C262">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D262" t="s">
-        <v>197</v>
+        <v>78</v>
       </c>
       <c r="E262" t="s">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="F262" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G262" t="s">
-        <v>193</v>
+        <v>75</v>
       </c>
       <c r="H262" t="s">
         <v>16</v>
@@ -9583,7 +9639,7 @@
         <v>17</v>
       </c>
       <c r="K262">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
@@ -9591,22 +9647,22 @@
         <v>18</v>
       </c>
       <c r="B263">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C263">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D263" t="s">
-        <v>19</v>
+        <v>242</v>
       </c>
       <c r="E263" t="s">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="F263" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G263" t="s">
-        <v>193</v>
+        <v>75</v>
       </c>
       <c r="H263" t="s">
         <v>16</v>
@@ -9615,7 +9671,7 @@
         <v>17</v>
       </c>
       <c r="K263">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
@@ -9623,22 +9679,22 @@
         <v>20</v>
       </c>
       <c r="B264">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C264">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D264" t="s">
-        <v>50</v>
+        <v>149</v>
       </c>
       <c r="E264" t="s">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="F264" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G264" t="s">
-        <v>193</v>
+        <v>75</v>
       </c>
       <c r="H264" t="s">
         <v>16</v>
@@ -9647,7 +9703,7 @@
         <v>17</v>
       </c>
       <c r="K264">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
@@ -9655,22 +9711,22 @@
         <v>22</v>
       </c>
       <c r="B265">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C265">
-        <v>38</v>
+        <v>94</v>
       </c>
       <c r="D265" t="s">
-        <v>113</v>
+        <v>241</v>
       </c>
       <c r="E265" t="s">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="F265" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G265" t="s">
-        <v>193</v>
+        <v>75</v>
       </c>
       <c r="H265" t="s">
         <v>16</v>
@@ -9679,7 +9735,7 @@
         <v>17</v>
       </c>
       <c r="K265">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
@@ -9687,7 +9743,7 @@
         <v>24</v>
       </c>
       <c r="B266">
-        <v>480</v>
+        <v>562</v>
       </c>
       <c r="C266">
         <v>0</v>
@@ -9696,13 +9752,13 @@
         <v>19</v>
       </c>
       <c r="E266" t="s">
-        <v>196</v>
+        <v>77</v>
       </c>
       <c r="F266" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G266" t="s">
-        <v>193</v>
+        <v>75</v>
       </c>
       <c r="H266" t="s">
         <v>16</v>
@@ -9711,7 +9767,7 @@
         <v>17</v>
       </c>
       <c r="K266">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
@@ -9719,22 +9775,22 @@
         <v>11</v>
       </c>
       <c r="B267">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C267">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="D267" t="s">
-        <v>195</v>
+        <v>127</v>
       </c>
       <c r="E267" t="s">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="F267" t="s">
         <v>27</v>
       </c>
       <c r="G267" t="s">
-        <v>193</v>
+        <v>75</v>
       </c>
       <c r="H267" t="s">
         <v>16</v>
@@ -9742,8 +9798,11 @@
       <c r="I267" t="s">
         <v>17</v>
       </c>
+      <c r="J267" t="s">
+        <v>240</v>
+      </c>
       <c r="K267">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
@@ -9751,7 +9810,7 @@
         <v>18</v>
       </c>
       <c r="B268">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C268">
         <v>0</v>
@@ -9760,13 +9819,13 @@
         <v>19</v>
       </c>
       <c r="E268" t="s">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="F268" t="s">
         <v>27</v>
       </c>
       <c r="G268" t="s">
-        <v>193</v>
+        <v>75</v>
       </c>
       <c r="H268" t="s">
         <v>16</v>
@@ -9775,7 +9834,7 @@
         <v>17</v>
       </c>
       <c r="K268">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
@@ -9783,22 +9842,22 @@
         <v>20</v>
       </c>
       <c r="B269">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="C269">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="D269" t="s">
-        <v>145</v>
+        <v>239</v>
       </c>
       <c r="E269" t="s">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="F269" t="s">
         <v>27</v>
       </c>
       <c r="G269" t="s">
-        <v>193</v>
+        <v>75</v>
       </c>
       <c r="H269" t="s">
         <v>16</v>
@@ -9807,7 +9866,7 @@
         <v>17</v>
       </c>
       <c r="K269">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
@@ -9815,22 +9874,22 @@
         <v>22</v>
       </c>
       <c r="B270">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C270">
-        <v>69</v>
+        <v>22</v>
       </c>
       <c r="D270" t="s">
-        <v>50</v>
+        <v>238</v>
       </c>
       <c r="E270" t="s">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="F270" t="s">
         <v>27</v>
       </c>
       <c r="G270" t="s">
-        <v>193</v>
+        <v>75</v>
       </c>
       <c r="H270" t="s">
         <v>16</v>
@@ -9839,7 +9898,7 @@
         <v>17</v>
       </c>
       <c r="K270">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
@@ -9847,7 +9906,7 @@
         <v>24</v>
       </c>
       <c r="B271">
-        <v>720</v>
+        <v>562</v>
       </c>
       <c r="C271">
         <v>0</v>
@@ -9856,13 +9915,13 @@
         <v>19</v>
       </c>
       <c r="E271" t="s">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="F271" t="s">
         <v>27</v>
       </c>
       <c r="G271" t="s">
-        <v>193</v>
+        <v>75</v>
       </c>
       <c r="H271" t="s">
         <v>16</v>
@@ -9871,7 +9930,7 @@
         <v>17</v>
       </c>
       <c r="K271">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/02 Febrero/Liquidacióncvs - liquidación/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="11_37DD5EEF9561BE0E62355476585DCE3A8747A48A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4779DC04-4745-473F-975B-84614F994CC6}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_37DD5EEF9561BE0E62355476585DCE3A8747A48A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BEC9DE7-4DD9-4128-B18B-C0CEE17D8E03}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1933" uniqueCount="257">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="259">
   <si>
     <t>Producto</t>
   </si>
@@ -364,24 +364,15 @@
     <t>Jeider Alberto Moreno Solano</t>
   </si>
   <si>
-    <t>162%</t>
-  </si>
-  <si>
     <t>74%</t>
   </si>
   <si>
-    <t>1504%</t>
-  </si>
-  <si>
     <t>242%</t>
   </si>
   <si>
     <t>Dayanis  Celsa Gamarra</t>
   </si>
   <si>
-    <t>126%</t>
-  </si>
-  <si>
     <t>94%</t>
   </si>
   <si>
@@ -397,9 +388,6 @@
     <t>Lider  Bagre</t>
   </si>
   <si>
-    <t>11%</t>
-  </si>
-  <si>
     <t>5%</t>
   </si>
   <si>
@@ -442,9 +430,6 @@
     <t>Bibiana Farley Rios Agudelo</t>
   </si>
   <si>
-    <t>82%</t>
-  </si>
-  <si>
     <t>60%</t>
   </si>
   <si>
@@ -463,12 +448,6 @@
     <t>LÃ­der Sandra Milena Jaramillo HolguÃ­n</t>
   </si>
   <si>
-    <t>55%</t>
-  </si>
-  <si>
-    <t>360%</t>
-  </si>
-  <si>
     <t>111%</t>
   </si>
   <si>
@@ -791,6 +770,33 @@
   </si>
   <si>
     <t>206%</t>
+  </si>
+  <si>
+    <t>121%</t>
+  </si>
+  <si>
+    <t>67%</t>
+  </si>
+  <si>
+    <t>160%</t>
+  </si>
+  <si>
+    <t>376%</t>
+  </si>
+  <si>
+    <t>78%</t>
+  </si>
+  <si>
+    <t>9%</t>
+  </si>
+  <si>
+    <t>vac del 23 de febrero al 11 de marzo</t>
+  </si>
+  <si>
+    <t>Reemplaza vac cajera 15 días y sale vacaciones el 23 elabora 3 días</t>
+  </si>
+  <si>
+    <t>12%</t>
   </si>
 </sst>
 </file>
@@ -1211,13 +1217,13 @@
         <v>57</v>
       </c>
       <c r="E2" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F2" t="s">
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
@@ -1240,16 +1246,16 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="E3" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
@@ -1272,16 +1278,16 @@
         <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="E4" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -1304,16 +1310,16 @@
         <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="E5" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
@@ -1339,13 +1345,13 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>185</v>
+        <v>178</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -1368,16 +1374,16 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>184</v>
+        <v>177</v>
       </c>
       <c r="E7" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F7" t="s">
         <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
@@ -1400,16 +1406,16 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>149</v>
+        <v>142</v>
       </c>
       <c r="E8" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F8" t="s">
         <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -1432,16 +1438,16 @@
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="E9" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F9" t="s">
         <v>27</v>
       </c>
       <c r="G9" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
@@ -1467,13 +1473,13 @@
         <v>31</v>
       </c>
       <c r="E10" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F10" t="s">
         <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -1499,13 +1505,13 @@
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="F11" t="s">
         <v>27</v>
       </c>
       <c r="G11" t="s">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -1528,16 +1534,16 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>180</v>
+        <v>173</v>
       </c>
       <c r="E12" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -1560,16 +1566,16 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
       <c r="E13" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -1595,13 +1601,13 @@
         <v>91</v>
       </c>
       <c r="E14" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -1624,16 +1630,16 @@
         <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>178</v>
+        <v>171</v>
       </c>
       <c r="E15" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -1659,13 +1665,13 @@
         <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>177</v>
+        <v>170</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
@@ -1688,16 +1694,16 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E17" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F17" t="s">
         <v>27</v>
       </c>
       <c r="G17" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
@@ -1720,16 +1726,16 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="E18" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F18" t="s">
         <v>27</v>
       </c>
       <c r="G18" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
@@ -1752,16 +1758,16 @@
         <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="E19" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F19" t="s">
         <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
@@ -1787,13 +1793,13 @@
         <v>52</v>
       </c>
       <c r="E20" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F20" t="s">
         <v>27</v>
       </c>
       <c r="G20" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -1819,13 +1825,13 @@
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="F21" t="s">
         <v>27</v>
       </c>
       <c r="G21" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
@@ -1851,13 +1857,13 @@
         <v>87</v>
       </c>
       <c r="E22" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F22" t="s">
         <v>27</v>
       </c>
       <c r="G22" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
@@ -1880,16 +1886,16 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="E23" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F23" t="s">
         <v>27</v>
       </c>
       <c r="G23" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
@@ -1912,16 +1918,16 @@
         <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>172</v>
+        <v>165</v>
       </c>
       <c r="E24" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F24" t="s">
         <v>27</v>
       </c>
       <c r="G24" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
@@ -1947,13 +1953,13 @@
         <v>109</v>
       </c>
       <c r="E25" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F25" t="s">
         <v>27</v>
       </c>
       <c r="G25" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -1979,13 +1985,13 @@
         <v>19</v>
       </c>
       <c r="E26" t="s">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="F26" t="s">
         <v>27</v>
       </c>
       <c r="G26" t="s">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -2011,13 +2017,13 @@
         <v>81</v>
       </c>
       <c r="E27" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -2043,13 +2049,13 @@
         <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -2072,16 +2078,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="E29" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -2104,16 +2110,16 @@
         <v>56</v>
       </c>
       <c r="D30" t="s">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="E30" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -2139,13 +2145,13 @@
         <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>168</v>
+        <v>161</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -2168,16 +2174,16 @@
         <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>167</v>
+        <v>160</v>
       </c>
       <c r="E32" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F32" t="s">
         <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -2200,16 +2206,16 @@
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="E33" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F33" t="s">
         <v>27</v>
       </c>
       <c r="G33" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -2235,13 +2241,13 @@
         <v>52</v>
       </c>
       <c r="E34" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F34" t="s">
         <v>27</v>
       </c>
       <c r="G34" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -2264,16 +2270,16 @@
         <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="E35" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F35" t="s">
         <v>27</v>
       </c>
       <c r="G35" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -2299,13 +2305,13 @@
         <v>19</v>
       </c>
       <c r="E36" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F36" t="s">
         <v>27</v>
       </c>
       <c r="G36" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -2328,16 +2334,16 @@
         <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="E37" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F37" t="s">
         <v>27</v>
       </c>
       <c r="G37" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -2360,16 +2366,16 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="E38" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F38" t="s">
         <v>27</v>
       </c>
       <c r="G38" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -2392,16 +2398,16 @@
         <v>42</v>
       </c>
       <c r="D39" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="E39" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F39" t="s">
         <v>27</v>
       </c>
       <c r="G39" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
@@ -2424,16 +2430,16 @@
         <v>63</v>
       </c>
       <c r="D40" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="E40" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F40" t="s">
         <v>27</v>
       </c>
       <c r="G40" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -2459,13 +2465,13 @@
         <v>19</v>
       </c>
       <c r="E41" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="F41" t="s">
         <v>27</v>
       </c>
       <c r="G41" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
@@ -2488,16 +2494,16 @@
         <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="E42" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
@@ -2523,13 +2529,13 @@
         <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
@@ -2555,13 +2561,13 @@
         <v>37</v>
       </c>
       <c r="E44" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
@@ -2584,16 +2590,16 @@
         <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="E45" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
@@ -2619,13 +2625,13 @@
         <v>19</v>
       </c>
       <c r="E46" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
@@ -2651,13 +2657,13 @@
         <v>52</v>
       </c>
       <c r="E47" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
@@ -2680,16 +2686,16 @@
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E48" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
@@ -2715,13 +2721,13 @@
         <v>44</v>
       </c>
       <c r="E49" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F49" t="s">
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
@@ -2744,16 +2750,16 @@
         <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E50" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F50" t="s">
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H50" t="s">
         <v>16</v>
@@ -2779,13 +2785,13 @@
         <v>19</v>
       </c>
       <c r="E51" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H51" t="s">
         <v>16</v>
@@ -2811,13 +2817,13 @@
         <v>31</v>
       </c>
       <c r="E52" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F52" t="s">
         <v>27</v>
       </c>
       <c r="G52" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H52" t="s">
         <v>16</v>
@@ -2840,16 +2846,16 @@
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="E53" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F53" t="s">
         <v>27</v>
       </c>
       <c r="G53" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H53" t="s">
         <v>16</v>
@@ -2875,13 +2881,13 @@
         <v>45</v>
       </c>
       <c r="E54" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F54" t="s">
         <v>27</v>
       </c>
       <c r="G54" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
@@ -2904,16 +2910,16 @@
         <v>79</v>
       </c>
       <c r="D55" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="E55" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F55" t="s">
         <v>27</v>
       </c>
       <c r="G55" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H55" t="s">
         <v>16</v>
@@ -2939,13 +2945,13 @@
         <v>19</v>
       </c>
       <c r="E56" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="F56" t="s">
         <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="H56" t="s">
         <v>16</v>
@@ -2962,22 +2968,22 @@
         <v>11</v>
       </c>
       <c r="B57">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="C57">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="D57" t="s">
-        <v>149</v>
+        <v>33</v>
       </c>
       <c r="E57" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="F57" t="s">
         <v>14</v>
       </c>
       <c r="G57" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="H57" t="s">
         <v>16</v>
@@ -2985,8 +2991,11 @@
       <c r="I57" t="s">
         <v>17</v>
       </c>
+      <c r="J57" t="s">
+        <v>36</v>
+      </c>
       <c r="K57">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.25">
@@ -2994,22 +3003,22 @@
         <v>18</v>
       </c>
       <c r="B58">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C58">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="D58" t="s">
-        <v>148</v>
+        <v>19</v>
       </c>
       <c r="E58" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="F58" t="s">
         <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="H58" t="s">
         <v>16</v>
@@ -3018,7 +3027,7 @@
         <v>17</v>
       </c>
       <c r="K58">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.25">
@@ -3026,22 +3035,22 @@
         <v>20</v>
       </c>
       <c r="B59">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C59">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="D59" t="s">
-        <v>147</v>
+        <v>37</v>
       </c>
       <c r="E59" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="F59" t="s">
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -3049,8 +3058,11 @@
       <c r="I59" t="s">
         <v>17</v>
       </c>
+      <c r="J59" t="s">
+        <v>38</v>
+      </c>
       <c r="K59">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.25">
@@ -3058,22 +3070,22 @@
         <v>22</v>
       </c>
       <c r="B60">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C60">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>107</v>
+        <v>39</v>
       </c>
       <c r="E60" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="F60" t="s">
         <v>14</v>
       </c>
       <c r="G60" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="H60" t="s">
         <v>16</v>
@@ -3081,8 +3093,11 @@
       <c r="I60" t="s">
         <v>17</v>
       </c>
+      <c r="J60" t="s">
+        <v>40</v>
+      </c>
       <c r="K60">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.25">
@@ -3090,7 +3105,7 @@
         <v>24</v>
       </c>
       <c r="B61">
-        <v>375</v>
+        <v>480</v>
       </c>
       <c r="C61">
         <v>0</v>
@@ -3099,13 +3114,13 @@
         <v>19</v>
       </c>
       <c r="E61" t="s">
-        <v>146</v>
+        <v>34</v>
       </c>
       <c r="F61" t="s">
         <v>14</v>
       </c>
       <c r="G61" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="H61" t="s">
         <v>16</v>
@@ -3113,8 +3128,11 @@
       <c r="I61" t="s">
         <v>17</v>
       </c>
+      <c r="J61" t="s">
+        <v>41</v>
+      </c>
       <c r="K61">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.25">
@@ -3122,22 +3140,22 @@
         <v>11</v>
       </c>
       <c r="B62">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C62">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
       <c r="E62" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="F62" t="s">
         <v>27</v>
       </c>
       <c r="G62" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="H62" t="s">
         <v>16</v>
@@ -3146,7 +3164,7 @@
         <v>17</v>
       </c>
       <c r="K62">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.25">
@@ -3154,22 +3172,22 @@
         <v>18</v>
       </c>
       <c r="B63">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C63">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D63" t="s">
-        <v>142</v>
+        <v>19</v>
       </c>
       <c r="E63" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="F63" t="s">
         <v>27</v>
       </c>
       <c r="G63" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="H63" t="s">
         <v>16</v>
@@ -3178,7 +3196,7 @@
         <v>17</v>
       </c>
       <c r="K63">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
@@ -3186,22 +3204,22 @@
         <v>20</v>
       </c>
       <c r="B64">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="C64">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="D64" t="s">
-        <v>123</v>
+        <v>44</v>
       </c>
       <c r="E64" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="F64" t="s">
         <v>27</v>
       </c>
       <c r="G64" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="H64" t="s">
         <v>16</v>
@@ -3210,7 +3228,7 @@
         <v>17</v>
       </c>
       <c r="K64">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -3218,22 +3236,22 @@
         <v>22</v>
       </c>
       <c r="B65">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="C65">
-        <v>62</v>
+        <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>145</v>
+        <v>45</v>
       </c>
       <c r="E65" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="F65" t="s">
         <v>27</v>
       </c>
       <c r="G65" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="H65" t="s">
         <v>16</v>
@@ -3242,7 +3260,7 @@
         <v>17</v>
       </c>
       <c r="K65">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -3250,7 +3268,7 @@
         <v>24</v>
       </c>
       <c r="B66">
-        <v>562</v>
+        <v>720</v>
       </c>
       <c r="C66">
         <v>0</v>
@@ -3259,13 +3277,13 @@
         <v>19</v>
       </c>
       <c r="E66" t="s">
-        <v>144</v>
+        <v>43</v>
       </c>
       <c r="F66" t="s">
         <v>27</v>
       </c>
       <c r="G66" t="s">
-        <v>138</v>
+        <v>35</v>
       </c>
       <c r="H66" t="s">
         <v>16</v>
@@ -3274,7 +3292,7 @@
         <v>17</v>
       </c>
       <c r="K66">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -3282,22 +3300,22 @@
         <v>11</v>
       </c>
       <c r="B67">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C67">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="D67" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E67" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F67" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G67" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="H67" t="s">
         <v>16</v>
@@ -3306,7 +3324,7 @@
         <v>17</v>
       </c>
       <c r="K67">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -3314,22 +3332,22 @@
         <v>18</v>
       </c>
       <c r="B68">
+        <v>0</v>
+      </c>
+      <c r="C68">
         <v>4</v>
       </c>
-      <c r="C68">
-        <v>5</v>
-      </c>
       <c r="D68" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="E68" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F68" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G68" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="H68" t="s">
         <v>16</v>
@@ -3338,7 +3356,7 @@
         <v>17</v>
       </c>
       <c r="K68">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -3346,22 +3364,22 @@
         <v>20</v>
       </c>
       <c r="B69">
-        <v>46</v>
+        <v>24</v>
       </c>
       <c r="C69">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="D69" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="E69" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F69" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G69" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="H69" t="s">
         <v>16</v>
@@ -3370,7 +3388,7 @@
         <v>17</v>
       </c>
       <c r="K69">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.25">
@@ -3378,22 +3396,22 @@
         <v>22</v>
       </c>
       <c r="B70">
-        <v>55</v>
+        <v>27</v>
       </c>
       <c r="C70">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="D70" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="E70" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F70" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G70" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="H70" t="s">
         <v>16</v>
@@ -3402,7 +3420,7 @@
         <v>17</v>
       </c>
       <c r="K70">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.25">
@@ -3410,7 +3428,7 @@
         <v>24</v>
       </c>
       <c r="B71">
-        <v>562</v>
+        <v>480</v>
       </c>
       <c r="C71">
         <v>0</v>
@@ -3419,13 +3437,13 @@
         <v>19</v>
       </c>
       <c r="E71" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="F71" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G71" t="s">
-        <v>138</v>
+        <v>124</v>
       </c>
       <c r="H71" t="s">
         <v>16</v>
@@ -3434,7 +3452,7 @@
         <v>17</v>
       </c>
       <c r="K71">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="72" spans="1:11" x14ac:dyDescent="0.25">
@@ -3442,22 +3460,22 @@
         <v>11</v>
       </c>
       <c r="B72">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="C72">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="D72" t="s">
-        <v>33</v>
+        <v>128</v>
       </c>
       <c r="E72" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="F72" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G72" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="H72" t="s">
         <v>16</v>
@@ -3465,11 +3483,8 @@
       <c r="I72" t="s">
         <v>17</v>
       </c>
-      <c r="J72" t="s">
-        <v>36</v>
-      </c>
       <c r="K72">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="73" spans="1:11" x14ac:dyDescent="0.25">
@@ -3477,22 +3492,22 @@
         <v>18</v>
       </c>
       <c r="B73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C73">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D73" t="s">
-        <v>19</v>
+        <v>127</v>
       </c>
       <c r="E73" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="F73" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G73" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="H73" t="s">
         <v>16</v>
@@ -3501,7 +3516,7 @@
         <v>17</v>
       </c>
       <c r="K73">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="74" spans="1:11" x14ac:dyDescent="0.25">
@@ -3509,22 +3524,22 @@
         <v>20</v>
       </c>
       <c r="B74">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C74">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
       <c r="E74" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="F74" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G74" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="H74" t="s">
         <v>16</v>
@@ -3532,11 +3547,8 @@
       <c r="I74" t="s">
         <v>17</v>
       </c>
-      <c r="J74" t="s">
-        <v>38</v>
-      </c>
       <c r="K74">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="75" spans="1:11" x14ac:dyDescent="0.25">
@@ -3544,22 +3556,22 @@
         <v>22</v>
       </c>
       <c r="B75">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="C75">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="D75" t="s">
-        <v>39</v>
+        <v>86</v>
       </c>
       <c r="E75" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="F75" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G75" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="H75" t="s">
         <v>16</v>
@@ -3567,11 +3579,8 @@
       <c r="I75" t="s">
         <v>17</v>
       </c>
-      <c r="J75" t="s">
-        <v>40</v>
-      </c>
       <c r="K75">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.25">
@@ -3579,7 +3588,7 @@
         <v>24</v>
       </c>
       <c r="B76">
-        <v>480</v>
+        <v>720</v>
       </c>
       <c r="C76">
         <v>0</v>
@@ -3588,13 +3597,13 @@
         <v>19</v>
       </c>
       <c r="E76" t="s">
-        <v>34</v>
+        <v>125</v>
       </c>
       <c r="F76" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G76" t="s">
-        <v>35</v>
+        <v>124</v>
       </c>
       <c r="H76" t="s">
         <v>16</v>
@@ -3602,11 +3611,8 @@
       <c r="I76" t="s">
         <v>17</v>
       </c>
-      <c r="J76" t="s">
-        <v>41</v>
-      </c>
       <c r="K76">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="77" spans="1:11" x14ac:dyDescent="0.25">
@@ -3614,22 +3620,22 @@
         <v>11</v>
       </c>
       <c r="B77">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="C77">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="D77" t="s">
-        <v>42</v>
+        <v>81</v>
       </c>
       <c r="E77" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="F77" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G77" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="H77" t="s">
         <v>16</v>
@@ -3638,7 +3644,7 @@
         <v>17</v>
       </c>
       <c r="K77">
-        <v>58</v>
+        <v>80</v>
       </c>
     </row>
     <row r="78" spans="1:11" x14ac:dyDescent="0.25">
@@ -3646,22 +3652,22 @@
         <v>18</v>
       </c>
       <c r="B78">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C78">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="D78" t="s">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="E78" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="F78" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G78" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="H78" t="s">
         <v>16</v>
@@ -3670,7 +3676,7 @@
         <v>17</v>
       </c>
       <c r="K78">
-        <v>58</v>
+        <v>80</v>
       </c>
     </row>
     <row r="79" spans="1:11" x14ac:dyDescent="0.25">
@@ -3678,22 +3684,22 @@
         <v>20</v>
       </c>
       <c r="B79">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="C79">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="D79" t="s">
-        <v>44</v>
+        <v>21</v>
       </c>
       <c r="E79" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="F79" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G79" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="H79" t="s">
         <v>16</v>
@@ -3702,7 +3708,7 @@
         <v>17</v>
       </c>
       <c r="K79">
-        <v>58</v>
+        <v>80</v>
       </c>
     </row>
     <row r="80" spans="1:11" x14ac:dyDescent="0.25">
@@ -3710,22 +3716,22 @@
         <v>22</v>
       </c>
       <c r="B80">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="C80">
-        <v>27</v>
+        <v>63</v>
       </c>
       <c r="D80" t="s">
-        <v>45</v>
+        <v>23</v>
       </c>
       <c r="E80" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="F80" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G80" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="H80" t="s">
         <v>16</v>
@@ -3734,7 +3740,7 @@
         <v>17</v>
       </c>
       <c r="K80">
-        <v>58</v>
+        <v>80</v>
       </c>
     </row>
     <row r="81" spans="1:11" x14ac:dyDescent="0.25">
@@ -3742,7 +3748,7 @@
         <v>24</v>
       </c>
       <c r="B81">
-        <v>720</v>
+        <v>375</v>
       </c>
       <c r="C81">
         <v>0</v>
@@ -3751,13 +3757,13 @@
         <v>19</v>
       </c>
       <c r="E81" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="F81" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G81" t="s">
-        <v>35</v>
+        <v>98</v>
       </c>
       <c r="H81" t="s">
         <v>16</v>
@@ -3766,7 +3772,7 @@
         <v>17</v>
       </c>
       <c r="K81">
-        <v>58</v>
+        <v>80</v>
       </c>
     </row>
     <row r="82" spans="1:11" x14ac:dyDescent="0.25">
@@ -3774,22 +3780,22 @@
         <v>11</v>
       </c>
       <c r="B82">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="C82">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="D82" t="s">
-        <v>137</v>
+        <v>109</v>
       </c>
       <c r="E82" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="F82" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G82" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="H82" t="s">
         <v>16</v>
@@ -3798,7 +3804,7 @@
         <v>17</v>
       </c>
       <c r="K82">
-        <v>48</v>
+        <v>80</v>
       </c>
     </row>
     <row r="83" spans="1:11" x14ac:dyDescent="0.25">
@@ -3806,22 +3812,22 @@
         <v>18</v>
       </c>
       <c r="B83">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="C83">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="D83" t="s">
-        <v>136</v>
+        <v>108</v>
       </c>
       <c r="E83" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="F83" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G83" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="H83" t="s">
         <v>16</v>
@@ -3830,7 +3836,7 @@
         <v>17</v>
       </c>
       <c r="K83">
-        <v>48</v>
+        <v>80</v>
       </c>
     </row>
     <row r="84" spans="1:11" x14ac:dyDescent="0.25">
@@ -3838,22 +3844,22 @@
         <v>20</v>
       </c>
       <c r="B84">
-        <v>24</v>
+        <v>47</v>
       </c>
       <c r="C84">
-        <v>21</v>
+        <v>40</v>
       </c>
       <c r="D84" t="s">
-        <v>135</v>
+        <v>107</v>
       </c>
       <c r="E84" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="F84" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G84" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="H84" t="s">
         <v>16</v>
@@ -3862,7 +3868,7 @@
         <v>17</v>
       </c>
       <c r="K84">
-        <v>48</v>
+        <v>80</v>
       </c>
     </row>
     <row r="85" spans="1:11" x14ac:dyDescent="0.25">
@@ -3870,22 +3876,22 @@
         <v>22</v>
       </c>
       <c r="B85">
-        <v>27</v>
+        <v>74</v>
       </c>
       <c r="C85">
-        <v>51</v>
+        <v>94</v>
       </c>
       <c r="D85" t="s">
-        <v>134</v>
+        <v>23</v>
       </c>
       <c r="E85" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="F85" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G85" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="H85" t="s">
         <v>16</v>
@@ -3894,7 +3900,7 @@
         <v>17</v>
       </c>
       <c r="K85">
-        <v>48</v>
+        <v>80</v>
       </c>
     </row>
     <row r="86" spans="1:11" x14ac:dyDescent="0.25">
@@ -3902,7 +3908,7 @@
         <v>24</v>
       </c>
       <c r="B86">
-        <v>480</v>
+        <v>562</v>
       </c>
       <c r="C86">
         <v>0</v>
@@ -3911,13 +3917,13 @@
         <v>19</v>
       </c>
       <c r="E86" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="F86" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G86" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="H86" t="s">
         <v>16</v>
@@ -3926,7 +3932,7 @@
         <v>17</v>
       </c>
       <c r="K86">
-        <v>48</v>
+        <v>80</v>
       </c>
     </row>
     <row r="87" spans="1:11" x14ac:dyDescent="0.25">
@@ -3934,22 +3940,22 @@
         <v>11</v>
       </c>
       <c r="B87">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C87">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="D87" t="s">
-        <v>132</v>
+        <v>81</v>
       </c>
       <c r="E87" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="F87" t="s">
         <v>27</v>
       </c>
       <c r="G87" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="H87" t="s">
         <v>16</v>
@@ -3957,8 +3963,11 @@
       <c r="I87" t="s">
         <v>17</v>
       </c>
+      <c r="J87" t="s">
+        <v>105</v>
+      </c>
       <c r="K87">
-        <v>48</v>
+        <v>80</v>
       </c>
     </row>
     <row r="88" spans="1:11" x14ac:dyDescent="0.25">
@@ -3966,22 +3975,22 @@
         <v>18</v>
       </c>
       <c r="B88">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="C88">
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="E88" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="F88" t="s">
         <v>27</v>
       </c>
       <c r="G88" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="H88" t="s">
         <v>16</v>
@@ -3989,8 +3998,11 @@
       <c r="I88" t="s">
         <v>17</v>
       </c>
+      <c r="J88" t="s">
+        <v>103</v>
+      </c>
       <c r="K88">
-        <v>48</v>
+        <v>80</v>
       </c>
     </row>
     <row r="89" spans="1:11" x14ac:dyDescent="0.25">
@@ -3998,22 +4010,22 @@
         <v>20</v>
       </c>
       <c r="B89">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C89">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="D89" t="s">
-        <v>130</v>
+        <v>102</v>
       </c>
       <c r="E89" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="F89" t="s">
         <v>27</v>
       </c>
       <c r="G89" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="H89" t="s">
         <v>16</v>
@@ -4021,8 +4033,11 @@
       <c r="I89" t="s">
         <v>17</v>
       </c>
+      <c r="J89" t="s">
+        <v>101</v>
+      </c>
       <c r="K89">
-        <v>48</v>
+        <v>80</v>
       </c>
     </row>
     <row r="90" spans="1:11" x14ac:dyDescent="0.25">
@@ -4030,22 +4045,22 @@
         <v>22</v>
       </c>
       <c r="B90">
-        <v>41</v>
+        <v>74</v>
       </c>
       <c r="C90">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="D90" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="E90" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="F90" t="s">
         <v>27</v>
       </c>
       <c r="G90" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="H90" t="s">
         <v>16</v>
@@ -4054,7 +4069,7 @@
         <v>17</v>
       </c>
       <c r="K90">
-        <v>48</v>
+        <v>80</v>
       </c>
     </row>
     <row r="91" spans="1:11" x14ac:dyDescent="0.25">
@@ -4062,7 +4077,7 @@
         <v>24</v>
       </c>
       <c r="B91">
-        <v>720</v>
+        <v>562</v>
       </c>
       <c r="C91">
         <v>0</v>
@@ -4071,13 +4086,13 @@
         <v>19</v>
       </c>
       <c r="E91" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="F91" t="s">
         <v>27</v>
       </c>
       <c r="G91" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
       <c r="H91" t="s">
         <v>16</v>
@@ -4085,8 +4100,11 @@
       <c r="I91" t="s">
         <v>17</v>
       </c>
+      <c r="J91" t="s">
+        <v>97</v>
+      </c>
       <c r="K91">
-        <v>48</v>
+        <v>80</v>
       </c>
     </row>
     <row r="92" spans="1:11" x14ac:dyDescent="0.25">
@@ -4094,22 +4112,22 @@
         <v>11</v>
       </c>
       <c r="B92">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="C92">
-        <v>2</v>
+        <v>14</v>
       </c>
       <c r="D92" t="s">
-        <v>127</v>
+        <v>12</v>
       </c>
       <c r="E92" t="s">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="F92" t="s">
         <v>14</v>
       </c>
       <c r="G92" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="H92" t="s">
         <v>16</v>
@@ -4118,7 +4136,7 @@
         <v>17</v>
       </c>
       <c r="K92">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -4135,13 +4153,13 @@
         <v>19</v>
       </c>
       <c r="E93" t="s">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="F93" t="s">
         <v>14</v>
       </c>
       <c r="G93" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="H93" t="s">
         <v>16</v>
@@ -4150,7 +4168,7 @@
         <v>17</v>
       </c>
       <c r="K93">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -4158,22 +4176,22 @@
         <v>20</v>
       </c>
       <c r="B94">
-        <v>42</v>
+        <v>91</v>
       </c>
       <c r="C94">
-        <v>2</v>
+        <v>82</v>
       </c>
       <c r="D94" t="s">
-        <v>126</v>
+        <v>21</v>
       </c>
       <c r="E94" t="s">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="F94" t="s">
         <v>14</v>
       </c>
       <c r="G94" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="H94" t="s">
         <v>16</v>
@@ -4182,7 +4200,7 @@
         <v>17</v>
       </c>
       <c r="K94">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -4190,22 +4208,22 @@
         <v>22</v>
       </c>
       <c r="B95">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="C95">
-        <v>4</v>
+        <v>62</v>
       </c>
       <c r="D95" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="E95" t="s">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="F95" t="s">
         <v>14</v>
       </c>
       <c r="G95" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="H95" t="s">
         <v>16</v>
@@ -4214,7 +4232,7 @@
         <v>17</v>
       </c>
       <c r="K95">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -4222,7 +4240,7 @@
         <v>24</v>
       </c>
       <c r="B96">
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -4231,13 +4249,13 @@
         <v>19</v>
       </c>
       <c r="E96" t="s">
-        <v>124</v>
+        <v>13</v>
       </c>
       <c r="F96" t="s">
         <v>14</v>
       </c>
       <c r="G96" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="H96" t="s">
         <v>16</v>
@@ -4245,8 +4263,11 @@
       <c r="I96" t="s">
         <v>17</v>
       </c>
+      <c r="J96" t="s">
+        <v>25</v>
+      </c>
       <c r="K96">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -4254,22 +4275,22 @@
         <v>11</v>
       </c>
       <c r="B97">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C97">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D97" t="s">
-        <v>59</v>
+        <v>12</v>
       </c>
       <c r="E97" t="s">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="F97" t="s">
         <v>27</v>
       </c>
       <c r="G97" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="H97" t="s">
         <v>16</v>
@@ -4277,8 +4298,11 @@
       <c r="I97" t="s">
         <v>17</v>
       </c>
+      <c r="J97" t="s">
+        <v>28</v>
+      </c>
       <c r="K97">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -4295,13 +4319,13 @@
         <v>19</v>
       </c>
       <c r="E98" t="s">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="F98" t="s">
         <v>27</v>
       </c>
       <c r="G98" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="H98" t="s">
         <v>16</v>
@@ -4310,7 +4334,7 @@
         <v>17</v>
       </c>
       <c r="K98">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -4318,22 +4342,22 @@
         <v>20</v>
       </c>
       <c r="B99">
-        <v>55</v>
+        <v>91</v>
       </c>
       <c r="C99">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="D99" t="s">
-        <v>123</v>
+        <v>29</v>
       </c>
       <c r="E99" t="s">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="F99" t="s">
         <v>27</v>
       </c>
       <c r="G99" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="H99" t="s">
         <v>16</v>
@@ -4341,8 +4365,11 @@
       <c r="I99" t="s">
         <v>17</v>
       </c>
+      <c r="J99" t="s">
+        <v>30</v>
+      </c>
       <c r="K99">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -4350,22 +4377,22 @@
         <v>22</v>
       </c>
       <c r="B100">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C100">
-        <v>71</v>
+        <v>30</v>
       </c>
       <c r="D100" t="s">
-        <v>121</v>
+        <v>31</v>
       </c>
       <c r="E100" t="s">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="F100" t="s">
         <v>27</v>
       </c>
       <c r="G100" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="H100" t="s">
         <v>16</v>
@@ -4373,8 +4400,11 @@
       <c r="I100" t="s">
         <v>17</v>
       </c>
+      <c r="J100" t="s">
+        <v>32</v>
+      </c>
       <c r="K100">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -4382,7 +4412,7 @@
         <v>24</v>
       </c>
       <c r="B101">
-        <v>399</v>
+        <v>750</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -4391,13 +4421,13 @@
         <v>19</v>
       </c>
       <c r="E101" t="s">
-        <v>122</v>
+        <v>26</v>
       </c>
       <c r="F101" t="s">
         <v>27</v>
       </c>
       <c r="G101" t="s">
-        <v>112</v>
+        <v>15</v>
       </c>
       <c r="H101" t="s">
         <v>16</v>
@@ -4405,8 +4435,11 @@
       <c r="I101" t="s">
         <v>17</v>
       </c>
+      <c r="J101" t="s">
+        <v>25</v>
+      </c>
       <c r="K101">
-        <v>98</v>
+        <v>62</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -4414,22 +4447,22 @@
         <v>11</v>
       </c>
       <c r="B102">
-        <v>11</v>
+        <v>840</v>
       </c>
       <c r="C102">
-        <v>17</v>
+        <v>988</v>
       </c>
       <c r="D102" t="s">
-        <v>121</v>
+        <v>86</v>
       </c>
       <c r="E102" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="F102" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G102" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="H102" t="s">
         <v>16</v>
@@ -4438,7 +4471,7 @@
         <v>17</v>
       </c>
       <c r="K102">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -4446,22 +4479,22 @@
         <v>18</v>
       </c>
       <c r="B103">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="C103">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="D103" t="s">
-        <v>19</v>
+        <v>96</v>
       </c>
       <c r="E103" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="F103" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G103" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="H103" t="s">
         <v>16</v>
@@ -4470,7 +4503,7 @@
         <v>17</v>
       </c>
       <c r="K103">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -4478,22 +4511,22 @@
         <v>20</v>
       </c>
       <c r="B104">
-        <v>55</v>
+        <v>2433</v>
       </c>
       <c r="C104">
-        <v>52</v>
+        <v>1767</v>
       </c>
       <c r="D104" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="E104" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="F104" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G104" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="H104" t="s">
         <v>16</v>
@@ -4502,7 +4535,7 @@
         <v>17</v>
       </c>
       <c r="K104">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -4510,22 +4543,22 @@
         <v>22</v>
       </c>
       <c r="B105">
-        <v>47</v>
+        <v>2738</v>
       </c>
       <c r="C105">
-        <v>59</v>
+        <v>3162</v>
       </c>
       <c r="D105" t="s">
-        <v>119</v>
+        <v>95</v>
       </c>
       <c r="E105" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="F105" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G105" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="H105" t="s">
         <v>16</v>
@@ -4534,7 +4567,7 @@
         <v>17</v>
       </c>
       <c r="K105">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -4542,7 +4575,7 @@
         <v>24</v>
       </c>
       <c r="B106">
-        <v>399</v>
+        <v>27700</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -4551,13 +4584,13 @@
         <v>19</v>
       </c>
       <c r="E106" t="s">
-        <v>118</v>
+        <v>94</v>
       </c>
       <c r="F106" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G106" t="s">
-        <v>112</v>
+        <v>93</v>
       </c>
       <c r="H106" t="s">
         <v>16</v>
@@ -4565,8 +4598,11 @@
       <c r="I106" t="s">
         <v>17</v>
       </c>
+      <c r="J106" t="s">
+        <v>92</v>
+      </c>
       <c r="K106">
-        <v>98</v>
+        <v>79</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -4574,22 +4610,22 @@
         <v>11</v>
       </c>
       <c r="B107">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C107">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="D107" t="s">
-        <v>117</v>
+        <v>50</v>
       </c>
       <c r="E107" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="F107" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G107" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="H107" t="s">
         <v>16</v>
@@ -4598,7 +4634,7 @@
         <v>17</v>
       </c>
       <c r="K107">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -4606,22 +4642,22 @@
         <v>18</v>
       </c>
       <c r="B108">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C108">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D108" t="s">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="E108" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="F108" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G108" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="H108" t="s">
         <v>16</v>
@@ -4630,7 +4666,7 @@
         <v>17</v>
       </c>
       <c r="K108">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -4638,22 +4674,22 @@
         <v>20</v>
       </c>
       <c r="B109">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C109">
-        <v>41</v>
+        <v>15</v>
       </c>
       <c r="D109" t="s">
-        <v>115</v>
+        <v>91</v>
       </c>
       <c r="E109" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="F109" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G109" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="H109" t="s">
         <v>16</v>
@@ -4662,7 +4698,7 @@
         <v>17</v>
       </c>
       <c r="K109">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -4670,22 +4706,22 @@
         <v>22</v>
       </c>
       <c r="B110">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="C110">
-        <v>76</v>
+        <v>63</v>
       </c>
       <c r="D110" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="E110" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="F110" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G110" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="H110" t="s">
         <v>16</v>
@@ -4694,7 +4730,7 @@
         <v>17</v>
       </c>
       <c r="K110">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -4702,7 +4738,7 @@
         <v>24</v>
       </c>
       <c r="B111">
-        <v>399</v>
+        <v>480</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -4711,13 +4747,13 @@
         <v>19</v>
       </c>
       <c r="E111" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="F111" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G111" t="s">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="H111" t="s">
         <v>16</v>
@@ -4726,7 +4762,7 @@
         <v>17</v>
       </c>
       <c r="K111">
-        <v>98</v>
+        <v>101</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -4734,22 +4770,22 @@
         <v>11</v>
       </c>
       <c r="B112">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C112">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D112" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E112" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="F112" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G112" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="H112" t="s">
         <v>16</v>
@@ -4758,7 +4794,7 @@
         <v>17</v>
       </c>
       <c r="K112">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -4769,19 +4805,19 @@
         <v>4</v>
       </c>
       <c r="C113">
-        <v>23</v>
+        <v>5</v>
       </c>
       <c r="D113" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="E113" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="F113" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G113" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="H113" t="s">
         <v>16</v>
@@ -4790,7 +4826,7 @@
         <v>17</v>
       </c>
       <c r="K113">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -4798,22 +4834,22 @@
         <v>20</v>
       </c>
       <c r="B114">
-        <v>31</v>
+        <v>44</v>
       </c>
       <c r="C114">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="D114" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="E114" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="F114" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G114" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="H114" t="s">
         <v>16</v>
@@ -4822,7 +4858,7 @@
         <v>17</v>
       </c>
       <c r="K114">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -4830,22 +4866,22 @@
         <v>22</v>
       </c>
       <c r="B115">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C115">
-        <v>63</v>
+        <v>91</v>
       </c>
       <c r="D115" t="s">
-        <v>23</v>
+        <v>86</v>
       </c>
       <c r="E115" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="F115" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G115" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="H115" t="s">
         <v>16</v>
@@ -4854,7 +4890,7 @@
         <v>17</v>
       </c>
       <c r="K115">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -4862,7 +4898,7 @@
         <v>24</v>
       </c>
       <c r="B116">
-        <v>375</v>
+        <v>720</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -4871,13 +4907,13 @@
         <v>19</v>
       </c>
       <c r="E116" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="F116" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G116" t="s">
-        <v>98</v>
+        <v>84</v>
       </c>
       <c r="H116" t="s">
         <v>16</v>
@@ -4886,7 +4922,7 @@
         <v>17</v>
       </c>
       <c r="K116">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -4894,22 +4930,22 @@
         <v>11</v>
       </c>
       <c r="B117">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="C117">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="D117" t="s">
-        <v>109</v>
+        <v>46</v>
       </c>
       <c r="E117" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="F117" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G117" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="H117" t="s">
         <v>16</v>
@@ -4918,7 +4954,7 @@
         <v>17</v>
       </c>
       <c r="K117">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="118" spans="1:11" x14ac:dyDescent="0.25">
@@ -4926,22 +4962,22 @@
         <v>18</v>
       </c>
       <c r="B118">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="C118">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="D118" t="s">
-        <v>108</v>
+        <v>49</v>
       </c>
       <c r="E118" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="F118" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G118" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="H118" t="s">
         <v>16</v>
@@ -4950,7 +4986,7 @@
         <v>17</v>
       </c>
       <c r="K118">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="119" spans="1:11" x14ac:dyDescent="0.25">
@@ -4958,22 +4994,22 @@
         <v>20</v>
       </c>
       <c r="B119">
+        <v>61</v>
+      </c>
+      <c r="C119">
+        <v>77</v>
+      </c>
+      <c r="D119" t="s">
+        <v>50</v>
+      </c>
+      <c r="E119" t="s">
         <v>47</v>
       </c>
-      <c r="C119">
-        <v>40</v>
-      </c>
-      <c r="D119" t="s">
-        <v>107</v>
-      </c>
-      <c r="E119" t="s">
-        <v>106</v>
-      </c>
       <c r="F119" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G119" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="H119" t="s">
         <v>16</v>
@@ -4982,7 +5018,7 @@
         <v>17</v>
       </c>
       <c r="K119">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="120" spans="1:11" x14ac:dyDescent="0.25">
@@ -4990,22 +5026,22 @@
         <v>22</v>
       </c>
       <c r="B120">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="C120">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c r="D120" t="s">
-        <v>23</v>
+        <v>51</v>
       </c>
       <c r="E120" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="F120" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G120" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="H120" t="s">
         <v>16</v>
@@ -5014,7 +5050,7 @@
         <v>17</v>
       </c>
       <c r="K120">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="121" spans="1:11" x14ac:dyDescent="0.25">
@@ -5022,7 +5058,7 @@
         <v>24</v>
       </c>
       <c r="B121">
-        <v>562</v>
+        <v>300</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -5031,13 +5067,13 @@
         <v>19</v>
       </c>
       <c r="E121" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
       <c r="F121" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G121" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="H121" t="s">
         <v>16</v>
@@ -5046,7 +5082,7 @@
         <v>17</v>
       </c>
       <c r="K121">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="122" spans="1:11" x14ac:dyDescent="0.25">
@@ -5054,22 +5090,22 @@
         <v>11</v>
       </c>
       <c r="B122">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C122">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="D122" t="s">
-        <v>81</v>
+        <v>52</v>
       </c>
       <c r="E122" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="F122" t="s">
         <v>27</v>
       </c>
       <c r="G122" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="H122" t="s">
         <v>16</v>
@@ -5078,10 +5114,10 @@
         <v>17</v>
       </c>
       <c r="J122" t="s">
-        <v>105</v>
+        <v>54</v>
       </c>
       <c r="K122">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="123" spans="1:11" x14ac:dyDescent="0.25">
@@ -5089,22 +5125,22 @@
         <v>18</v>
       </c>
       <c r="B123">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C123">
         <v>1</v>
       </c>
       <c r="D123" t="s">
-        <v>104</v>
+        <v>55</v>
       </c>
       <c r="E123" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="F123" t="s">
         <v>27</v>
       </c>
       <c r="G123" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="H123" t="s">
         <v>16</v>
@@ -5113,10 +5149,10 @@
         <v>17</v>
       </c>
       <c r="J123" t="s">
-        <v>103</v>
+        <v>56</v>
       </c>
       <c r="K123">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="124" spans="1:11" x14ac:dyDescent="0.25">
@@ -5124,22 +5160,22 @@
         <v>20</v>
       </c>
       <c r="B124">
-        <v>47</v>
+        <v>82</v>
       </c>
       <c r="C124">
-        <v>27</v>
+        <v>38</v>
       </c>
       <c r="D124" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="E124" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="F124" t="s">
         <v>27</v>
       </c>
       <c r="G124" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="H124" t="s">
         <v>16</v>
@@ -5148,10 +5184,10 @@
         <v>17</v>
       </c>
       <c r="J124" t="s">
-        <v>101</v>
+        <v>58</v>
       </c>
       <c r="K124">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="125" spans="1:11" x14ac:dyDescent="0.25">
@@ -5159,22 +5195,22 @@
         <v>22</v>
       </c>
       <c r="B125">
-        <v>74</v>
+        <v>51</v>
       </c>
       <c r="C125">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="D125" t="s">
-        <v>100</v>
+        <v>59</v>
       </c>
       <c r="E125" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="F125" t="s">
         <v>27</v>
       </c>
       <c r="G125" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="H125" t="s">
         <v>16</v>
@@ -5182,8 +5218,11 @@
       <c r="I125" t="s">
         <v>17</v>
       </c>
+      <c r="J125" t="s">
+        <v>60</v>
+      </c>
       <c r="K125">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="126" spans="1:11" x14ac:dyDescent="0.25">
@@ -5191,7 +5230,7 @@
         <v>24</v>
       </c>
       <c r="B126">
-        <v>562</v>
+        <v>399</v>
       </c>
       <c r="C126">
         <v>0</v>
@@ -5200,13 +5239,13 @@
         <v>19</v>
       </c>
       <c r="E126" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="F126" t="s">
         <v>27</v>
       </c>
       <c r="G126" t="s">
-        <v>98</v>
+        <v>48</v>
       </c>
       <c r="H126" t="s">
         <v>16</v>
@@ -5215,10 +5254,10 @@
         <v>17</v>
       </c>
       <c r="J126" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="K126">
-        <v>80</v>
+        <v>92</v>
       </c>
     </row>
     <row r="127" spans="1:11" x14ac:dyDescent="0.25">
@@ -5226,22 +5265,22 @@
         <v>11</v>
       </c>
       <c r="B127">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C127">
-        <v>14</v>
+        <v>53</v>
       </c>
       <c r="D127" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="E127" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="F127" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G127" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H127" t="s">
         <v>16</v>
@@ -5250,7 +5289,7 @@
         <v>17</v>
       </c>
       <c r="K127">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -5258,22 +5297,22 @@
         <v>18</v>
       </c>
       <c r="B128">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C128">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="D128" t="s">
-        <v>19</v>
+        <v>63</v>
       </c>
       <c r="E128" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="F128" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G128" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H128" t="s">
         <v>16</v>
@@ -5282,7 +5321,7 @@
         <v>17</v>
       </c>
       <c r="K128">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -5290,22 +5329,22 @@
         <v>20</v>
       </c>
       <c r="B129">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C129">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="D129" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="E129" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="F129" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G129" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H129" t="s">
         <v>16</v>
@@ -5314,7 +5353,7 @@
         <v>17</v>
       </c>
       <c r="K129">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -5322,22 +5361,22 @@
         <v>22</v>
       </c>
       <c r="B130">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C130">
+        <v>154</v>
+      </c>
+      <c r="D130" t="s">
+        <v>65</v>
+      </c>
+      <c r="E130" t="s">
         <v>62</v>
       </c>
-      <c r="D130" t="s">
-        <v>23</v>
-      </c>
-      <c r="E130" t="s">
-        <v>13</v>
-      </c>
       <c r="F130" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G130" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H130" t="s">
         <v>16</v>
@@ -5346,7 +5385,7 @@
         <v>17</v>
       </c>
       <c r="K130">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -5354,7 +5393,7 @@
         <v>24</v>
       </c>
       <c r="B131">
-        <v>750</v>
+        <v>399</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -5363,13 +5402,13 @@
         <v>19</v>
       </c>
       <c r="E131" t="s">
-        <v>13</v>
+        <v>62</v>
       </c>
       <c r="F131" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G131" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H131" t="s">
         <v>16</v>
@@ -5377,11 +5416,8 @@
       <c r="I131" t="s">
         <v>17</v>
       </c>
-      <c r="J131" t="s">
-        <v>25</v>
-      </c>
       <c r="K131">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -5389,22 +5425,22 @@
         <v>11</v>
       </c>
       <c r="B132">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="C132">
-        <v>14</v>
+        <v>46</v>
       </c>
       <c r="D132" t="s">
-        <v>12</v>
+        <v>66</v>
       </c>
       <c r="E132" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="F132" t="s">
         <v>27</v>
       </c>
       <c r="G132" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H132" t="s">
         <v>16</v>
@@ -5413,10 +5449,10 @@
         <v>17</v>
       </c>
       <c r="J132" t="s">
-        <v>28</v>
+        <v>68</v>
       </c>
       <c r="K132">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -5424,22 +5460,22 @@
         <v>18</v>
       </c>
       <c r="B133">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C133">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D133" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="E133" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="F133" t="s">
         <v>27</v>
       </c>
       <c r="G133" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H133" t="s">
         <v>16</v>
@@ -5447,8 +5483,11 @@
       <c r="I133" t="s">
         <v>17</v>
       </c>
+      <c r="J133" t="s">
+        <v>70</v>
+      </c>
       <c r="K133">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -5456,22 +5495,22 @@
         <v>20</v>
       </c>
       <c r="B134">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C134">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="D134" t="s">
-        <v>29</v>
+        <v>71</v>
       </c>
       <c r="E134" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="F134" t="s">
         <v>27</v>
       </c>
       <c r="G134" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H134" t="s">
         <v>16</v>
@@ -5480,10 +5519,10 @@
         <v>17</v>
       </c>
       <c r="J134" t="s">
-        <v>30</v>
+        <v>72</v>
       </c>
       <c r="K134">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -5491,22 +5530,22 @@
         <v>22</v>
       </c>
       <c r="B135">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C135">
-        <v>30</v>
+        <v>78</v>
       </c>
       <c r="D135" t="s">
-        <v>31</v>
+        <v>73</v>
       </c>
       <c r="E135" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="F135" t="s">
         <v>27</v>
       </c>
       <c r="G135" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H135" t="s">
         <v>16</v>
@@ -5514,11 +5553,8 @@
       <c r="I135" t="s">
         <v>17</v>
       </c>
-      <c r="J135" t="s">
-        <v>32</v>
-      </c>
       <c r="K135">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -5526,7 +5562,7 @@
         <v>24</v>
       </c>
       <c r="B136">
-        <v>750</v>
+        <v>399</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -5535,13 +5571,13 @@
         <v>19</v>
       </c>
       <c r="E136" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="F136" t="s">
         <v>27</v>
       </c>
       <c r="G136" t="s">
-        <v>15</v>
+        <v>48</v>
       </c>
       <c r="H136" t="s">
         <v>16</v>
@@ -5549,11 +5585,8 @@
       <c r="I136" t="s">
         <v>17</v>
       </c>
-      <c r="J136" t="s">
-        <v>25</v>
-      </c>
       <c r="K136">
-        <v>62</v>
+        <v>92</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -5561,22 +5594,22 @@
         <v>11</v>
       </c>
       <c r="B137">
-        <v>840</v>
+        <v>7</v>
       </c>
       <c r="C137">
-        <v>988</v>
+        <v>6</v>
       </c>
       <c r="D137" t="s">
-        <v>86</v>
+        <v>230</v>
       </c>
       <c r="E137" t="s">
-        <v>94</v>
+        <v>227</v>
       </c>
       <c r="F137" t="s">
         <v>14</v>
       </c>
       <c r="G137" t="s">
-        <v>93</v>
+        <v>225</v>
       </c>
       <c r="H137" t="s">
         <v>16</v>
@@ -5585,7 +5618,7 @@
         <v>17</v>
       </c>
       <c r="K137">
-        <v>79</v>
+        <v>22</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -5593,22 +5626,22 @@
         <v>18</v>
       </c>
       <c r="B138">
-        <v>131</v>
+        <v>2</v>
       </c>
       <c r="C138">
-        <v>231</v>
+        <v>0</v>
       </c>
       <c r="D138" t="s">
-        <v>96</v>
+        <v>19</v>
       </c>
       <c r="E138" t="s">
-        <v>94</v>
+        <v>227</v>
       </c>
       <c r="F138" t="s">
         <v>14</v>
       </c>
       <c r="G138" t="s">
-        <v>93</v>
+        <v>225</v>
       </c>
       <c r="H138" t="s">
         <v>16</v>
@@ -5617,7 +5650,7 @@
         <v>17</v>
       </c>
       <c r="K138">
-        <v>79</v>
+        <v>22</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -5625,22 +5658,22 @@
         <v>20</v>
       </c>
       <c r="B139">
-        <v>2433</v>
+        <v>13</v>
       </c>
       <c r="C139">
-        <v>1767</v>
+        <v>5</v>
       </c>
       <c r="D139" t="s">
-        <v>71</v>
+        <v>229</v>
       </c>
       <c r="E139" t="s">
-        <v>94</v>
+        <v>227</v>
       </c>
       <c r="F139" t="s">
         <v>14</v>
       </c>
       <c r="G139" t="s">
-        <v>93</v>
+        <v>225</v>
       </c>
       <c r="H139" t="s">
         <v>16</v>
@@ -5649,7 +5682,7 @@
         <v>17</v>
       </c>
       <c r="K139">
-        <v>79</v>
+        <v>22</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
@@ -5657,22 +5690,22 @@
         <v>22</v>
       </c>
       <c r="B140">
-        <v>2738</v>
+        <v>22</v>
       </c>
       <c r="C140">
-        <v>3162</v>
+        <v>23</v>
       </c>
       <c r="D140" t="s">
-        <v>95</v>
+        <v>228</v>
       </c>
       <c r="E140" t="s">
-        <v>94</v>
+        <v>227</v>
       </c>
       <c r="F140" t="s">
         <v>14</v>
       </c>
       <c r="G140" t="s">
-        <v>93</v>
+        <v>225</v>
       </c>
       <c r="H140" t="s">
         <v>16</v>
@@ -5681,7 +5714,7 @@
         <v>17</v>
       </c>
       <c r="K140">
-        <v>79</v>
+        <v>22</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
@@ -5689,7 +5722,7 @@
         <v>24</v>
       </c>
       <c r="B141">
-        <v>27700</v>
+        <v>480</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -5698,13 +5731,13 @@
         <v>19</v>
       </c>
       <c r="E141" t="s">
-        <v>94</v>
+        <v>227</v>
       </c>
       <c r="F141" t="s">
         <v>14</v>
       </c>
       <c r="G141" t="s">
-        <v>93</v>
+        <v>225</v>
       </c>
       <c r="H141" t="s">
         <v>16</v>
@@ -5712,11 +5745,8 @@
       <c r="I141" t="s">
         <v>17</v>
       </c>
-      <c r="J141" t="s">
-        <v>92</v>
-      </c>
       <c r="K141">
-        <v>79</v>
+        <v>22</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -5724,22 +5754,22 @@
         <v>11</v>
       </c>
       <c r="B142">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C142">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="D142" t="s">
-        <v>50</v>
+        <v>195</v>
       </c>
       <c r="E142" t="s">
-        <v>90</v>
+        <v>226</v>
       </c>
       <c r="F142" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G142" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="H142" t="s">
         <v>16</v>
@@ -5748,7 +5778,7 @@
         <v>17</v>
       </c>
       <c r="K142">
-        <v>101</v>
+        <v>22</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -5756,22 +5786,22 @@
         <v>18</v>
       </c>
       <c r="B143">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C143">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D143" t="s">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="E143" t="s">
-        <v>90</v>
+        <v>226</v>
       </c>
       <c r="F143" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G143" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="H143" t="s">
         <v>16</v>
@@ -5780,7 +5810,7 @@
         <v>17</v>
       </c>
       <c r="K143">
-        <v>101</v>
+        <v>22</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -5788,22 +5818,22 @@
         <v>20</v>
       </c>
       <c r="B144">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="C144">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D144" t="s">
-        <v>91</v>
+        <v>217</v>
       </c>
       <c r="E144" t="s">
-        <v>90</v>
+        <v>226</v>
       </c>
       <c r="F144" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G144" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="H144" t="s">
         <v>16</v>
@@ -5812,7 +5842,7 @@
         <v>17</v>
       </c>
       <c r="K144">
-        <v>101</v>
+        <v>22</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -5820,22 +5850,22 @@
         <v>22</v>
       </c>
       <c r="B145">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C145">
-        <v>63</v>
+        <v>42</v>
       </c>
       <c r="D145" t="s">
-        <v>81</v>
+        <v>89</v>
       </c>
       <c r="E145" t="s">
-        <v>90</v>
+        <v>226</v>
       </c>
       <c r="F145" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G145" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="H145" t="s">
         <v>16</v>
@@ -5844,7 +5874,7 @@
         <v>17</v>
       </c>
       <c r="K145">
-        <v>101</v>
+        <v>22</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -5852,7 +5882,7 @@
         <v>24</v>
       </c>
       <c r="B146">
-        <v>480</v>
+        <v>720</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -5861,13 +5891,13 @@
         <v>19</v>
       </c>
       <c r="E146" t="s">
-        <v>90</v>
+        <v>226</v>
       </c>
       <c r="F146" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G146" t="s">
-        <v>84</v>
+        <v>225</v>
       </c>
       <c r="H146" t="s">
         <v>16</v>
@@ -5876,7 +5906,7 @@
         <v>17</v>
       </c>
       <c r="K146">
-        <v>101</v>
+        <v>22</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -5884,22 +5914,22 @@
         <v>11</v>
       </c>
       <c r="B147">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C147">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D147" t="s">
-        <v>89</v>
+        <v>218</v>
       </c>
       <c r="E147" t="s">
-        <v>85</v>
+        <v>216</v>
       </c>
       <c r="F147" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G147" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="H147" t="s">
         <v>16</v>
@@ -5908,7 +5938,7 @@
         <v>17</v>
       </c>
       <c r="K147">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -5919,19 +5949,19 @@
         <v>4</v>
       </c>
       <c r="C148">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D148" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E148" t="s">
-        <v>85</v>
+        <v>216</v>
       </c>
       <c r="F148" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G148" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="H148" t="s">
         <v>16</v>
@@ -5940,7 +5970,7 @@
         <v>17</v>
       </c>
       <c r="K148">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -5948,22 +5978,22 @@
         <v>20</v>
       </c>
       <c r="B149">
+        <v>39</v>
+      </c>
+      <c r="C149">
         <v>44</v>
       </c>
-      <c r="C149">
-        <v>38</v>
-      </c>
       <c r="D149" t="s">
-        <v>87</v>
+        <v>140</v>
       </c>
       <c r="E149" t="s">
-        <v>85</v>
+        <v>216</v>
       </c>
       <c r="F149" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G149" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="H149" t="s">
         <v>16</v>
@@ -5972,7 +6002,7 @@
         <v>17</v>
       </c>
       <c r="K149">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -5980,22 +6010,22 @@
         <v>22</v>
       </c>
       <c r="B150">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C150">
-        <v>91</v>
+        <v>64</v>
       </c>
       <c r="D150" t="s">
-        <v>86</v>
+        <v>217</v>
       </c>
       <c r="E150" t="s">
-        <v>85</v>
+        <v>216</v>
       </c>
       <c r="F150" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G150" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="H150" t="s">
         <v>16</v>
@@ -6004,7 +6034,7 @@
         <v>17</v>
       </c>
       <c r="K150">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -6012,7 +6042,7 @@
         <v>24</v>
       </c>
       <c r="B151">
-        <v>720</v>
+        <v>1200</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -6021,13 +6051,13 @@
         <v>19</v>
       </c>
       <c r="E151" t="s">
-        <v>85</v>
+        <v>216</v>
       </c>
       <c r="F151" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G151" t="s">
-        <v>84</v>
+        <v>215</v>
       </c>
       <c r="H151" t="s">
         <v>16</v>
@@ -6036,7 +6066,7 @@
         <v>17</v>
       </c>
       <c r="K151">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -6044,22 +6074,22 @@
         <v>11</v>
       </c>
       <c r="B152">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="C152">
-        <v>65</v>
+        <v>19</v>
       </c>
       <c r="D152" t="s">
-        <v>46</v>
+        <v>208</v>
       </c>
       <c r="E152" t="s">
-        <v>47</v>
+        <v>207</v>
       </c>
       <c r="F152" t="s">
         <v>14</v>
       </c>
       <c r="G152" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="H152" t="s">
         <v>16</v>
@@ -6068,7 +6098,7 @@
         <v>17</v>
       </c>
       <c r="K152">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -6076,22 +6106,22 @@
         <v>18</v>
       </c>
       <c r="B153">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C153">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D153" t="s">
-        <v>49</v>
+        <v>19</v>
       </c>
       <c r="E153" t="s">
-        <v>47</v>
+        <v>207</v>
       </c>
       <c r="F153" t="s">
         <v>14</v>
       </c>
       <c r="G153" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="H153" t="s">
         <v>16</v>
@@ -6100,7 +6130,7 @@
         <v>17</v>
       </c>
       <c r="K153">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -6108,22 +6138,22 @@
         <v>20</v>
       </c>
       <c r="B154">
-        <v>61</v>
+        <v>31</v>
       </c>
       <c r="C154">
-        <v>77</v>
+        <v>23</v>
       </c>
       <c r="D154" t="s">
-        <v>50</v>
+        <v>114</v>
       </c>
       <c r="E154" t="s">
-        <v>47</v>
+        <v>207</v>
       </c>
       <c r="F154" t="s">
         <v>14</v>
       </c>
       <c r="G154" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="H154" t="s">
         <v>16</v>
@@ -6132,7 +6162,7 @@
         <v>17</v>
       </c>
       <c r="K154">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -6140,22 +6170,22 @@
         <v>22</v>
       </c>
       <c r="B155">
-        <v>38</v>
+        <v>73</v>
       </c>
       <c r="C155">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="D155" t="s">
-        <v>51</v>
+        <v>154</v>
       </c>
       <c r="E155" t="s">
-        <v>47</v>
+        <v>207</v>
       </c>
       <c r="F155" t="s">
         <v>14</v>
       </c>
       <c r="G155" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="H155" t="s">
         <v>16</v>
@@ -6164,7 +6194,7 @@
         <v>17</v>
       </c>
       <c r="K155">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -6172,7 +6202,7 @@
         <v>24</v>
       </c>
       <c r="B156">
-        <v>300</v>
+        <v>480</v>
       </c>
       <c r="C156">
         <v>0</v>
@@ -6181,13 +6211,13 @@
         <v>19</v>
       </c>
       <c r="E156" t="s">
-        <v>47</v>
+        <v>207</v>
       </c>
       <c r="F156" t="s">
         <v>14</v>
       </c>
       <c r="G156" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="H156" t="s">
         <v>16</v>
@@ -6196,7 +6226,7 @@
         <v>17</v>
       </c>
       <c r="K156">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -6204,22 +6234,22 @@
         <v>11</v>
       </c>
       <c r="B157">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="C157">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="D157" t="s">
-        <v>52</v>
+        <v>206</v>
       </c>
       <c r="E157" t="s">
-        <v>53</v>
+        <v>203</v>
       </c>
       <c r="F157" t="s">
         <v>27</v>
       </c>
       <c r="G157" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="H157" t="s">
         <v>16</v>
@@ -6227,11 +6257,8 @@
       <c r="I157" t="s">
         <v>17</v>
       </c>
-      <c r="J157" t="s">
-        <v>54</v>
-      </c>
       <c r="K157">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -6239,22 +6266,22 @@
         <v>18</v>
       </c>
       <c r="B158">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C158">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D158" t="s">
-        <v>55</v>
+        <v>19</v>
       </c>
       <c r="E158" t="s">
-        <v>53</v>
+        <v>203</v>
       </c>
       <c r="F158" t="s">
         <v>27</v>
       </c>
       <c r="G158" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="H158" t="s">
         <v>16</v>
@@ -6262,11 +6289,8 @@
       <c r="I158" t="s">
         <v>17</v>
       </c>
-      <c r="J158" t="s">
-        <v>56</v>
-      </c>
       <c r="K158">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -6274,22 +6298,22 @@
         <v>20</v>
       </c>
       <c r="B159">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="C159">
-        <v>38</v>
+        <v>23</v>
       </c>
       <c r="D159" t="s">
-        <v>57</v>
+        <v>205</v>
       </c>
       <c r="E159" t="s">
-        <v>53</v>
+        <v>203</v>
       </c>
       <c r="F159" t="s">
         <v>27</v>
       </c>
       <c r="G159" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="H159" t="s">
         <v>16</v>
@@ -6297,11 +6321,8 @@
       <c r="I159" t="s">
         <v>17</v>
       </c>
-      <c r="J159" t="s">
-        <v>58</v>
-      </c>
       <c r="K159">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -6309,22 +6330,22 @@
         <v>22</v>
       </c>
       <c r="B160">
-        <v>51</v>
+        <v>110</v>
       </c>
       <c r="C160">
-        <v>73</v>
+        <v>164</v>
       </c>
       <c r="D160" t="s">
-        <v>59</v>
+        <v>204</v>
       </c>
       <c r="E160" t="s">
-        <v>53</v>
+        <v>203</v>
       </c>
       <c r="F160" t="s">
         <v>27</v>
       </c>
       <c r="G160" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="H160" t="s">
         <v>16</v>
@@ -6332,11 +6353,8 @@
       <c r="I160" t="s">
         <v>17</v>
       </c>
-      <c r="J160" t="s">
-        <v>60</v>
-      </c>
       <c r="K160">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -6344,7 +6362,7 @@
         <v>24</v>
       </c>
       <c r="B161">
-        <v>399</v>
+        <v>720</v>
       </c>
       <c r="C161">
         <v>0</v>
@@ -6353,13 +6371,13 @@
         <v>19</v>
       </c>
       <c r="E161" t="s">
-        <v>53</v>
+        <v>203</v>
       </c>
       <c r="F161" t="s">
         <v>27</v>
       </c>
       <c r="G161" t="s">
-        <v>48</v>
+        <v>202</v>
       </c>
       <c r="H161" t="s">
         <v>16</v>
@@ -6367,11 +6385,8 @@
       <c r="I161" t="s">
         <v>17</v>
       </c>
-      <c r="J161" t="s">
-        <v>74</v>
-      </c>
       <c r="K161">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
@@ -6379,22 +6394,22 @@
         <v>11</v>
       </c>
       <c r="B162">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="C162">
-        <v>53</v>
+        <v>15</v>
       </c>
       <c r="D162" t="s">
-        <v>61</v>
+        <v>192</v>
       </c>
       <c r="E162" t="s">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="F162" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G162" t="s">
-        <v>48</v>
+        <v>187</v>
       </c>
       <c r="H162" t="s">
         <v>16</v>
@@ -6403,7 +6418,7 @@
         <v>17</v>
       </c>
       <c r="K162">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
@@ -6411,22 +6426,22 @@
         <v>18</v>
       </c>
       <c r="B163">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C163">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="D163" t="s">
-        <v>63</v>
+        <v>181</v>
       </c>
       <c r="E163" t="s">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="F163" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G163" t="s">
-        <v>48</v>
+        <v>187</v>
       </c>
       <c r="H163" t="s">
         <v>16</v>
@@ -6435,7 +6450,7 @@
         <v>17</v>
       </c>
       <c r="K163">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -6443,22 +6458,22 @@
         <v>20</v>
       </c>
       <c r="B164">
-        <v>82</v>
+        <v>31</v>
       </c>
       <c r="C164">
-        <v>85</v>
+        <v>31</v>
       </c>
       <c r="D164" t="s">
-        <v>64</v>
+        <v>171</v>
       </c>
       <c r="E164" t="s">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="F164" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G164" t="s">
-        <v>48</v>
+        <v>187</v>
       </c>
       <c r="H164" t="s">
         <v>16</v>
@@ -6467,7 +6482,7 @@
         <v>17</v>
       </c>
       <c r="K164">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -6475,22 +6490,22 @@
         <v>22</v>
       </c>
       <c r="B165">
-        <v>51</v>
+        <v>67</v>
       </c>
       <c r="C165">
-        <v>154</v>
+        <v>74</v>
       </c>
       <c r="D165" t="s">
-        <v>65</v>
+        <v>191</v>
       </c>
       <c r="E165" t="s">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="F165" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G165" t="s">
-        <v>48</v>
+        <v>187</v>
       </c>
       <c r="H165" t="s">
         <v>16</v>
@@ -6499,7 +6514,7 @@
         <v>17</v>
       </c>
       <c r="K165">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -6507,7 +6522,7 @@
         <v>24</v>
       </c>
       <c r="B166">
-        <v>399</v>
+        <v>480</v>
       </c>
       <c r="C166">
         <v>0</v>
@@ -6516,13 +6531,13 @@
         <v>19</v>
       </c>
       <c r="E166" t="s">
-        <v>62</v>
+        <v>190</v>
       </c>
       <c r="F166" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G166" t="s">
-        <v>48</v>
+        <v>187</v>
       </c>
       <c r="H166" t="s">
         <v>16</v>
@@ -6531,7 +6546,7 @@
         <v>17</v>
       </c>
       <c r="K166">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -6539,22 +6554,22 @@
         <v>11</v>
       </c>
       <c r="B167">
-        <v>27</v>
+        <v>13</v>
       </c>
       <c r="C167">
-        <v>46</v>
+        <v>22</v>
       </c>
       <c r="D167" t="s">
-        <v>66</v>
+        <v>127</v>
       </c>
       <c r="E167" t="s">
-        <v>67</v>
+        <v>188</v>
       </c>
       <c r="F167" t="s">
         <v>27</v>
       </c>
       <c r="G167" t="s">
-        <v>48</v>
+        <v>187</v>
       </c>
       <c r="H167" t="s">
         <v>16</v>
@@ -6562,11 +6577,8 @@
       <c r="I167" t="s">
         <v>17</v>
       </c>
-      <c r="J167" t="s">
-        <v>68</v>
-      </c>
       <c r="K167">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -6577,19 +6589,19 @@
         <v>4</v>
       </c>
       <c r="C168">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D168" t="s">
-        <v>69</v>
+        <v>127</v>
       </c>
       <c r="E168" t="s">
-        <v>67</v>
+        <v>188</v>
       </c>
       <c r="F168" t="s">
         <v>27</v>
       </c>
       <c r="G168" t="s">
-        <v>48</v>
+        <v>187</v>
       </c>
       <c r="H168" t="s">
         <v>16</v>
@@ -6597,11 +6609,8 @@
       <c r="I168" t="s">
         <v>17</v>
       </c>
-      <c r="J168" t="s">
-        <v>70</v>
-      </c>
       <c r="K168">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -6609,22 +6618,22 @@
         <v>20</v>
       </c>
       <c r="B169">
-        <v>82</v>
+        <v>47</v>
       </c>
       <c r="C169">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="D169" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="E169" t="s">
-        <v>67</v>
+        <v>188</v>
       </c>
       <c r="F169" t="s">
         <v>27</v>
       </c>
       <c r="G169" t="s">
-        <v>48</v>
+        <v>187</v>
       </c>
       <c r="H169" t="s">
         <v>16</v>
@@ -6632,11 +6641,8 @@
       <c r="I169" t="s">
         <v>17</v>
       </c>
-      <c r="J169" t="s">
-        <v>72</v>
-      </c>
       <c r="K169">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -6644,22 +6650,22 @@
         <v>22</v>
       </c>
       <c r="B170">
-        <v>51</v>
+        <v>101</v>
       </c>
       <c r="C170">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="D170" t="s">
-        <v>73</v>
+        <v>189</v>
       </c>
       <c r="E170" t="s">
-        <v>67</v>
+        <v>188</v>
       </c>
       <c r="F170" t="s">
         <v>27</v>
       </c>
       <c r="G170" t="s">
-        <v>48</v>
+        <v>187</v>
       </c>
       <c r="H170" t="s">
         <v>16</v>
@@ -6668,7 +6674,7 @@
         <v>17</v>
       </c>
       <c r="K170">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
@@ -6676,7 +6682,7 @@
         <v>24</v>
       </c>
       <c r="B171">
-        <v>399</v>
+        <v>720</v>
       </c>
       <c r="C171">
         <v>0</v>
@@ -6685,13 +6691,13 @@
         <v>19</v>
       </c>
       <c r="E171" t="s">
-        <v>67</v>
+        <v>188</v>
       </c>
       <c r="F171" t="s">
         <v>27</v>
       </c>
       <c r="G171" t="s">
-        <v>48</v>
+        <v>187</v>
       </c>
       <c r="H171" t="s">
         <v>16</v>
@@ -6700,7 +6706,7 @@
         <v>17</v>
       </c>
       <c r="K171">
-        <v>92</v>
+        <v>81</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
@@ -6708,22 +6714,22 @@
         <v>11</v>
       </c>
       <c r="B172">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="C172">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="D172" t="s">
-        <v>237</v>
+        <v>186</v>
       </c>
       <c r="E172" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="F172" t="s">
         <v>14</v>
       </c>
       <c r="G172" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="H172" t="s">
         <v>16</v>
@@ -6732,7 +6738,7 @@
         <v>17</v>
       </c>
       <c r="K172">
-        <v>22</v>
+        <v>119</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -6740,7 +6746,7 @@
         <v>18</v>
       </c>
       <c r="B173">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -6749,13 +6755,13 @@
         <v>19</v>
       </c>
       <c r="E173" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="F173" t="s">
         <v>14</v>
       </c>
       <c r="G173" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="H173" t="s">
         <v>16</v>
@@ -6764,7 +6770,7 @@
         <v>17</v>
       </c>
       <c r="K173">
-        <v>22</v>
+        <v>119</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -6772,22 +6778,22 @@
         <v>20</v>
       </c>
       <c r="B174">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="C174">
-        <v>5</v>
+        <v>47</v>
       </c>
       <c r="D174" t="s">
-        <v>236</v>
+        <v>50</v>
       </c>
       <c r="E174" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="F174" t="s">
         <v>14</v>
       </c>
       <c r="G174" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="H174" t="s">
         <v>16</v>
@@ -6796,7 +6802,7 @@
         <v>17</v>
       </c>
       <c r="K174">
-        <v>22</v>
+        <v>119</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -6804,22 +6810,22 @@
         <v>22</v>
       </c>
       <c r="B175">
-        <v>22</v>
+        <v>37</v>
       </c>
       <c r="C175">
-        <v>23</v>
+        <v>38</v>
       </c>
       <c r="D175" t="s">
-        <v>235</v>
+        <v>109</v>
       </c>
       <c r="E175" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="F175" t="s">
         <v>14</v>
       </c>
       <c r="G175" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="H175" t="s">
         <v>16</v>
@@ -6828,7 +6834,7 @@
         <v>17</v>
       </c>
       <c r="K175">
-        <v>22</v>
+        <v>119</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -6845,13 +6851,13 @@
         <v>19</v>
       </c>
       <c r="E176" t="s">
-        <v>234</v>
+        <v>185</v>
       </c>
       <c r="F176" t="s">
         <v>14</v>
       </c>
       <c r="G176" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="H176" t="s">
         <v>16</v>
@@ -6860,7 +6866,7 @@
         <v>17</v>
       </c>
       <c r="K176">
-        <v>22</v>
+        <v>119</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -6868,22 +6874,22 @@
         <v>11</v>
       </c>
       <c r="B177">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C177">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="D177" t="s">
-        <v>202</v>
+        <v>184</v>
       </c>
       <c r="E177" t="s">
-        <v>233</v>
+        <v>183</v>
       </c>
       <c r="F177" t="s">
         <v>27</v>
       </c>
       <c r="G177" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="H177" t="s">
         <v>16</v>
@@ -6892,7 +6898,7 @@
         <v>17</v>
       </c>
       <c r="K177">
-        <v>22</v>
+        <v>119</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -6900,22 +6906,22 @@
         <v>18</v>
       </c>
       <c r="B178">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C178">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D178" t="s">
-        <v>207</v>
+        <v>19</v>
       </c>
       <c r="E178" t="s">
-        <v>233</v>
+        <v>183</v>
       </c>
       <c r="F178" t="s">
         <v>27</v>
       </c>
       <c r="G178" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="H178" t="s">
         <v>16</v>
@@ -6924,7 +6930,7 @@
         <v>17</v>
       </c>
       <c r="K178">
-        <v>22</v>
+        <v>119</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -6932,22 +6938,22 @@
         <v>20</v>
       </c>
       <c r="B179">
-        <v>20</v>
+        <v>56</v>
       </c>
       <c r="C179">
-        <v>17</v>
+        <v>34</v>
       </c>
       <c r="D179" t="s">
-        <v>224</v>
+        <v>136</v>
       </c>
       <c r="E179" t="s">
-        <v>233</v>
+        <v>183</v>
       </c>
       <c r="F179" t="s">
         <v>27</v>
       </c>
       <c r="G179" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="H179" t="s">
         <v>16</v>
@@ -6956,7 +6962,7 @@
         <v>17</v>
       </c>
       <c r="K179">
-        <v>22</v>
+        <v>119</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -6964,22 +6970,22 @@
         <v>22</v>
       </c>
       <c r="B180">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="C180">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="D180" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="E180" t="s">
-        <v>233</v>
+        <v>183</v>
       </c>
       <c r="F180" t="s">
         <v>27</v>
       </c>
       <c r="G180" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="H180" t="s">
         <v>16</v>
@@ -6988,7 +6994,7 @@
         <v>17</v>
       </c>
       <c r="K180">
-        <v>22</v>
+        <v>119</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -7005,13 +7011,13 @@
         <v>19</v>
       </c>
       <c r="E181" t="s">
-        <v>233</v>
+        <v>183</v>
       </c>
       <c r="F181" t="s">
         <v>27</v>
       </c>
       <c r="G181" t="s">
-        <v>232</v>
+        <v>182</v>
       </c>
       <c r="H181" t="s">
         <v>16</v>
@@ -7020,7 +7026,7 @@
         <v>17</v>
       </c>
       <c r="K181">
-        <v>22</v>
+        <v>119</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -7028,22 +7034,22 @@
         <v>11</v>
       </c>
       <c r="B182">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C182">
-        <v>27</v>
+        <v>11</v>
       </c>
       <c r="D182" t="s">
-        <v>225</v>
+        <v>201</v>
       </c>
       <c r="E182" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="F182" t="s">
         <v>14</v>
       </c>
       <c r="G182" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="H182" t="s">
         <v>16</v>
@@ -7052,7 +7058,7 @@
         <v>17</v>
       </c>
       <c r="K182">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="183" spans="1:11" x14ac:dyDescent="0.25">
@@ -7060,22 +7066,22 @@
         <v>18</v>
       </c>
       <c r="B183">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C183">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D183" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="E183" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="F183" t="s">
         <v>14</v>
       </c>
       <c r="G183" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="H183" t="s">
         <v>16</v>
@@ -7084,7 +7090,7 @@
         <v>17</v>
       </c>
       <c r="K183">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="184" spans="1:11" x14ac:dyDescent="0.25">
@@ -7092,22 +7098,22 @@
         <v>20</v>
       </c>
       <c r="B184">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="C184">
-        <v>44</v>
+        <v>26</v>
       </c>
       <c r="D184" t="s">
-        <v>145</v>
+        <v>87</v>
       </c>
       <c r="E184" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="F184" t="s">
         <v>14</v>
       </c>
       <c r="G184" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="H184" t="s">
         <v>16</v>
@@ -7116,7 +7122,7 @@
         <v>17</v>
       </c>
       <c r="K184">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="185" spans="1:11" x14ac:dyDescent="0.25">
@@ -7124,31 +7130,31 @@
         <v>22</v>
       </c>
       <c r="B185">
-        <v>74</v>
+        <v>32</v>
       </c>
       <c r="C185">
+        <v>65</v>
+      </c>
+      <c r="D185" t="s">
+        <v>249</v>
+      </c>
+      <c r="E185" t="s">
+        <v>199</v>
+      </c>
+      <c r="F185" t="s">
+        <v>14</v>
+      </c>
+      <c r="G185" t="s">
+        <v>193</v>
+      </c>
+      <c r="H185" t="s">
+        <v>16</v>
+      </c>
+      <c r="I185" t="s">
+        <v>17</v>
+      </c>
+      <c r="K185">
         <v>64</v>
-      </c>
-      <c r="D185" t="s">
-        <v>224</v>
-      </c>
-      <c r="E185" t="s">
-        <v>223</v>
-      </c>
-      <c r="F185" t="s">
-        <v>14</v>
-      </c>
-      <c r="G185" t="s">
-        <v>222</v>
-      </c>
-      <c r="H185" t="s">
-        <v>16</v>
-      </c>
-      <c r="I185" t="s">
-        <v>17</v>
-      </c>
-      <c r="K185">
-        <v>79</v>
       </c>
     </row>
     <row r="186" spans="1:11" x14ac:dyDescent="0.25">
@@ -7156,7 +7162,7 @@
         <v>24</v>
       </c>
       <c r="B186">
-        <v>1200</v>
+        <v>375</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -7165,13 +7171,13 @@
         <v>19</v>
       </c>
       <c r="E186" t="s">
-        <v>223</v>
+        <v>199</v>
       </c>
       <c r="F186" t="s">
         <v>14</v>
       </c>
       <c r="G186" t="s">
-        <v>222</v>
+        <v>193</v>
       </c>
       <c r="H186" t="s">
         <v>16</v>
@@ -7180,7 +7186,7 @@
         <v>17</v>
       </c>
       <c r="K186">
-        <v>79</v>
+        <v>64</v>
       </c>
     </row>
     <row r="187" spans="1:11" x14ac:dyDescent="0.25">
@@ -7188,22 +7194,22 @@
         <v>11</v>
       </c>
       <c r="B187">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C187">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="D187" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="E187" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="F187" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G187" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="H187" t="s">
         <v>16</v>
@@ -7212,7 +7218,7 @@
         <v>17</v>
       </c>
       <c r="K187">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -7220,22 +7226,22 @@
         <v>18</v>
       </c>
       <c r="B188">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C188">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D188" t="s">
-        <v>19</v>
+        <v>49</v>
       </c>
       <c r="E188" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="F188" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G188" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="H188" t="s">
         <v>16</v>
@@ -7244,7 +7250,7 @@
         <v>17</v>
       </c>
       <c r="K188">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
@@ -7252,22 +7258,22 @@
         <v>20</v>
       </c>
       <c r="B189">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C189">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="D189" t="s">
-        <v>115</v>
+        <v>176</v>
       </c>
       <c r="E189" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="F189" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G189" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="H189" t="s">
         <v>16</v>
@@ -7276,7 +7282,7 @@
         <v>17</v>
       </c>
       <c r="K189">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -7284,22 +7290,22 @@
         <v>22</v>
       </c>
       <c r="B190">
-        <v>73</v>
+        <v>47</v>
       </c>
       <c r="C190">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="D190" t="s">
-        <v>161</v>
+        <v>81</v>
       </c>
       <c r="E190" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="F190" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G190" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="H190" t="s">
         <v>16</v>
@@ -7308,7 +7314,7 @@
         <v>17</v>
       </c>
       <c r="K190">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -7316,7 +7322,7 @@
         <v>24</v>
       </c>
       <c r="B191">
-        <v>480</v>
+        <v>562</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -7325,13 +7331,13 @@
         <v>19</v>
       </c>
       <c r="E191" t="s">
-        <v>214</v>
+        <v>196</v>
       </c>
       <c r="F191" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G191" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="H191" t="s">
         <v>16</v>
@@ -7340,7 +7346,7 @@
         <v>17</v>
       </c>
       <c r="K191">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -7348,22 +7354,22 @@
         <v>11</v>
       </c>
       <c r="B192">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="C192">
-        <v>39</v>
+        <v>7</v>
       </c>
       <c r="D192" t="s">
-        <v>213</v>
+        <v>168</v>
       </c>
       <c r="E192" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="F192" t="s">
         <v>27</v>
       </c>
       <c r="G192" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="H192" t="s">
         <v>16</v>
@@ -7371,8 +7377,11 @@
       <c r="I192" t="s">
         <v>17</v>
       </c>
+      <c r="J192" t="s">
+        <v>248</v>
+      </c>
       <c r="K192">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -7380,7 +7389,7 @@
         <v>18</v>
       </c>
       <c r="B193">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -7389,13 +7398,13 @@
         <v>19</v>
       </c>
       <c r="E193" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="F193" t="s">
         <v>27</v>
       </c>
       <c r="G193" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="H193" t="s">
         <v>16</v>
@@ -7403,8 +7412,11 @@
       <c r="I193" t="s">
         <v>17</v>
       </c>
+      <c r="J193" t="s">
+        <v>247</v>
+      </c>
       <c r="K193">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -7412,22 +7424,22 @@
         <v>20</v>
       </c>
       <c r="B194">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="C194">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="D194" t="s">
-        <v>212</v>
+        <v>177</v>
       </c>
       <c r="E194" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="F194" t="s">
         <v>27</v>
       </c>
       <c r="G194" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="H194" t="s">
         <v>16</v>
@@ -7435,8 +7447,11 @@
       <c r="I194" t="s">
         <v>17</v>
       </c>
+      <c r="J194" t="s">
+        <v>246</v>
+      </c>
       <c r="K194">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -7444,22 +7459,22 @@
         <v>22</v>
       </c>
       <c r="B195">
-        <v>110</v>
+        <v>47</v>
       </c>
       <c r="C195">
-        <v>164</v>
+        <v>31</v>
       </c>
       <c r="D195" t="s">
-        <v>211</v>
+        <v>179</v>
       </c>
       <c r="E195" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="F195" t="s">
         <v>27</v>
       </c>
       <c r="G195" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="H195" t="s">
         <v>16</v>
@@ -7467,8 +7482,11 @@
       <c r="I195" t="s">
         <v>17</v>
       </c>
+      <c r="J195" t="s">
+        <v>245</v>
+      </c>
       <c r="K195">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -7476,7 +7494,7 @@
         <v>24</v>
       </c>
       <c r="B196">
-        <v>720</v>
+        <v>562</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -7485,13 +7503,13 @@
         <v>19</v>
       </c>
       <c r="E196" t="s">
-        <v>210</v>
+        <v>194</v>
       </c>
       <c r="F196" t="s">
         <v>27</v>
       </c>
       <c r="G196" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="H196" t="s">
         <v>16</v>
@@ -7500,7 +7518,7 @@
         <v>17</v>
       </c>
       <c r="K196">
-        <v>71</v>
+        <v>64</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -7508,22 +7526,22 @@
         <v>11</v>
       </c>
       <c r="B197">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C197">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="D197" t="s">
-        <v>199</v>
+        <v>224</v>
       </c>
       <c r="E197" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="F197" t="s">
         <v>14</v>
       </c>
       <c r="G197" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="H197" t="s">
         <v>16</v>
@@ -7532,7 +7550,7 @@
         <v>17</v>
       </c>
       <c r="K197">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -7540,22 +7558,22 @@
         <v>18</v>
       </c>
       <c r="B198">
+        <v>0</v>
+      </c>
+      <c r="C198">
         <v>2</v>
       </c>
-      <c r="C198">
-        <v>5</v>
-      </c>
       <c r="D198" t="s">
-        <v>188</v>
+        <v>146</v>
       </c>
       <c r="E198" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="F198" t="s">
         <v>14</v>
       </c>
       <c r="G198" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="H198" t="s">
         <v>16</v>
@@ -7564,7 +7582,7 @@
         <v>17</v>
       </c>
       <c r="K198">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
@@ -7572,22 +7590,22 @@
         <v>20</v>
       </c>
       <c r="B199">
-        <v>31</v>
+        <v>43</v>
       </c>
       <c r="C199">
-        <v>31</v>
+        <v>40</v>
       </c>
       <c r="D199" t="s">
-        <v>178</v>
+        <v>223</v>
       </c>
       <c r="E199" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="F199" t="s">
         <v>14</v>
       </c>
       <c r="G199" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="H199" t="s">
         <v>16</v>
@@ -7596,7 +7614,7 @@
         <v>17</v>
       </c>
       <c r="K199">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -7604,22 +7622,22 @@
         <v>22</v>
       </c>
       <c r="B200">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="C200">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D200" t="s">
-        <v>198</v>
+        <v>244</v>
       </c>
       <c r="E200" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="F200" t="s">
         <v>14</v>
       </c>
       <c r="G200" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="H200" t="s">
         <v>16</v>
@@ -7628,7 +7646,7 @@
         <v>17</v>
       </c>
       <c r="K200">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -7636,7 +7654,7 @@
         <v>24</v>
       </c>
       <c r="B201">
-        <v>480</v>
+        <v>320</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -7645,13 +7663,13 @@
         <v>19</v>
       </c>
       <c r="E201" t="s">
-        <v>197</v>
+        <v>222</v>
       </c>
       <c r="F201" t="s">
         <v>14</v>
       </c>
       <c r="G201" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="H201" t="s">
         <v>16</v>
@@ -7660,7 +7678,7 @@
         <v>17</v>
       </c>
       <c r="K201">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
@@ -7668,22 +7686,22 @@
         <v>11</v>
       </c>
       <c r="B202">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="C202">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="D202" t="s">
-        <v>131</v>
+        <v>221</v>
       </c>
       <c r="E202" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="F202" t="s">
         <v>27</v>
       </c>
       <c r="G202" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="H202" t="s">
         <v>16</v>
@@ -7691,8 +7709,11 @@
       <c r="I202" t="s">
         <v>17</v>
       </c>
+      <c r="J202" t="s">
+        <v>243</v>
+      </c>
       <c r="K202">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -7700,22 +7721,22 @@
         <v>18</v>
       </c>
       <c r="B203">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C203">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D203" t="s">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="E203" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="F203" t="s">
         <v>27</v>
       </c>
       <c r="G203" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="H203" t="s">
         <v>16</v>
@@ -7724,7 +7745,7 @@
         <v>17</v>
       </c>
       <c r="K203">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
@@ -7732,22 +7753,22 @@
         <v>20</v>
       </c>
       <c r="B204">
-        <v>47</v>
+        <v>64</v>
       </c>
       <c r="C204">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="D204" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="E204" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="F204" t="s">
         <v>27</v>
       </c>
       <c r="G204" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="H204" t="s">
         <v>16</v>
@@ -7755,8 +7776,11 @@
       <c r="I204" t="s">
         <v>17</v>
       </c>
+      <c r="J204" t="s">
+        <v>242</v>
+      </c>
       <c r="K204">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
@@ -7764,22 +7788,22 @@
         <v>22</v>
       </c>
       <c r="B205">
-        <v>101</v>
+        <v>36</v>
       </c>
       <c r="C205">
-        <v>85</v>
+        <v>32</v>
       </c>
       <c r="D205" t="s">
-        <v>196</v>
+        <v>131</v>
       </c>
       <c r="E205" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="F205" t="s">
         <v>27</v>
       </c>
       <c r="G205" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="H205" t="s">
         <v>16</v>
@@ -7787,8 +7811,11 @@
       <c r="I205" t="s">
         <v>17</v>
       </c>
+      <c r="J205" t="s">
+        <v>241</v>
+      </c>
       <c r="K205">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -7796,7 +7823,7 @@
         <v>24</v>
       </c>
       <c r="B206">
-        <v>720</v>
+        <v>480</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -7805,13 +7832,13 @@
         <v>19</v>
       </c>
       <c r="E206" t="s">
-        <v>195</v>
+        <v>220</v>
       </c>
       <c r="F206" t="s">
         <v>27</v>
       </c>
       <c r="G206" t="s">
-        <v>194</v>
+        <v>219</v>
       </c>
       <c r="H206" t="s">
         <v>16</v>
@@ -7820,7 +7847,7 @@
         <v>17</v>
       </c>
       <c r="K206">
-        <v>81</v>
+        <v>62</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
@@ -7828,22 +7855,22 @@
         <v>11</v>
       </c>
       <c r="B207">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="C207">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="D207" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="E207" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="F207" t="s">
         <v>14</v>
       </c>
       <c r="G207" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H207" t="s">
         <v>16</v>
@@ -7851,8 +7878,11 @@
       <c r="I207" t="s">
         <v>17</v>
       </c>
+      <c r="J207" t="s">
+        <v>240</v>
+      </c>
       <c r="K207">
-        <v>119</v>
+        <v>76</v>
       </c>
     </row>
     <row r="208" spans="1:11" x14ac:dyDescent="0.25">
@@ -7860,22 +7890,22 @@
         <v>18</v>
       </c>
       <c r="B208">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C208">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D208" t="s">
-        <v>19</v>
+        <v>239</v>
       </c>
       <c r="E208" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="F208" t="s">
         <v>14</v>
       </c>
       <c r="G208" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H208" t="s">
         <v>16</v>
@@ -7884,7 +7914,7 @@
         <v>17</v>
       </c>
       <c r="K208">
-        <v>119</v>
+        <v>76</v>
       </c>
     </row>
     <row r="209" spans="1:11" x14ac:dyDescent="0.25">
@@ -7892,22 +7922,22 @@
         <v>20</v>
       </c>
       <c r="B209">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="C209">
-        <v>47</v>
+        <v>21</v>
       </c>
       <c r="D209" t="s">
-        <v>50</v>
+        <v>230</v>
       </c>
       <c r="E209" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="F209" t="s">
         <v>14</v>
       </c>
       <c r="G209" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H209" t="s">
         <v>16</v>
@@ -7916,7 +7946,7 @@
         <v>17</v>
       </c>
       <c r="K209">
-        <v>119</v>
+        <v>76</v>
       </c>
     </row>
     <row r="210" spans="1:11" x14ac:dyDescent="0.25">
@@ -7924,22 +7954,22 @@
         <v>22</v>
       </c>
       <c r="B210">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C210">
-        <v>38</v>
+        <v>54</v>
       </c>
       <c r="D210" t="s">
-        <v>109</v>
+        <v>197</v>
       </c>
       <c r="E210" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="F210" t="s">
         <v>14</v>
       </c>
       <c r="G210" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H210" t="s">
         <v>16</v>
@@ -7948,7 +7978,7 @@
         <v>17</v>
       </c>
       <c r="K210">
-        <v>119</v>
+        <v>76</v>
       </c>
     </row>
     <row r="211" spans="1:11" x14ac:dyDescent="0.25">
@@ -7956,7 +7986,7 @@
         <v>24</v>
       </c>
       <c r="B211">
-        <v>480</v>
+        <v>375</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -7965,13 +7995,13 @@
         <v>19</v>
       </c>
       <c r="E211" t="s">
-        <v>192</v>
+        <v>214</v>
       </c>
       <c r="F211" t="s">
         <v>14</v>
       </c>
       <c r="G211" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H211" t="s">
         <v>16</v>
@@ -7980,7 +8010,7 @@
         <v>17</v>
       </c>
       <c r="K211">
-        <v>119</v>
+        <v>76</v>
       </c>
     </row>
     <row r="212" spans="1:11" x14ac:dyDescent="0.25">
@@ -7988,22 +8018,22 @@
         <v>11</v>
       </c>
       <c r="B212">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="C212">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="D212" t="s">
-        <v>191</v>
+        <v>238</v>
       </c>
       <c r="E212" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="F212" t="s">
         <v>27</v>
       </c>
       <c r="G212" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H212" t="s">
         <v>16</v>
@@ -8012,7 +8042,7 @@
         <v>17</v>
       </c>
       <c r="K212">
-        <v>119</v>
+        <v>76</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -8020,22 +8050,22 @@
         <v>18</v>
       </c>
       <c r="B213">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C213">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D213" t="s">
-        <v>19</v>
+        <v>78</v>
       </c>
       <c r="E213" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="F213" t="s">
         <v>27</v>
       </c>
       <c r="G213" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H213" t="s">
         <v>16</v>
@@ -8044,7 +8074,7 @@
         <v>17</v>
       </c>
       <c r="K213">
-        <v>119</v>
+        <v>76</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -8052,22 +8082,22 @@
         <v>20</v>
       </c>
       <c r="B214">
-        <v>56</v>
+        <v>36</v>
       </c>
       <c r="C214">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="D214" t="s">
-        <v>141</v>
+        <v>42</v>
       </c>
       <c r="E214" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="F214" t="s">
         <v>27</v>
       </c>
       <c r="G214" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H214" t="s">
         <v>16</v>
@@ -8076,7 +8106,7 @@
         <v>17</v>
       </c>
       <c r="K214">
-        <v>119</v>
+        <v>76</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -8084,22 +8114,22 @@
         <v>22</v>
       </c>
       <c r="B215">
-        <v>55</v>
+        <v>68</v>
       </c>
       <c r="C215">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="D215" t="s">
-        <v>50</v>
+        <v>198</v>
       </c>
       <c r="E215" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="F215" t="s">
         <v>27</v>
       </c>
       <c r="G215" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H215" t="s">
         <v>16</v>
@@ -8108,7 +8138,7 @@
         <v>17</v>
       </c>
       <c r="K215">
-        <v>119</v>
+        <v>76</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -8116,7 +8146,7 @@
         <v>24</v>
       </c>
       <c r="B216">
-        <v>720</v>
+        <v>562</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -8125,13 +8155,13 @@
         <v>19</v>
       </c>
       <c r="E216" t="s">
-        <v>190</v>
+        <v>213</v>
       </c>
       <c r="F216" t="s">
         <v>27</v>
       </c>
       <c r="G216" t="s">
-        <v>189</v>
+        <v>209</v>
       </c>
       <c r="H216" t="s">
         <v>16</v>
@@ -8140,7 +8170,7 @@
         <v>17</v>
       </c>
       <c r="K216">
-        <v>119</v>
+        <v>76</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -8148,22 +8178,22 @@
         <v>11</v>
       </c>
       <c r="B217">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C217">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="D217" t="s">
-        <v>208</v>
+        <v>33</v>
       </c>
       <c r="E217" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F217" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G217" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="H217" t="s">
         <v>16</v>
@@ -8171,8 +8201,11 @@
       <c r="I217" t="s">
         <v>17</v>
       </c>
+      <c r="J217" t="s">
+        <v>237</v>
+      </c>
       <c r="K217">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -8180,22 +8213,22 @@
         <v>18</v>
       </c>
       <c r="B218">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C218">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D218" t="s">
-        <v>19</v>
+        <v>71</v>
       </c>
       <c r="E218" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F218" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G218" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="H218" t="s">
         <v>16</v>
@@ -8204,7 +8237,7 @@
         <v>17</v>
       </c>
       <c r="K218">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -8212,22 +8245,22 @@
         <v>20</v>
       </c>
       <c r="B219">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="C219">
-        <v>26</v>
+        <v>7</v>
       </c>
       <c r="D219" t="s">
-        <v>87</v>
+        <v>212</v>
       </c>
       <c r="E219" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F219" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G219" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="H219" t="s">
         <v>16</v>
@@ -8236,7 +8269,7 @@
         <v>17</v>
       </c>
       <c r="K219">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -8244,22 +8277,22 @@
         <v>22</v>
       </c>
       <c r="B220">
-        <v>32</v>
+        <v>68</v>
       </c>
       <c r="C220">
-        <v>65</v>
+        <v>43</v>
       </c>
       <c r="D220" t="s">
-        <v>256</v>
+        <v>211</v>
       </c>
       <c r="E220" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F220" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G220" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="H220" t="s">
         <v>16</v>
@@ -8268,7 +8301,7 @@
         <v>17</v>
       </c>
       <c r="K220">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -8276,7 +8309,7 @@
         <v>24</v>
       </c>
       <c r="B221">
-        <v>375</v>
+        <v>562</v>
       </c>
       <c r="C221">
         <v>0</v>
@@ -8285,13 +8318,13 @@
         <v>19</v>
       </c>
       <c r="E221" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="F221" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G221" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="H221" t="s">
         <v>16</v>
@@ -8300,7 +8333,7 @@
         <v>17</v>
       </c>
       <c r="K221">
-        <v>64</v>
+        <v>76</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
@@ -8311,19 +8344,19 @@
         <v>11</v>
       </c>
       <c r="C222">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="D222" t="s">
-        <v>205</v>
+        <v>83</v>
       </c>
       <c r="E222" t="s">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="F222" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G222" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="H222" t="s">
         <v>16</v>
@@ -8332,7 +8365,7 @@
         <v>17</v>
       </c>
       <c r="K222">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
@@ -8340,22 +8373,22 @@
         <v>18</v>
       </c>
       <c r="B223">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C223">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="D223" t="s">
-        <v>49</v>
+        <v>236</v>
       </c>
       <c r="E223" t="s">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="F223" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G223" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="H223" t="s">
         <v>16</v>
@@ -8364,7 +8397,7 @@
         <v>17</v>
       </c>
       <c r="K223">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -8372,22 +8405,22 @@
         <v>20</v>
       </c>
       <c r="B224">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="C224">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D224" t="s">
-        <v>183</v>
+        <v>228</v>
       </c>
       <c r="E224" t="s">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="F224" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G224" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="H224" t="s">
         <v>16</v>
@@ -8396,7 +8429,7 @@
         <v>17</v>
       </c>
       <c r="K224">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
@@ -8404,22 +8437,22 @@
         <v>22</v>
       </c>
       <c r="B225">
-        <v>47</v>
+        <v>38</v>
       </c>
       <c r="C225">
-        <v>58</v>
+        <v>77</v>
       </c>
       <c r="D225" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E225" t="s">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="F225" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G225" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="H225" t="s">
         <v>16</v>
@@ -8428,7 +8461,7 @@
         <v>17</v>
       </c>
       <c r="K225">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
@@ -8436,7 +8469,7 @@
         <v>24</v>
       </c>
       <c r="B226">
-        <v>562</v>
+        <v>375</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -8445,13 +8478,13 @@
         <v>19</v>
       </c>
       <c r="E226" t="s">
-        <v>203</v>
+        <v>79</v>
       </c>
       <c r="F226" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G226" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="H226" t="s">
         <v>16</v>
@@ -8460,7 +8493,7 @@
         <v>17</v>
       </c>
       <c r="K226">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
@@ -8468,31 +8501,28 @@
         <v>11</v>
       </c>
       <c r="B227">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C227">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="D227" t="s">
-        <v>175</v>
+        <v>78</v>
       </c>
       <c r="E227" t="s">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="F227" t="s">
         <v>27</v>
       </c>
       <c r="G227" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="H227" t="s">
         <v>16</v>
       </c>
       <c r="I227" t="s">
         <v>17</v>
-      </c>
-      <c r="J227" t="s">
-        <v>255</v>
       </c>
       <c r="K227">
         <v>64</v>
@@ -8506,28 +8536,25 @@
         <v>4</v>
       </c>
       <c r="C228">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="D228" t="s">
-        <v>19</v>
+        <v>235</v>
       </c>
       <c r="E228" t="s">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="F228" t="s">
         <v>27</v>
       </c>
       <c r="G228" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="H228" t="s">
         <v>16</v>
       </c>
       <c r="I228" t="s">
         <v>17</v>
-      </c>
-      <c r="J228" t="s">
-        <v>254</v>
       </c>
       <c r="K228">
         <v>64</v>
@@ -8538,31 +8565,28 @@
         <v>20</v>
       </c>
       <c r="B229">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="C229">
-        <v>16</v>
+        <v>39</v>
       </c>
       <c r="D229" t="s">
-        <v>184</v>
+        <v>142</v>
       </c>
       <c r="E229" t="s">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="F229" t="s">
         <v>27</v>
       </c>
       <c r="G229" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="H229" t="s">
         <v>16</v>
       </c>
       <c r="I229" t="s">
         <v>17</v>
-      </c>
-      <c r="J229" t="s">
-        <v>253</v>
       </c>
       <c r="K229">
         <v>64</v>
@@ -8573,31 +8597,28 @@
         <v>22</v>
       </c>
       <c r="B230">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="C230">
-        <v>31</v>
+        <v>94</v>
       </c>
       <c r="D230" t="s">
-        <v>186</v>
+        <v>234</v>
       </c>
       <c r="E230" t="s">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="F230" t="s">
         <v>27</v>
       </c>
       <c r="G230" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="H230" t="s">
         <v>16</v>
       </c>
       <c r="I230" t="s">
         <v>17</v>
-      </c>
-      <c r="J230" t="s">
-        <v>252</v>
       </c>
       <c r="K230">
         <v>64</v>
@@ -8617,13 +8638,13 @@
         <v>19</v>
       </c>
       <c r="E231" t="s">
-        <v>201</v>
+        <v>77</v>
       </c>
       <c r="F231" t="s">
         <v>27</v>
       </c>
       <c r="G231" t="s">
-        <v>200</v>
+        <v>75</v>
       </c>
       <c r="H231" t="s">
         <v>16</v>
@@ -8640,22 +8661,22 @@
         <v>11</v>
       </c>
       <c r="B232">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C232">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D232" t="s">
-        <v>231</v>
+        <v>123</v>
       </c>
       <c r="E232" t="s">
-        <v>229</v>
+        <v>76</v>
       </c>
       <c r="F232" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G232" t="s">
-        <v>226</v>
+        <v>75</v>
       </c>
       <c r="H232" t="s">
         <v>16</v>
@@ -8663,8 +8684,11 @@
       <c r="I232" t="s">
         <v>17</v>
       </c>
+      <c r="J232" t="s">
+        <v>233</v>
+      </c>
       <c r="K232">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
@@ -8672,22 +8696,22 @@
         <v>18</v>
       </c>
       <c r="B233">
+        <v>4</v>
+      </c>
+      <c r="C233">
         <v>0</v>
       </c>
-      <c r="C233">
-        <v>2</v>
-      </c>
       <c r="D233" t="s">
-        <v>153</v>
+        <v>19</v>
       </c>
       <c r="E233" t="s">
-        <v>229</v>
+        <v>76</v>
       </c>
       <c r="F233" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G233" t="s">
-        <v>226</v>
+        <v>75</v>
       </c>
       <c r="H233" t="s">
         <v>16</v>
@@ -8696,7 +8720,7 @@
         <v>17</v>
       </c>
       <c r="K233">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
@@ -8704,22 +8728,22 @@
         <v>20</v>
       </c>
       <c r="B234">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="C234">
-        <v>40</v>
+        <v>8</v>
       </c>
       <c r="D234" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E234" t="s">
-        <v>229</v>
+        <v>76</v>
       </c>
       <c r="F234" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G234" t="s">
-        <v>226</v>
+        <v>75</v>
       </c>
       <c r="H234" t="s">
         <v>16</v>
@@ -8728,7 +8752,7 @@
         <v>17</v>
       </c>
       <c r="K234">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -8736,22 +8760,22 @@
         <v>22</v>
       </c>
       <c r="B235">
-        <v>24</v>
+        <v>57</v>
       </c>
       <c r="C235">
-        <v>44</v>
+        <v>22</v>
       </c>
       <c r="D235" t="s">
-        <v>251</v>
+        <v>231</v>
       </c>
       <c r="E235" t="s">
-        <v>229</v>
+        <v>76</v>
       </c>
       <c r="F235" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G235" t="s">
-        <v>226</v>
+        <v>75</v>
       </c>
       <c r="H235" t="s">
         <v>16</v>
@@ -8760,7 +8784,7 @@
         <v>17</v>
       </c>
       <c r="K235">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
@@ -8768,7 +8792,7 @@
         <v>24</v>
       </c>
       <c r="B236">
-        <v>320</v>
+        <v>562</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -8777,13 +8801,13 @@
         <v>19</v>
       </c>
       <c r="E236" t="s">
-        <v>229</v>
+        <v>76</v>
       </c>
       <c r="F236" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G236" t="s">
-        <v>226</v>
+        <v>75</v>
       </c>
       <c r="H236" t="s">
         <v>16</v>
@@ -8792,7 +8816,7 @@
         <v>17</v>
       </c>
       <c r="K236">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
@@ -8803,19 +8827,19 @@
         <v>8</v>
       </c>
       <c r="C237">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D237" t="s">
-        <v>228</v>
+        <v>258</v>
       </c>
       <c r="E237" t="s">
-        <v>227</v>
+        <v>121</v>
       </c>
       <c r="F237" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G237" t="s">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="H237" t="s">
         <v>16</v>
@@ -8824,10 +8848,10 @@
         <v>17</v>
       </c>
       <c r="J237" t="s">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="K237">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="238" spans="1:11" x14ac:dyDescent="0.25">
@@ -8835,7 +8859,7 @@
         <v>18</v>
       </c>
       <c r="B238">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C238">
         <v>0</v>
@@ -8844,13 +8868,13 @@
         <v>19</v>
       </c>
       <c r="E238" t="s">
-        <v>227</v>
+        <v>121</v>
       </c>
       <c r="F238" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G238" t="s">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="H238" t="s">
         <v>16</v>
@@ -8858,8 +8882,11 @@
       <c r="I238" t="s">
         <v>17</v>
       </c>
+      <c r="J238" t="s">
+        <v>256</v>
+      </c>
       <c r="K238">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="239" spans="1:11" x14ac:dyDescent="0.25">
@@ -8867,22 +8894,22 @@
         <v>20</v>
       </c>
       <c r="B239">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="C239">
-        <v>36</v>
+        <v>2</v>
       </c>
       <c r="D239" t="s">
-        <v>33</v>
+        <v>122</v>
       </c>
       <c r="E239" t="s">
-        <v>227</v>
+        <v>121</v>
       </c>
       <c r="F239" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G239" t="s">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="H239" t="s">
         <v>16</v>
@@ -8890,11 +8917,8 @@
       <c r="I239" t="s">
         <v>17</v>
       </c>
-      <c r="J239" t="s">
-        <v>249</v>
-      </c>
       <c r="K239">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="240" spans="1:11" x14ac:dyDescent="0.25">
@@ -8902,22 +8926,22 @@
         <v>22</v>
       </c>
       <c r="B240">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C240">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="D240" t="s">
-        <v>135</v>
+        <v>255</v>
       </c>
       <c r="E240" t="s">
-        <v>227</v>
+        <v>121</v>
       </c>
       <c r="F240" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G240" t="s">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="H240" t="s">
         <v>16</v>
@@ -8925,11 +8949,8 @@
       <c r="I240" t="s">
         <v>17</v>
       </c>
-      <c r="J240" t="s">
-        <v>248</v>
-      </c>
       <c r="K240">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="241" spans="1:11" x14ac:dyDescent="0.25">
@@ -8937,7 +8958,7 @@
         <v>24</v>
       </c>
       <c r="B241">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -8946,13 +8967,13 @@
         <v>19</v>
       </c>
       <c r="E241" t="s">
-        <v>227</v>
+        <v>121</v>
       </c>
       <c r="F241" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G241" t="s">
-        <v>226</v>
+        <v>112</v>
       </c>
       <c r="H241" t="s">
         <v>16</v>
@@ -8961,7 +8982,7 @@
         <v>17</v>
       </c>
       <c r="K241">
-        <v>62</v>
+        <v>98</v>
       </c>
     </row>
     <row r="242" spans="1:11" x14ac:dyDescent="0.25">
@@ -8969,22 +8990,22 @@
         <v>11</v>
       </c>
       <c r="B242">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C242">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D242" t="s">
-        <v>191</v>
+        <v>59</v>
       </c>
       <c r="E242" t="s">
-        <v>221</v>
+        <v>119</v>
       </c>
       <c r="F242" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G242" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="H242" t="s">
         <v>16</v>
@@ -8992,11 +9013,8 @@
       <c r="I242" t="s">
         <v>17</v>
       </c>
-      <c r="J242" t="s">
-        <v>247</v>
-      </c>
       <c r="K242">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="243" spans="1:11" x14ac:dyDescent="0.25">
@@ -9004,22 +9022,22 @@
         <v>18</v>
       </c>
       <c r="B243">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="C243">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D243" t="s">
-        <v>246</v>
+        <v>19</v>
       </c>
       <c r="E243" t="s">
-        <v>221</v>
+        <v>119</v>
       </c>
       <c r="F243" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G243" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="H243" t="s">
         <v>16</v>
@@ -9028,7 +9046,7 @@
         <v>17</v>
       </c>
       <c r="K243">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="244" spans="1:11" x14ac:dyDescent="0.25">
@@ -9036,22 +9054,22 @@
         <v>20</v>
       </c>
       <c r="B244">
-        <v>24</v>
+        <v>55</v>
       </c>
       <c r="C244">
-        <v>21</v>
+        <v>43</v>
       </c>
       <c r="D244" t="s">
-        <v>237</v>
+        <v>254</v>
       </c>
       <c r="E244" t="s">
-        <v>221</v>
+        <v>119</v>
       </c>
       <c r="F244" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G244" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="H244" t="s">
         <v>16</v>
@@ -9060,7 +9078,7 @@
         <v>17</v>
       </c>
       <c r="K244">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="245" spans="1:11" x14ac:dyDescent="0.25">
@@ -9068,22 +9086,22 @@
         <v>22</v>
       </c>
       <c r="B245">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C245">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="D245" t="s">
-        <v>204</v>
+        <v>78</v>
       </c>
       <c r="E245" t="s">
-        <v>221</v>
+        <v>119</v>
       </c>
       <c r="F245" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G245" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="H245" t="s">
         <v>16</v>
@@ -9092,7 +9110,7 @@
         <v>17</v>
       </c>
       <c r="K245">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="246" spans="1:11" x14ac:dyDescent="0.25">
@@ -9100,7 +9118,7 @@
         <v>24</v>
       </c>
       <c r="B246">
-        <v>375</v>
+        <v>399</v>
       </c>
       <c r="C246">
         <v>0</v>
@@ -9109,13 +9127,13 @@
         <v>19</v>
       </c>
       <c r="E246" t="s">
-        <v>221</v>
+        <v>119</v>
       </c>
       <c r="F246" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G246" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="H246" t="s">
         <v>16</v>
@@ -9124,7 +9142,7 @@
         <v>17</v>
       </c>
       <c r="K246">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="247" spans="1:11" x14ac:dyDescent="0.25">
@@ -9132,22 +9150,22 @@
         <v>11</v>
       </c>
       <c r="B247">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C247">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="D247" t="s">
-        <v>245</v>
+        <v>118</v>
       </c>
       <c r="E247" t="s">
-        <v>220</v>
+        <v>116</v>
       </c>
       <c r="F247" t="s">
         <v>27</v>
       </c>
       <c r="G247" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="H247" t="s">
         <v>16</v>
@@ -9156,7 +9174,7 @@
         <v>17</v>
       </c>
       <c r="K247">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -9164,22 +9182,22 @@
         <v>18</v>
       </c>
       <c r="B248">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C248">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D248" t="s">
-        <v>78</v>
+        <v>19</v>
       </c>
       <c r="E248" t="s">
-        <v>220</v>
+        <v>116</v>
       </c>
       <c r="F248" t="s">
         <v>27</v>
       </c>
       <c r="G248" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="H248" t="s">
         <v>16</v>
@@ -9188,7 +9206,7 @@
         <v>17</v>
       </c>
       <c r="K248">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -9196,22 +9214,22 @@
         <v>20</v>
       </c>
       <c r="B249">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C249">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="D249" t="s">
-        <v>42</v>
+        <v>117</v>
       </c>
       <c r="E249" t="s">
-        <v>220</v>
+        <v>116</v>
       </c>
       <c r="F249" t="s">
         <v>27</v>
       </c>
       <c r="G249" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="H249" t="s">
         <v>16</v>
@@ -9220,7 +9238,7 @@
         <v>17</v>
       </c>
       <c r="K249">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -9228,22 +9246,22 @@
         <v>22</v>
       </c>
       <c r="B250">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C250">
-        <v>84</v>
+        <v>48</v>
       </c>
       <c r="D250" t="s">
-        <v>205</v>
+        <v>109</v>
       </c>
       <c r="E250" t="s">
-        <v>220</v>
+        <v>116</v>
       </c>
       <c r="F250" t="s">
         <v>27</v>
       </c>
       <c r="G250" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="H250" t="s">
         <v>16</v>
@@ -9252,7 +9270,7 @@
         <v>17</v>
       </c>
       <c r="K250">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -9260,7 +9278,7 @@
         <v>24</v>
       </c>
       <c r="B251">
-        <v>562</v>
+        <v>399</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -9269,13 +9287,13 @@
         <v>19</v>
       </c>
       <c r="E251" t="s">
-        <v>220</v>
+        <v>116</v>
       </c>
       <c r="F251" t="s">
         <v>27</v>
       </c>
       <c r="G251" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="H251" t="s">
         <v>16</v>
@@ -9284,7 +9302,7 @@
         <v>17</v>
       </c>
       <c r="K251">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -9292,22 +9310,22 @@
         <v>11</v>
       </c>
       <c r="B252">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C252">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D252" t="s">
-        <v>33</v>
+        <v>115</v>
       </c>
       <c r="E252" t="s">
-        <v>217</v>
+        <v>113</v>
       </c>
       <c r="F252" t="s">
         <v>27</v>
       </c>
       <c r="G252" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="H252" t="s">
         <v>16</v>
@@ -9315,11 +9333,8 @@
       <c r="I252" t="s">
         <v>17</v>
       </c>
-      <c r="J252" t="s">
-        <v>244</v>
-      </c>
       <c r="K252">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -9327,22 +9342,22 @@
         <v>18</v>
       </c>
       <c r="B253">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C253">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D253" t="s">
-        <v>71</v>
+        <v>253</v>
       </c>
       <c r="E253" t="s">
-        <v>217</v>
+        <v>113</v>
       </c>
       <c r="F253" t="s">
         <v>27</v>
       </c>
       <c r="G253" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="H253" t="s">
         <v>16</v>
@@ -9351,7 +9366,7 @@
         <v>17</v>
       </c>
       <c r="K253">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -9359,22 +9374,22 @@
         <v>20</v>
       </c>
       <c r="B254">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C254">
-        <v>7</v>
+        <v>41</v>
       </c>
       <c r="D254" t="s">
-        <v>219</v>
+        <v>114</v>
       </c>
       <c r="E254" t="s">
-        <v>217</v>
+        <v>113</v>
       </c>
       <c r="F254" t="s">
         <v>27</v>
       </c>
       <c r="G254" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="H254" t="s">
         <v>16</v>
@@ -9383,7 +9398,7 @@
         <v>17</v>
       </c>
       <c r="K254">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -9391,22 +9406,22 @@
         <v>22</v>
       </c>
       <c r="B255">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="C255">
-        <v>43</v>
+        <v>69</v>
       </c>
       <c r="D255" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="E255" t="s">
-        <v>217</v>
+        <v>113</v>
       </c>
       <c r="F255" t="s">
         <v>27</v>
       </c>
       <c r="G255" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="H255" t="s">
         <v>16</v>
@@ -9415,7 +9430,7 @@
         <v>17</v>
       </c>
       <c r="K255">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -9423,7 +9438,7 @@
         <v>24</v>
       </c>
       <c r="B256">
-        <v>562</v>
+        <v>399</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -9432,13 +9447,13 @@
         <v>19</v>
       </c>
       <c r="E256" t="s">
-        <v>217</v>
+        <v>113</v>
       </c>
       <c r="F256" t="s">
         <v>27</v>
       </c>
       <c r="G256" t="s">
-        <v>216</v>
+        <v>112</v>
       </c>
       <c r="H256" t="s">
         <v>16</v>
@@ -9447,7 +9462,7 @@
         <v>17</v>
       </c>
       <c r="K256">
-        <v>76</v>
+        <v>98</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -9455,22 +9470,22 @@
         <v>11</v>
       </c>
       <c r="B257">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C257">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D257" t="s">
-        <v>83</v>
+        <v>142</v>
       </c>
       <c r="E257" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="F257" t="s">
         <v>14</v>
       </c>
       <c r="G257" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H257" t="s">
         <v>16</v>
@@ -9479,7 +9494,7 @@
         <v>17</v>
       </c>
       <c r="K257">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="258" spans="1:11" x14ac:dyDescent="0.25">
@@ -9490,19 +9505,19 @@
         <v>2</v>
       </c>
       <c r="C258">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="D258" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="E258" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="F258" t="s">
         <v>14</v>
       </c>
       <c r="G258" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H258" t="s">
         <v>16</v>
@@ -9511,7 +9526,7 @@
         <v>17</v>
       </c>
       <c r="K258">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="259" spans="1:11" x14ac:dyDescent="0.25">
@@ -9519,22 +9534,22 @@
         <v>20</v>
       </c>
       <c r="B259">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C259">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="D259" t="s">
-        <v>235</v>
+        <v>126</v>
       </c>
       <c r="E259" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="F259" t="s">
         <v>14</v>
       </c>
       <c r="G259" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H259" t="s">
         <v>16</v>
@@ -9543,7 +9558,7 @@
         <v>17</v>
       </c>
       <c r="K259">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="260" spans="1:11" x14ac:dyDescent="0.25">
@@ -9551,22 +9566,22 @@
         <v>22</v>
       </c>
       <c r="B260">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C260">
-        <v>77</v>
+        <v>35</v>
       </c>
       <c r="D260" t="s">
-        <v>80</v>
+        <v>138</v>
       </c>
       <c r="E260" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="F260" t="s">
         <v>14</v>
       </c>
       <c r="G260" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H260" t="s">
         <v>16</v>
@@ -9575,7 +9590,7 @@
         <v>17</v>
       </c>
       <c r="K260">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="261" spans="1:11" x14ac:dyDescent="0.25">
@@ -9592,13 +9607,13 @@
         <v>19</v>
       </c>
       <c r="E261" t="s">
-        <v>79</v>
+        <v>141</v>
       </c>
       <c r="F261" t="s">
         <v>14</v>
       </c>
       <c r="G261" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H261" t="s">
         <v>16</v>
@@ -9607,7 +9622,7 @@
         <v>17</v>
       </c>
       <c r="K261">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="262" spans="1:11" x14ac:dyDescent="0.25">
@@ -9615,22 +9630,22 @@
         <v>11</v>
       </c>
       <c r="B262">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C262">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="D262" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="E262" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="F262" t="s">
         <v>27</v>
       </c>
       <c r="G262" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H262" t="s">
         <v>16</v>
@@ -9639,7 +9654,7 @@
         <v>17</v>
       </c>
       <c r="K262">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
@@ -9650,19 +9665,19 @@
         <v>4</v>
       </c>
       <c r="C263">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="D263" t="s">
-        <v>242</v>
+        <v>120</v>
       </c>
       <c r="E263" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="F263" t="s">
         <v>27</v>
       </c>
       <c r="G263" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H263" t="s">
         <v>16</v>
@@ -9671,7 +9686,7 @@
         <v>17</v>
       </c>
       <c r="K263">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
@@ -9679,22 +9694,22 @@
         <v>20</v>
       </c>
       <c r="B264">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C264">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D264" t="s">
-        <v>149</v>
+        <v>251</v>
       </c>
       <c r="E264" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="F264" t="s">
         <v>27</v>
       </c>
       <c r="G264" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H264" t="s">
         <v>16</v>
@@ -9703,7 +9718,7 @@
         <v>17</v>
       </c>
       <c r="K264">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
@@ -9711,22 +9726,22 @@
         <v>22</v>
       </c>
       <c r="B265">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C265">
-        <v>94</v>
+        <v>66</v>
       </c>
       <c r="D265" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="E265" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="F265" t="s">
         <v>27</v>
       </c>
       <c r="G265" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H265" t="s">
         <v>16</v>
@@ -9735,7 +9750,7 @@
         <v>17</v>
       </c>
       <c r="K265">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
@@ -9752,13 +9767,13 @@
         <v>19</v>
       </c>
       <c r="E266" t="s">
-        <v>77</v>
+        <v>139</v>
       </c>
       <c r="F266" t="s">
         <v>27</v>
       </c>
       <c r="G266" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H266" t="s">
         <v>16</v>
@@ -9767,7 +9782,7 @@
         <v>17</v>
       </c>
       <c r="K266">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
@@ -9775,22 +9790,22 @@
         <v>11</v>
       </c>
       <c r="B267">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C267">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="D267" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
       <c r="E267" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="F267" t="s">
         <v>27</v>
       </c>
       <c r="G267" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H267" t="s">
         <v>16</v>
@@ -9798,11 +9813,8 @@
       <c r="I267" t="s">
         <v>17</v>
       </c>
-      <c r="J267" t="s">
-        <v>240</v>
-      </c>
       <c r="K267">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
@@ -9813,19 +9825,19 @@
         <v>4</v>
       </c>
       <c r="C268">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D268" t="s">
-        <v>19</v>
+        <v>137</v>
       </c>
       <c r="E268" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="F268" t="s">
         <v>27</v>
       </c>
       <c r="G268" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H268" t="s">
         <v>16</v>
@@ -9834,7 +9846,7 @@
         <v>17</v>
       </c>
       <c r="K268">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
@@ -9842,22 +9854,22 @@
         <v>20</v>
       </c>
       <c r="B269">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="C269">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="D269" t="s">
-        <v>239</v>
+        <v>205</v>
       </c>
       <c r="E269" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="F269" t="s">
         <v>27</v>
       </c>
       <c r="G269" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H269" t="s">
         <v>16</v>
@@ -9866,7 +9878,7 @@
         <v>17</v>
       </c>
       <c r="K269">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
@@ -9874,22 +9886,22 @@
         <v>22</v>
       </c>
       <c r="B270">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="C270">
-        <v>22</v>
+        <v>50</v>
       </c>
       <c r="D270" t="s">
-        <v>238</v>
+        <v>52</v>
       </c>
       <c r="E270" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="F270" t="s">
         <v>27</v>
       </c>
       <c r="G270" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H270" t="s">
         <v>16</v>
@@ -9898,7 +9910,7 @@
         <v>17</v>
       </c>
       <c r="K270">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
@@ -9915,13 +9927,13 @@
         <v>19</v>
       </c>
       <c r="E271" t="s">
-        <v>76</v>
+        <v>135</v>
       </c>
       <c r="F271" t="s">
         <v>27</v>
       </c>
       <c r="G271" t="s">
-        <v>75</v>
+        <v>134</v>
       </c>
       <c r="H271" t="s">
         <v>16</v>
@@ -9930,7 +9942,7 @@
         <v>17</v>
       </c>
       <c r="K271">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/data/historico_comisiones.xlsx
+++ b/data/historico_comisiones.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://sercomunicaciones2-my.sharepoint.com/personal/auxcomisiones_sercomunicaciones_com/Documents/PAOLA/AUXCOMISIÓN/3 Liquidación CVS comerciales/2026/02 Febrero/Liquidacióncvs - liquidación/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_37DD5EEF9561BE0E62355476585DCE3A8747A48A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4BEC9DE7-4DD9-4128-B18B-C0CEE17D8E03}"/>
+  <xr:revisionPtr revIDLastSave="15" documentId="11_37DD5EEF9561BE0E62355476585DCE3A8747A48A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{29D6E704-B639-4A3E-8B05-D297D7A1E5C2}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1935" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2043" uniqueCount="270">
   <si>
     <t>Producto</t>
   </si>
@@ -106,12 +106,6 @@
     <t>ASESOR</t>
   </si>
   <si>
-    <t>Elaboró 18 días</t>
-  </si>
-  <si>
-    <t>35%</t>
-  </si>
-  <si>
     <t>meta 68 %cump.47%</t>
   </si>
   <si>
@@ -797,6 +791,45 @@
   </si>
   <si>
     <t>12%</t>
+  </si>
+  <si>
+    <t>Elaboró 18 días puntos 975</t>
+  </si>
+  <si>
+    <t>117%</t>
+  </si>
+  <si>
+    <t>8%</t>
+  </si>
+  <si>
+    <t>Johan Daniel Herrera Mazo</t>
+  </si>
+  <si>
+    <t>NUMERARIO</t>
+  </si>
+  <si>
+    <t>1 día en Envigado y 1 día en Junín</t>
+  </si>
+  <si>
+    <t>Kelly Yuliana Ospina Saldarriaga</t>
+  </si>
+  <si>
+    <t>1%</t>
+  </si>
+  <si>
+    <t>11%</t>
+  </si>
+  <si>
+    <t>3%</t>
+  </si>
+  <si>
+    <t>Sara Julieth Acevedo Gutierrez</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 días en Barbosa </t>
+  </si>
+  <si>
+    <t>6 días en Dabeiba</t>
   </si>
 </sst>
 </file>
@@ -1159,10 +1192,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K271"/>
+  <dimension ref="A1:K286"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="45.42578125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="50" bestFit="1" customWidth="1"/>
@@ -1214,16 +1248,16 @@
         <v>7</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="E2" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F2" t="s">
         <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H2" t="s">
         <v>16</v>
@@ -1246,16 +1280,16 @@
         <v>5</v>
       </c>
       <c r="D3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E3" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F3" t="s">
         <v>14</v>
       </c>
       <c r="G3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H3" t="s">
         <v>16</v>
@@ -1278,16 +1312,16 @@
         <v>32</v>
       </c>
       <c r="D4" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="E4" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F4" t="s">
         <v>14</v>
       </c>
       <c r="G4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H4" t="s">
         <v>16</v>
@@ -1310,16 +1344,16 @@
         <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="E5" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F5" t="s">
         <v>14</v>
       </c>
       <c r="G5" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H5" t="s">
         <v>16</v>
@@ -1345,13 +1379,13 @@
         <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F6" t="s">
         <v>14</v>
       </c>
       <c r="G6" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H6" t="s">
         <v>16</v>
@@ -1374,16 +1408,16 @@
         <v>8</v>
       </c>
       <c r="D7" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E7" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F7" t="s">
         <v>27</v>
       </c>
       <c r="G7" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H7" t="s">
         <v>16</v>
@@ -1406,16 +1440,16 @@
         <v>4</v>
       </c>
       <c r="D8" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E8" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F8" t="s">
         <v>27</v>
       </c>
       <c r="G8" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H8" t="s">
         <v>16</v>
@@ -1438,16 +1472,16 @@
         <v>28</v>
       </c>
       <c r="D9" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="E9" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F9" t="s">
         <v>27</v>
       </c>
       <c r="G9" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H9" t="s">
         <v>16</v>
@@ -1470,16 +1504,16 @@
         <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E10" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F10" t="s">
         <v>27</v>
       </c>
       <c r="G10" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H10" t="s">
         <v>16</v>
@@ -1505,13 +1539,13 @@
         <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F11" t="s">
         <v>27</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H11" t="s">
         <v>16</v>
@@ -1534,16 +1568,16 @@
         <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="E12" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F12" t="s">
         <v>14</v>
       </c>
       <c r="G12" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H12" t="s">
         <v>16</v>
@@ -1566,16 +1600,16 @@
         <v>12</v>
       </c>
       <c r="D13" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="E13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F13" t="s">
         <v>14</v>
       </c>
       <c r="G13" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H13" t="s">
         <v>16</v>
@@ -1598,16 +1632,16 @@
         <v>17</v>
       </c>
       <c r="D14" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F14" t="s">
         <v>14</v>
       </c>
       <c r="G14" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H14" t="s">
         <v>16</v>
@@ -1630,16 +1664,16 @@
         <v>32</v>
       </c>
       <c r="D15" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="E15" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F15" t="s">
         <v>14</v>
       </c>
       <c r="G15" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H15" t="s">
         <v>16</v>
@@ -1665,13 +1699,13 @@
         <v>19</v>
       </c>
       <c r="E16" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F16" t="s">
         <v>14</v>
       </c>
       <c r="G16" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H16" t="s">
         <v>16</v>
@@ -1694,16 +1728,16 @@
         <v>18</v>
       </c>
       <c r="D17" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F17" t="s">
         <v>27</v>
       </c>
       <c r="G17" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H17" t="s">
         <v>16</v>
@@ -1726,16 +1760,16 @@
         <v>8</v>
       </c>
       <c r="D18" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E18" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F18" t="s">
         <v>27</v>
       </c>
       <c r="G18" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H18" t="s">
         <v>16</v>
@@ -1758,16 +1792,16 @@
         <v>31</v>
       </c>
       <c r="D19" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E19" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F19" t="s">
         <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H19" t="s">
         <v>16</v>
@@ -1790,16 +1824,16 @@
         <v>44</v>
       </c>
       <c r="D20" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E20" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F20" t="s">
         <v>27</v>
       </c>
       <c r="G20" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H20" t="s">
         <v>16</v>
@@ -1825,13 +1859,13 @@
         <v>19</v>
       </c>
       <c r="E21" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F21" t="s">
         <v>27</v>
       </c>
       <c r="G21" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H21" t="s">
         <v>16</v>
@@ -1854,16 +1888,16 @@
         <v>17</v>
       </c>
       <c r="D22" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F22" t="s">
         <v>27</v>
       </c>
       <c r="G22" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H22" t="s">
         <v>16</v>
@@ -1886,16 +1920,16 @@
         <v>13</v>
       </c>
       <c r="D23" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E23" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F23" t="s">
         <v>27</v>
       </c>
       <c r="G23" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H23" t="s">
         <v>16</v>
@@ -1918,16 +1952,16 @@
         <v>38</v>
       </c>
       <c r="D24" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="E24" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F24" t="s">
         <v>27</v>
       </c>
       <c r="G24" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H24" t="s">
         <v>16</v>
@@ -1950,16 +1984,16 @@
         <v>50</v>
       </c>
       <c r="D25" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E25" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F25" t="s">
         <v>27</v>
       </c>
       <c r="G25" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H25" t="s">
         <v>16</v>
@@ -1985,13 +2019,13 @@
         <v>19</v>
       </c>
       <c r="E26" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F26" t="s">
         <v>27</v>
       </c>
       <c r="G26" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H26" t="s">
         <v>16</v>
@@ -2014,16 +2048,16 @@
         <v>19</v>
       </c>
       <c r="D27" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E27" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F27" t="s">
         <v>14</v>
       </c>
       <c r="G27" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H27" t="s">
         <v>16</v>
@@ -2049,13 +2083,13 @@
         <v>19</v>
       </c>
       <c r="E28" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F28" t="s">
         <v>14</v>
       </c>
       <c r="G28" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H28" t="s">
         <v>16</v>
@@ -2078,16 +2112,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E29" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F29" t="s">
         <v>14</v>
       </c>
       <c r="G29" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H29" t="s">
         <v>16</v>
@@ -2110,16 +2144,16 @@
         <v>56</v>
       </c>
       <c r="D30" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E30" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F30" t="s">
         <v>14</v>
       </c>
       <c r="G30" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H30" t="s">
         <v>16</v>
@@ -2145,13 +2179,13 @@
         <v>19</v>
       </c>
       <c r="E31" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F31" t="s">
         <v>14</v>
       </c>
       <c r="G31" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H31" t="s">
         <v>16</v>
@@ -2174,16 +2208,16 @@
         <v>28</v>
       </c>
       <c r="D32" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E32" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F32" t="s">
         <v>27</v>
       </c>
       <c r="G32" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H32" t="s">
         <v>16</v>
@@ -2206,16 +2240,16 @@
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="E33" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F33" t="s">
         <v>27</v>
       </c>
       <c r="G33" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H33" t="s">
         <v>16</v>
@@ -2238,16 +2272,16 @@
         <v>55</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E34" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F34" t="s">
         <v>27</v>
       </c>
       <c r="G34" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H34" t="s">
         <v>16</v>
@@ -2270,16 +2304,16 @@
         <v>75</v>
       </c>
       <c r="D35" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="E35" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F35" t="s">
         <v>27</v>
       </c>
       <c r="G35" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H35" t="s">
         <v>16</v>
@@ -2305,13 +2339,13 @@
         <v>19</v>
       </c>
       <c r="E36" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="F36" t="s">
         <v>27</v>
       </c>
       <c r="G36" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H36" t="s">
         <v>16</v>
@@ -2334,16 +2368,16 @@
         <v>32</v>
       </c>
       <c r="D37" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="E37" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F37" t="s">
         <v>27</v>
       </c>
       <c r="G37" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H37" t="s">
         <v>16</v>
@@ -2366,16 +2400,16 @@
         <v>17</v>
       </c>
       <c r="D38" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E38" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F38" t="s">
         <v>27</v>
       </c>
       <c r="G38" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H38" t="s">
         <v>16</v>
@@ -2398,16 +2432,16 @@
         <v>42</v>
       </c>
       <c r="D39" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="E39" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F39" t="s">
         <v>27</v>
       </c>
       <c r="G39" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H39" t="s">
         <v>16</v>
@@ -2430,16 +2464,16 @@
         <v>63</v>
       </c>
       <c r="D40" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E40" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F40" t="s">
         <v>27</v>
       </c>
       <c r="G40" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H40" t="s">
         <v>16</v>
@@ -2465,13 +2499,13 @@
         <v>19</v>
       </c>
       <c r="E41" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F41" t="s">
         <v>27</v>
       </c>
       <c r="G41" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H41" t="s">
         <v>16</v>
@@ -2494,16 +2528,16 @@
         <v>6</v>
       </c>
       <c r="D42" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="E42" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F42" t="s">
         <v>14</v>
       </c>
       <c r="G42" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H42" t="s">
         <v>16</v>
@@ -2529,13 +2563,13 @@
         <v>19</v>
       </c>
       <c r="E43" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F43" t="s">
         <v>14</v>
       </c>
       <c r="G43" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H43" t="s">
         <v>16</v>
@@ -2558,16 +2592,16 @@
         <v>30</v>
       </c>
       <c r="D44" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E44" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F44" t="s">
         <v>14</v>
       </c>
       <c r="G44" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H44" t="s">
         <v>16</v>
@@ -2590,16 +2624,16 @@
         <v>22</v>
       </c>
       <c r="D45" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E45" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F45" t="s">
         <v>14</v>
       </c>
       <c r="G45" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H45" t="s">
         <v>16</v>
@@ -2625,13 +2659,13 @@
         <v>19</v>
       </c>
       <c r="E46" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="F46" t="s">
         <v>14</v>
       </c>
       <c r="G46" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H46" t="s">
         <v>16</v>
@@ -2654,16 +2688,16 @@
         <v>12</v>
       </c>
       <c r="D47" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E47" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F47" t="s">
         <v>14</v>
       </c>
       <c r="G47" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H47" t="s">
         <v>16</v>
@@ -2686,16 +2720,16 @@
         <v>4</v>
       </c>
       <c r="D48" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E48" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F48" t="s">
         <v>14</v>
       </c>
       <c r="G48" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H48" t="s">
         <v>16</v>
@@ -2718,16 +2752,16 @@
         <v>27</v>
       </c>
       <c r="D49" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E49" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F49" t="s">
         <v>14</v>
       </c>
       <c r="G49" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H49" t="s">
         <v>16</v>
@@ -2750,16 +2784,16 @@
         <v>44</v>
       </c>
       <c r="D50" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E50" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F50" t="s">
         <v>14</v>
       </c>
       <c r="G50" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H50" t="s">
         <v>16</v>
@@ -2785,13 +2819,13 @@
         <v>19</v>
       </c>
       <c r="E51" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F51" t="s">
         <v>14</v>
       </c>
       <c r="G51" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H51" t="s">
         <v>16</v>
@@ -2814,16 +2848,16 @@
         <v>12</v>
       </c>
       <c r="D52" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E52" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F52" t="s">
         <v>27</v>
       </c>
       <c r="G52" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H52" t="s">
         <v>16</v>
@@ -2846,16 +2880,16 @@
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="E53" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F53" t="s">
         <v>27</v>
       </c>
       <c r="G53" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H53" t="s">
         <v>16</v>
@@ -2878,16 +2912,16 @@
         <v>33</v>
       </c>
       <c r="D54" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E54" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F54" t="s">
         <v>27</v>
       </c>
       <c r="G54" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H54" t="s">
         <v>16</v>
@@ -2910,16 +2944,16 @@
         <v>79</v>
       </c>
       <c r="D55" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E55" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F55" t="s">
         <v>27</v>
       </c>
       <c r="G55" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H55" t="s">
         <v>16</v>
@@ -2945,13 +2979,13 @@
         <v>19</v>
       </c>
       <c r="E56" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F56" t="s">
         <v>27</v>
       </c>
       <c r="G56" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="H56" t="s">
         <v>16</v>
@@ -2974,25 +3008,25 @@
         <v>4</v>
       </c>
       <c r="D57" t="s">
+        <v>31</v>
+      </c>
+      <c r="E57" t="s">
+        <v>32</v>
+      </c>
+      <c r="F57" t="s">
+        <v>14</v>
+      </c>
+      <c r="G57" t="s">
         <v>33</v>
       </c>
-      <c r="E57" t="s">
+      <c r="H57" t="s">
+        <v>16</v>
+      </c>
+      <c r="I57" t="s">
+        <v>17</v>
+      </c>
+      <c r="J57" t="s">
         <v>34</v>
-      </c>
-      <c r="F57" t="s">
-        <v>14</v>
-      </c>
-      <c r="G57" t="s">
-        <v>35</v>
-      </c>
-      <c r="H57" t="s">
-        <v>16</v>
-      </c>
-      <c r="I57" t="s">
-        <v>17</v>
-      </c>
-      <c r="J57" t="s">
-        <v>36</v>
       </c>
       <c r="K57">
         <v>58</v>
@@ -3012,13 +3046,13 @@
         <v>19</v>
       </c>
       <c r="E58" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F58" t="s">
         <v>14</v>
       </c>
       <c r="G58" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H58" t="s">
         <v>16</v>
@@ -3041,16 +3075,16 @@
         <v>12</v>
       </c>
       <c r="D59" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E59" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F59" t="s">
         <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H59" t="s">
         <v>16</v>
@@ -3059,7 +3093,7 @@
         <v>17</v>
       </c>
       <c r="J59" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="K59">
         <v>58</v>
@@ -3076,16 +3110,16 @@
         <v>8</v>
       </c>
       <c r="D60" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E60" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F60" t="s">
         <v>14</v>
       </c>
       <c r="G60" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H60" t="s">
         <v>16</v>
@@ -3094,7 +3128,7 @@
         <v>17</v>
       </c>
       <c r="J60" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K60">
         <v>58</v>
@@ -3114,13 +3148,13 @@
         <v>19</v>
       </c>
       <c r="E61" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F61" t="s">
         <v>14</v>
       </c>
       <c r="G61" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H61" t="s">
         <v>16</v>
@@ -3129,7 +3163,7 @@
         <v>17</v>
       </c>
       <c r="J61" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="K61">
         <v>58</v>
@@ -3146,16 +3180,16 @@
         <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E62" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F62" t="s">
         <v>27</v>
       </c>
       <c r="G62" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H62" t="s">
         <v>16</v>
@@ -3181,13 +3215,13 @@
         <v>19</v>
       </c>
       <c r="E63" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F63" t="s">
         <v>27</v>
       </c>
       <c r="G63" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H63" t="s">
         <v>16</v>
@@ -3210,16 +3244,16 @@
         <v>31</v>
       </c>
       <c r="D64" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E64" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F64" t="s">
         <v>27</v>
       </c>
       <c r="G64" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H64" t="s">
         <v>16</v>
@@ -3242,16 +3276,16 @@
         <v>27</v>
       </c>
       <c r="D65" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E65" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F65" t="s">
         <v>27</v>
       </c>
       <c r="G65" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H65" t="s">
         <v>16</v>
@@ -3277,13 +3311,13 @@
         <v>19</v>
       </c>
       <c r="E66" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F66" t="s">
         <v>27</v>
       </c>
       <c r="G66" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="H66" t="s">
         <v>16</v>
@@ -3306,16 +3340,16 @@
         <v>21</v>
       </c>
       <c r="D67" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="E67" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F67" t="s">
         <v>14</v>
       </c>
       <c r="G67" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H67" t="s">
         <v>16</v>
@@ -3338,16 +3372,16 @@
         <v>4</v>
       </c>
       <c r="D68" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="E68" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F68" t="s">
         <v>14</v>
       </c>
       <c r="G68" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H68" t="s">
         <v>16</v>
@@ -3370,16 +3404,16 @@
         <v>21</v>
       </c>
       <c r="D69" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E69" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F69" t="s">
         <v>14</v>
       </c>
       <c r="G69" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H69" t="s">
         <v>16</v>
@@ -3402,16 +3436,16 @@
         <v>51</v>
       </c>
       <c r="D70" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="E70" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F70" t="s">
         <v>14</v>
       </c>
       <c r="G70" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H70" t="s">
         <v>16</v>
@@ -3437,13 +3471,13 @@
         <v>19</v>
       </c>
       <c r="E71" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="F71" t="s">
         <v>14</v>
       </c>
       <c r="G71" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H71" t="s">
         <v>16</v>
@@ -3466,16 +3500,16 @@
         <v>18</v>
       </c>
       <c r="D72" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="E72" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F72" t="s">
         <v>27</v>
       </c>
       <c r="G72" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H72" t="s">
         <v>16</v>
@@ -3498,16 +3532,16 @@
         <v>1</v>
       </c>
       <c r="D73" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E73" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F73" t="s">
         <v>27</v>
       </c>
       <c r="G73" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H73" t="s">
         <v>16</v>
@@ -3530,16 +3564,16 @@
         <v>15</v>
       </c>
       <c r="D74" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="E74" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F74" t="s">
         <v>27</v>
       </c>
       <c r="G74" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H74" t="s">
         <v>16</v>
@@ -3562,16 +3596,16 @@
         <v>48</v>
       </c>
       <c r="D75" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="E75" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F75" t="s">
         <v>27</v>
       </c>
       <c r="G75" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H75" t="s">
         <v>16</v>
@@ -3597,13 +3631,13 @@
         <v>19</v>
       </c>
       <c r="E76" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="F76" t="s">
         <v>27</v>
       </c>
       <c r="G76" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H76" t="s">
         <v>16</v>
@@ -3626,16 +3660,16 @@
         <v>24</v>
       </c>
       <c r="D77" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E77" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F77" t="s">
         <v>14</v>
       </c>
       <c r="G77" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H77" t="s">
         <v>16</v>
@@ -3658,16 +3692,16 @@
         <v>23</v>
       </c>
       <c r="D78" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="E78" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F78" t="s">
         <v>14</v>
       </c>
       <c r="G78" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H78" t="s">
         <v>16</v>
@@ -3693,13 +3727,13 @@
         <v>21</v>
       </c>
       <c r="E79" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F79" t="s">
         <v>14</v>
       </c>
       <c r="G79" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H79" t="s">
         <v>16</v>
@@ -3725,13 +3759,13 @@
         <v>23</v>
       </c>
       <c r="E80" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F80" t="s">
         <v>14</v>
       </c>
       <c r="G80" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H80" t="s">
         <v>16</v>
@@ -3757,13 +3791,13 @@
         <v>19</v>
       </c>
       <c r="E81" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="F81" t="s">
         <v>14</v>
       </c>
       <c r="G81" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H81" t="s">
         <v>16</v>
@@ -3786,16 +3820,16 @@
         <v>30</v>
       </c>
       <c r="D82" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="E82" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F82" t="s">
         <v>27</v>
       </c>
       <c r="G82" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H82" t="s">
         <v>16</v>
@@ -3818,16 +3852,16 @@
         <v>9</v>
       </c>
       <c r="D83" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E83" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F83" t="s">
         <v>27</v>
       </c>
       <c r="G83" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H83" t="s">
         <v>16</v>
@@ -3850,16 +3884,16 @@
         <v>40</v>
       </c>
       <c r="D84" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="E84" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F84" t="s">
         <v>27</v>
       </c>
       <c r="G84" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H84" t="s">
         <v>16</v>
@@ -3885,13 +3919,13 @@
         <v>23</v>
       </c>
       <c r="E85" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F85" t="s">
         <v>27</v>
       </c>
       <c r="G85" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H85" t="s">
         <v>16</v>
@@ -3917,13 +3951,13 @@
         <v>19</v>
       </c>
       <c r="E86" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="F86" t="s">
         <v>27</v>
       </c>
       <c r="G86" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H86" t="s">
         <v>16</v>
@@ -3946,16 +3980,16 @@
         <v>36</v>
       </c>
       <c r="D87" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E87" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F87" t="s">
         <v>27</v>
       </c>
       <c r="G87" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H87" t="s">
         <v>16</v>
@@ -3964,7 +3998,7 @@
         <v>17</v>
       </c>
       <c r="J87" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="K87">
         <v>80</v>
@@ -3981,16 +4015,16 @@
         <v>1</v>
       </c>
       <c r="D88" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="E88" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F88" t="s">
         <v>27</v>
       </c>
       <c r="G88" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H88" t="s">
         <v>16</v>
@@ -3999,7 +4033,7 @@
         <v>17</v>
       </c>
       <c r="J88" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="K88">
         <v>80</v>
@@ -4016,25 +4050,25 @@
         <v>27</v>
       </c>
       <c r="D89" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E89" t="s">
+        <v>97</v>
+      </c>
+      <c r="F89" t="s">
+        <v>27</v>
+      </c>
+      <c r="G89" t="s">
+        <v>96</v>
+      </c>
+      <c r="H89" t="s">
+        <v>16</v>
+      </c>
+      <c r="I89" t="s">
+        <v>17</v>
+      </c>
+      <c r="J89" t="s">
         <v>99</v>
-      </c>
-      <c r="F89" t="s">
-        <v>27</v>
-      </c>
-      <c r="G89" t="s">
-        <v>98</v>
-      </c>
-      <c r="H89" t="s">
-        <v>16</v>
-      </c>
-      <c r="I89" t="s">
-        <v>17</v>
-      </c>
-      <c r="J89" t="s">
-        <v>101</v>
       </c>
       <c r="K89">
         <v>80</v>
@@ -4051,16 +4085,16 @@
         <v>76</v>
       </c>
       <c r="D90" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E90" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F90" t="s">
         <v>27</v>
       </c>
       <c r="G90" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H90" t="s">
         <v>16</v>
@@ -4086,13 +4120,13 @@
         <v>19</v>
       </c>
       <c r="E91" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F91" t="s">
         <v>27</v>
       </c>
       <c r="G91" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H91" t="s">
         <v>16</v>
@@ -4101,7 +4135,7 @@
         <v>17</v>
       </c>
       <c r="J91" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="K91">
         <v>80</v>
@@ -4112,22 +4146,22 @@
         <v>11</v>
       </c>
       <c r="B92">
-        <v>13</v>
+        <v>840</v>
       </c>
       <c r="C92">
-        <v>14</v>
+        <v>988</v>
       </c>
       <c r="D92" t="s">
-        <v>12</v>
+        <v>84</v>
       </c>
       <c r="E92" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="F92" t="s">
         <v>14</v>
       </c>
       <c r="G92" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="H92" t="s">
         <v>16</v>
@@ -4136,7 +4170,7 @@
         <v>17</v>
       </c>
       <c r="K92">
-        <v>62</v>
+        <v>79</v>
       </c>
     </row>
     <row r="93" spans="1:11" x14ac:dyDescent="0.25">
@@ -4144,22 +4178,22 @@
         <v>18</v>
       </c>
       <c r="B93">
-        <v>0</v>
+        <v>131</v>
       </c>
       <c r="C93">
-        <v>0</v>
+        <v>231</v>
       </c>
       <c r="D93" t="s">
-        <v>19</v>
+        <v>94</v>
       </c>
       <c r="E93" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="F93" t="s">
         <v>14</v>
       </c>
       <c r="G93" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="H93" t="s">
         <v>16</v>
@@ -4168,7 +4202,7 @@
         <v>17</v>
       </c>
       <c r="K93">
-        <v>62</v>
+        <v>79</v>
       </c>
     </row>
     <row r="94" spans="1:11" x14ac:dyDescent="0.25">
@@ -4176,23 +4210,23 @@
         <v>20</v>
       </c>
       <c r="B94">
+        <v>2433</v>
+      </c>
+      <c r="C94">
+        <v>1767</v>
+      </c>
+      <c r="D94" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" t="s">
+        <v>92</v>
+      </c>
+      <c r="F94" t="s">
+        <v>14</v>
+      </c>
+      <c r="G94" t="s">
         <v>91</v>
       </c>
-      <c r="C94">
-        <v>82</v>
-      </c>
-      <c r="D94" t="s">
-        <v>21</v>
-      </c>
-      <c r="E94" t="s">
-        <v>13</v>
-      </c>
-      <c r="F94" t="s">
-        <v>14</v>
-      </c>
-      <c r="G94" t="s">
-        <v>15</v>
-      </c>
       <c r="H94" t="s">
         <v>16</v>
       </c>
@@ -4200,7 +4234,7 @@
         <v>17</v>
       </c>
       <c r="K94">
-        <v>62</v>
+        <v>79</v>
       </c>
     </row>
     <row r="95" spans="1:11" x14ac:dyDescent="0.25">
@@ -4208,22 +4242,22 @@
         <v>22</v>
       </c>
       <c r="B95">
-        <v>49</v>
+        <v>2738</v>
       </c>
       <c r="C95">
-        <v>62</v>
+        <v>3162</v>
       </c>
       <c r="D95" t="s">
-        <v>23</v>
+        <v>93</v>
       </c>
       <c r="E95" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="F95" t="s">
         <v>14</v>
       </c>
       <c r="G95" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="H95" t="s">
         <v>16</v>
@@ -4232,7 +4266,7 @@
         <v>17</v>
       </c>
       <c r="K95">
-        <v>62</v>
+        <v>79</v>
       </c>
     </row>
     <row r="96" spans="1:11" x14ac:dyDescent="0.25">
@@ -4240,7 +4274,7 @@
         <v>24</v>
       </c>
       <c r="B96">
-        <v>750</v>
+        <v>27700</v>
       </c>
       <c r="C96">
         <v>0</v>
@@ -4249,13 +4283,13 @@
         <v>19</v>
       </c>
       <c r="E96" t="s">
-        <v>13</v>
+        <v>92</v>
       </c>
       <c r="F96" t="s">
         <v>14</v>
       </c>
       <c r="G96" t="s">
-        <v>15</v>
+        <v>91</v>
       </c>
       <c r="H96" t="s">
         <v>16</v>
@@ -4264,10 +4298,10 @@
         <v>17</v>
       </c>
       <c r="J96" t="s">
-        <v>25</v>
+        <v>90</v>
       </c>
       <c r="K96">
-        <v>62</v>
+        <v>79</v>
       </c>
     </row>
     <row r="97" spans="1:11" x14ac:dyDescent="0.25">
@@ -4278,19 +4312,19 @@
         <v>13</v>
       </c>
       <c r="C97">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="D97" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="E97" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="F97" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G97" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="H97" t="s">
         <v>16</v>
@@ -4298,11 +4332,8 @@
       <c r="I97" t="s">
         <v>17</v>
       </c>
-      <c r="J97" t="s">
-        <v>28</v>
-      </c>
       <c r="K97">
-        <v>62</v>
+        <v>101</v>
       </c>
     </row>
     <row r="98" spans="1:11" x14ac:dyDescent="0.25">
@@ -4310,22 +4341,22 @@
         <v>18</v>
       </c>
       <c r="B98">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C98">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>19</v>
+        <v>48</v>
       </c>
       <c r="E98" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="F98" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G98" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="H98" t="s">
         <v>16</v>
@@ -4334,7 +4365,7 @@
         <v>17</v>
       </c>
       <c r="K98">
-        <v>62</v>
+        <v>101</v>
       </c>
     </row>
     <row r="99" spans="1:11" x14ac:dyDescent="0.25">
@@ -4342,22 +4373,22 @@
         <v>20</v>
       </c>
       <c r="B99">
-        <v>91</v>
+        <v>29</v>
       </c>
       <c r="C99">
-        <v>32</v>
+        <v>15</v>
       </c>
       <c r="D99" t="s">
-        <v>29</v>
+        <v>89</v>
       </c>
       <c r="E99" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="F99" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G99" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="H99" t="s">
         <v>16</v>
@@ -4365,11 +4396,8 @@
       <c r="I99" t="s">
         <v>17</v>
       </c>
-      <c r="J99" t="s">
-        <v>30</v>
-      </c>
       <c r="K99">
-        <v>62</v>
+        <v>101</v>
       </c>
     </row>
     <row r="100" spans="1:11" x14ac:dyDescent="0.25">
@@ -4377,22 +4405,22 @@
         <v>22</v>
       </c>
       <c r="B100">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C100">
-        <v>30</v>
+        <v>63</v>
       </c>
       <c r="D100" t="s">
-        <v>31</v>
+        <v>79</v>
       </c>
       <c r="E100" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="F100" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G100" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="H100" t="s">
         <v>16</v>
@@ -4400,11 +4428,8 @@
       <c r="I100" t="s">
         <v>17</v>
       </c>
-      <c r="J100" t="s">
-        <v>32</v>
-      </c>
       <c r="K100">
-        <v>62</v>
+        <v>101</v>
       </c>
     </row>
     <row r="101" spans="1:11" x14ac:dyDescent="0.25">
@@ -4412,7 +4437,7 @@
         <v>24</v>
       </c>
       <c r="B101">
-        <v>750</v>
+        <v>480</v>
       </c>
       <c r="C101">
         <v>0</v>
@@ -4421,13 +4446,13 @@
         <v>19</v>
       </c>
       <c r="E101" t="s">
-        <v>26</v>
+        <v>88</v>
       </c>
       <c r="F101" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G101" t="s">
-        <v>15</v>
+        <v>82</v>
       </c>
       <c r="H101" t="s">
         <v>16</v>
@@ -4435,11 +4460,8 @@
       <c r="I101" t="s">
         <v>17</v>
       </c>
-      <c r="J101" t="s">
-        <v>25</v>
-      </c>
       <c r="K101">
-        <v>62</v>
+        <v>101</v>
       </c>
     </row>
     <row r="102" spans="1:11" x14ac:dyDescent="0.25">
@@ -4447,22 +4469,22 @@
         <v>11</v>
       </c>
       <c r="B102">
-        <v>840</v>
+        <v>19</v>
       </c>
       <c r="C102">
-        <v>988</v>
+        <v>25</v>
       </c>
       <c r="D102" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E102" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F102" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G102" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H102" t="s">
         <v>16</v>
@@ -4471,7 +4493,7 @@
         <v>17</v>
       </c>
       <c r="K102">
-        <v>79</v>
+        <v>101</v>
       </c>
     </row>
     <row r="103" spans="1:11" x14ac:dyDescent="0.25">
@@ -4479,22 +4501,22 @@
         <v>18</v>
       </c>
       <c r="B103">
-        <v>131</v>
+        <v>4</v>
       </c>
       <c r="C103">
-        <v>231</v>
+        <v>5</v>
       </c>
       <c r="D103" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
       <c r="E103" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F103" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G103" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H103" t="s">
         <v>16</v>
@@ -4503,7 +4525,7 @@
         <v>17</v>
       </c>
       <c r="K103">
-        <v>79</v>
+        <v>101</v>
       </c>
     </row>
     <row r="104" spans="1:11" x14ac:dyDescent="0.25">
@@ -4511,22 +4533,22 @@
         <v>20</v>
       </c>
       <c r="B104">
-        <v>2433</v>
+        <v>44</v>
       </c>
       <c r="C104">
-        <v>1767</v>
+        <v>38</v>
       </c>
       <c r="D104" t="s">
-        <v>71</v>
+        <v>85</v>
       </c>
       <c r="E104" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F104" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G104" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H104" t="s">
         <v>16</v>
@@ -4535,7 +4557,7 @@
         <v>17</v>
       </c>
       <c r="K104">
-        <v>79</v>
+        <v>101</v>
       </c>
     </row>
     <row r="105" spans="1:11" x14ac:dyDescent="0.25">
@@ -4543,22 +4565,22 @@
         <v>22</v>
       </c>
       <c r="B105">
-        <v>2738</v>
+        <v>77</v>
       </c>
       <c r="C105">
-        <v>3162</v>
+        <v>91</v>
       </c>
       <c r="D105" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="E105" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F105" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G105" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H105" t="s">
         <v>16</v>
@@ -4567,7 +4589,7 @@
         <v>17</v>
       </c>
       <c r="K105">
-        <v>79</v>
+        <v>101</v>
       </c>
     </row>
     <row r="106" spans="1:11" x14ac:dyDescent="0.25">
@@ -4575,7 +4597,7 @@
         <v>24</v>
       </c>
       <c r="B106">
-        <v>27700</v>
+        <v>720</v>
       </c>
       <c r="C106">
         <v>0</v>
@@ -4584,13 +4606,13 @@
         <v>19</v>
       </c>
       <c r="E106" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="F106" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G106" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="H106" t="s">
         <v>16</v>
@@ -4598,11 +4620,8 @@
       <c r="I106" t="s">
         <v>17</v>
       </c>
-      <c r="J106" t="s">
-        <v>92</v>
-      </c>
       <c r="K106">
-        <v>79</v>
+        <v>101</v>
       </c>
     </row>
     <row r="107" spans="1:11" x14ac:dyDescent="0.25">
@@ -4610,22 +4629,22 @@
         <v>11</v>
       </c>
       <c r="B107">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="C107">
-        <v>16</v>
+        <v>65</v>
       </c>
       <c r="D107" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="E107" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="F107" t="s">
         <v>14</v>
       </c>
       <c r="G107" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="H107" t="s">
         <v>16</v>
@@ -4634,7 +4653,7 @@
         <v>17</v>
       </c>
       <c r="K107">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="108" spans="1:11" x14ac:dyDescent="0.25">
@@ -4642,22 +4661,22 @@
         <v>18</v>
       </c>
       <c r="B108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C108">
         <v>3</v>
       </c>
       <c r="D108" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E108" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="F108" t="s">
         <v>14</v>
       </c>
       <c r="G108" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="H108" t="s">
         <v>16</v>
@@ -4666,7 +4685,7 @@
         <v>17</v>
       </c>
       <c r="K108">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="109" spans="1:11" x14ac:dyDescent="0.25">
@@ -4674,22 +4693,22 @@
         <v>20</v>
       </c>
       <c r="B109">
-        <v>29</v>
+        <v>61</v>
       </c>
       <c r="C109">
-        <v>15</v>
+        <v>77</v>
       </c>
       <c r="D109" t="s">
-        <v>91</v>
+        <v>48</v>
       </c>
       <c r="E109" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="F109" t="s">
         <v>14</v>
       </c>
       <c r="G109" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="H109" t="s">
         <v>16</v>
@@ -4698,7 +4717,7 @@
         <v>17</v>
       </c>
       <c r="K109">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="110" spans="1:11" x14ac:dyDescent="0.25">
@@ -4706,22 +4725,22 @@
         <v>22</v>
       </c>
       <c r="B110">
-        <v>51</v>
+        <v>38</v>
       </c>
       <c r="C110">
-        <v>63</v>
+        <v>142</v>
       </c>
       <c r="D110" t="s">
-        <v>81</v>
+        <v>49</v>
       </c>
       <c r="E110" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="F110" t="s">
         <v>14</v>
       </c>
       <c r="G110" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="H110" t="s">
         <v>16</v>
@@ -4730,7 +4749,7 @@
         <v>17</v>
       </c>
       <c r="K110">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="111" spans="1:11" x14ac:dyDescent="0.25">
@@ -4738,7 +4757,7 @@
         <v>24</v>
       </c>
       <c r="B111">
-        <v>480</v>
+        <v>300</v>
       </c>
       <c r="C111">
         <v>0</v>
@@ -4747,13 +4766,13 @@
         <v>19</v>
       </c>
       <c r="E111" t="s">
-        <v>90</v>
+        <v>45</v>
       </c>
       <c r="F111" t="s">
         <v>14</v>
       </c>
       <c r="G111" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="H111" t="s">
         <v>16</v>
@@ -4762,7 +4781,7 @@
         <v>17</v>
       </c>
       <c r="K111">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.25">
@@ -4770,22 +4789,22 @@
         <v>11</v>
       </c>
       <c r="B112">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="C112">
         <v>25</v>
       </c>
       <c r="D112" t="s">
-        <v>89</v>
+        <v>50</v>
       </c>
       <c r="E112" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="F112" t="s">
         <v>27</v>
       </c>
       <c r="G112" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="H112" t="s">
         <v>16</v>
@@ -4793,8 +4812,11 @@
       <c r="I112" t="s">
         <v>17</v>
       </c>
+      <c r="J112" t="s">
+        <v>52</v>
+      </c>
       <c r="K112">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="113" spans="1:11" x14ac:dyDescent="0.25">
@@ -4805,19 +4827,19 @@
         <v>4</v>
       </c>
       <c r="C113">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D113" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="E113" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="F113" t="s">
         <v>27</v>
       </c>
       <c r="G113" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="H113" t="s">
         <v>16</v>
@@ -4825,8 +4847,11 @@
       <c r="I113" t="s">
         <v>17</v>
       </c>
+      <c r="J113" t="s">
+        <v>54</v>
+      </c>
       <c r="K113">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="114" spans="1:11" x14ac:dyDescent="0.25">
@@ -4834,22 +4859,22 @@
         <v>20</v>
       </c>
       <c r="B114">
-        <v>44</v>
+        <v>82</v>
       </c>
       <c r="C114">
         <v>38</v>
       </c>
       <c r="D114" t="s">
-        <v>87</v>
+        <v>55</v>
       </c>
       <c r="E114" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="F114" t="s">
         <v>27</v>
       </c>
       <c r="G114" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="H114" t="s">
         <v>16</v>
@@ -4857,8 +4882,11 @@
       <c r="I114" t="s">
         <v>17</v>
       </c>
+      <c r="J114" t="s">
+        <v>56</v>
+      </c>
       <c r="K114">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="115" spans="1:11" x14ac:dyDescent="0.25">
@@ -4866,22 +4894,22 @@
         <v>22</v>
       </c>
       <c r="B115">
-        <v>77</v>
+        <v>51</v>
       </c>
       <c r="C115">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="D115" t="s">
-        <v>86</v>
+        <v>57</v>
       </c>
       <c r="E115" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="F115" t="s">
         <v>27</v>
       </c>
       <c r="G115" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="H115" t="s">
         <v>16</v>
@@ -4889,8 +4917,11 @@
       <c r="I115" t="s">
         <v>17</v>
       </c>
+      <c r="J115" t="s">
+        <v>58</v>
+      </c>
       <c r="K115">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="116" spans="1:11" x14ac:dyDescent="0.25">
@@ -4898,7 +4929,7 @@
         <v>24</v>
       </c>
       <c r="B116">
-        <v>720</v>
+        <v>399</v>
       </c>
       <c r="C116">
         <v>0</v>
@@ -4907,13 +4938,13 @@
         <v>19</v>
       </c>
       <c r="E116" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="F116" t="s">
         <v>27</v>
       </c>
       <c r="G116" t="s">
-        <v>84</v>
+        <v>46</v>
       </c>
       <c r="H116" t="s">
         <v>16</v>
@@ -4921,8 +4952,11 @@
       <c r="I116" t="s">
         <v>17</v>
       </c>
+      <c r="J116" t="s">
+        <v>72</v>
+      </c>
       <c r="K116">
-        <v>101</v>
+        <v>92</v>
       </c>
     </row>
     <row r="117" spans="1:11" x14ac:dyDescent="0.25">
@@ -4930,22 +4964,22 @@
         <v>11</v>
       </c>
       <c r="B117">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="C117">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D117" t="s">
+        <v>59</v>
+      </c>
+      <c r="E117" t="s">
+        <v>60</v>
+      </c>
+      <c r="F117" t="s">
+        <v>27</v>
+      </c>
+      <c r="G117" t="s">
         <v>46</v>
-      </c>
-      <c r="E117" t="s">
-        <v>47</v>
-      </c>
-      <c r="F117" t="s">
-        <v>14</v>
-      </c>
-      <c r="G117" t="s">
-        <v>48</v>
       </c>
       <c r="H117" t="s">
         <v>16</v>
@@ -4962,22 +4996,22 @@
         <v>18</v>
       </c>
       <c r="B118">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C118">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="D118" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="E118" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F118" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G118" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H118" t="s">
         <v>16</v>
@@ -4994,22 +5028,22 @@
         <v>20</v>
       </c>
       <c r="B119">
-        <v>61</v>
+        <v>82</v>
       </c>
       <c r="C119">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D119" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E119" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F119" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G119" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H119" t="s">
         <v>16</v>
@@ -5026,22 +5060,22 @@
         <v>22</v>
       </c>
       <c r="B120">
-        <v>38</v>
+        <v>51</v>
       </c>
       <c r="C120">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="D120" t="s">
-        <v>51</v>
+        <v>63</v>
       </c>
       <c r="E120" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F120" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G120" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H120" t="s">
         <v>16</v>
@@ -5058,7 +5092,7 @@
         <v>24</v>
       </c>
       <c r="B121">
-        <v>300</v>
+        <v>399</v>
       </c>
       <c r="C121">
         <v>0</v>
@@ -5067,13 +5101,13 @@
         <v>19</v>
       </c>
       <c r="E121" t="s">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="F121" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G121" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H121" t="s">
         <v>16</v>
@@ -5093,19 +5127,19 @@
         <v>27</v>
       </c>
       <c r="C122">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="D122" t="s">
-        <v>52</v>
+        <v>64</v>
       </c>
       <c r="E122" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F122" t="s">
         <v>27</v>
       </c>
       <c r="G122" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H122" t="s">
         <v>16</v>
@@ -5114,7 +5148,7 @@
         <v>17</v>
       </c>
       <c r="J122" t="s">
-        <v>54</v>
+        <v>66</v>
       </c>
       <c r="K122">
         <v>92</v>
@@ -5128,19 +5162,19 @@
         <v>4</v>
       </c>
       <c r="C123">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D123" t="s">
-        <v>55</v>
+        <v>67</v>
       </c>
       <c r="E123" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F123" t="s">
         <v>27</v>
       </c>
       <c r="G123" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H123" t="s">
         <v>16</v>
@@ -5149,7 +5183,7 @@
         <v>17</v>
       </c>
       <c r="J123" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="K123">
         <v>92</v>
@@ -5163,19 +5197,19 @@
         <v>82</v>
       </c>
       <c r="C124">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="D124" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="E124" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F124" t="s">
         <v>27</v>
       </c>
       <c r="G124" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H124" t="s">
         <v>16</v>
@@ -5184,7 +5218,7 @@
         <v>17</v>
       </c>
       <c r="J124" t="s">
-        <v>58</v>
+        <v>70</v>
       </c>
       <c r="K124">
         <v>92</v>
@@ -5198,28 +5232,25 @@
         <v>51</v>
       </c>
       <c r="C125">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="D125" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="E125" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F125" t="s">
         <v>27</v>
       </c>
       <c r="G125" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H125" t="s">
         <v>16</v>
       </c>
       <c r="I125" t="s">
         <v>17</v>
-      </c>
-      <c r="J125" t="s">
-        <v>60</v>
       </c>
       <c r="K125">
         <v>92</v>
@@ -5239,22 +5270,19 @@
         <v>19</v>
       </c>
       <c r="E126" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="F126" t="s">
         <v>27</v>
       </c>
       <c r="G126" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H126" t="s">
         <v>16</v>
       </c>
       <c r="I126" t="s">
         <v>17</v>
-      </c>
-      <c r="J126" t="s">
-        <v>74</v>
       </c>
       <c r="K126">
         <v>92</v>
@@ -5265,22 +5293,22 @@
         <v>11</v>
       </c>
       <c r="B127">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="C127">
-        <v>53</v>
+        <v>6</v>
       </c>
       <c r="D127" t="s">
-        <v>61</v>
+        <v>228</v>
       </c>
       <c r="E127" t="s">
-        <v>62</v>
+        <v>225</v>
       </c>
       <c r="F127" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G127" t="s">
-        <v>48</v>
+        <v>223</v>
       </c>
       <c r="H127" t="s">
         <v>16</v>
@@ -5289,7 +5317,7 @@
         <v>17</v>
       </c>
       <c r="K127">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="128" spans="1:11" x14ac:dyDescent="0.25">
@@ -5297,22 +5325,22 @@
         <v>18</v>
       </c>
       <c r="B128">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C128">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="D128" t="s">
-        <v>63</v>
+        <v>19</v>
       </c>
       <c r="E128" t="s">
-        <v>62</v>
+        <v>225</v>
       </c>
       <c r="F128" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G128" t="s">
-        <v>48</v>
+        <v>223</v>
       </c>
       <c r="H128" t="s">
         <v>16</v>
@@ -5321,7 +5349,7 @@
         <v>17</v>
       </c>
       <c r="K128">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="129" spans="1:11" x14ac:dyDescent="0.25">
@@ -5329,22 +5357,22 @@
         <v>20</v>
       </c>
       <c r="B129">
-        <v>82</v>
+        <v>13</v>
       </c>
       <c r="C129">
-        <v>85</v>
+        <v>5</v>
       </c>
       <c r="D129" t="s">
-        <v>64</v>
+        <v>227</v>
       </c>
       <c r="E129" t="s">
-        <v>62</v>
+        <v>225</v>
       </c>
       <c r="F129" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G129" t="s">
-        <v>48</v>
+        <v>223</v>
       </c>
       <c r="H129" t="s">
         <v>16</v>
@@ -5353,7 +5381,7 @@
         <v>17</v>
       </c>
       <c r="K129">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="130" spans="1:11" x14ac:dyDescent="0.25">
@@ -5361,22 +5389,22 @@
         <v>22</v>
       </c>
       <c r="B130">
-        <v>51</v>
+        <v>22</v>
       </c>
       <c r="C130">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="D130" t="s">
-        <v>65</v>
+        <v>226</v>
       </c>
       <c r="E130" t="s">
-        <v>62</v>
+        <v>225</v>
       </c>
       <c r="F130" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G130" t="s">
-        <v>48</v>
+        <v>223</v>
       </c>
       <c r="H130" t="s">
         <v>16</v>
@@ -5385,7 +5413,7 @@
         <v>17</v>
       </c>
       <c r="K130">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="131" spans="1:11" x14ac:dyDescent="0.25">
@@ -5393,7 +5421,7 @@
         <v>24</v>
       </c>
       <c r="B131">
-        <v>399</v>
+        <v>480</v>
       </c>
       <c r="C131">
         <v>0</v>
@@ -5402,13 +5430,13 @@
         <v>19</v>
       </c>
       <c r="E131" t="s">
-        <v>62</v>
+        <v>225</v>
       </c>
       <c r="F131" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G131" t="s">
-        <v>48</v>
+        <v>223</v>
       </c>
       <c r="H131" t="s">
         <v>16</v>
@@ -5417,7 +5445,7 @@
         <v>17</v>
       </c>
       <c r="K131">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="132" spans="1:11" x14ac:dyDescent="0.25">
@@ -5425,22 +5453,22 @@
         <v>11</v>
       </c>
       <c r="B132">
-        <v>27</v>
+        <v>10</v>
       </c>
       <c r="C132">
-        <v>46</v>
+        <v>6</v>
       </c>
       <c r="D132" t="s">
-        <v>66</v>
+        <v>193</v>
       </c>
       <c r="E132" t="s">
-        <v>67</v>
+        <v>224</v>
       </c>
       <c r="F132" t="s">
         <v>27</v>
       </c>
       <c r="G132" t="s">
-        <v>48</v>
+        <v>223</v>
       </c>
       <c r="H132" t="s">
         <v>16</v>
@@ -5448,11 +5476,8 @@
       <c r="I132" t="s">
         <v>17</v>
       </c>
-      <c r="J132" t="s">
-        <v>68</v>
-      </c>
       <c r="K132">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="133" spans="1:11" x14ac:dyDescent="0.25">
@@ -5463,19 +5488,19 @@
         <v>4</v>
       </c>
       <c r="C133">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D133" t="s">
-        <v>69</v>
+        <v>198</v>
       </c>
       <c r="E133" t="s">
-        <v>67</v>
+        <v>224</v>
       </c>
       <c r="F133" t="s">
         <v>27</v>
       </c>
       <c r="G133" t="s">
-        <v>48</v>
+        <v>223</v>
       </c>
       <c r="H133" t="s">
         <v>16</v>
@@ -5483,11 +5508,8 @@
       <c r="I133" t="s">
         <v>17</v>
       </c>
-      <c r="J133" t="s">
-        <v>70</v>
-      </c>
       <c r="K133">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="134" spans="1:11" x14ac:dyDescent="0.25">
@@ -5495,22 +5517,22 @@
         <v>20</v>
       </c>
       <c r="B134">
-        <v>82</v>
+        <v>20</v>
       </c>
       <c r="C134">
-        <v>60</v>
+        <v>17</v>
       </c>
       <c r="D134" t="s">
-        <v>71</v>
+        <v>215</v>
       </c>
       <c r="E134" t="s">
-        <v>67</v>
+        <v>224</v>
       </c>
       <c r="F134" t="s">
         <v>27</v>
       </c>
       <c r="G134" t="s">
-        <v>48</v>
+        <v>223</v>
       </c>
       <c r="H134" t="s">
         <v>16</v>
@@ -5518,11 +5540,8 @@
       <c r="I134" t="s">
         <v>17</v>
       </c>
-      <c r="J134" t="s">
-        <v>72</v>
-      </c>
       <c r="K134">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="135" spans="1:11" x14ac:dyDescent="0.25">
@@ -5530,22 +5549,22 @@
         <v>22</v>
       </c>
       <c r="B135">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="C135">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="D135" t="s">
-        <v>73</v>
+        <v>87</v>
       </c>
       <c r="E135" t="s">
-        <v>67</v>
+        <v>224</v>
       </c>
       <c r="F135" t="s">
         <v>27</v>
       </c>
       <c r="G135" t="s">
-        <v>48</v>
+        <v>223</v>
       </c>
       <c r="H135" t="s">
         <v>16</v>
@@ -5554,7 +5573,7 @@
         <v>17</v>
       </c>
       <c r="K135">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="136" spans="1:11" x14ac:dyDescent="0.25">
@@ -5562,7 +5581,7 @@
         <v>24</v>
       </c>
       <c r="B136">
-        <v>399</v>
+        <v>720</v>
       </c>
       <c r="C136">
         <v>0</v>
@@ -5571,13 +5590,13 @@
         <v>19</v>
       </c>
       <c r="E136" t="s">
-        <v>67</v>
+        <v>224</v>
       </c>
       <c r="F136" t="s">
         <v>27</v>
       </c>
       <c r="G136" t="s">
-        <v>48</v>
+        <v>223</v>
       </c>
       <c r="H136" t="s">
         <v>16</v>
@@ -5586,7 +5605,7 @@
         <v>17</v>
       </c>
       <c r="K136">
-        <v>92</v>
+        <v>22</v>
       </c>
     </row>
     <row r="137" spans="1:11" x14ac:dyDescent="0.25">
@@ -5594,22 +5613,22 @@
         <v>11</v>
       </c>
       <c r="B137">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C137">
-        <v>6</v>
+        <v>27</v>
       </c>
       <c r="D137" t="s">
-        <v>230</v>
+        <v>216</v>
       </c>
       <c r="E137" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="F137" t="s">
         <v>14</v>
       </c>
       <c r="G137" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="H137" t="s">
         <v>16</v>
@@ -5618,7 +5637,7 @@
         <v>17</v>
       </c>
       <c r="K137">
-        <v>22</v>
+        <v>79</v>
       </c>
     </row>
     <row r="138" spans="1:11" x14ac:dyDescent="0.25">
@@ -5626,22 +5645,22 @@
         <v>18</v>
       </c>
       <c r="B138">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C138">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="D138" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="E138" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="F138" t="s">
         <v>14</v>
       </c>
       <c r="G138" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="H138" t="s">
         <v>16</v>
@@ -5650,7 +5669,7 @@
         <v>17</v>
       </c>
       <c r="K138">
-        <v>22</v>
+        <v>79</v>
       </c>
     </row>
     <row r="139" spans="1:11" x14ac:dyDescent="0.25">
@@ -5658,22 +5677,22 @@
         <v>20</v>
       </c>
       <c r="B139">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C139">
-        <v>5</v>
+        <v>44</v>
       </c>
       <c r="D139" t="s">
-        <v>229</v>
+        <v>138</v>
       </c>
       <c r="E139" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="F139" t="s">
         <v>14</v>
       </c>
       <c r="G139" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="H139" t="s">
         <v>16</v>
@@ -5682,7 +5701,7 @@
         <v>17</v>
       </c>
       <c r="K139">
-        <v>22</v>
+        <v>79</v>
       </c>
     </row>
     <row r="140" spans="1:11" x14ac:dyDescent="0.25">
@@ -5690,22 +5709,22 @@
         <v>22</v>
       </c>
       <c r="B140">
-        <v>22</v>
+        <v>74</v>
       </c>
       <c r="C140">
-        <v>23</v>
+        <v>64</v>
       </c>
       <c r="D140" t="s">
-        <v>228</v>
+        <v>215</v>
       </c>
       <c r="E140" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="F140" t="s">
         <v>14</v>
       </c>
       <c r="G140" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="H140" t="s">
         <v>16</v>
@@ -5714,7 +5733,7 @@
         <v>17</v>
       </c>
       <c r="K140">
-        <v>22</v>
+        <v>79</v>
       </c>
     </row>
     <row r="141" spans="1:11" x14ac:dyDescent="0.25">
@@ -5722,7 +5741,7 @@
         <v>24</v>
       </c>
       <c r="B141">
-        <v>480</v>
+        <v>1200</v>
       </c>
       <c r="C141">
         <v>0</v>
@@ -5731,13 +5750,13 @@
         <v>19</v>
       </c>
       <c r="E141" t="s">
-        <v>227</v>
+        <v>214</v>
       </c>
       <c r="F141" t="s">
         <v>14</v>
       </c>
       <c r="G141" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
       <c r="H141" t="s">
         <v>16</v>
@@ -5746,7 +5765,7 @@
         <v>17</v>
       </c>
       <c r="K141">
-        <v>22</v>
+        <v>79</v>
       </c>
     </row>
     <row r="142" spans="1:11" x14ac:dyDescent="0.25">
@@ -5754,22 +5773,22 @@
         <v>11</v>
       </c>
       <c r="B142">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="C142">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="D142" t="s">
-        <v>195</v>
+        <v>206</v>
       </c>
       <c r="E142" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F142" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G142" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="H142" t="s">
         <v>16</v>
@@ -5778,7 +5797,7 @@
         <v>17</v>
       </c>
       <c r="K142">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="143" spans="1:11" x14ac:dyDescent="0.25">
@@ -5786,23 +5805,23 @@
         <v>18</v>
       </c>
       <c r="B143">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C143">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="D143" t="s">
+        <v>19</v>
+      </c>
+      <c r="E143" t="s">
+        <v>205</v>
+      </c>
+      <c r="F143" t="s">
+        <v>14</v>
+      </c>
+      <c r="G143" t="s">
         <v>200</v>
       </c>
-      <c r="E143" t="s">
-        <v>226</v>
-      </c>
-      <c r="F143" t="s">
-        <v>27</v>
-      </c>
-      <c r="G143" t="s">
-        <v>225</v>
-      </c>
       <c r="H143" t="s">
         <v>16</v>
       </c>
@@ -5810,7 +5829,7 @@
         <v>17</v>
       </c>
       <c r="K143">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="144" spans="1:11" x14ac:dyDescent="0.25">
@@ -5818,22 +5837,22 @@
         <v>20</v>
       </c>
       <c r="B144">
-        <v>20</v>
+        <v>31</v>
       </c>
       <c r="C144">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D144" t="s">
-        <v>217</v>
+        <v>112</v>
       </c>
       <c r="E144" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F144" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G144" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="H144" t="s">
         <v>16</v>
@@ -5842,7 +5861,7 @@
         <v>17</v>
       </c>
       <c r="K144">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="145" spans="1:11" x14ac:dyDescent="0.25">
@@ -5850,22 +5869,22 @@
         <v>22</v>
       </c>
       <c r="B145">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="C145">
-        <v>42</v>
+        <v>67</v>
       </c>
       <c r="D145" t="s">
-        <v>89</v>
+        <v>152</v>
       </c>
       <c r="E145" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F145" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G145" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="H145" t="s">
         <v>16</v>
@@ -5874,7 +5893,7 @@
         <v>17</v>
       </c>
       <c r="K145">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="146" spans="1:11" x14ac:dyDescent="0.25">
@@ -5882,7 +5901,7 @@
         <v>24</v>
       </c>
       <c r="B146">
-        <v>720</v>
+        <v>480</v>
       </c>
       <c r="C146">
         <v>0</v>
@@ -5891,13 +5910,13 @@
         <v>19</v>
       </c>
       <c r="E146" t="s">
-        <v>226</v>
+        <v>205</v>
       </c>
       <c r="F146" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G146" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
       <c r="H146" t="s">
         <v>16</v>
@@ -5906,7 +5925,7 @@
         <v>17</v>
       </c>
       <c r="K146">
-        <v>22</v>
+        <v>71</v>
       </c>
     </row>
     <row r="147" spans="1:11" x14ac:dyDescent="0.25">
@@ -5914,22 +5933,22 @@
         <v>11</v>
       </c>
       <c r="B147">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C147">
-        <v>27</v>
+        <v>39</v>
       </c>
       <c r="D147" t="s">
-        <v>218</v>
+        <v>204</v>
       </c>
       <c r="E147" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="F147" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G147" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="H147" t="s">
         <v>16</v>
@@ -5938,7 +5957,7 @@
         <v>17</v>
       </c>
       <c r="K147">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="148" spans="1:11" x14ac:dyDescent="0.25">
@@ -5946,22 +5965,22 @@
         <v>18</v>
       </c>
       <c r="B148">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C148">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="D148" t="s">
-        <v>82</v>
+        <v>19</v>
       </c>
       <c r="E148" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="F148" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G148" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="H148" t="s">
         <v>16</v>
@@ -5970,7 +5989,7 @@
         <v>17</v>
       </c>
       <c r="K148">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="149" spans="1:11" x14ac:dyDescent="0.25">
@@ -5978,22 +5997,22 @@
         <v>20</v>
       </c>
       <c r="B149">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C149">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="D149" t="s">
-        <v>140</v>
+        <v>203</v>
       </c>
       <c r="E149" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="F149" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G149" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="H149" t="s">
         <v>16</v>
@@ -6002,7 +6021,7 @@
         <v>17</v>
       </c>
       <c r="K149">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="150" spans="1:11" x14ac:dyDescent="0.25">
@@ -6010,22 +6029,22 @@
         <v>22</v>
       </c>
       <c r="B150">
-        <v>74</v>
+        <v>110</v>
       </c>
       <c r="C150">
-        <v>64</v>
+        <v>164</v>
       </c>
       <c r="D150" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="E150" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="F150" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G150" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="H150" t="s">
         <v>16</v>
@@ -6034,7 +6053,7 @@
         <v>17</v>
       </c>
       <c r="K150">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="151" spans="1:11" x14ac:dyDescent="0.25">
@@ -6042,7 +6061,7 @@
         <v>24</v>
       </c>
       <c r="B151">
-        <v>1200</v>
+        <v>720</v>
       </c>
       <c r="C151">
         <v>0</v>
@@ -6051,13 +6070,13 @@
         <v>19</v>
       </c>
       <c r="E151" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="F151" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G151" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="H151" t="s">
         <v>16</v>
@@ -6066,7 +6085,7 @@
         <v>17</v>
       </c>
       <c r="K151">
-        <v>79</v>
+        <v>71</v>
       </c>
     </row>
     <row r="152" spans="1:11" x14ac:dyDescent="0.25">
@@ -6074,22 +6093,22 @@
         <v>11</v>
       </c>
       <c r="B152">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="C152">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="D152" t="s">
-        <v>208</v>
+        <v>190</v>
       </c>
       <c r="E152" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="F152" t="s">
         <v>14</v>
       </c>
       <c r="G152" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="H152" t="s">
         <v>16</v>
@@ -6098,7 +6117,7 @@
         <v>17</v>
       </c>
       <c r="K152">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="153" spans="1:11" x14ac:dyDescent="0.25">
@@ -6106,22 +6125,22 @@
         <v>18</v>
       </c>
       <c r="B153">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C153">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D153" t="s">
-        <v>19</v>
+        <v>179</v>
       </c>
       <c r="E153" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="F153" t="s">
         <v>14</v>
       </c>
       <c r="G153" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="H153" t="s">
         <v>16</v>
@@ -6130,7 +6149,7 @@
         <v>17</v>
       </c>
       <c r="K153">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="154" spans="1:11" x14ac:dyDescent="0.25">
@@ -6141,19 +6160,19 @@
         <v>31</v>
       </c>
       <c r="C154">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D154" t="s">
-        <v>114</v>
+        <v>169</v>
       </c>
       <c r="E154" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="F154" t="s">
         <v>14</v>
       </c>
       <c r="G154" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="H154" t="s">
         <v>16</v>
@@ -6162,7 +6181,7 @@
         <v>17</v>
       </c>
       <c r="K154">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="155" spans="1:11" x14ac:dyDescent="0.25">
@@ -6170,22 +6189,22 @@
         <v>22</v>
       </c>
       <c r="B155">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="C155">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="D155" t="s">
-        <v>154</v>
+        <v>189</v>
       </c>
       <c r="E155" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="F155" t="s">
         <v>14</v>
       </c>
       <c r="G155" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="H155" t="s">
         <v>16</v>
@@ -6194,7 +6213,7 @@
         <v>17</v>
       </c>
       <c r="K155">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="156" spans="1:11" x14ac:dyDescent="0.25">
@@ -6211,13 +6230,13 @@
         <v>19</v>
       </c>
       <c r="E156" t="s">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="F156" t="s">
         <v>14</v>
       </c>
       <c r="G156" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="H156" t="s">
         <v>16</v>
@@ -6226,7 +6245,7 @@
         <v>17</v>
       </c>
       <c r="K156">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="157" spans="1:11" x14ac:dyDescent="0.25">
@@ -6234,22 +6253,22 @@
         <v>11</v>
       </c>
       <c r="B157">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="C157">
-        <v>39</v>
+        <v>22</v>
       </c>
       <c r="D157" t="s">
-        <v>206</v>
+        <v>125</v>
       </c>
       <c r="E157" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="F157" t="s">
         <v>27</v>
       </c>
       <c r="G157" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="H157" t="s">
         <v>16</v>
@@ -6258,7 +6277,7 @@
         <v>17</v>
       </c>
       <c r="K157">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="158" spans="1:11" x14ac:dyDescent="0.25">
@@ -6266,22 +6285,22 @@
         <v>18</v>
       </c>
       <c r="B158">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C158">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D158" t="s">
-        <v>19</v>
+        <v>125</v>
       </c>
       <c r="E158" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="F158" t="s">
         <v>27</v>
       </c>
       <c r="G158" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="H158" t="s">
         <v>16</v>
@@ -6290,7 +6309,7 @@
         <v>17</v>
       </c>
       <c r="K158">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="159" spans="1:11" x14ac:dyDescent="0.25">
@@ -6301,19 +6320,19 @@
         <v>47</v>
       </c>
       <c r="C159">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D159" t="s">
-        <v>205</v>
+        <v>89</v>
       </c>
       <c r="E159" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="F159" t="s">
         <v>27</v>
       </c>
       <c r="G159" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="H159" t="s">
         <v>16</v>
@@ -6322,7 +6341,7 @@
         <v>17</v>
       </c>
       <c r="K159">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="160" spans="1:11" x14ac:dyDescent="0.25">
@@ -6330,22 +6349,22 @@
         <v>22</v>
       </c>
       <c r="B160">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="C160">
-        <v>164</v>
+        <v>85</v>
       </c>
       <c r="D160" t="s">
-        <v>204</v>
+        <v>187</v>
       </c>
       <c r="E160" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="F160" t="s">
         <v>27</v>
       </c>
       <c r="G160" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="H160" t="s">
         <v>16</v>
@@ -6354,7 +6373,7 @@
         <v>17</v>
       </c>
       <c r="K160">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="161" spans="1:11" x14ac:dyDescent="0.25">
@@ -6371,13 +6390,13 @@
         <v>19</v>
       </c>
       <c r="E161" t="s">
-        <v>203</v>
+        <v>186</v>
       </c>
       <c r="F161" t="s">
         <v>27</v>
       </c>
       <c r="G161" t="s">
-        <v>202</v>
+        <v>185</v>
       </c>
       <c r="H161" t="s">
         <v>16</v>
@@ -6386,7 +6405,7 @@
         <v>17</v>
       </c>
       <c r="K161">
-        <v>71</v>
+        <v>81</v>
       </c>
     </row>
     <row r="162" spans="1:11" x14ac:dyDescent="0.25">
@@ -6397,19 +6416,19 @@
         <v>9</v>
       </c>
       <c r="C162">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D162" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="E162" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F162" t="s">
         <v>14</v>
       </c>
       <c r="G162" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="H162" t="s">
         <v>16</v>
@@ -6418,7 +6437,7 @@
         <v>17</v>
       </c>
       <c r="K162">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="163" spans="1:11" x14ac:dyDescent="0.25">
@@ -6426,22 +6445,22 @@
         <v>18</v>
       </c>
       <c r="B163">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="C163">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D163" t="s">
-        <v>181</v>
+        <v>19</v>
       </c>
       <c r="E163" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F163" t="s">
         <v>14</v>
       </c>
       <c r="G163" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="H163" t="s">
         <v>16</v>
@@ -6450,7 +6469,7 @@
         <v>17</v>
       </c>
       <c r="K163">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="164" spans="1:11" x14ac:dyDescent="0.25">
@@ -6458,22 +6477,22 @@
         <v>20</v>
       </c>
       <c r="B164">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C164">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="D164" t="s">
-        <v>171</v>
+        <v>48</v>
       </c>
       <c r="E164" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F164" t="s">
         <v>14</v>
       </c>
       <c r="G164" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="H164" t="s">
         <v>16</v>
@@ -6482,7 +6501,7 @@
         <v>17</v>
       </c>
       <c r="K164">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="165" spans="1:11" x14ac:dyDescent="0.25">
@@ -6490,22 +6509,22 @@
         <v>22</v>
       </c>
       <c r="B165">
-        <v>67</v>
+        <v>37</v>
       </c>
       <c r="C165">
-        <v>74</v>
+        <v>38</v>
       </c>
       <c r="D165" t="s">
-        <v>191</v>
+        <v>107</v>
       </c>
       <c r="E165" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F165" t="s">
         <v>14</v>
       </c>
       <c r="G165" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="H165" t="s">
         <v>16</v>
@@ -6514,7 +6533,7 @@
         <v>17</v>
       </c>
       <c r="K165">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="166" spans="1:11" x14ac:dyDescent="0.25">
@@ -6531,13 +6550,13 @@
         <v>19</v>
       </c>
       <c r="E166" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="F166" t="s">
         <v>14</v>
       </c>
       <c r="G166" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="H166" t="s">
         <v>16</v>
@@ -6546,7 +6565,7 @@
         <v>17</v>
       </c>
       <c r="K166">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="167" spans="1:11" x14ac:dyDescent="0.25">
@@ -6554,22 +6573,22 @@
         <v>11</v>
       </c>
       <c r="B167">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C167">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="D167" t="s">
-        <v>127</v>
+        <v>182</v>
       </c>
       <c r="E167" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F167" t="s">
         <v>27</v>
       </c>
       <c r="G167" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="H167" t="s">
         <v>16</v>
@@ -6578,7 +6597,7 @@
         <v>17</v>
       </c>
       <c r="K167">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
@@ -6586,22 +6605,22 @@
         <v>18</v>
       </c>
       <c r="B168">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C168">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="D168" t="s">
-        <v>127</v>
+        <v>19</v>
       </c>
       <c r="E168" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F168" t="s">
         <v>27</v>
       </c>
       <c r="G168" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="H168" t="s">
         <v>16</v>
@@ -6610,7 +6629,7 @@
         <v>17</v>
       </c>
       <c r="K168">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
@@ -6618,22 +6637,22 @@
         <v>20</v>
       </c>
       <c r="B169">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="C169">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="D169" t="s">
-        <v>91</v>
+        <v>134</v>
       </c>
       <c r="E169" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F169" t="s">
         <v>27</v>
       </c>
       <c r="G169" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="H169" t="s">
         <v>16</v>
@@ -6642,7 +6661,7 @@
         <v>17</v>
       </c>
       <c r="K169">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
@@ -6650,22 +6669,22 @@
         <v>22</v>
       </c>
       <c r="B170">
-        <v>101</v>
+        <v>55</v>
       </c>
       <c r="C170">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D170" t="s">
-        <v>189</v>
+        <v>48</v>
       </c>
       <c r="E170" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F170" t="s">
         <v>27</v>
       </c>
       <c r="G170" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="H170" t="s">
         <v>16</v>
@@ -6674,7 +6693,7 @@
         <v>17</v>
       </c>
       <c r="K170">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="171" spans="1:11" x14ac:dyDescent="0.25">
@@ -6691,13 +6710,13 @@
         <v>19</v>
       </c>
       <c r="E171" t="s">
-        <v>188</v>
+        <v>181</v>
       </c>
       <c r="F171" t="s">
         <v>27</v>
       </c>
       <c r="G171" t="s">
-        <v>187</v>
+        <v>180</v>
       </c>
       <c r="H171" t="s">
         <v>16</v>
@@ -6706,7 +6725,7 @@
         <v>17</v>
       </c>
       <c r="K171">
-        <v>81</v>
+        <v>119</v>
       </c>
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
@@ -6714,22 +6733,22 @@
         <v>11</v>
       </c>
       <c r="B172">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C172">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="D172" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="E172" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F172" t="s">
         <v>14</v>
       </c>
       <c r="G172" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H172" t="s">
         <v>16</v>
@@ -6738,7 +6757,7 @@
         <v>17</v>
       </c>
       <c r="K172">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
@@ -6746,7 +6765,7 @@
         <v>18</v>
       </c>
       <c r="B173">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C173">
         <v>0</v>
@@ -6755,13 +6774,13 @@
         <v>19</v>
       </c>
       <c r="E173" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F173" t="s">
         <v>14</v>
       </c>
       <c r="G173" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H173" t="s">
         <v>16</v>
@@ -6770,7 +6789,7 @@
         <v>17</v>
       </c>
       <c r="K173">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
@@ -6778,22 +6797,22 @@
         <v>20</v>
       </c>
       <c r="B174">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C174">
-        <v>47</v>
+        <v>26</v>
       </c>
       <c r="D174" t="s">
-        <v>50</v>
+        <v>85</v>
       </c>
       <c r="E174" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F174" t="s">
         <v>14</v>
       </c>
       <c r="G174" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H174" t="s">
         <v>16</v>
@@ -6802,7 +6821,7 @@
         <v>17</v>
       </c>
       <c r="K174">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
@@ -6810,22 +6829,22 @@
         <v>22</v>
       </c>
       <c r="B175">
-        <v>37</v>
+        <v>32</v>
       </c>
       <c r="C175">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="D175" t="s">
-        <v>109</v>
+        <v>247</v>
       </c>
       <c r="E175" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F175" t="s">
         <v>14</v>
       </c>
       <c r="G175" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H175" t="s">
         <v>16</v>
@@ -6834,7 +6853,7 @@
         <v>17</v>
       </c>
       <c r="K175">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
@@ -6842,7 +6861,7 @@
         <v>24</v>
       </c>
       <c r="B176">
-        <v>480</v>
+        <v>375</v>
       </c>
       <c r="C176">
         <v>0</v>
@@ -6851,13 +6870,13 @@
         <v>19</v>
       </c>
       <c r="E176" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="F176" t="s">
         <v>14</v>
       </c>
       <c r="G176" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H176" t="s">
         <v>16</v>
@@ -6866,7 +6885,7 @@
         <v>17</v>
       </c>
       <c r="K176">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="177" spans="1:11" x14ac:dyDescent="0.25">
@@ -6874,22 +6893,22 @@
         <v>11</v>
       </c>
       <c r="B177">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C177">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D177" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="E177" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F177" t="s">
         <v>27</v>
       </c>
       <c r="G177" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H177" t="s">
         <v>16</v>
@@ -6898,7 +6917,7 @@
         <v>17</v>
       </c>
       <c r="K177">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="178" spans="1:11" x14ac:dyDescent="0.25">
@@ -6906,22 +6925,22 @@
         <v>18</v>
       </c>
       <c r="B178">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C178">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D178" t="s">
-        <v>19</v>
+        <v>47</v>
       </c>
       <c r="E178" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F178" t="s">
         <v>27</v>
       </c>
       <c r="G178" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H178" t="s">
         <v>16</v>
@@ -6930,7 +6949,7 @@
         <v>17</v>
       </c>
       <c r="K178">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="179" spans="1:11" x14ac:dyDescent="0.25">
@@ -6938,22 +6957,22 @@
         <v>20</v>
       </c>
       <c r="B179">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C179">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D179" t="s">
-        <v>136</v>
+        <v>174</v>
       </c>
       <c r="E179" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F179" t="s">
         <v>27</v>
       </c>
       <c r="G179" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H179" t="s">
         <v>16</v>
@@ -6962,7 +6981,7 @@
         <v>17</v>
       </c>
       <c r="K179">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="180" spans="1:11" x14ac:dyDescent="0.25">
@@ -6970,22 +6989,22 @@
         <v>22</v>
       </c>
       <c r="B180">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C180">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="D180" t="s">
-        <v>50</v>
+        <v>79</v>
       </c>
       <c r="E180" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F180" t="s">
         <v>27</v>
       </c>
       <c r="G180" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H180" t="s">
         <v>16</v>
@@ -6994,7 +7013,7 @@
         <v>17</v>
       </c>
       <c r="K180">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="181" spans="1:11" x14ac:dyDescent="0.25">
@@ -7002,7 +7021,7 @@
         <v>24</v>
       </c>
       <c r="B181">
-        <v>720</v>
+        <v>562</v>
       </c>
       <c r="C181">
         <v>0</v>
@@ -7011,13 +7030,13 @@
         <v>19</v>
       </c>
       <c r="E181" t="s">
-        <v>183</v>
+        <v>194</v>
       </c>
       <c r="F181" t="s">
         <v>27</v>
       </c>
       <c r="G181" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="H181" t="s">
         <v>16</v>
@@ -7026,7 +7045,7 @@
         <v>17</v>
       </c>
       <c r="K181">
-        <v>119</v>
+        <v>64</v>
       </c>
     </row>
     <row r="182" spans="1:11" x14ac:dyDescent="0.25">
@@ -7034,28 +7053,31 @@
         <v>11</v>
       </c>
       <c r="B182">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C182">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D182" t="s">
-        <v>201</v>
+        <v>166</v>
       </c>
       <c r="E182" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F182" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G182" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H182" t="s">
         <v>16</v>
       </c>
       <c r="I182" t="s">
         <v>17</v>
+      </c>
+      <c r="J182" t="s">
+        <v>246</v>
       </c>
       <c r="K182">
         <v>64</v>
@@ -7066,7 +7088,7 @@
         <v>18</v>
       </c>
       <c r="B183">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C183">
         <v>0</v>
@@ -7075,19 +7097,22 @@
         <v>19</v>
       </c>
       <c r="E183" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F183" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G183" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H183" t="s">
         <v>16</v>
       </c>
       <c r="I183" t="s">
         <v>17</v>
+      </c>
+      <c r="J183" t="s">
+        <v>245</v>
       </c>
       <c r="K183">
         <v>64</v>
@@ -7098,28 +7123,31 @@
         <v>20</v>
       </c>
       <c r="B184">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="C184">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="D184" t="s">
-        <v>87</v>
+        <v>175</v>
       </c>
       <c r="E184" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F184" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G184" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H184" t="s">
         <v>16</v>
       </c>
       <c r="I184" t="s">
         <v>17</v>
+      </c>
+      <c r="J184" t="s">
+        <v>244</v>
       </c>
       <c r="K184">
         <v>64</v>
@@ -7130,28 +7158,31 @@
         <v>22</v>
       </c>
       <c r="B185">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="C185">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="D185" t="s">
-        <v>249</v>
+        <v>177</v>
       </c>
       <c r="E185" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F185" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G185" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H185" t="s">
         <v>16</v>
       </c>
       <c r="I185" t="s">
         <v>17</v>
+      </c>
+      <c r="J185" t="s">
+        <v>243</v>
       </c>
       <c r="K185">
         <v>64</v>
@@ -7162,7 +7193,7 @@
         <v>24</v>
       </c>
       <c r="B186">
-        <v>375</v>
+        <v>562</v>
       </c>
       <c r="C186">
         <v>0</v>
@@ -7171,13 +7202,13 @@
         <v>19</v>
       </c>
       <c r="E186" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="F186" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G186" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H186" t="s">
         <v>16</v>
@@ -7194,22 +7225,22 @@
         <v>11</v>
       </c>
       <c r="B187">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="C187">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D187" t="s">
-        <v>198</v>
+        <v>222</v>
       </c>
       <c r="E187" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="F187" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G187" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="H187" t="s">
         <v>16</v>
@@ -7218,7 +7249,7 @@
         <v>17</v>
       </c>
       <c r="K187">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="188" spans="1:11" x14ac:dyDescent="0.25">
@@ -7226,22 +7257,22 @@
         <v>18</v>
       </c>
       <c r="B188">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C188">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D188" t="s">
-        <v>49</v>
+        <v>144</v>
       </c>
       <c r="E188" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="F188" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G188" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="H188" t="s">
         <v>16</v>
@@ -7250,7 +7281,7 @@
         <v>17</v>
       </c>
       <c r="K188">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="189" spans="1:11" x14ac:dyDescent="0.25">
@@ -7258,22 +7289,22 @@
         <v>20</v>
       </c>
       <c r="B189">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C189">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="D189" t="s">
-        <v>176</v>
+        <v>221</v>
       </c>
       <c r="E189" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="F189" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G189" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="H189" t="s">
         <v>16</v>
@@ -7282,7 +7313,7 @@
         <v>17</v>
       </c>
       <c r="K189">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="190" spans="1:11" x14ac:dyDescent="0.25">
@@ -7290,22 +7321,22 @@
         <v>22</v>
       </c>
       <c r="B190">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="C190">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="D190" t="s">
-        <v>81</v>
+        <v>242</v>
       </c>
       <c r="E190" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="F190" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G190" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="H190" t="s">
         <v>16</v>
@@ -7314,7 +7345,7 @@
         <v>17</v>
       </c>
       <c r="K190">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="191" spans="1:11" x14ac:dyDescent="0.25">
@@ -7322,7 +7353,7 @@
         <v>24</v>
       </c>
       <c r="B191">
-        <v>562</v>
+        <v>320</v>
       </c>
       <c r="C191">
         <v>0</v>
@@ -7331,13 +7362,13 @@
         <v>19</v>
       </c>
       <c r="E191" t="s">
-        <v>196</v>
+        <v>220</v>
       </c>
       <c r="F191" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G191" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="H191" t="s">
         <v>16</v>
@@ -7346,7 +7377,7 @@
         <v>17</v>
       </c>
       <c r="K191">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="192" spans="1:11" x14ac:dyDescent="0.25">
@@ -7354,22 +7385,22 @@
         <v>11</v>
       </c>
       <c r="B192">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C192">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D192" t="s">
-        <v>168</v>
+        <v>219</v>
       </c>
       <c r="E192" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="F192" t="s">
         <v>27</v>
       </c>
       <c r="G192" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="H192" t="s">
         <v>16</v>
@@ -7378,10 +7409,10 @@
         <v>17</v>
       </c>
       <c r="J192" t="s">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="K192">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="193" spans="1:11" x14ac:dyDescent="0.25">
@@ -7389,7 +7420,7 @@
         <v>18</v>
       </c>
       <c r="B193">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C193">
         <v>0</v>
@@ -7398,13 +7429,13 @@
         <v>19</v>
       </c>
       <c r="E193" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="F193" t="s">
         <v>27</v>
       </c>
       <c r="G193" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="H193" t="s">
         <v>16</v>
@@ -7412,11 +7443,8 @@
       <c r="I193" t="s">
         <v>17</v>
       </c>
-      <c r="J193" t="s">
-        <v>247</v>
-      </c>
       <c r="K193">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="194" spans="1:11" x14ac:dyDescent="0.25">
@@ -7424,22 +7452,22 @@
         <v>20</v>
       </c>
       <c r="B194">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C194">
-        <v>16</v>
+        <v>36</v>
       </c>
       <c r="D194" t="s">
-        <v>177</v>
+        <v>31</v>
       </c>
       <c r="E194" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="F194" t="s">
         <v>27</v>
       </c>
       <c r="G194" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="H194" t="s">
         <v>16</v>
@@ -7448,10 +7476,10 @@
         <v>17</v>
       </c>
       <c r="J194" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="K194">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="195" spans="1:11" x14ac:dyDescent="0.25">
@@ -7459,22 +7487,22 @@
         <v>22</v>
       </c>
       <c r="B195">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C195">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D195" t="s">
-        <v>179</v>
+        <v>129</v>
       </c>
       <c r="E195" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="F195" t="s">
         <v>27</v>
       </c>
       <c r="G195" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="H195" t="s">
         <v>16</v>
@@ -7483,10 +7511,10 @@
         <v>17</v>
       </c>
       <c r="J195" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="K195">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="196" spans="1:11" x14ac:dyDescent="0.25">
@@ -7494,7 +7522,7 @@
         <v>24</v>
       </c>
       <c r="B196">
-        <v>562</v>
+        <v>480</v>
       </c>
       <c r="C196">
         <v>0</v>
@@ -7503,13 +7531,13 @@
         <v>19</v>
       </c>
       <c r="E196" t="s">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="F196" t="s">
         <v>27</v>
       </c>
       <c r="G196" t="s">
-        <v>193</v>
+        <v>217</v>
       </c>
       <c r="H196" t="s">
         <v>16</v>
@@ -7518,7 +7546,7 @@
         <v>17</v>
       </c>
       <c r="K196">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="197" spans="1:11" x14ac:dyDescent="0.25">
@@ -7526,22 +7554,22 @@
         <v>11</v>
       </c>
       <c r="B197">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C197">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="D197" t="s">
-        <v>224</v>
+        <v>182</v>
       </c>
       <c r="E197" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F197" t="s">
         <v>14</v>
       </c>
       <c r="G197" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="H197" t="s">
         <v>16</v>
@@ -7549,8 +7577,11 @@
       <c r="I197" t="s">
         <v>17</v>
       </c>
+      <c r="J197" t="s">
+        <v>238</v>
+      </c>
       <c r="K197">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="198" spans="1:11" x14ac:dyDescent="0.25">
@@ -7558,22 +7589,22 @@
         <v>18</v>
       </c>
       <c r="B198">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C198">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D198" t="s">
-        <v>146</v>
+        <v>237</v>
       </c>
       <c r="E198" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F198" t="s">
         <v>14</v>
       </c>
       <c r="G198" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="H198" t="s">
         <v>16</v>
@@ -7582,7 +7613,7 @@
         <v>17</v>
       </c>
       <c r="K198">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="199" spans="1:11" x14ac:dyDescent="0.25">
@@ -7590,22 +7621,22 @@
         <v>20</v>
       </c>
       <c r="B199">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="C199">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="D199" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="E199" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F199" t="s">
         <v>14</v>
       </c>
       <c r="G199" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="H199" t="s">
         <v>16</v>
@@ -7614,7 +7645,7 @@
         <v>17</v>
       </c>
       <c r="K199">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="200" spans="1:11" x14ac:dyDescent="0.25">
@@ -7622,22 +7653,22 @@
         <v>22</v>
       </c>
       <c r="B200">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="C200">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="D200" t="s">
-        <v>244</v>
+        <v>195</v>
       </c>
       <c r="E200" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F200" t="s">
         <v>14</v>
       </c>
       <c r="G200" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="H200" t="s">
         <v>16</v>
@@ -7646,7 +7677,7 @@
         <v>17</v>
       </c>
       <c r="K200">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="201" spans="1:11" x14ac:dyDescent="0.25">
@@ -7654,7 +7685,7 @@
         <v>24</v>
       </c>
       <c r="B201">
-        <v>320</v>
+        <v>375</v>
       </c>
       <c r="C201">
         <v>0</v>
@@ -7663,13 +7694,13 @@
         <v>19</v>
       </c>
       <c r="E201" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="F201" t="s">
         <v>14</v>
       </c>
       <c r="G201" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="H201" t="s">
         <v>16</v>
@@ -7678,7 +7709,7 @@
         <v>17</v>
       </c>
       <c r="K201">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="202" spans="1:11" x14ac:dyDescent="0.25">
@@ -7686,22 +7717,22 @@
         <v>11</v>
       </c>
       <c r="B202">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="C202">
-        <v>5</v>
+        <v>26</v>
       </c>
       <c r="D202" t="s">
-        <v>221</v>
+        <v>236</v>
       </c>
       <c r="E202" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="F202" t="s">
         <v>27</v>
       </c>
       <c r="G202" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="H202" t="s">
         <v>16</v>
@@ -7709,11 +7740,8 @@
       <c r="I202" t="s">
         <v>17</v>
       </c>
-      <c r="J202" t="s">
-        <v>243</v>
-      </c>
       <c r="K202">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="203" spans="1:11" x14ac:dyDescent="0.25">
@@ -7721,22 +7749,22 @@
         <v>18</v>
       </c>
       <c r="B203">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C203">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D203" t="s">
-        <v>19</v>
+        <v>76</v>
       </c>
       <c r="E203" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="F203" t="s">
         <v>27</v>
       </c>
       <c r="G203" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="H203" t="s">
         <v>16</v>
@@ -7745,7 +7773,7 @@
         <v>17</v>
       </c>
       <c r="K203">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="204" spans="1:11" x14ac:dyDescent="0.25">
@@ -7753,22 +7781,22 @@
         <v>20</v>
       </c>
       <c r="B204">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="C204">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D204" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="E204" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="F204" t="s">
         <v>27</v>
       </c>
       <c r="G204" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="H204" t="s">
         <v>16</v>
@@ -7776,11 +7804,8 @@
       <c r="I204" t="s">
         <v>17</v>
       </c>
-      <c r="J204" t="s">
-        <v>242</v>
-      </c>
       <c r="K204">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="205" spans="1:11" x14ac:dyDescent="0.25">
@@ -7788,22 +7813,22 @@
         <v>22</v>
       </c>
       <c r="B205">
-        <v>36</v>
+        <v>68</v>
       </c>
       <c r="C205">
-        <v>32</v>
+        <v>84</v>
       </c>
       <c r="D205" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
       <c r="E205" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="F205" t="s">
         <v>27</v>
       </c>
       <c r="G205" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="H205" t="s">
         <v>16</v>
@@ -7811,11 +7836,8 @@
       <c r="I205" t="s">
         <v>17</v>
       </c>
-      <c r="J205" t="s">
-        <v>241</v>
-      </c>
       <c r="K205">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="206" spans="1:11" x14ac:dyDescent="0.25">
@@ -7823,7 +7845,7 @@
         <v>24</v>
       </c>
       <c r="B206">
-        <v>480</v>
+        <v>562</v>
       </c>
       <c r="C206">
         <v>0</v>
@@ -7832,13 +7854,13 @@
         <v>19</v>
       </c>
       <c r="E206" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="F206" t="s">
         <v>27</v>
       </c>
       <c r="G206" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
       <c r="H206" t="s">
         <v>16</v>
@@ -7847,7 +7869,7 @@
         <v>17</v>
       </c>
       <c r="K206">
-        <v>62</v>
+        <v>76</v>
       </c>
     </row>
     <row r="207" spans="1:11" x14ac:dyDescent="0.25">
@@ -7855,22 +7877,22 @@
         <v>11</v>
       </c>
       <c r="B207">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="C207">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D207" t="s">
-        <v>184</v>
+        <v>31</v>
       </c>
       <c r="E207" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F207" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G207" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H207" t="s">
         <v>16</v>
@@ -7879,7 +7901,7 @@
         <v>17</v>
       </c>
       <c r="J207" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="K207">
         <v>76</v>
@@ -7890,22 +7912,22 @@
         <v>18</v>
       </c>
       <c r="B208">
+        <v>4</v>
+      </c>
+      <c r="C208">
         <v>3</v>
       </c>
-      <c r="C208">
-        <v>5</v>
-      </c>
       <c r="D208" t="s">
-        <v>239</v>
+        <v>69</v>
       </c>
       <c r="E208" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F208" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G208" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H208" t="s">
         <v>16</v>
@@ -7922,22 +7944,22 @@
         <v>20</v>
       </c>
       <c r="B209">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="C209">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="D209" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="E209" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F209" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G209" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H209" t="s">
         <v>16</v>
@@ -7954,22 +7976,22 @@
         <v>22</v>
       </c>
       <c r="B210">
-        <v>45</v>
+        <v>68</v>
       </c>
       <c r="C210">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="D210" t="s">
-        <v>197</v>
+        <v>209</v>
       </c>
       <c r="E210" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F210" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G210" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H210" t="s">
         <v>16</v>
@@ -7986,7 +8008,7 @@
         <v>24</v>
       </c>
       <c r="B211">
-        <v>375</v>
+        <v>562</v>
       </c>
       <c r="C211">
         <v>0</v>
@@ -7995,13 +8017,13 @@
         <v>19</v>
       </c>
       <c r="E211" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="F211" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G211" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H211" t="s">
         <v>16</v>
@@ -8018,22 +8040,22 @@
         <v>11</v>
       </c>
       <c r="B212">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="C212">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="D212" t="s">
-        <v>238</v>
+        <v>81</v>
       </c>
       <c r="E212" t="s">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="F212" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G212" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="H212" t="s">
         <v>16</v>
@@ -8042,7 +8064,7 @@
         <v>17</v>
       </c>
       <c r="K212">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="213" spans="1:11" x14ac:dyDescent="0.25">
@@ -8050,22 +8072,22 @@
         <v>18</v>
       </c>
       <c r="B213">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="C213">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="D213" t="s">
-        <v>78</v>
+        <v>234</v>
       </c>
       <c r="E213" t="s">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="F213" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G213" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="H213" t="s">
         <v>16</v>
@@ -8074,7 +8096,7 @@
         <v>17</v>
       </c>
       <c r="K213">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="214" spans="1:11" x14ac:dyDescent="0.25">
@@ -8082,22 +8104,22 @@
         <v>20</v>
       </c>
       <c r="B214">
-        <v>36</v>
+        <v>24</v>
       </c>
       <c r="C214">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="D214" t="s">
-        <v>42</v>
+        <v>226</v>
       </c>
       <c r="E214" t="s">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="F214" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G214" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="H214" t="s">
         <v>16</v>
@@ -8106,7 +8128,7 @@
         <v>17</v>
       </c>
       <c r="K214">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="215" spans="1:11" x14ac:dyDescent="0.25">
@@ -8114,22 +8136,22 @@
         <v>22</v>
       </c>
       <c r="B215">
-        <v>68</v>
+        <v>38</v>
       </c>
       <c r="C215">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="D215" t="s">
-        <v>198</v>
+        <v>78</v>
       </c>
       <c r="E215" t="s">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="F215" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G215" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="H215" t="s">
         <v>16</v>
@@ -8138,7 +8160,7 @@
         <v>17</v>
       </c>
       <c r="K215">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="216" spans="1:11" x14ac:dyDescent="0.25">
@@ -8146,7 +8168,7 @@
         <v>24</v>
       </c>
       <c r="B216">
-        <v>562</v>
+        <v>375</v>
       </c>
       <c r="C216">
         <v>0</v>
@@ -8155,13 +8177,13 @@
         <v>19</v>
       </c>
       <c r="E216" t="s">
-        <v>213</v>
+        <v>77</v>
       </c>
       <c r="F216" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G216" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="H216" t="s">
         <v>16</v>
@@ -8170,7 +8192,7 @@
         <v>17</v>
       </c>
       <c r="K216">
-        <v>76</v>
+        <v>63</v>
       </c>
     </row>
     <row r="217" spans="1:11" x14ac:dyDescent="0.25">
@@ -8178,22 +8200,22 @@
         <v>11</v>
       </c>
       <c r="B217">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C217">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="D217" t="s">
-        <v>33</v>
+        <v>76</v>
       </c>
       <c r="E217" t="s">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="F217" t="s">
         <v>27</v>
       </c>
       <c r="G217" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="H217" t="s">
         <v>16</v>
@@ -8201,11 +8223,8 @@
       <c r="I217" t="s">
         <v>17</v>
       </c>
-      <c r="J217" t="s">
-        <v>237</v>
-      </c>
       <c r="K217">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="218" spans="1:11" x14ac:dyDescent="0.25">
@@ -8216,19 +8235,19 @@
         <v>4</v>
       </c>
       <c r="C218">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="D218" t="s">
-        <v>71</v>
+        <v>233</v>
       </c>
       <c r="E218" t="s">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="F218" t="s">
         <v>27</v>
       </c>
       <c r="G218" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="H218" t="s">
         <v>16</v>
@@ -8237,7 +8256,7 @@
         <v>17</v>
       </c>
       <c r="K218">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="219" spans="1:11" x14ac:dyDescent="0.25">
@@ -8245,22 +8264,22 @@
         <v>20</v>
       </c>
       <c r="B219">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C219">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="D219" t="s">
-        <v>212</v>
+        <v>140</v>
       </c>
       <c r="E219" t="s">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="F219" t="s">
         <v>27</v>
       </c>
       <c r="G219" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="H219" t="s">
         <v>16</v>
@@ -8269,7 +8288,7 @@
         <v>17</v>
       </c>
       <c r="K219">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="220" spans="1:11" x14ac:dyDescent="0.25">
@@ -8277,22 +8296,22 @@
         <v>22</v>
       </c>
       <c r="B220">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C220">
-        <v>43</v>
+        <v>94</v>
       </c>
       <c r="D220" t="s">
-        <v>211</v>
+        <v>232</v>
       </c>
       <c r="E220" t="s">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="F220" t="s">
         <v>27</v>
       </c>
       <c r="G220" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="H220" t="s">
         <v>16</v>
@@ -8301,7 +8320,7 @@
         <v>17</v>
       </c>
       <c r="K220">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="221" spans="1:11" x14ac:dyDescent="0.25">
@@ -8318,13 +8337,13 @@
         <v>19</v>
       </c>
       <c r="E221" t="s">
-        <v>210</v>
+        <v>75</v>
       </c>
       <c r="F221" t="s">
         <v>27</v>
       </c>
       <c r="G221" t="s">
-        <v>209</v>
+        <v>73</v>
       </c>
       <c r="H221" t="s">
         <v>16</v>
@@ -8333,7 +8352,7 @@
         <v>17</v>
       </c>
       <c r="K221">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="222" spans="1:11" x14ac:dyDescent="0.25">
@@ -8341,22 +8360,22 @@
         <v>11</v>
       </c>
       <c r="B222">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="C222">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="D222" t="s">
-        <v>83</v>
+        <v>121</v>
       </c>
       <c r="E222" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F222" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G222" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H222" t="s">
         <v>16</v>
@@ -8364,8 +8383,11 @@
       <c r="I222" t="s">
         <v>17</v>
       </c>
+      <c r="J222" t="s">
+        <v>231</v>
+      </c>
       <c r="K222">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="223" spans="1:11" x14ac:dyDescent="0.25">
@@ -8373,22 +8395,22 @@
         <v>18</v>
       </c>
       <c r="B223">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C223">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="D223" t="s">
-        <v>236</v>
+        <v>19</v>
       </c>
       <c r="E223" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F223" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G223" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H223" t="s">
         <v>16</v>
@@ -8397,7 +8419,7 @@
         <v>17</v>
       </c>
       <c r="K223">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="224" spans="1:11" x14ac:dyDescent="0.25">
@@ -8405,22 +8427,22 @@
         <v>20</v>
       </c>
       <c r="B224">
-        <v>24</v>
+        <v>35</v>
       </c>
       <c r="C224">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="D224" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E224" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F224" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G224" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H224" t="s">
         <v>16</v>
@@ -8429,7 +8451,7 @@
         <v>17</v>
       </c>
       <c r="K224">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="225" spans="1:11" x14ac:dyDescent="0.25">
@@ -8437,22 +8459,22 @@
         <v>22</v>
       </c>
       <c r="B225">
-        <v>38</v>
+        <v>57</v>
       </c>
       <c r="C225">
-        <v>77</v>
+        <v>22</v>
       </c>
       <c r="D225" t="s">
-        <v>80</v>
+        <v>229</v>
       </c>
       <c r="E225" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F225" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G225" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H225" t="s">
         <v>16</v>
@@ -8461,7 +8483,7 @@
         <v>17</v>
       </c>
       <c r="K225">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="226" spans="1:11" x14ac:dyDescent="0.25">
@@ -8469,7 +8491,7 @@
         <v>24</v>
       </c>
       <c r="B226">
-        <v>375</v>
+        <v>562</v>
       </c>
       <c r="C226">
         <v>0</v>
@@ -8478,13 +8500,13 @@
         <v>19</v>
       </c>
       <c r="E226" t="s">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="F226" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G226" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="H226" t="s">
         <v>16</v>
@@ -8493,7 +8515,7 @@
         <v>17</v>
       </c>
       <c r="K226">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="227" spans="1:11" x14ac:dyDescent="0.25">
@@ -8501,22 +8523,22 @@
         <v>11</v>
       </c>
       <c r="B227">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C227">
-        <v>24</v>
+        <v>1</v>
       </c>
       <c r="D227" t="s">
-        <v>78</v>
+        <v>256</v>
       </c>
       <c r="E227" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="F227" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G227" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="H227" t="s">
         <v>16</v>
@@ -8524,8 +8546,11 @@
       <c r="I227" t="s">
         <v>17</v>
       </c>
+      <c r="J227" t="s">
+        <v>255</v>
+      </c>
       <c r="K227">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="228" spans="1:11" x14ac:dyDescent="0.25">
@@ -8533,22 +8558,22 @@
         <v>18</v>
       </c>
       <c r="B228">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C228">
+        <v>0</v>
+      </c>
+      <c r="D228" t="s">
         <v>19</v>
       </c>
-      <c r="D228" t="s">
-        <v>235</v>
-      </c>
       <c r="E228" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="F228" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G228" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="H228" t="s">
         <v>16</v>
@@ -8556,8 +8581,11 @@
       <c r="I228" t="s">
         <v>17</v>
       </c>
+      <c r="J228" t="s">
+        <v>254</v>
+      </c>
       <c r="K228">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="229" spans="1:11" x14ac:dyDescent="0.25">
@@ -8565,22 +8593,22 @@
         <v>20</v>
       </c>
       <c r="B229">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="C229">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="D229" t="s">
-        <v>142</v>
+        <v>120</v>
       </c>
       <c r="E229" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="F229" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G229" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="H229" t="s">
         <v>16</v>
@@ -8589,7 +8617,7 @@
         <v>17</v>
       </c>
       <c r="K229">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="230" spans="1:11" x14ac:dyDescent="0.25">
@@ -8597,22 +8625,22 @@
         <v>22</v>
       </c>
       <c r="B230">
-        <v>57</v>
+        <v>35</v>
       </c>
       <c r="C230">
-        <v>94</v>
+        <v>3</v>
       </c>
       <c r="D230" t="s">
-        <v>234</v>
+        <v>253</v>
       </c>
       <c r="E230" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="F230" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G230" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="H230" t="s">
         <v>16</v>
@@ -8621,7 +8649,7 @@
         <v>17</v>
       </c>
       <c r="K230">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="231" spans="1:11" x14ac:dyDescent="0.25">
@@ -8629,7 +8657,7 @@
         <v>24</v>
       </c>
       <c r="B231">
-        <v>562</v>
+        <v>300</v>
       </c>
       <c r="C231">
         <v>0</v>
@@ -8638,13 +8666,13 @@
         <v>19</v>
       </c>
       <c r="E231" t="s">
-        <v>77</v>
+        <v>119</v>
       </c>
       <c r="F231" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G231" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="H231" t="s">
         <v>16</v>
@@ -8653,7 +8681,7 @@
         <v>17</v>
       </c>
       <c r="K231">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="232" spans="1:11" x14ac:dyDescent="0.25">
@@ -8661,22 +8689,22 @@
         <v>11</v>
       </c>
       <c r="B232">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="C232">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="D232" t="s">
-        <v>123</v>
+        <v>57</v>
       </c>
       <c r="E232" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="F232" t="s">
         <v>27</v>
       </c>
       <c r="G232" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="H232" t="s">
         <v>16</v>
@@ -8684,11 +8712,8 @@
       <c r="I232" t="s">
         <v>17</v>
       </c>
-      <c r="J232" t="s">
-        <v>233</v>
-      </c>
       <c r="K232">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="233" spans="1:11" x14ac:dyDescent="0.25">
@@ -8696,7 +8721,7 @@
         <v>18</v>
       </c>
       <c r="B233">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C233">
         <v>0</v>
@@ -8705,13 +8730,13 @@
         <v>19</v>
       </c>
       <c r="E233" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="F233" t="s">
         <v>27</v>
       </c>
       <c r="G233" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="H233" t="s">
         <v>16</v>
@@ -8720,7 +8745,7 @@
         <v>17</v>
       </c>
       <c r="K233">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="234" spans="1:11" x14ac:dyDescent="0.25">
@@ -8728,22 +8753,22 @@
         <v>20</v>
       </c>
       <c r="B234">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="C234">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="D234" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="E234" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="F234" t="s">
         <v>27</v>
       </c>
       <c r="G234" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="H234" t="s">
         <v>16</v>
@@ -8752,7 +8777,7 @@
         <v>17</v>
       </c>
       <c r="K234">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="235" spans="1:11" x14ac:dyDescent="0.25">
@@ -8760,22 +8785,22 @@
         <v>22</v>
       </c>
       <c r="B235">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C235">
-        <v>22</v>
+        <v>68</v>
       </c>
       <c r="D235" t="s">
-        <v>231</v>
+        <v>76</v>
       </c>
       <c r="E235" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="F235" t="s">
         <v>27</v>
       </c>
       <c r="G235" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="H235" t="s">
         <v>16</v>
@@ -8784,7 +8809,7 @@
         <v>17</v>
       </c>
       <c r="K235">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="236" spans="1:11" x14ac:dyDescent="0.25">
@@ -8792,7 +8817,7 @@
         <v>24</v>
       </c>
       <c r="B236">
-        <v>562</v>
+        <v>399</v>
       </c>
       <c r="C236">
         <v>0</v>
@@ -8801,13 +8826,13 @@
         <v>19</v>
       </c>
       <c r="E236" t="s">
-        <v>76</v>
+        <v>117</v>
       </c>
       <c r="F236" t="s">
         <v>27</v>
       </c>
       <c r="G236" t="s">
-        <v>75</v>
+        <v>110</v>
       </c>
       <c r="H236" t="s">
         <v>16</v>
@@ -8816,7 +8841,7 @@
         <v>17</v>
       </c>
       <c r="K236">
-        <v>64</v>
+        <v>98</v>
       </c>
     </row>
     <row r="237" spans="1:11" x14ac:dyDescent="0.25">
@@ -8824,31 +8849,28 @@
         <v>11</v>
       </c>
       <c r="B237">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C237">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D237" t="s">
-        <v>258</v>
+        <v>116</v>
       </c>
       <c r="E237" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F237" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G237" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H237" t="s">
         <v>16</v>
       </c>
       <c r="I237" t="s">
         <v>17</v>
-      </c>
-      <c r="J237" t="s">
-        <v>257</v>
       </c>
       <c r="K237">
         <v>98</v>
@@ -8868,22 +8890,19 @@
         <v>19</v>
       </c>
       <c r="E238" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F238" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G238" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H238" t="s">
         <v>16</v>
       </c>
       <c r="I238" t="s">
         <v>17</v>
-      </c>
-      <c r="J238" t="s">
-        <v>256</v>
       </c>
       <c r="K238">
         <v>98</v>
@@ -8894,22 +8913,22 @@
         <v>20</v>
       </c>
       <c r="B239">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="C239">
-        <v>2</v>
+        <v>52</v>
       </c>
       <c r="D239" t="s">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="E239" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F239" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G239" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H239" t="s">
         <v>16</v>
@@ -8926,22 +8945,22 @@
         <v>22</v>
       </c>
       <c r="B240">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C240">
-        <v>3</v>
+        <v>48</v>
       </c>
       <c r="D240" t="s">
-        <v>255</v>
+        <v>107</v>
       </c>
       <c r="E240" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F240" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G240" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H240" t="s">
         <v>16</v>
@@ -8958,7 +8977,7 @@
         <v>24</v>
       </c>
       <c r="B241">
-        <v>300</v>
+        <v>399</v>
       </c>
       <c r="C241">
         <v>0</v>
@@ -8967,13 +8986,13 @@
         <v>19</v>
       </c>
       <c r="E241" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="F241" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G241" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H241" t="s">
         <v>16</v>
@@ -8993,19 +9012,19 @@
         <v>11</v>
       </c>
       <c r="C242">
-        <v>16</v>
+        <v>27</v>
       </c>
       <c r="D242" t="s">
-        <v>59</v>
+        <v>113</v>
       </c>
       <c r="E242" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F242" t="s">
         <v>27</v>
       </c>
       <c r="G242" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H242" t="s">
         <v>16</v>
@@ -9025,19 +9044,19 @@
         <v>0</v>
       </c>
       <c r="C243">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D243" t="s">
-        <v>19</v>
+        <v>251</v>
       </c>
       <c r="E243" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F243" t="s">
         <v>27</v>
       </c>
       <c r="G243" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H243" t="s">
         <v>16</v>
@@ -9057,19 +9076,19 @@
         <v>55</v>
       </c>
       <c r="C244">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="D244" t="s">
-        <v>254</v>
+        <v>112</v>
       </c>
       <c r="E244" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F244" t="s">
         <v>27</v>
       </c>
       <c r="G244" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H244" t="s">
         <v>16</v>
@@ -9089,19 +9108,19 @@
         <v>47</v>
       </c>
       <c r="C245">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D245" t="s">
-        <v>78</v>
+        <v>199</v>
       </c>
       <c r="E245" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F245" t="s">
         <v>27</v>
       </c>
       <c r="G245" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H245" t="s">
         <v>16</v>
@@ -9127,13 +9146,13 @@
         <v>19</v>
       </c>
       <c r="E246" t="s">
-        <v>119</v>
+        <v>111</v>
       </c>
       <c r="F246" t="s">
         <v>27</v>
       </c>
       <c r="G246" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H246" t="s">
         <v>16</v>
@@ -9150,22 +9169,22 @@
         <v>11</v>
       </c>
       <c r="B247">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C247">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D247" t="s">
-        <v>118</v>
+        <v>140</v>
       </c>
       <c r="E247" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="F247" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G247" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="H247" t="s">
         <v>16</v>
@@ -9174,7 +9193,7 @@
         <v>17</v>
       </c>
       <c r="K247">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="248" spans="1:11" x14ac:dyDescent="0.25">
@@ -9182,22 +9201,22 @@
         <v>18</v>
       </c>
       <c r="B248">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C248">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D248" t="s">
-        <v>19</v>
+        <v>250</v>
       </c>
       <c r="E248" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="F248" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G248" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="H248" t="s">
         <v>16</v>
@@ -9206,7 +9225,7 @@
         <v>17</v>
       </c>
       <c r="K248">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="249" spans="1:11" x14ac:dyDescent="0.25">
@@ -9214,22 +9233,22 @@
         <v>20</v>
       </c>
       <c r="B249">
-        <v>55</v>
+        <v>31</v>
       </c>
       <c r="C249">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D249" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="E249" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="F249" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G249" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="H249" t="s">
         <v>16</v>
@@ -9238,7 +9257,7 @@
         <v>17</v>
       </c>
       <c r="K249">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="250" spans="1:11" x14ac:dyDescent="0.25">
@@ -9246,22 +9265,22 @@
         <v>22</v>
       </c>
       <c r="B250">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="C250">
-        <v>48</v>
+        <v>35</v>
       </c>
       <c r="D250" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="E250" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="F250" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G250" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="H250" t="s">
         <v>16</v>
@@ -9270,7 +9289,7 @@
         <v>17</v>
       </c>
       <c r="K250">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="251" spans="1:11" x14ac:dyDescent="0.25">
@@ -9278,7 +9297,7 @@
         <v>24</v>
       </c>
       <c r="B251">
-        <v>399</v>
+        <v>375</v>
       </c>
       <c r="C251">
         <v>0</v>
@@ -9287,13 +9306,13 @@
         <v>19</v>
       </c>
       <c r="E251" t="s">
-        <v>116</v>
+        <v>139</v>
       </c>
       <c r="F251" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G251" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="H251" t="s">
         <v>16</v>
@@ -9302,7 +9321,7 @@
         <v>17</v>
       </c>
       <c r="K251">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="252" spans="1:11" x14ac:dyDescent="0.25">
@@ -9310,22 +9329,22 @@
         <v>11</v>
       </c>
       <c r="B252">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="C252">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="D252" t="s">
-        <v>115</v>
+        <v>98</v>
       </c>
       <c r="E252" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="F252" t="s">
         <v>27</v>
       </c>
       <c r="G252" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="H252" t="s">
         <v>16</v>
@@ -9334,7 +9353,7 @@
         <v>17</v>
       </c>
       <c r="K252">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="253" spans="1:11" x14ac:dyDescent="0.25">
@@ -9342,22 +9361,22 @@
         <v>18</v>
       </c>
       <c r="B253">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C253">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D253" t="s">
-        <v>253</v>
+        <v>118</v>
       </c>
       <c r="E253" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="F253" t="s">
         <v>27</v>
       </c>
       <c r="G253" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="H253" t="s">
         <v>16</v>
@@ -9366,7 +9385,7 @@
         <v>17</v>
       </c>
       <c r="K253">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="254" spans="1:11" x14ac:dyDescent="0.25">
@@ -9374,22 +9393,22 @@
         <v>20</v>
       </c>
       <c r="B254">
-        <v>55</v>
+        <v>46</v>
       </c>
       <c r="C254">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="D254" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="E254" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="F254" t="s">
         <v>27</v>
       </c>
       <c r="G254" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="H254" t="s">
         <v>16</v>
@@ -9398,7 +9417,7 @@
         <v>17</v>
       </c>
       <c r="K254">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="255" spans="1:11" x14ac:dyDescent="0.25">
@@ -9406,22 +9425,22 @@
         <v>22</v>
       </c>
       <c r="B255">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C255">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="D255" t="s">
-        <v>201</v>
+        <v>248</v>
       </c>
       <c r="E255" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="F255" t="s">
         <v>27</v>
       </c>
       <c r="G255" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="H255" t="s">
         <v>16</v>
@@ -9430,7 +9449,7 @@
         <v>17</v>
       </c>
       <c r="K255">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="256" spans="1:11" x14ac:dyDescent="0.25">
@@ -9438,7 +9457,7 @@
         <v>24</v>
       </c>
       <c r="B256">
-        <v>399</v>
+        <v>562</v>
       </c>
       <c r="C256">
         <v>0</v>
@@ -9447,13 +9466,13 @@
         <v>19</v>
       </c>
       <c r="E256" t="s">
-        <v>113</v>
+        <v>137</v>
       </c>
       <c r="F256" t="s">
         <v>27</v>
       </c>
       <c r="G256" t="s">
-        <v>112</v>
+        <v>132</v>
       </c>
       <c r="H256" t="s">
         <v>16</v>
@@ -9462,7 +9481,7 @@
         <v>17</v>
       </c>
       <c r="K256">
-        <v>98</v>
+        <v>65</v>
       </c>
     </row>
     <row r="257" spans="1:11" x14ac:dyDescent="0.25">
@@ -9470,22 +9489,22 @@
         <v>11</v>
       </c>
       <c r="B257">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="C257">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D257" t="s">
-        <v>142</v>
+        <v>136</v>
       </c>
       <c r="E257" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F257" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G257" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H257" t="s">
         <v>16</v>
@@ -9502,22 +9521,22 @@
         <v>18</v>
       </c>
       <c r="B258">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C258">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D258" t="s">
-        <v>252</v>
+        <v>135</v>
       </c>
       <c r="E258" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F258" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G258" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H258" t="s">
         <v>16</v>
@@ -9534,22 +9553,22 @@
         <v>20</v>
       </c>
       <c r="B259">
-        <v>31</v>
+        <v>46</v>
       </c>
       <c r="C259">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="D259" t="s">
-        <v>126</v>
+        <v>203</v>
       </c>
       <c r="E259" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F259" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G259" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H259" t="s">
         <v>16</v>
@@ -9566,22 +9585,22 @@
         <v>22</v>
       </c>
       <c r="B260">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="C260">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="D260" t="s">
-        <v>138</v>
+        <v>50</v>
       </c>
       <c r="E260" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F260" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G260" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H260" t="s">
         <v>16</v>
@@ -9598,7 +9617,7 @@
         <v>24</v>
       </c>
       <c r="B261">
-        <v>375</v>
+        <v>562</v>
       </c>
       <c r="C261">
         <v>0</v>
@@ -9607,13 +9626,13 @@
         <v>19</v>
       </c>
       <c r="E261" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="F261" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
       <c r="G261" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="H261" t="s">
         <v>16</v>
@@ -9630,22 +9649,22 @@
         <v>11</v>
       </c>
       <c r="B262">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C262">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="D262" t="s">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="E262" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="F262" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G262" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="H262" t="s">
         <v>16</v>
@@ -9654,7 +9673,7 @@
         <v>17</v>
       </c>
       <c r="K262">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263" spans="1:11" x14ac:dyDescent="0.25">
@@ -9662,22 +9681,22 @@
         <v>18</v>
       </c>
       <c r="B263">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C263">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D263" t="s">
-        <v>120</v>
+        <v>19</v>
       </c>
       <c r="E263" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="F263" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G263" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="H263" t="s">
         <v>16</v>
@@ -9686,7 +9705,7 @@
         <v>17</v>
       </c>
       <c r="K263">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="264" spans="1:11" x14ac:dyDescent="0.25">
@@ -9694,22 +9713,22 @@
         <v>20</v>
       </c>
       <c r="B264">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C264">
-        <v>31</v>
+        <v>82</v>
       </c>
       <c r="D264" t="s">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="E264" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="F264" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G264" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="H264" t="s">
         <v>16</v>
@@ -9718,7 +9737,7 @@
         <v>17</v>
       </c>
       <c r="K264">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265" spans="1:11" x14ac:dyDescent="0.25">
@@ -9726,22 +9745,22 @@
         <v>22</v>
       </c>
       <c r="B265">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C265">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D265" t="s">
-        <v>250</v>
+        <v>23</v>
       </c>
       <c r="E265" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="F265" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G265" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="H265" t="s">
         <v>16</v>
@@ -9750,7 +9769,7 @@
         <v>17</v>
       </c>
       <c r="K265">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266" spans="1:11" x14ac:dyDescent="0.25">
@@ -9758,22 +9777,22 @@
         <v>24</v>
       </c>
       <c r="B266">
-        <v>562</v>
+        <v>750</v>
       </c>
       <c r="C266">
-        <v>0</v>
+        <v>293</v>
       </c>
       <c r="D266" t="s">
-        <v>19</v>
+        <v>229</v>
       </c>
       <c r="E266" t="s">
-        <v>139</v>
+        <v>13</v>
       </c>
       <c r="F266" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="G266" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="H266" t="s">
         <v>16</v>
@@ -9781,8 +9800,11 @@
       <c r="I266" t="s">
         <v>17</v>
       </c>
+      <c r="J266" t="s">
+        <v>25</v>
+      </c>
       <c r="K266">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267" spans="1:11" x14ac:dyDescent="0.25">
@@ -9790,22 +9812,22 @@
         <v>11</v>
       </c>
       <c r="B267">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="C267">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D267" t="s">
-        <v>138</v>
+        <v>12</v>
       </c>
       <c r="E267" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="F267" t="s">
         <v>27</v>
       </c>
       <c r="G267" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="H267" t="s">
         <v>16</v>
@@ -9813,8 +9835,11 @@
       <c r="I267" t="s">
         <v>17</v>
       </c>
+      <c r="J267" t="s">
+        <v>257</v>
+      </c>
       <c r="K267">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="268" spans="1:11" x14ac:dyDescent="0.25">
@@ -9822,22 +9847,22 @@
         <v>18</v>
       </c>
       <c r="B268">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="C268">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="D268" t="s">
-        <v>137</v>
+        <v>19</v>
       </c>
       <c r="E268" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="F268" t="s">
         <v>27</v>
       </c>
       <c r="G268" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="H268" t="s">
         <v>16</v>
@@ -9846,7 +9871,7 @@
         <v>17</v>
       </c>
       <c r="K268">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269" spans="1:11" x14ac:dyDescent="0.25">
@@ -9854,22 +9879,22 @@
         <v>20</v>
       </c>
       <c r="B269">
-        <v>46</v>
+        <v>70</v>
       </c>
       <c r="C269">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="D269" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="E269" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="F269" t="s">
         <v>27</v>
       </c>
       <c r="G269" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="H269" t="s">
         <v>16</v>
@@ -9877,8 +9902,11 @@
       <c r="I269" t="s">
         <v>17</v>
       </c>
+      <c r="J269" t="s">
+        <v>28</v>
+      </c>
       <c r="K269">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="270" spans="1:11" x14ac:dyDescent="0.25">
@@ -9886,22 +9914,22 @@
         <v>22</v>
       </c>
       <c r="B270">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C270">
-        <v>50</v>
+        <v>29</v>
       </c>
       <c r="D270" t="s">
-        <v>52</v>
+        <v>193</v>
       </c>
       <c r="E270" t="s">
-        <v>135</v>
+        <v>26</v>
       </c>
       <c r="F270" t="s">
         <v>27</v>
       </c>
       <c r="G270" t="s">
-        <v>134</v>
+        <v>15</v>
       </c>
       <c r="H270" t="s">
         <v>16</v>
@@ -9909,8 +9937,11 @@
       <c r="I270" t="s">
         <v>17</v>
       </c>
+      <c r="J270" t="s">
+        <v>30</v>
+      </c>
       <c r="K270">
-        <v>65</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271" spans="1:11" x14ac:dyDescent="0.25">
@@ -9918,31 +9949,523 @@
         <v>24</v>
       </c>
       <c r="B271">
+        <v>750</v>
+      </c>
+      <c r="C271">
+        <v>293</v>
+      </c>
+      <c r="D271" t="s">
+        <v>229</v>
+      </c>
+      <c r="E271" t="s">
+        <v>26</v>
+      </c>
+      <c r="F271" t="s">
+        <v>27</v>
+      </c>
+      <c r="G271" t="s">
+        <v>15</v>
+      </c>
+      <c r="H271" t="s">
+        <v>16</v>
+      </c>
+      <c r="I271" t="s">
+        <v>17</v>
+      </c>
+      <c r="J271" t="s">
+        <v>25</v>
+      </c>
+      <c r="K271">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A272" t="s">
+        <v>11</v>
+      </c>
+      <c r="B272">
+        <v>26</v>
+      </c>
+      <c r="C272">
+        <v>2</v>
+      </c>
+      <c r="D272" t="s">
+        <v>259</v>
+      </c>
+      <c r="E272" t="s">
+        <v>260</v>
+      </c>
+      <c r="F272" t="s">
+        <v>14</v>
+      </c>
+      <c r="G272" t="s">
+        <v>261</v>
+      </c>
+      <c r="H272" t="s">
+        <v>16</v>
+      </c>
+      <c r="I272" t="s">
+        <v>17</v>
+      </c>
+      <c r="J272" t="s">
+        <v>262</v>
+      </c>
+      <c r="K272">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A273" t="s">
+        <v>18</v>
+      </c>
+      <c r="B273">
+        <v>0</v>
+      </c>
+      <c r="C273">
+        <v>0</v>
+      </c>
+      <c r="D273" t="s">
+        <v>19</v>
+      </c>
+      <c r="E273" t="s">
+        <v>260</v>
+      </c>
+      <c r="F273" t="s">
+        <v>14</v>
+      </c>
+      <c r="G273" t="s">
+        <v>261</v>
+      </c>
+      <c r="H273" t="s">
+        <v>16</v>
+      </c>
+      <c r="I273" t="s">
+        <v>17</v>
+      </c>
+      <c r="K273">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>20</v>
+      </c>
+      <c r="B274">
+        <v>608</v>
+      </c>
+      <c r="C274">
+        <v>3</v>
+      </c>
+      <c r="D274" t="s">
+        <v>19</v>
+      </c>
+      <c r="E274" t="s">
+        <v>260</v>
+      </c>
+      <c r="F274" t="s">
+        <v>14</v>
+      </c>
+      <c r="G274" t="s">
+        <v>261</v>
+      </c>
+      <c r="H274" t="s">
+        <v>16</v>
+      </c>
+      <c r="I274" t="s">
+        <v>17</v>
+      </c>
+      <c r="K274">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="275" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A275" t="s">
+        <v>22</v>
+      </c>
+      <c r="B275">
+        <v>48</v>
+      </c>
+      <c r="C275">
+        <v>8</v>
+      </c>
+      <c r="D275" t="s">
+        <v>102</v>
+      </c>
+      <c r="E275" t="s">
+        <v>260</v>
+      </c>
+      <c r="F275" t="s">
+        <v>14</v>
+      </c>
+      <c r="G275" t="s">
+        <v>261</v>
+      </c>
+      <c r="H275" t="s">
+        <v>16</v>
+      </c>
+      <c r="I275" t="s">
+        <v>17</v>
+      </c>
+      <c r="K275">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A276" t="s">
+        <v>24</v>
+      </c>
+      <c r="B276">
+        <v>375</v>
+      </c>
+      <c r="C276">
+        <v>0</v>
+      </c>
+      <c r="D276" t="s">
+        <v>19</v>
+      </c>
+      <c r="E276" t="s">
+        <v>260</v>
+      </c>
+      <c r="F276" t="s">
+        <v>14</v>
+      </c>
+      <c r="G276" t="s">
+        <v>261</v>
+      </c>
+      <c r="H276" t="s">
+        <v>16</v>
+      </c>
+      <c r="I276" t="s">
+        <v>17</v>
+      </c>
+      <c r="K276">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A277" t="s">
+        <v>11</v>
+      </c>
+      <c r="B277">
+        <v>39</v>
+      </c>
+      <c r="C277">
+        <v>0</v>
+      </c>
+      <c r="D277" t="s">
+        <v>19</v>
+      </c>
+      <c r="E277" t="s">
+        <v>263</v>
+      </c>
+      <c r="F277" t="s">
+        <v>27</v>
+      </c>
+      <c r="G277" t="s">
+        <v>261</v>
+      </c>
+      <c r="H277" t="s">
+        <v>16</v>
+      </c>
+      <c r="I277" t="s">
+        <v>17</v>
+      </c>
+      <c r="K277">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A278" t="s">
+        <v>18</v>
+      </c>
+      <c r="B278">
+        <v>0</v>
+      </c>
+      <c r="C278">
+        <v>0</v>
+      </c>
+      <c r="D278" t="s">
+        <v>19</v>
+      </c>
+      <c r="E278" t="s">
+        <v>263</v>
+      </c>
+      <c r="F278" t="s">
+        <v>27</v>
+      </c>
+      <c r="G278" t="s">
+        <v>261</v>
+      </c>
+      <c r="H278" t="s">
+        <v>16</v>
+      </c>
+      <c r="I278" t="s">
+        <v>17</v>
+      </c>
+      <c r="K278">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>20</v>
+      </c>
+      <c r="B279">
+        <v>912</v>
+      </c>
+      <c r="C279">
+        <v>7</v>
+      </c>
+      <c r="D279" t="s">
+        <v>264</v>
+      </c>
+      <c r="E279" t="s">
+        <v>263</v>
+      </c>
+      <c r="F279" t="s">
+        <v>27</v>
+      </c>
+      <c r="G279" t="s">
+        <v>261</v>
+      </c>
+      <c r="H279" t="s">
+        <v>16</v>
+      </c>
+      <c r="I279" t="s">
+        <v>17</v>
+      </c>
+      <c r="K279">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="280" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>22</v>
+      </c>
+      <c r="B280">
+        <v>72</v>
+      </c>
+      <c r="C280">
+        <v>8</v>
+      </c>
+      <c r="D280" t="s">
+        <v>265</v>
+      </c>
+      <c r="E280" t="s">
+        <v>263</v>
+      </c>
+      <c r="F280" t="s">
+        <v>27</v>
+      </c>
+      <c r="G280" t="s">
+        <v>261</v>
+      </c>
+      <c r="H280" t="s">
+        <v>16</v>
+      </c>
+      <c r="I280" t="s">
+        <v>17</v>
+      </c>
+      <c r="K280">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="281" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
+        <v>24</v>
+      </c>
+      <c r="B281">
         <v>562</v>
       </c>
-      <c r="C271">
-        <v>0</v>
-      </c>
-      <c r="D271" t="s">
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281" t="s">
         <v>19</v>
       </c>
-      <c r="E271" t="s">
-        <v>135</v>
-      </c>
-      <c r="F271" t="s">
-        <v>27</v>
-      </c>
-      <c r="G271" t="s">
-        <v>134</v>
-      </c>
-      <c r="H271" t="s">
-        <v>16</v>
-      </c>
-      <c r="I271" t="s">
-        <v>17</v>
-      </c>
-      <c r="K271">
-        <v>65</v>
+      <c r="E281" t="s">
+        <v>263</v>
+      </c>
+      <c r="F281" t="s">
+        <v>27</v>
+      </c>
+      <c r="G281" t="s">
+        <v>261</v>
+      </c>
+      <c r="H281" t="s">
+        <v>16</v>
+      </c>
+      <c r="I281" t="s">
+        <v>17</v>
+      </c>
+      <c r="K281">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="282" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A282" t="s">
+        <v>11</v>
+      </c>
+      <c r="B282">
+        <v>39</v>
+      </c>
+      <c r="C282">
+        <v>1</v>
+      </c>
+      <c r="D282" t="s">
+        <v>266</v>
+      </c>
+      <c r="E282" t="s">
+        <v>267</v>
+      </c>
+      <c r="F282" t="s">
+        <v>27</v>
+      </c>
+      <c r="G282" t="s">
+        <v>261</v>
+      </c>
+      <c r="H282" t="s">
+        <v>16</v>
+      </c>
+      <c r="I282" t="s">
+        <v>17</v>
+      </c>
+      <c r="J282" t="s">
+        <v>268</v>
+      </c>
+      <c r="K282">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="283" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A283" t="s">
+        <v>18</v>
+      </c>
+      <c r="B283">
+        <v>0</v>
+      </c>
+      <c r="C283">
+        <v>0</v>
+      </c>
+      <c r="D283" t="s">
+        <v>19</v>
+      </c>
+      <c r="E283" t="s">
+        <v>267</v>
+      </c>
+      <c r="F283" t="s">
+        <v>27</v>
+      </c>
+      <c r="G283" t="s">
+        <v>261</v>
+      </c>
+      <c r="H283" t="s">
+        <v>16</v>
+      </c>
+      <c r="I283" t="s">
+        <v>17</v>
+      </c>
+      <c r="J283" t="s">
+        <v>269</v>
+      </c>
+      <c r="K283">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A284" t="s">
+        <v>20</v>
+      </c>
+      <c r="B284">
+        <v>912</v>
+      </c>
+      <c r="C284">
+        <v>12</v>
+      </c>
+      <c r="D284" t="s">
+        <v>264</v>
+      </c>
+      <c r="E284" t="s">
+        <v>267</v>
+      </c>
+      <c r="F284" t="s">
+        <v>27</v>
+      </c>
+      <c r="G284" t="s">
+        <v>261</v>
+      </c>
+      <c r="H284" t="s">
+        <v>16</v>
+      </c>
+      <c r="I284" t="s">
+        <v>17</v>
+      </c>
+      <c r="K284">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="285" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A285" t="s">
+        <v>22</v>
+      </c>
+      <c r="B285">
+        <v>72</v>
+      </c>
+      <c r="C285">
+        <v>12</v>
+      </c>
+      <c r="D285" t="s">
+        <v>102</v>
+      </c>
+      <c r="E285" t="s">
+        <v>267</v>
+      </c>
+      <c r="F285" t="s">
+        <v>27</v>
+      </c>
+      <c r="G285" t="s">
+        <v>261</v>
+      </c>
+      <c r="H285" t="s">
+        <v>16</v>
+      </c>
+      <c r="I285" t="s">
+        <v>17</v>
+      </c>
+      <c r="K285">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="286" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A286" t="s">
+        <v>24</v>
+      </c>
+      <c r="B286">
+        <v>562</v>
+      </c>
+      <c r="C286">
+        <v>0</v>
+      </c>
+      <c r="D286" t="s">
+        <v>19</v>
+      </c>
+      <c r="E286" t="s">
+        <v>267</v>
+      </c>
+      <c r="F286" t="s">
+        <v>27</v>
+      </c>
+      <c r="G286" t="s">
+        <v>261</v>
+      </c>
+      <c r="H286" t="s">
+        <v>16</v>
+      </c>
+      <c r="I286" t="s">
+        <v>17</v>
+      </c>
+      <c r="K286">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
